--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FB1F727-D047-4E94-8927-8E6474A59B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC882A7A-3DED-428C-B4A9-22EB1E9A2DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="760" windowWidth="19110" windowHeight="8970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="7" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="670">
   <si>
     <t>Date Received</t>
   </si>
@@ -938,12 +938,12 @@
     <t>P.F. CHANG'S CHINA BISTRO, INC.</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DnAi/PsQ06rfrLt2A8hC1UKmSPXyLtRhTdP2bt3fWa.P3Mao</t>
+  </si>
+  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001Dn9p/B92tz6zaPaYm5.lAsW0F6GS2hq_bm.DPaGZFyNbmJNI</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DnAi/PsQ06rfrLt2A8hC1UKmSPXyLtRhTdP2bt3fWa.P3Mao</t>
-  </si>
-  <si>
     <t>Galt House Hotel &amp; Suites</t>
   </si>
   <si>
@@ -968,18 +968,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000nXqL/60wOB.ZYyAFW_S_R8hleRIp7jxvj5pSKHPafgMy.D34</t>
   </si>
   <si>
+    <t>Vino Volo</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n3UK/pGrkwz.TW4TwVggStmZ08DA7.gkV29a2hXqMxuex7_w</t>
+  </si>
+  <si>
     <t>WestRock Comany</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n28b/Jn1rUm_cAXF2P3ZrPaqixkhcq2ejA4cVozic81IBDBc</t>
   </si>
   <si>
-    <t>Vino Volo</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n3UK/pGrkwz.TW4TwVggStmZ08DA7.gkV29a2hXqMxuex7_w</t>
-  </si>
-  <si>
     <t>Republic Airline Inc.</t>
   </si>
   <si>
@@ -1004,24 +1004,24 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjW4/G_5.Fi2tenUK8iONlECvyrpM3qeWoSn_lcSPHmqPLhs</t>
   </si>
   <si>
+    <t>Rhino Group LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHT/LD5kPxqA490uoPjJTUYgS_DByLIc4TIotUjmADqJaU0</t>
+  </si>
+  <si>
+    <t>CAM  Mining LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHd/LirRegwEOo6tABsdbsKLD3wZvWNuvAk8O7lo662CRW4</t>
+  </si>
+  <si>
     <t>Rhino Energy LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHO/J4gmK3FhqJupdRaSOCMq.CU3rKIt8M2k3PeCmNPgsTk</t>
   </si>
   <si>
-    <t>Rhino Group LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHT/LD5kPxqA490uoPjJTUYgS_DByLIc4TIotUjmADqJaU0</t>
-  </si>
-  <si>
-    <t>CAM  Mining LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHd/LirRegwEOo6tABsdbsKLD3wZvWNuvAk8O7lo662CRW4</t>
-  </si>
-  <si>
     <t>Kenco Logistic Services, LLC</t>
   </si>
   <si>
@@ -1034,18 +1034,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mbmQ/9yrMN2fZ9lM_WFND1MVmz49r2LWQW_YPfme4l9kv7vQ</t>
   </si>
   <si>
+    <t>White Lodging</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mQOc/n1sZCwQd4vfgRuAJcoxekQuz3b.06sV.9AeRbOhK1PM</t>
+  </si>
+  <si>
     <t>White Lodging Services Corporation-Marriott Louisville</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mQMM/MUcpqh7WMzyqGxAgtNciUI_khMYIUzsdlrg4oaWjGG8</t>
   </si>
   <si>
-    <t>White Lodging</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mQOc/n1sZCwQd4vfgRuAJcoxekQuz3b.06sV.9AeRbOhK1PM</t>
-  </si>
-  <si>
     <t>Out of State</t>
   </si>
   <si>
@@ -1241,27 +1241,27 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlC/hEdK2CiuQJ0bVuYeIRqwIFPEy53bOvrnmZtKCFG3OTk</t>
   </si>
   <si>
+    <t>AVIS BUDGET CAR RENTAL LLC-Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlW/CYo8uyV1lqLUe_XJLwXgKKbMGcUSOnm2YuFWlCcEjao</t>
+  </si>
+  <si>
     <t>AVIS BUDGET CAR RENTAL LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlM/.Zk80i_XFS7aZoaHWgUxXaHRiKaZbtC_7AhdxqU6wug</t>
   </si>
   <si>
-    <t>AVIS BUDGET CAR RENTAL LLC-Louisville</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlW/CYo8uyV1lqLUe_XJLwXgKKbMGcUSOnm2YuFWlCcEjao</t>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owfY/PmJV_yGxFZQyYhZo1Z3JUNNKeymCbhxmj4tTRLPEQdQ</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe6/AOd4ALEemb0aAShUt5dhhnJlPDFohiL8zcc9JttELyY</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe1/_JzvIyNP00OZFCdiwLq50NqX4Pv5uhASRmnOON4x7JM</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owfY/PmJV_yGxFZQyYhZo1Z3JUNNKeymCbhxmj4tTRLPEQdQ</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe6/AOd4ALEemb0aAShUt5dhhnJlPDFohiL8zcc9JttELyY</t>
-  </si>
-  <si>
     <t>GUESS Distribution Center</t>
   </si>
   <si>
@@ -1274,18 +1274,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc5/NegKIAQd.3f3pmcw73INUcvkRVIbZTkujR6EIS0ot58</t>
   </si>
   <si>
+    <t>Newport Aquarium LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owce/l.sHHNbu0GPlyDLBohqkTc6rmr3iMKC.C7bGdM4pAc0</t>
+  </si>
+  <si>
     <t>Bedding Acquisition LLC-Hollander Sleep Products</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc0/YfonXN9YuzXLk_UAXU4_FKNeT7YOIM6p5kka_JgwN0Y</t>
   </si>
   <si>
-    <t>Newport Aquarium LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owce/l.sHHNbu0GPlyDLBohqkTc6rmr3iMKC.C7bGdM4pAc0</t>
-  </si>
-  <si>
     <t>Vitro Automotive/Pittsburgh Glass Works</t>
   </si>
   <si>
@@ -1328,87 +1328,93 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVx/qvIScRk9GM5Elj.GBDk.q4vXbyNWeEoZlek.EdFKUGs</t>
   </si>
   <si>
+    <t>Communicare Services - Bardstown</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW7/vxvDkskTDW8u8rCe_lHYjJe3ywqVHolgywHu7LkriIg</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Communicare Services - Springfield</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWC/G1vvtarZYPJdOhvrIz1yR8EPnXsOq0_BH2dWoGiRDP4</t>
+  </si>
+  <si>
+    <t>Breckinridge</t>
+  </si>
+  <si>
+    <t>Communicare Clinic LLC - Hardinsburg</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWR/145nfIPWN0_U_cemfoWJlEEcFSVIRIo8wdyDtysKwiE</t>
+  </si>
+  <si>
+    <t>Marion</t>
+  </si>
+  <si>
+    <t>Communicare Clinic - Lebanon</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWW/6KnRleJzURSaBY_6FARK03ypKCpBzXNzxwnFAWGUcwk</t>
+  </si>
+  <si>
+    <t>Communicare Services - Lebanon</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWg/9p9FS.JQp0PTPMhD3HxrAxxsoxTEr_upxaagBfFMogM</t>
+  </si>
+  <si>
+    <t>Communicare Clinic - Radcliff</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWl/rS8vJCQrLNj0CL7FyoK6cd2Ubo0vr1icry6WlMYbX7U</t>
+  </si>
+  <si>
+    <t>Communicare Services - Radcliff</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWq/Vfpl8UYl0gbX_iFIJoUfIBUwxuS8TiJTC_7F4sKJFYw</t>
+  </si>
+  <si>
+    <t>Communicare Services - Leitchfield</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX5/hqgTkrEKeD2diZgwtvYubxlNzxik77T983Z_rFk92oU</t>
+  </si>
+  <si>
+    <t>Communicare  Services - Brandenburg</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owXA/mAUPSS8QJjeTFI7E27u8VQgWHFFi6LRZfcfzfkHq1Jo</t>
+  </si>
+  <si>
     <t>Communicare Professional Counselling and Treatment Service</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW2/m6.18mqxu4V91wnL7oO6sVnlaLN8Ty2M97cFVaRMbUI</t>
   </si>
   <si>
-    <t>Communicare Services - Bardstown</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW7/vxvDkskTDW8u8rCe_lHYjJe3ywqVHolgywHu7LkriIg</t>
-  </si>
-  <si>
-    <t>Washington</t>
-  </si>
-  <si>
-    <t>Communicare Services - Springfield</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWC/G1vvtarZYPJdOhvrIz1yR8EPnXsOq0_BH2dWoGiRDP4</t>
-  </si>
-  <si>
-    <t>Breckinridge</t>
-  </si>
-  <si>
-    <t>Communicare Clinic LLC - Hardinsburg</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWR/145nfIPWN0_U_cemfoWJlEEcFSVIRIo8wdyDtysKwiE</t>
-  </si>
-  <si>
-    <t>Marion</t>
-  </si>
-  <si>
-    <t>Communicare Clinic - Lebanon</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWW/6KnRleJzURSaBY_6FARK03ypKCpBzXNzxwnFAWGUcwk</t>
-  </si>
-  <si>
-    <t>Communicare Services - Lebanon</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWg/9p9FS.JQp0PTPMhD3HxrAxxsoxTEr_upxaagBfFMogM</t>
-  </si>
-  <si>
-    <t>Communicare Clinic - Radcliff</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWl/rS8vJCQrLNj0CL7FyoK6cd2Ubo0vr1icry6WlMYbX7U</t>
-  </si>
-  <si>
-    <t>Communicare Services - Radcliff</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWq/Vfpl8UYl0gbX_iFIJoUfIBUwxuS8TiJTC_7F4sKJFYw</t>
-  </si>
-  <si>
-    <t>Communicare Services - Leitchfield</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX5/hqgTkrEKeD2diZgwtvYubxlNzxik77T983Z_rFk92oU</t>
-  </si>
-  <si>
     <t>Hendrickson Trailer Commercial Vehicle Systems</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX0/V6hwrqZ0Qlr_eFlMYEYrZXlE5AKDheKuIEjfBsUaPdQ</t>
   </si>
   <si>
-    <t>Communicare  Services - Brandenburg</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owXA/mAUPSS8QJjeTFI7E27u8VQgWHFFi6LRZfcfzfkHq1Jo</t>
-  </si>
-  <si>
     <t>Jackson Warewashing Systems</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVY/2COXMu6Bd1MCYgNNs.Sc62L0asFJOG..KVsIGQuqD5g</t>
   </si>
   <si>
+    <t>IHG Army Hotels &amp; Holiday Inn Express</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
+  </si>
+  <si>
     <t>Huhtamaki, Inc.</t>
   </si>
   <si>
@@ -1421,12 +1427,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVT/U2oN7sbm_kSzNb7xiYNnrUVaoC_094PGtzzEyvZMQHo</t>
   </si>
   <si>
-    <t>IHG Army Hotels &amp; Holiday Inn Express</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUQ/kIkf6vaRVWxJL33J4laXNMoRoo4Ps.CEaVYB4.M3PIU</t>
   </si>
   <si>
@@ -1457,33 +1457,33 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUB/Q4XhuwPlCqUiegEdy255dEODFtbl._noeWqruyQLy9c</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVE/C0OZ4Bz9aNkrc9YrcMiSzi1G1WqI2.arpnDnUUJqUr8</t>
+  </si>
+  <si>
+    <t>Muhlenberg</t>
+  </si>
+  <si>
+    <t>THE MUHLENBERG COUNTY COAL COMPANY</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVJ/Dg9.VOc4xZE0CzOT2WBULH9AF2F_W3myXxa4ijm196A</t>
+  </si>
+  <si>
+    <t>Bourbon</t>
+  </si>
+  <si>
+    <t>Murray Euipment &amp; Machine</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVO/fRo8DiZxbz2baMUvWanGYLiXkNdGw2BDb3YAGYVqjWI</t>
+  </si>
+  <si>
     <t>ALJSCO</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUL/QiUorU3I0MCyonZFb9WQqn78BNq1UIJjwP_tw34J1Sw</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVE/C0OZ4Bz9aNkrc9YrcMiSzi1G1WqI2.arpnDnUUJqUr8</t>
-  </si>
-  <si>
-    <t>Muhlenberg</t>
-  </si>
-  <si>
-    <t>THE MUHLENBERG COUNTY COAL COMPANY</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVJ/Dg9.VOc4xZE0CzOT2WBULH9AF2F_W3myXxa4ijm196A</t>
-  </si>
-  <si>
-    <t>Bourbon</t>
-  </si>
-  <si>
-    <t>Murray Euipment &amp; Machine</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVO/fRo8DiZxbz2baMUvWanGYLiXkNdGw2BDb3YAGYVqjWI</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owPN/jDHwTapPX.yBsZhb3qC7qy.geYOtPuuz3LjGauQ08h8</t>
   </si>
   <si>
@@ -1809,6 +1809,15 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000001oY17/5h0K2TokLeEb9PXrbvX4oWNviT4MCksNDEalEHDjlHE</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>Cyngus Home Services LLC dba Yelloh</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y00000544MI/vnMtNAO2IDHH1y45KfEINnNzB33rEWvX_p_qBQ_YiNU</t>
   </si>
   <si>
     <t>CEVA Logistics, LLC</t>
@@ -2657,7 +2666,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
@@ -2710,34 +2719,34 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
-        <v>45222</v>
+        <v>45261</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>342</v>
+        <v>587</v>
       </c>
       <c r="D2" s="55" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E2" s="55">
-        <v>488510</v>
+        <v>424420</v>
       </c>
       <c r="F2" s="55">
-        <v>135</v>
+        <v>1</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H2" s="54">
-        <v>45222</v>
+        <v>45318</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J2" s="53" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K2" s="57" t="str">
         <f>IF(ISBLANK(J2),"",HYPERLINK(J2,"WARN"))</f>
@@ -2746,70 +2755,70 @@
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
-        <v>45191</v>
+        <v>45222</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>589</v>
+        <v>342</v>
       </c>
       <c r="D3" s="55" t="s">
         <v>590</v>
       </c>
       <c r="E3" s="55">
-        <v>445110</v>
+        <v>488510</v>
       </c>
       <c r="F3" s="55">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="G3" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H3" s="54">
-        <v>45196</v>
+        <v>45222</v>
       </c>
       <c r="I3" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J3" s="53" t="s">
         <v>591</v>
       </c>
       <c r="K3" s="57" t="str">
-        <f t="shared" ref="K3:K42" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <f t="shared" ref="K3:K43" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
         <v>WARN</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54">
-        <v>45167</v>
+        <v>45191</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>333</v>
+        <v>592</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E4" s="55">
-        <v>5221</v>
+        <v>445110</v>
       </c>
       <c r="F4" s="55">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H4" s="54">
-        <v>45260</v>
+        <v>45196</v>
       </c>
       <c r="I4" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J4" s="53" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K4" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2818,34 +2827,34 @@
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54">
-        <v>45159</v>
+        <v>45167</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>15</v>
+        <v>332</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E5" s="55">
-        <v>326291</v>
+        <v>5221</v>
       </c>
       <c r="F5" s="55">
-        <v>221</v>
+        <v>17</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H5" s="54">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="I5" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J5" s="53" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K5" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2854,34 +2863,34 @@
     </row>
     <row r="6" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54">
-        <v>45139</v>
+        <v>45159</v>
       </c>
       <c r="B6" s="55" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>509</v>
+        <v>270</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E6" s="55">
-        <v>624120</v>
+        <v>326291</v>
       </c>
       <c r="F6" s="55">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="G6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="54">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="I6" s="55" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J6" s="53" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K6" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2890,34 +2899,34 @@
     </row>
     <row r="7" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54">
-        <v>45137</v>
+        <v>45139</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>226</v>
+        <v>509</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E7" s="55">
-        <v>484110</v>
-      </c>
-      <c r="F7" s="55" t="s">
-        <v>10</v>
+        <v>624120</v>
+      </c>
+      <c r="F7" s="55">
+        <v>284</v>
       </c>
       <c r="G7" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="54">
-        <v>45137</v>
+        <v>45199</v>
       </c>
       <c r="I7" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J7" s="53" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="K7" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2929,13 +2938,13 @@
         <v>45137</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E8" s="55">
         <v>484110</v>
@@ -2953,7 +2962,7 @@
         <v>13</v>
       </c>
       <c r="J8" s="53" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K8" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2965,13 +2974,13 @@
         <v>45137</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E9" s="55">
         <v>484110</v>
@@ -2989,7 +2998,7 @@
         <v>13</v>
       </c>
       <c r="J9" s="53" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K9" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2998,34 +3007,34 @@
     </row>
     <row r="10" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="54">
-        <v>45127</v>
+        <v>45137</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>517</v>
+        <v>601</v>
       </c>
       <c r="E10" s="55">
-        <v>336390</v>
-      </c>
-      <c r="F10" s="55">
-        <v>135</v>
+        <v>484110</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>10</v>
       </c>
       <c r="G10" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="54">
-        <v>45290</v>
+        <v>45137</v>
       </c>
       <c r="I10" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="K10" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3037,31 +3046,31 @@
         <v>45127</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>603</v>
+        <v>517</v>
       </c>
       <c r="E11" s="55">
-        <v>2121</v>
+        <v>336390</v>
       </c>
       <c r="F11" s="55">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="G11" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H11" s="54">
-        <v>45179</v>
+        <v>45290</v>
       </c>
       <c r="I11" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K11" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3079,13 +3088,13 @@
         <v>251</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E12" s="55">
         <v>2121</v>
       </c>
       <c r="F12" s="55">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G12" s="55" t="s">
         <v>16</v>
@@ -3097,7 +3106,7 @@
         <v>13</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K12" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3115,13 +3124,13 @@
         <v>251</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E13" s="55">
         <v>2121</v>
       </c>
       <c r="F13" s="55">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G13" s="55" t="s">
         <v>16</v>
@@ -3133,7 +3142,7 @@
         <v>13</v>
       </c>
       <c r="J13" s="53" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K13" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3151,25 +3160,25 @@
         <v>251</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E14" s="55">
         <v>2121</v>
       </c>
       <c r="F14" s="55">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G14" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="54">
-        <v>45132</v>
+        <v>45179</v>
       </c>
       <c r="I14" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K14" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3187,25 +3196,25 @@
         <v>251</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E15" s="55">
         <v>2121</v>
       </c>
       <c r="F15" s="55">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G15" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="54">
-        <v>45179</v>
+        <v>45132</v>
       </c>
       <c r="I15" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K15" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3223,13 +3232,13 @@
         <v>251</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E16" s="55">
         <v>2121</v>
       </c>
       <c r="F16" s="55">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G16" s="55" t="s">
         <v>16</v>
@@ -3241,7 +3250,7 @@
         <v>13</v>
       </c>
       <c r="J16" s="53" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K16" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3259,25 +3268,25 @@
         <v>251</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E17" s="55">
         <v>2121</v>
       </c>
       <c r="F17" s="55">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="G17" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="54">
-        <v>45132</v>
+        <v>45179</v>
       </c>
       <c r="I17" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J17" s="53" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K17" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3295,25 +3304,25 @@
         <v>251</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E18" s="55">
         <v>2121</v>
       </c>
       <c r="F18" s="55">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G18" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H18" s="54">
-        <v>45179</v>
+        <v>45132</v>
       </c>
       <c r="I18" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J18" s="53" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="K18" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3322,34 +3331,34 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="54">
-        <v>45117</v>
+        <v>45127</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E19" s="55">
-        <v>561440</v>
+        <v>2121</v>
       </c>
       <c r="F19" s="55">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G19" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H19" s="54">
-        <v>45175</v>
+        <v>45179</v>
       </c>
       <c r="I19" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J19" s="53" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K19" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3358,34 +3367,34 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="54">
-        <v>45110</v>
+        <v>45117</v>
       </c>
       <c r="B20" s="55" t="s">
         <v>40</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D20" s="55" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E20" s="55">
-        <v>323111</v>
+        <v>561440</v>
       </c>
       <c r="F20" s="55">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="G20" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="54">
-        <v>45291</v>
+        <v>45175</v>
       </c>
       <c r="I20" s="55" t="s">
         <v>10</v>
       </c>
       <c r="J20" s="53" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K20" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3394,34 +3403,34 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="54">
-        <v>45097</v>
+        <v>45110</v>
       </c>
       <c r="B21" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>482</v>
+        <v>231</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E21" s="55">
-        <v>324199</v>
+        <v>323111</v>
       </c>
       <c r="F21" s="55">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="G21" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H21" s="54">
-        <v>45163</v>
+        <v>45291</v>
       </c>
       <c r="I21" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J21" s="53" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K21" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3430,34 +3439,34 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="54">
-        <v>45090</v>
+        <v>45097</v>
       </c>
       <c r="B22" s="55" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>227</v>
+        <v>482</v>
       </c>
       <c r="D22" s="55" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E22" s="55">
-        <v>336390</v>
+        <v>324199</v>
       </c>
       <c r="F22" s="55">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="G22" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H22" s="54">
-        <v>45153</v>
+        <v>45163</v>
       </c>
       <c r="I22" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J22" s="53" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="K22" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3466,34 +3475,34 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="54">
-        <v>45083</v>
+        <v>45090</v>
       </c>
       <c r="B23" s="55" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="D23" s="55" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E23" s="55">
-        <v>2121</v>
+        <v>336390</v>
       </c>
       <c r="F23" s="55">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="G23" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H23" s="54">
-        <v>45094</v>
+        <v>45153</v>
       </c>
       <c r="I23" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J23" s="53" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K23" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3502,34 +3511,34 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="54">
-        <v>45079</v>
+        <v>45083</v>
       </c>
       <c r="B24" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="D24" s="55" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E24" s="55">
-        <v>541219</v>
+        <v>2121</v>
       </c>
       <c r="F24" s="55">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="G24" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H24" s="54">
-        <v>45138</v>
+        <v>45094</v>
       </c>
       <c r="I24" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="53" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="K24" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3538,22 +3547,22 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="54">
-        <v>45078</v>
+        <v>45079</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E25" s="55">
-        <v>621910</v>
+        <v>541219</v>
       </c>
       <c r="F25" s="55">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="G25" s="55" t="s">
         <v>16</v>
@@ -3565,7 +3574,7 @@
         <v>13</v>
       </c>
       <c r="J25" s="53" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K25" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3577,19 +3586,19 @@
         <v>45078</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D26" s="55" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E26" s="55">
         <v>621910</v>
       </c>
       <c r="F26" s="55">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="G26" s="55" t="s">
         <v>16</v>
@@ -3601,7 +3610,7 @@
         <v>13</v>
       </c>
       <c r="J26" s="53" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="K26" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3610,28 +3619,28 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="54">
-        <v>45076</v>
+        <v>45078</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>635</v>
+        <v>226</v>
       </c>
       <c r="D27" s="55" t="s">
         <v>636</v>
       </c>
       <c r="E27" s="55">
-        <v>334514</v>
+        <v>621910</v>
       </c>
       <c r="F27" s="55">
-        <v>235</v>
+        <v>72</v>
       </c>
       <c r="G27" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H27" s="54">
-        <v>45199</v>
+        <v>45138</v>
       </c>
       <c r="I27" s="55" t="s">
         <v>13</v>
@@ -3646,34 +3655,34 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="54">
-        <v>45062</v>
+        <v>45076</v>
       </c>
       <c r="B28" s="55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>251</v>
+        <v>638</v>
       </c>
       <c r="D28" s="55" t="s">
-        <v>558</v>
+        <v>639</v>
       </c>
       <c r="E28" s="55">
-        <v>722310</v>
+        <v>334514</v>
       </c>
       <c r="F28" s="55">
-        <v>59</v>
+        <v>235</v>
       </c>
       <c r="G28" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H28" s="54">
-        <v>45138</v>
+        <v>45199</v>
       </c>
       <c r="I28" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J28" s="53" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="K28" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3682,34 +3691,34 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="54">
-        <v>45051</v>
+        <v>45062</v>
       </c>
       <c r="B29" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D29" s="55" t="s">
-        <v>639</v>
+        <v>558</v>
       </c>
       <c r="E29" s="55">
-        <v>624120</v>
+        <v>722310</v>
       </c>
       <c r="F29" s="55">
-        <v>450</v>
+        <v>59</v>
       </c>
       <c r="G29" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H29" s="54">
-        <v>45052</v>
+        <v>45138</v>
       </c>
       <c r="I29" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="53" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K29" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3718,34 +3727,34 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="54">
-        <v>45044</v>
+        <v>45051</v>
       </c>
       <c r="B30" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>342</v>
+        <v>226</v>
       </c>
       <c r="D30" s="55" t="s">
-        <v>587</v>
+        <v>642</v>
       </c>
       <c r="E30" s="55">
-        <v>488510</v>
+        <v>624120</v>
       </c>
       <c r="F30" s="55">
-        <v>74</v>
+        <v>450</v>
       </c>
       <c r="G30" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H30" s="54">
-        <v>45113</v>
+        <v>45052</v>
       </c>
       <c r="I30" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J30" s="53" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K30" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3754,31 +3763,31 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="54">
-        <v>45042</v>
+        <v>45044</v>
       </c>
       <c r="B31" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C31" s="55" t="s">
-        <v>642</v>
+        <v>342</v>
       </c>
       <c r="D31" s="55" t="s">
-        <v>643</v>
+        <v>590</v>
       </c>
       <c r="E31" s="55">
-        <v>541614</v>
+        <v>488510</v>
       </c>
       <c r="F31" s="55">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G31" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H31" s="54">
-        <v>45138</v>
+        <v>45113</v>
       </c>
       <c r="I31" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J31" s="53" t="s">
         <v>644</v>
@@ -3793,31 +3802,31 @@
         <v>45042</v>
       </c>
       <c r="B32" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>342</v>
+        <v>645</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E32" s="55">
-        <v>541714</v>
+        <v>541614</v>
       </c>
       <c r="F32" s="55">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G32" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="54">
-        <v>45044</v>
+        <v>45138</v>
       </c>
       <c r="I32" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J32" s="53" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K32" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3826,34 +3835,34 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="54">
-        <v>45026</v>
+        <v>45042</v>
       </c>
       <c r="B33" s="55" t="s">
         <v>108</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>238</v>
+        <v>342</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E33" s="55">
-        <v>33392</v>
+        <v>541714</v>
       </c>
       <c r="F33" s="55">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G33" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H33" s="54">
-        <v>45086</v>
+        <v>45044</v>
       </c>
       <c r="I33" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J33" s="53" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K33" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3862,34 +3871,34 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="54">
-        <v>45019</v>
+        <v>45026</v>
       </c>
       <c r="B34" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="D34" s="55" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E34" s="55">
-        <v>541614</v>
+        <v>33392</v>
       </c>
       <c r="F34" s="55">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="G34" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H34" s="54">
-        <v>45083</v>
+        <v>45086</v>
       </c>
       <c r="I34" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J34" s="53" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="K34" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3898,34 +3907,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="54">
-        <v>45006</v>
+        <v>45019</v>
       </c>
       <c r="B35" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C35" s="55" t="s">
-        <v>128</v>
+        <v>274</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E35" s="55">
-        <v>323111</v>
+        <v>541614</v>
       </c>
       <c r="F35" s="55">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="G35" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H35" s="54">
-        <v>45066</v>
+        <v>45083</v>
       </c>
       <c r="I35" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J35" s="53" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="K35" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3934,34 +3943,34 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="54">
-        <v>44984</v>
+        <v>45006</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>239</v>
+        <v>128</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E36" s="55">
-        <v>322130</v>
+        <v>323111</v>
       </c>
       <c r="F36" s="55">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G36" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H36" s="54">
-        <v>45033</v>
+        <v>45066</v>
       </c>
       <c r="I36" s="55" t="s">
         <v>10</v>
       </c>
       <c r="J36" s="53" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="K36" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3970,34 +3979,34 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="54">
-        <v>44956</v>
+        <v>44984</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>512</v>
+        <v>239</v>
       </c>
       <c r="D37" s="55" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E37" s="55">
-        <v>332999</v>
+        <v>322130</v>
       </c>
       <c r="F37" s="55">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G37" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H37" s="54">
-        <v>44949</v>
+        <v>45033</v>
       </c>
       <c r="I37" s="55" t="s">
         <v>10</v>
       </c>
       <c r="J37" s="53" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K37" s="57" t="str">
         <f t="shared" si="0"/>
@@ -4006,34 +4015,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="54">
-        <v>44950</v>
+        <v>44956</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>238</v>
+        <v>512</v>
       </c>
       <c r="D38" s="55" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E38" s="55">
-        <v>493110</v>
+        <v>332999</v>
       </c>
       <c r="F38" s="55">
-        <v>236</v>
+        <v>90</v>
       </c>
       <c r="G38" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H38" s="54">
-        <v>45107</v>
+        <v>44949</v>
       </c>
       <c r="I38" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J38" s="53" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K38" s="57" t="str">
         <f t="shared" si="0"/>
@@ -4042,34 +4051,34 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="54">
-        <v>44945</v>
+        <v>44950</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C39" s="55" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E39" s="55">
-        <v>336323</v>
+        <v>493110</v>
       </c>
       <c r="F39" s="55">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="G39" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H39" s="54">
-        <v>45017</v>
+        <v>45107</v>
       </c>
       <c r="I39" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="53" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="K39" s="57" t="str">
         <f t="shared" si="0"/>
@@ -4078,34 +4087,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="54">
-        <v>44943</v>
+        <v>44945</v>
       </c>
       <c r="B40" s="55" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="D40" s="55" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E40" s="55">
-        <v>488210</v>
+        <v>336323</v>
       </c>
       <c r="F40" s="55">
-        <v>93</v>
+        <v>212</v>
       </c>
       <c r="G40" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H40" s="54">
-        <v>45016</v>
+        <v>45017</v>
       </c>
       <c r="I40" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J40" s="53" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="K40" s="57" t="str">
         <f t="shared" si="0"/>
@@ -4114,34 +4123,34 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="54">
-        <v>44937</v>
+        <v>44943</v>
       </c>
       <c r="B41" s="55" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>128</v>
+        <v>259</v>
       </c>
       <c r="D41" s="55" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E41" s="55">
-        <v>321199</v>
+        <v>488210</v>
       </c>
       <c r="F41" s="55">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G41" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H41" s="54">
-        <v>44990</v>
+        <v>45016</v>
       </c>
       <c r="I41" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J41" s="53" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K41" s="57" t="str">
         <f t="shared" si="0"/>
@@ -4153,33 +4162,69 @@
         <v>44937</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>332</v>
+        <v>108</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>333</v>
+        <v>128</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E42" s="55">
-        <v>485320</v>
+        <v>321199</v>
       </c>
       <c r="F42" s="55">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="G42" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H42" s="54">
+        <v>44990</v>
+      </c>
+      <c r="I42" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="53" t="s">
+        <v>667</v>
+      </c>
+      <c r="K42" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A43" s="54">
+        <v>44937</v>
+      </c>
+      <c r="B43" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="C43" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="D43" s="55" t="s">
+        <v>668</v>
+      </c>
+      <c r="E43" s="55">
+        <v>485320</v>
+      </c>
+      <c r="F43" s="55">
+        <v>90</v>
+      </c>
+      <c r="G43" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="54">
         <v>44977</v>
       </c>
-      <c r="I42" s="55" t="s">
+      <c r="I43" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="J42" s="53" t="s">
-        <v>666</v>
-      </c>
-      <c r="K42" s="57" t="str">
+      <c r="J43" s="53" t="s">
+        <v>669</v>
+      </c>
+      <c r="K43" s="57" t="str">
         <f t="shared" si="0"/>
         <v>WARN</v>
       </c>
@@ -6031,10 +6076,10 @@
         <v>44092</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D12" s="55" t="s">
         <v>295</v>
@@ -6067,10 +6112,10 @@
         <v>44092</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D13" s="55" t="s">
         <v>295</v>
@@ -6247,25 +6292,25 @@
         <v>44050</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D18" s="55" t="s">
         <v>306</v>
       </c>
       <c r="E18" s="55">
-        <v>3221</v>
+        <v>72251</v>
       </c>
       <c r="F18" s="55">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G18" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H18" s="54">
-        <v>44104</v>
+        <v>43926</v>
       </c>
       <c r="I18" s="55" t="s">
         <v>13</v>
@@ -6283,25 +6328,25 @@
         <v>44050</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D19" s="55" t="s">
         <v>308</v>
       </c>
       <c r="E19" s="55">
-        <v>72251</v>
+        <v>3221</v>
       </c>
       <c r="F19" s="55">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G19" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H19" s="54">
-        <v>43926</v>
+        <v>44104</v>
       </c>
       <c r="I19" s="55" t="s">
         <v>13</v>
@@ -6475,16 +6520,16 @@
         <v>213113</v>
       </c>
       <c r="F24" s="55">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G24" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="54">
-        <v>44094</v>
+        <v>44098</v>
       </c>
       <c r="I24" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J24" s="53" t="s">
         <v>319</v>
@@ -6499,10 +6544,10 @@
         <v>44035</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D25" s="55" t="s">
         <v>320</v>
@@ -6511,13 +6556,13 @@
         <v>213113</v>
       </c>
       <c r="F25" s="55">
-        <v>5</v>
+        <v>194</v>
       </c>
       <c r="G25" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H25" s="54">
-        <v>44098</v>
+        <v>44094</v>
       </c>
       <c r="I25" s="55" t="s">
         <v>13</v>
@@ -6535,10 +6580,10 @@
         <v>44035</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="D26" s="55" t="s">
         <v>322</v>
@@ -6547,7 +6592,7 @@
         <v>213113</v>
       </c>
       <c r="F26" s="55">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="G26" s="55" t="s">
         <v>11</v>
@@ -6556,7 +6601,7 @@
         <v>44094</v>
       </c>
       <c r="I26" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J26" s="53" t="s">
         <v>323</v>
@@ -6655,7 +6700,7 @@
         <v>722110</v>
       </c>
       <c r="F29" s="55">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="G29" s="55" t="s">
         <v>16</v>
@@ -6691,7 +6736,7 @@
         <v>722110</v>
       </c>
       <c r="F30" s="55">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="G30" s="55" t="s">
         <v>16</v>
@@ -7867,10 +7912,10 @@
         <v>43938</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C63" s="55" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="D63" s="55" t="s">
         <v>397</v>
@@ -7879,7 +7924,7 @@
         <v>532111</v>
       </c>
       <c r="F63" s="55">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G63" s="55" t="s">
         <v>16</v>
@@ -7903,10 +7948,10 @@
         <v>43938</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C64" s="55" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="D64" s="55" t="s">
         <v>399</v>
@@ -7915,7 +7960,7 @@
         <v>532111</v>
       </c>
       <c r="F64" s="55">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>16</v>
@@ -7939,19 +7984,19 @@
         <v>43936</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C65" s="55" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>349</v>
+        <v>133</v>
       </c>
       <c r="E65" s="55">
-        <v>488190</v>
+        <v>337215</v>
       </c>
       <c r="F65" s="55">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="G65" s="55" t="s">
         <v>16</v>
@@ -7978,16 +8023,16 @@
         <v>40</v>
       </c>
       <c r="C66" s="55" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D66" s="55" t="s">
         <v>133</v>
       </c>
       <c r="E66" s="55">
-        <v>337215</v>
+        <v>33791</v>
       </c>
       <c r="F66" s="55">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="G66" s="55" t="s">
         <v>16</v>
@@ -8011,19 +8056,19 @@
         <v>43936</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>133</v>
+        <v>349</v>
       </c>
       <c r="E67" s="55">
-        <v>33791</v>
+        <v>488190</v>
       </c>
       <c r="F67" s="55">
-        <v>271</v>
+        <v>17</v>
       </c>
       <c r="G67" s="55" t="s">
         <v>16</v>
@@ -8119,25 +8164,25 @@
         <v>43935</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C70" s="55" t="s">
-        <v>128</v>
+        <v>267</v>
       </c>
       <c r="D70" s="55" t="s">
         <v>408</v>
       </c>
       <c r="E70" s="55">
-        <v>337910</v>
+        <v>712130</v>
       </c>
       <c r="F70" s="55">
-        <v>234</v>
+        <v>88</v>
       </c>
       <c r="G70" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H70" s="54">
-        <v>43924</v>
+        <v>43941</v>
       </c>
       <c r="I70" s="55" t="s">
         <v>13</v>
@@ -8155,25 +8200,25 @@
         <v>43935</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C71" s="55" t="s">
-        <v>267</v>
+        <v>128</v>
       </c>
       <c r="D71" s="55" t="s">
         <v>410</v>
       </c>
       <c r="E71" s="55">
-        <v>712130</v>
+        <v>337910</v>
       </c>
       <c r="F71" s="55">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="G71" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H71" s="54">
-        <v>43941</v>
+        <v>43924</v>
       </c>
       <c r="I71" s="55" t="s">
         <v>13</v>
@@ -8446,7 +8491,7 @@
         <v>70</v>
       </c>
       <c r="C79" s="55" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D79" s="55" t="s">
         <v>426</v>
@@ -8455,7 +8500,7 @@
         <v>623110</v>
       </c>
       <c r="F79" s="55">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="G79" s="55" t="s">
         <v>16</v>
@@ -8482,16 +8527,16 @@
         <v>70</v>
       </c>
       <c r="C80" s="55" t="s">
-        <v>264</v>
+        <v>428</v>
       </c>
       <c r="D80" s="55" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E80" s="55">
         <v>623110</v>
       </c>
       <c r="F80" s="55">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G80" s="55" t="s">
         <v>16</v>
@@ -8503,7 +8548,7 @@
         <v>13</v>
       </c>
       <c r="J80" s="53" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K80" s="57" t="str">
         <f t="shared" si="1"/>
@@ -8518,16 +8563,16 @@
         <v>70</v>
       </c>
       <c r="C81" s="55" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D81" s="55" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E81" s="55">
         <v>623110</v>
       </c>
       <c r="F81" s="55">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G81" s="55" t="s">
         <v>16</v>
@@ -8539,7 +8584,7 @@
         <v>13</v>
       </c>
       <c r="J81" s="53" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K81" s="57" t="str">
         <f t="shared" si="1"/>
@@ -8554,16 +8599,16 @@
         <v>70</v>
       </c>
       <c r="C82" s="55" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E82" s="55">
         <v>623110</v>
       </c>
       <c r="F82" s="55">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G82" s="55" t="s">
         <v>16</v>
@@ -8575,7 +8620,7 @@
         <v>13</v>
       </c>
       <c r="J82" s="53" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K82" s="57" t="str">
         <f t="shared" si="1"/>
@@ -8590,7 +8635,7 @@
         <v>70</v>
       </c>
       <c r="C83" s="55" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D83" s="55" t="s">
         <v>437</v>
@@ -8626,7 +8671,7 @@
         <v>70</v>
       </c>
       <c r="C84" s="55" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="D84" s="55" t="s">
         <v>439</v>
@@ -8635,7 +8680,7 @@
         <v>623110</v>
       </c>
       <c r="F84" s="55">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G84" s="55" t="s">
         <v>16</v>
@@ -8698,7 +8743,7 @@
         <v>70</v>
       </c>
       <c r="C86" s="55" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="D86" s="55" t="s">
         <v>443</v>
@@ -8707,7 +8752,7 @@
         <v>623110</v>
       </c>
       <c r="F86" s="55">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G86" s="55" t="s">
         <v>16</v>
@@ -8734,7 +8779,7 @@
         <v>70</v>
       </c>
       <c r="C87" s="55" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="D87" s="55" t="s">
         <v>445</v>
@@ -8743,7 +8788,7 @@
         <v>623110</v>
       </c>
       <c r="F87" s="55">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G87" s="55" t="s">
         <v>16</v>
@@ -8770,22 +8815,22 @@
         <v>70</v>
       </c>
       <c r="C88" s="55" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="D88" s="55" t="s">
         <v>447</v>
       </c>
       <c r="E88" s="55">
-        <v>423110</v>
+        <v>623110</v>
       </c>
       <c r="F88" s="55">
-        <v>117</v>
+        <v>63</v>
       </c>
       <c r="G88" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H88" s="54">
-        <v>43934</v>
+        <v>43910</v>
       </c>
       <c r="I88" s="55" t="s">
         <v>13</v>
@@ -8806,22 +8851,22 @@
         <v>70</v>
       </c>
       <c r="C89" s="55" t="s">
-        <v>273</v>
+        <v>434</v>
       </c>
       <c r="D89" s="55" t="s">
         <v>449</v>
       </c>
       <c r="E89" s="55">
-        <v>623110</v>
+        <v>423110</v>
       </c>
       <c r="F89" s="55">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="G89" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="54">
-        <v>43910</v>
+        <v>43934</v>
       </c>
       <c r="I89" s="55" t="s">
         <v>13</v>
@@ -8875,25 +8920,25 @@
         <v>43923</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="D91" s="55" t="s">
         <v>453</v>
       </c>
       <c r="E91" s="55">
-        <v>333999</v>
+        <v>721110</v>
       </c>
       <c r="F91" s="55">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="G91" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H91" s="54">
-        <v>43926</v>
+        <v>43910</v>
       </c>
       <c r="I91" s="55" t="s">
         <v>13</v>
@@ -8911,25 +8956,25 @@
         <v>43923</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>128</v>
+        <v>258</v>
       </c>
       <c r="D92" s="55" t="s">
         <v>455</v>
       </c>
       <c r="E92" s="55">
-        <v>721110</v>
+        <v>333999</v>
       </c>
       <c r="F92" s="55">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G92" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H92" s="54">
-        <v>43906</v>
+        <v>43926</v>
       </c>
       <c r="I92" s="55" t="s">
         <v>13</v>
@@ -8947,10 +8992,10 @@
         <v>43923</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C93" s="55" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="D93" s="55" t="s">
         <v>457</v>
@@ -8959,13 +9004,13 @@
         <v>721110</v>
       </c>
       <c r="F93" s="55">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="G93" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H93" s="54">
-        <v>43910</v>
+        <v>43906</v>
       </c>
       <c r="I93" s="55" t="s">
         <v>13</v>
@@ -9199,31 +9244,31 @@
         <v>43922</v>
       </c>
       <c r="B100" s="55" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C100" s="55" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="D100" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="E100" s="55">
+        <v>21211</v>
+      </c>
+      <c r="F100" s="55">
+        <v>42</v>
+      </c>
+      <c r="G100" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="54">
+        <v>43984</v>
+      </c>
+      <c r="I100" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="53" t="s">
         <v>469</v>
-      </c>
-      <c r="E100" s="55">
-        <v>541611</v>
-      </c>
-      <c r="F100" s="55">
-        <v>4</v>
-      </c>
-      <c r="G100" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H100" s="54">
-        <v>43920</v>
-      </c>
-      <c r="I100" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J100" s="53" t="s">
-        <v>470</v>
       </c>
       <c r="K100" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9235,22 +9280,22 @@
         <v>43922</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C101" s="55" t="s">
-        <v>227</v>
+        <v>470</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>201</v>
+        <v>471</v>
       </c>
       <c r="E101" s="55">
         <v>21211</v>
       </c>
       <c r="F101" s="55">
-        <v>42</v>
+        <v>254</v>
       </c>
       <c r="G101" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H101" s="54">
         <v>43984</v>
@@ -9259,7 +9304,7 @@
         <v>13</v>
       </c>
       <c r="J101" s="53" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K101" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9271,19 +9316,19 @@
         <v>43922</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C102" s="55" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D102" s="55" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E102" s="55">
-        <v>21211</v>
+        <v>423520</v>
       </c>
       <c r="F102" s="55">
-        <v>254</v>
+        <v>11</v>
       </c>
       <c r="G102" s="55" t="s">
         <v>11</v>
@@ -9295,7 +9340,7 @@
         <v>13</v>
       </c>
       <c r="J102" s="53" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K102" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9307,25 +9352,25 @@
         <v>43922</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C103" s="55" t="s">
-        <v>475</v>
+        <v>128</v>
       </c>
       <c r="D103" s="55" t="s">
         <v>476</v>
       </c>
       <c r="E103" s="55">
-        <v>423520</v>
+        <v>541611</v>
       </c>
       <c r="F103" s="55">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G103" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H103" s="54">
-        <v>43984</v>
+        <v>43920</v>
       </c>
       <c r="I103" s="55" t="s">
         <v>13</v>
@@ -14185,5 +14230,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B816BC6D-CD14-407F-9AF9-9E9EE6991560}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27CEE514-E64C-4682-872F-66DA0246325F}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC882A7A-3DED-428C-B4A9-22EB1E9A2DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73327EF8-0D9B-466A-87CF-0774DC3244F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="760" windowWidth="19110" windowHeight="8970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="7" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="672">
   <si>
     <t>Date Received</t>
   </si>
@@ -938,12 +938,12 @@
     <t>P.F. CHANG'S CHINA BISTRO, INC.</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001Dn9p/B92tz6zaPaYm5.lAsW0F6GS2hq_bm.DPaGZFyNbmJNI</t>
+  </si>
+  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DnAi/PsQ06rfrLt2A8hC1UKmSPXyLtRhTdP2bt3fWa.P3Mao</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001Dn9p/B92tz6zaPaYm5.lAsW0F6GS2hq_bm.DPaGZFyNbmJNI</t>
-  </si>
-  <si>
     <t>Galt House Hotel &amp; Suites</t>
   </si>
   <si>
@@ -968,18 +968,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000nXqL/60wOB.ZYyAFW_S_R8hleRIp7jxvj5pSKHPafgMy.D34</t>
   </si>
   <si>
+    <t>WestRock Comany</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n28b/Jn1rUm_cAXF2P3ZrPaqixkhcq2ejA4cVozic81IBDBc</t>
+  </si>
+  <si>
     <t>Vino Volo</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n3UK/pGrkwz.TW4TwVggStmZ08DA7.gkV29a2hXqMxuex7_w</t>
   </si>
   <si>
-    <t>WestRock Comany</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n28b/Jn1rUm_cAXF2P3ZrPaqixkhcq2ejA4cVozic81IBDBc</t>
-  </si>
-  <si>
     <t>Republic Airline Inc.</t>
   </si>
   <si>
@@ -1004,6 +1004,12 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjW4/G_5.Fi2tenUK8iONlECvyrpM3qeWoSn_lcSPHmqPLhs</t>
   </si>
   <si>
+    <t>Rhino Energy LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHO/J4gmK3FhqJupdRaSOCMq.CU3rKIt8M2k3PeCmNPgsTk</t>
+  </si>
+  <si>
     <t>Rhino Group LLC</t>
   </si>
   <si>
@@ -1016,12 +1022,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHd/LirRegwEOo6tABsdbsKLD3wZvWNuvAk8O7lo662CRW4</t>
   </si>
   <si>
-    <t>Rhino Energy LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHO/J4gmK3FhqJupdRaSOCMq.CU3rKIt8M2k3PeCmNPgsTk</t>
-  </si>
-  <si>
     <t>Kenco Logistic Services, LLC</t>
   </si>
   <si>
@@ -1034,18 +1034,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mbmQ/9yrMN2fZ9lM_WFND1MVmz49r2LWQW_YPfme4l9kv7vQ</t>
   </si>
   <si>
+    <t>White Lodging Services Corporation-Marriott Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mQMM/MUcpqh7WMzyqGxAgtNciUI_khMYIUzsdlrg4oaWjGG8</t>
+  </si>
+  <si>
     <t>White Lodging</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mQOc/n1sZCwQd4vfgRuAJcoxekQuz3b.06sV.9AeRbOhK1PM</t>
   </si>
   <si>
-    <t>White Lodging Services Corporation-Marriott Louisville</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mQMM/MUcpqh7WMzyqGxAgtNciUI_khMYIUzsdlrg4oaWjGG8</t>
-  </si>
-  <si>
     <t>Out of State</t>
   </si>
   <si>
@@ -1241,16 +1241,19 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlC/hEdK2CiuQJ0bVuYeIRqwIFPEy53bOvrnmZtKCFG3OTk</t>
   </si>
   <si>
+    <t>AVIS BUDGET CAR RENTAL LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlM/.Zk80i_XFS7aZoaHWgUxXaHRiKaZbtC_7AhdxqU6wug</t>
+  </si>
+  <si>
     <t>AVIS BUDGET CAR RENTAL LLC-Louisville</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlW/CYo8uyV1lqLUe_XJLwXgKKbMGcUSOnm2YuFWlCcEjao</t>
   </si>
   <si>
-    <t>AVIS BUDGET CAR RENTAL LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlM/.Zk80i_XFS7aZoaHWgUxXaHRiKaZbtC_7AhdxqU6wug</t>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe1/_JzvIyNP00OZFCdiwLq50NqX4Pv5uhASRmnOON4x7JM</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owfY/PmJV_yGxFZQyYhZo1Z3JUNNKeymCbhxmj4tTRLPEQdQ</t>
@@ -1259,9 +1262,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe6/AOd4ALEemb0aAShUt5dhhnJlPDFohiL8zcc9JttELyY</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe1/_JzvIyNP00OZFCdiwLq50NqX4Pv5uhASRmnOON4x7JM</t>
-  </si>
-  <si>
     <t>GUESS Distribution Center</t>
   </si>
   <si>
@@ -1274,18 +1274,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc5/NegKIAQd.3f3pmcw73INUcvkRVIbZTkujR6EIS0ot58</t>
   </si>
   <si>
+    <t>Bedding Acquisition LLC-Hollander Sleep Products</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc0/YfonXN9YuzXLk_UAXU4_FKNeT7YOIM6p5kka_JgwN0Y</t>
+  </si>
+  <si>
     <t>Newport Aquarium LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owce/l.sHHNbu0GPlyDLBohqkTc6rmr3iMKC.C7bGdM4pAc0</t>
   </si>
   <si>
-    <t>Bedding Acquisition LLC-Hollander Sleep Products</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc0/YfonXN9YuzXLk_UAXU4_FKNeT7YOIM6p5kka_JgwN0Y</t>
-  </si>
-  <si>
     <t>Vitro Automotive/Pittsburgh Glass Works</t>
   </si>
   <si>
@@ -1328,6 +1328,12 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVx/qvIScRk9GM5Elj.GBDk.q4vXbyNWeEoZlek.EdFKUGs</t>
   </si>
   <si>
+    <t>Communicare Professional Counselling and Treatment Service</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW2/m6.18mqxu4V91wnL7oO6sVnlaLN8Ty2M97cFVaRMbUI</t>
+  </si>
+  <si>
     <t>Communicare Services - Bardstown</t>
   </si>
   <si>
@@ -1385,48 +1391,42 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX5/hqgTkrEKeD2diZgwtvYubxlNzxik77T983Z_rFk92oU</t>
   </si>
   <si>
+    <t>Hendrickson Trailer Commercial Vehicle Systems</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX0/V6hwrqZ0Qlr_eFlMYEYrZXlE5AKDheKuIEjfBsUaPdQ</t>
+  </si>
+  <si>
     <t>Communicare  Services - Brandenburg</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owXA/mAUPSS8QJjeTFI7E27u8VQgWHFFi6LRZfcfzfkHq1Jo</t>
   </si>
   <si>
-    <t>Communicare Professional Counselling and Treatment Service</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW2/m6.18mqxu4V91wnL7oO6sVnlaLN8Ty2M97cFVaRMbUI</t>
-  </si>
-  <si>
-    <t>Hendrickson Trailer Commercial Vehicle Systems</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX0/V6hwrqZ0Qlr_eFlMYEYrZXlE5AKDheKuIEjfBsUaPdQ</t>
-  </si>
-  <si>
     <t>Jackson Warewashing Systems</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVY/2COXMu6Bd1MCYgNNs.Sc62L0asFJOG..KVsIGQuqD5g</t>
   </si>
   <si>
+    <t>Huhtamaki, Inc.</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUa/gQ7KCmO7r.5JxftEeBG61Dp0YG0btnF0QmbfOv3Jqwg</t>
+  </si>
+  <si>
+    <t>SCHULTE COMPANIES</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVT/U2oN7sbm_kSzNb7xiYNnrUVaoC_094PGtzzEyvZMQHo</t>
+  </si>
+  <si>
     <t>IHG Army Hotels &amp; Holiday Inn Express</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
   </si>
   <si>
-    <t>Huhtamaki, Inc.</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUa/gQ7KCmO7r.5JxftEeBG61Dp0YG0btnF0QmbfOv3Jqwg</t>
-  </si>
-  <si>
-    <t>SCHULTE COMPANIES</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVT/U2oN7sbm_kSzNb7xiYNnrUVaoC_094PGtzzEyvZMQHo</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUQ/kIkf6vaRVWxJL33J4laXNMoRoo4Ps.CEaVYB4.M3PIU</t>
   </si>
   <si>
@@ -1457,6 +1457,12 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUB/Q4XhuwPlCqUiegEdy255dEODFtbl._noeWqruyQLy9c</t>
   </si>
   <si>
+    <t>ALJSCO</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUL/QiUorU3I0MCyonZFb9WQqn78BNq1UIJjwP_tw34J1Sw</t>
+  </si>
+  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVE/C0OZ4Bz9aNkrc9YrcMiSzi1G1WqI2.arpnDnUUJqUr8</t>
   </si>
   <si>
@@ -1478,12 +1484,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVO/fRo8DiZxbz2baMUvWanGYLiXkNdGw2BDb3YAGYVqjWI</t>
   </si>
   <si>
-    <t>ALJSCO</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUL/QiUorU3I0MCyonZFb9WQqn78BNq1UIJjwP_tw34J1Sw</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owPN/jDHwTapPX.yBsZhb3qC7qy.geYOtPuuz3LjGauQ08h8</t>
   </si>
   <si>
@@ -1809,6 +1809,12 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000001oY17/5h0K2TokLeEb9PXrbvX4oWNviT4MCksNDEalEHDjlHE</t>
+  </si>
+  <si>
+    <t>Charter Communications</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y0000055Og6/rQQXQgsrFTLb1QqpfmKAUhLQyhbZx7x96n8IcKxxF1A</t>
   </si>
   <si>
     <t>Franklin</t>
@@ -2666,7 +2672,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
@@ -2719,34 +2725,34 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
-        <v>45261</v>
+        <v>45266</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C2" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="55" t="s">
         <v>587</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="E2" s="55">
+        <v>561422</v>
+      </c>
+      <c r="F2" s="55">
+        <v>227</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="54">
+        <v>45296</v>
+      </c>
+      <c r="I2" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="53" t="s">
         <v>588</v>
-      </c>
-      <c r="E2" s="55">
-        <v>424420</v>
-      </c>
-      <c r="F2" s="55">
-        <v>1</v>
-      </c>
-      <c r="G2" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="54">
-        <v>45318</v>
-      </c>
-      <c r="I2" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="53" t="s">
-        <v>589</v>
       </c>
       <c r="K2" s="57" t="str">
         <f>IF(ISBLANK(J2),"",HYPERLINK(J2,"WARN"))</f>
@@ -2755,70 +2761,70 @@
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
-        <v>45222</v>
+        <v>45261</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>342</v>
+        <v>589</v>
       </c>
       <c r="D3" s="55" t="s">
         <v>590</v>
       </c>
       <c r="E3" s="55">
-        <v>488510</v>
+        <v>424420</v>
       </c>
       <c r="F3" s="55">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="G3" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H3" s="54">
-        <v>45222</v>
+        <v>45318</v>
       </c>
       <c r="I3" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J3" s="53" t="s">
         <v>591</v>
       </c>
       <c r="K3" s="57" t="str">
-        <f t="shared" ref="K3:K43" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <f t="shared" ref="K3:K44" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
         <v>WARN</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54">
-        <v>45191</v>
+        <v>45222</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C4" s="55" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="55" t="s">
         <v>592</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="E4" s="55">
+        <v>488510</v>
+      </c>
+      <c r="F4" s="55">
+        <v>135</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="54">
+        <v>45222</v>
+      </c>
+      <c r="I4" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="53" t="s">
         <v>593</v>
-      </c>
-      <c r="E4" s="55">
-        <v>445110</v>
-      </c>
-      <c r="F4" s="55">
-        <v>15</v>
-      </c>
-      <c r="G4" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="54">
-        <v>45196</v>
-      </c>
-      <c r="I4" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="53" t="s">
-        <v>594</v>
       </c>
       <c r="K4" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2827,28 +2833,28 @@
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54">
-        <v>45167</v>
+        <v>45191</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>333</v>
+        <v>594</v>
       </c>
       <c r="D5" s="55" t="s">
         <v>595</v>
       </c>
       <c r="E5" s="55">
-        <v>5221</v>
+        <v>445110</v>
       </c>
       <c r="F5" s="55">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H5" s="54">
-        <v>45260</v>
+        <v>45196</v>
       </c>
       <c r="I5" s="55" t="s">
         <v>13</v>
@@ -2863,31 +2869,31 @@
     </row>
     <row r="6" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54">
-        <v>45159</v>
+        <v>45167</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>15</v>
+        <v>332</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="D6" s="55" t="s">
         <v>597</v>
       </c>
       <c r="E6" s="55">
-        <v>326291</v>
+        <v>5221</v>
       </c>
       <c r="F6" s="55">
-        <v>221</v>
+        <v>17</v>
       </c>
       <c r="G6" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H6" s="54">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="I6" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J6" s="53" t="s">
         <v>598</v>
@@ -2899,31 +2905,31 @@
     </row>
     <row r="7" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54">
-        <v>45139</v>
+        <v>45159</v>
       </c>
       <c r="B7" s="55" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>509</v>
+        <v>270</v>
       </c>
       <c r="D7" s="55" t="s">
         <v>599</v>
       </c>
       <c r="E7" s="55">
-        <v>624120</v>
+        <v>326291</v>
       </c>
       <c r="F7" s="55">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="G7" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="54">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="I7" s="55" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J7" s="53" t="s">
         <v>600</v>
@@ -2935,31 +2941,31 @@
     </row>
     <row r="8" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="54">
-        <v>45137</v>
+        <v>45139</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>226</v>
+        <v>509</v>
       </c>
       <c r="D8" s="55" t="s">
         <v>601</v>
       </c>
       <c r="E8" s="55">
-        <v>484110</v>
-      </c>
-      <c r="F8" s="55" t="s">
-        <v>10</v>
+        <v>624120</v>
+      </c>
+      <c r="F8" s="55">
+        <v>284</v>
       </c>
       <c r="G8" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="54">
-        <v>45137</v>
+        <v>45199</v>
       </c>
       <c r="I8" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J8" s="53" t="s">
         <v>602</v>
@@ -2974,13 +2980,13 @@
         <v>45137</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E9" s="55">
         <v>484110</v>
@@ -2998,7 +3004,7 @@
         <v>13</v>
       </c>
       <c r="J9" s="53" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="K9" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3010,13 +3016,13 @@
         <v>45137</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E10" s="55">
         <v>484110</v>
@@ -3034,7 +3040,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K10" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3043,34 +3049,34 @@
     </row>
     <row r="11" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="54">
-        <v>45127</v>
+        <v>45137</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>517</v>
+        <v>603</v>
       </c>
       <c r="E11" s="55">
-        <v>336390</v>
-      </c>
-      <c r="F11" s="55">
-        <v>135</v>
+        <v>484110</v>
+      </c>
+      <c r="F11" s="55" t="s">
+        <v>10</v>
       </c>
       <c r="G11" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H11" s="54">
-        <v>45290</v>
+        <v>45137</v>
       </c>
       <c r="I11" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K11" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3082,25 +3088,25 @@
         <v>45127</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>606</v>
+        <v>517</v>
       </c>
       <c r="E12" s="55">
-        <v>2121</v>
+        <v>336390</v>
       </c>
       <c r="F12" s="55">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H12" s="54">
-        <v>45179</v>
+        <v>45290</v>
       </c>
       <c r="I12" s="55" t="s">
         <v>13</v>
@@ -3130,7 +3136,7 @@
         <v>2121</v>
       </c>
       <c r="F13" s="55">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G13" s="55" t="s">
         <v>16</v>
@@ -3166,7 +3172,7 @@
         <v>2121</v>
       </c>
       <c r="F14" s="55">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G14" s="55" t="s">
         <v>16</v>
@@ -3202,13 +3208,13 @@
         <v>2121</v>
       </c>
       <c r="F15" s="55">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G15" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H15" s="54">
-        <v>45132</v>
+        <v>45179</v>
       </c>
       <c r="I15" s="55" t="s">
         <v>13</v>
@@ -3238,13 +3244,13 @@
         <v>2121</v>
       </c>
       <c r="F16" s="55">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G16" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H16" s="54">
-        <v>45179</v>
+        <v>45132</v>
       </c>
       <c r="I16" s="55" t="s">
         <v>13</v>
@@ -3274,7 +3280,7 @@
         <v>2121</v>
       </c>
       <c r="F17" s="55">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G17" s="55" t="s">
         <v>16</v>
@@ -3310,13 +3316,13 @@
         <v>2121</v>
       </c>
       <c r="F18" s="55">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="G18" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H18" s="54">
-        <v>45132</v>
+        <v>45179</v>
       </c>
       <c r="I18" s="55" t="s">
         <v>13</v>
@@ -3346,13 +3352,13 @@
         <v>2121</v>
       </c>
       <c r="F19" s="55">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G19" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H19" s="54">
-        <v>45179</v>
+        <v>45132</v>
       </c>
       <c r="I19" s="55" t="s">
         <v>13</v>
@@ -3367,31 +3373,31 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="54">
-        <v>45117</v>
+        <v>45127</v>
       </c>
       <c r="B20" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D20" s="55" t="s">
         <v>622</v>
       </c>
       <c r="E20" s="55">
-        <v>561440</v>
+        <v>2121</v>
       </c>
       <c r="F20" s="55">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G20" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H20" s="54">
-        <v>45175</v>
+        <v>45179</v>
       </c>
       <c r="I20" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J20" s="53" t="s">
         <v>623</v>
@@ -3403,28 +3409,28 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="54">
-        <v>45110</v>
+        <v>45117</v>
       </c>
       <c r="B21" s="55" t="s">
         <v>40</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D21" s="55" t="s">
         <v>624</v>
       </c>
       <c r="E21" s="55">
-        <v>323111</v>
+        <v>561440</v>
       </c>
       <c r="F21" s="55">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="G21" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="54">
-        <v>45291</v>
+        <v>45175</v>
       </c>
       <c r="I21" s="55" t="s">
         <v>10</v>
@@ -3439,31 +3445,31 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="54">
-        <v>45097</v>
+        <v>45110</v>
       </c>
       <c r="B22" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>482</v>
+        <v>231</v>
       </c>
       <c r="D22" s="55" t="s">
         <v>626</v>
       </c>
       <c r="E22" s="55">
-        <v>324199</v>
+        <v>323111</v>
       </c>
       <c r="F22" s="55">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="G22" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H22" s="54">
-        <v>45163</v>
+        <v>45291</v>
       </c>
       <c r="I22" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J22" s="53" t="s">
         <v>627</v>
@@ -3475,31 +3481,31 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="54">
-        <v>45090</v>
+        <v>45097</v>
       </c>
       <c r="B23" s="55" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>227</v>
+        <v>482</v>
       </c>
       <c r="D23" s="55" t="s">
         <v>628</v>
       </c>
       <c r="E23" s="55">
-        <v>336390</v>
+        <v>324199</v>
       </c>
       <c r="F23" s="55">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="G23" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H23" s="54">
-        <v>45153</v>
+        <v>45163</v>
       </c>
       <c r="I23" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J23" s="53" t="s">
         <v>629</v>
@@ -3511,31 +3517,31 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="54">
-        <v>45083</v>
+        <v>45090</v>
       </c>
       <c r="B24" s="55" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="D24" s="55" t="s">
         <v>630</v>
       </c>
       <c r="E24" s="55">
-        <v>2121</v>
+        <v>336390</v>
       </c>
       <c r="F24" s="55">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="G24" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="54">
-        <v>45094</v>
+        <v>45153</v>
       </c>
       <c r="I24" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J24" s="53" t="s">
         <v>631</v>
@@ -3547,28 +3553,28 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="54">
-        <v>45079</v>
+        <v>45083</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="D25" s="55" t="s">
         <v>632</v>
       </c>
       <c r="E25" s="55">
-        <v>541219</v>
+        <v>2121</v>
       </c>
       <c r="F25" s="55">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="G25" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H25" s="54">
-        <v>45138</v>
+        <v>45094</v>
       </c>
       <c r="I25" s="55" t="s">
         <v>13</v>
@@ -3583,22 +3589,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="54">
-        <v>45078</v>
+        <v>45079</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D26" s="55" t="s">
         <v>634</v>
       </c>
       <c r="E26" s="55">
-        <v>621910</v>
+        <v>541219</v>
       </c>
       <c r="F26" s="55">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="G26" s="55" t="s">
         <v>16</v>
@@ -3622,10 +3628,10 @@
         <v>45078</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D27" s="55" t="s">
         <v>636</v>
@@ -3634,7 +3640,7 @@
         <v>621910</v>
       </c>
       <c r="F27" s="55">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="G27" s="55" t="s">
         <v>16</v>
@@ -3655,34 +3661,34 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="54">
-        <v>45076</v>
+        <v>45078</v>
       </c>
       <c r="B28" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C28" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="D28" s="55" t="s">
         <v>638</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="E28" s="55">
+        <v>621910</v>
+      </c>
+      <c r="F28" s="55">
+        <v>72</v>
+      </c>
+      <c r="G28" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="54">
+        <v>45138</v>
+      </c>
+      <c r="I28" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="53" t="s">
         <v>639</v>
-      </c>
-      <c r="E28" s="55">
-        <v>334514</v>
-      </c>
-      <c r="F28" s="55">
-        <v>235</v>
-      </c>
-      <c r="G28" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="54">
-        <v>45199</v>
-      </c>
-      <c r="I28" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J28" s="53" t="s">
-        <v>640</v>
       </c>
       <c r="K28" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3691,34 +3697,34 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="54">
-        <v>45062</v>
+        <v>45076</v>
       </c>
       <c r="B29" s="55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>251</v>
+        <v>640</v>
       </c>
       <c r="D29" s="55" t="s">
-        <v>558</v>
+        <v>641</v>
       </c>
       <c r="E29" s="55">
-        <v>722310</v>
+        <v>334514</v>
       </c>
       <c r="F29" s="55">
-        <v>59</v>
+        <v>235</v>
       </c>
       <c r="G29" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H29" s="54">
-        <v>45138</v>
+        <v>45199</v>
       </c>
       <c r="I29" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J29" s="53" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K29" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3727,28 +3733,28 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="54">
-        <v>45051</v>
+        <v>45062</v>
       </c>
       <c r="B30" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D30" s="55" t="s">
-        <v>642</v>
+        <v>558</v>
       </c>
       <c r="E30" s="55">
-        <v>624120</v>
+        <v>722310</v>
       </c>
       <c r="F30" s="55">
-        <v>450</v>
+        <v>59</v>
       </c>
       <c r="G30" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H30" s="54">
-        <v>45052</v>
+        <v>45138</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>13</v>
@@ -3763,34 +3769,34 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="54">
-        <v>45044</v>
+        <v>45051</v>
       </c>
       <c r="B31" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C31" s="55" t="s">
-        <v>342</v>
+        <v>226</v>
       </c>
       <c r="D31" s="55" t="s">
-        <v>590</v>
+        <v>644</v>
       </c>
       <c r="E31" s="55">
-        <v>488510</v>
+        <v>624120</v>
       </c>
       <c r="F31" s="55">
-        <v>74</v>
+        <v>450</v>
       </c>
       <c r="G31" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H31" s="54">
-        <v>45113</v>
+        <v>45052</v>
       </c>
       <c r="I31" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J31" s="53" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="K31" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3799,34 +3805,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="54">
-        <v>45042</v>
+        <v>45044</v>
       </c>
       <c r="B32" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>645</v>
+        <v>342</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>646</v>
+        <v>592</v>
       </c>
       <c r="E32" s="55">
-        <v>541614</v>
+        <v>488510</v>
       </c>
       <c r="F32" s="55">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G32" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="54">
-        <v>45138</v>
+        <v>45113</v>
       </c>
       <c r="I32" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J32" s="53" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="K32" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3838,28 +3844,28 @@
         <v>45042</v>
       </c>
       <c r="B33" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>342</v>
+        <v>647</v>
       </c>
       <c r="D33" s="55" t="s">
         <v>648</v>
       </c>
       <c r="E33" s="55">
-        <v>541714</v>
+        <v>541614</v>
       </c>
       <c r="F33" s="55">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G33" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="54">
-        <v>45044</v>
+        <v>45138</v>
       </c>
       <c r="I33" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J33" s="53" t="s">
         <v>649</v>
@@ -3871,31 +3877,31 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="54">
-        <v>45026</v>
+        <v>45042</v>
       </c>
       <c r="B34" s="55" t="s">
         <v>108</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>238</v>
+        <v>342</v>
       </c>
       <c r="D34" s="55" t="s">
         <v>650</v>
       </c>
       <c r="E34" s="55">
-        <v>33392</v>
+        <v>541714</v>
       </c>
       <c r="F34" s="55">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G34" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H34" s="54">
-        <v>45086</v>
+        <v>45044</v>
       </c>
       <c r="I34" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J34" s="53" t="s">
         <v>651</v>
@@ -3907,28 +3913,28 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="54">
-        <v>45019</v>
+        <v>45026</v>
       </c>
       <c r="B35" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C35" s="55" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="D35" s="55" t="s">
         <v>652</v>
       </c>
       <c r="E35" s="55">
-        <v>541614</v>
+        <v>33392</v>
       </c>
       <c r="F35" s="55">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="G35" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H35" s="54">
-        <v>45083</v>
+        <v>45086</v>
       </c>
       <c r="I35" s="55" t="s">
         <v>13</v>
@@ -3943,31 +3949,31 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="54">
-        <v>45006</v>
+        <v>45019</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>128</v>
+        <v>274</v>
       </c>
       <c r="D36" s="55" t="s">
         <v>654</v>
       </c>
       <c r="E36" s="55">
-        <v>323111</v>
+        <v>541614</v>
       </c>
       <c r="F36" s="55">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="G36" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H36" s="54">
-        <v>45066</v>
+        <v>45083</v>
       </c>
       <c r="I36" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J36" s="53" t="s">
         <v>655</v>
@@ -3979,28 +3985,28 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="54">
-        <v>44984</v>
+        <v>45006</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>239</v>
+        <v>128</v>
       </c>
       <c r="D37" s="55" t="s">
         <v>656</v>
       </c>
       <c r="E37" s="55">
-        <v>322130</v>
+        <v>323111</v>
       </c>
       <c r="F37" s="55">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G37" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H37" s="54">
-        <v>45033</v>
+        <v>45066</v>
       </c>
       <c r="I37" s="55" t="s">
         <v>10</v>
@@ -4015,28 +4021,28 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="54">
-        <v>44956</v>
+        <v>44984</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>512</v>
+        <v>239</v>
       </c>
       <c r="D38" s="55" t="s">
         <v>658</v>
       </c>
       <c r="E38" s="55">
-        <v>332999</v>
+        <v>322130</v>
       </c>
       <c r="F38" s="55">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G38" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H38" s="54">
-        <v>44949</v>
+        <v>45033</v>
       </c>
       <c r="I38" s="55" t="s">
         <v>10</v>
@@ -4051,31 +4057,31 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="54">
-        <v>44950</v>
+        <v>44956</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C39" s="55" t="s">
-        <v>238</v>
+        <v>512</v>
       </c>
       <c r="D39" s="55" t="s">
         <v>660</v>
       </c>
       <c r="E39" s="55">
-        <v>493110</v>
+        <v>332999</v>
       </c>
       <c r="F39" s="55">
-        <v>236</v>
+        <v>90</v>
       </c>
       <c r="G39" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H39" s="54">
-        <v>45107</v>
+        <v>44949</v>
       </c>
       <c r="I39" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J39" s="53" t="s">
         <v>661</v>
@@ -4087,28 +4093,28 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="54">
-        <v>44945</v>
+        <v>44950</v>
       </c>
       <c r="B40" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D40" s="55" t="s">
         <v>662</v>
       </c>
       <c r="E40" s="55">
-        <v>336323</v>
+        <v>493110</v>
       </c>
       <c r="F40" s="55">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="G40" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H40" s="54">
-        <v>45017</v>
+        <v>45107</v>
       </c>
       <c r="I40" s="55" t="s">
         <v>13</v>
@@ -4123,31 +4129,31 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="54">
-        <v>44943</v>
+        <v>44945</v>
       </c>
       <c r="B41" s="55" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="D41" s="55" t="s">
         <v>664</v>
       </c>
       <c r="E41" s="55">
-        <v>488210</v>
+        <v>336323</v>
       </c>
       <c r="F41" s="55">
-        <v>93</v>
+        <v>212</v>
       </c>
       <c r="G41" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H41" s="54">
-        <v>45016</v>
+        <v>45017</v>
       </c>
       <c r="I41" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J41" s="53" t="s">
         <v>665</v>
@@ -4159,31 +4165,31 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="54">
-        <v>44937</v>
+        <v>44943</v>
       </c>
       <c r="B42" s="55" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>128</v>
+        <v>259</v>
       </c>
       <c r="D42" s="55" t="s">
         <v>666</v>
       </c>
       <c r="E42" s="55">
-        <v>321199</v>
+        <v>488210</v>
       </c>
       <c r="F42" s="55">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G42" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H42" s="54">
-        <v>44990</v>
+        <v>45016</v>
       </c>
       <c r="I42" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J42" s="53" t="s">
         <v>667</v>
@@ -4198,33 +4204,69 @@
         <v>44937</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>332</v>
+        <v>108</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>333</v>
+        <v>128</v>
       </c>
       <c r="D43" s="55" t="s">
         <v>668</v>
       </c>
       <c r="E43" s="55">
-        <v>485320</v>
+        <v>321199</v>
       </c>
       <c r="F43" s="55">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="G43" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="54">
-        <v>44977</v>
+        <v>44990</v>
       </c>
       <c r="I43" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J43" s="53" t="s">
         <v>669</v>
       </c>
       <c r="K43" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A44" s="54">
+        <v>44937</v>
+      </c>
+      <c r="B44" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="C44" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="D44" s="55" t="s">
+        <v>670</v>
+      </c>
+      <c r="E44" s="55">
+        <v>485320</v>
+      </c>
+      <c r="F44" s="55">
+        <v>90</v>
+      </c>
+      <c r="G44" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="54">
+        <v>44977</v>
+      </c>
+      <c r="I44" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="53" t="s">
+        <v>671</v>
+      </c>
+      <c r="K44" s="57" t="str">
         <f t="shared" si="0"/>
         <v>WARN</v>
       </c>
@@ -6076,10 +6118,10 @@
         <v>44092</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D12" s="55" t="s">
         <v>295</v>
@@ -6112,10 +6154,10 @@
         <v>44092</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D13" s="55" t="s">
         <v>295</v>
@@ -6292,25 +6334,25 @@
         <v>44050</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D18" s="55" t="s">
         <v>306</v>
       </c>
       <c r="E18" s="55">
-        <v>72251</v>
+        <v>3221</v>
       </c>
       <c r="F18" s="55">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G18" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H18" s="54">
-        <v>43926</v>
+        <v>44104</v>
       </c>
       <c r="I18" s="55" t="s">
         <v>13</v>
@@ -6328,25 +6370,25 @@
         <v>44050</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D19" s="55" t="s">
         <v>308</v>
       </c>
       <c r="E19" s="55">
-        <v>3221</v>
+        <v>72251</v>
       </c>
       <c r="F19" s="55">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G19" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H19" s="54">
-        <v>44104</v>
+        <v>43926</v>
       </c>
       <c r="I19" s="55" t="s">
         <v>13</v>
@@ -6520,16 +6562,16 @@
         <v>213113</v>
       </c>
       <c r="F24" s="55">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G24" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="54">
-        <v>44098</v>
+        <v>44094</v>
       </c>
       <c r="I24" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J24" s="53" t="s">
         <v>319</v>
@@ -6544,10 +6586,10 @@
         <v>44035</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="D25" s="55" t="s">
         <v>320</v>
@@ -6556,13 +6598,13 @@
         <v>213113</v>
       </c>
       <c r="F25" s="55">
-        <v>194</v>
+        <v>5</v>
       </c>
       <c r="G25" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H25" s="54">
-        <v>44094</v>
+        <v>44098</v>
       </c>
       <c r="I25" s="55" t="s">
         <v>13</v>
@@ -6580,10 +6622,10 @@
         <v>44035</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D26" s="55" t="s">
         <v>322</v>
@@ -6592,7 +6634,7 @@
         <v>213113</v>
       </c>
       <c r="F26" s="55">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="G26" s="55" t="s">
         <v>11</v>
@@ -6601,7 +6643,7 @@
         <v>44094</v>
       </c>
       <c r="I26" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J26" s="53" t="s">
         <v>323</v>
@@ -6700,7 +6742,7 @@
         <v>722110</v>
       </c>
       <c r="F29" s="55">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="G29" s="55" t="s">
         <v>16</v>
@@ -6736,7 +6778,7 @@
         <v>722110</v>
       </c>
       <c r="F30" s="55">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="G30" s="55" t="s">
         <v>16</v>
@@ -7912,10 +7954,10 @@
         <v>43938</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C63" s="55" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="D63" s="55" t="s">
         <v>397</v>
@@ -7924,7 +7966,7 @@
         <v>532111</v>
       </c>
       <c r="F63" s="55">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G63" s="55" t="s">
         <v>16</v>
@@ -7948,10 +7990,10 @@
         <v>43938</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C64" s="55" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="D64" s="55" t="s">
         <v>399</v>
@@ -7960,7 +8002,7 @@
         <v>532111</v>
       </c>
       <c r="F64" s="55">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>16</v>
@@ -7984,19 +8026,19 @@
         <v>43936</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C65" s="55" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>133</v>
+        <v>349</v>
       </c>
       <c r="E65" s="55">
-        <v>337215</v>
+        <v>488190</v>
       </c>
       <c r="F65" s="55">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="G65" s="55" t="s">
         <v>16</v>
@@ -8023,16 +8065,16 @@
         <v>40</v>
       </c>
       <c r="C66" s="55" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D66" s="55" t="s">
         <v>133</v>
       </c>
       <c r="E66" s="55">
-        <v>33791</v>
+        <v>337215</v>
       </c>
       <c r="F66" s="55">
-        <v>271</v>
+        <v>151</v>
       </c>
       <c r="G66" s="55" t="s">
         <v>16</v>
@@ -8056,19 +8098,19 @@
         <v>43936</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>349</v>
+        <v>133</v>
       </c>
       <c r="E67" s="55">
-        <v>488190</v>
+        <v>33791</v>
       </c>
       <c r="F67" s="55">
-        <v>17</v>
+        <v>271</v>
       </c>
       <c r="G67" s="55" t="s">
         <v>16</v>
@@ -8164,25 +8206,25 @@
         <v>43935</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C70" s="55" t="s">
-        <v>267</v>
+        <v>128</v>
       </c>
       <c r="D70" s="55" t="s">
         <v>408</v>
       </c>
       <c r="E70" s="55">
-        <v>712130</v>
+        <v>337910</v>
       </c>
       <c r="F70" s="55">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="G70" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H70" s="54">
-        <v>43941</v>
+        <v>43924</v>
       </c>
       <c r="I70" s="55" t="s">
         <v>13</v>
@@ -8200,25 +8242,25 @@
         <v>43935</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C71" s="55" t="s">
-        <v>128</v>
+        <v>267</v>
       </c>
       <c r="D71" s="55" t="s">
         <v>410</v>
       </c>
       <c r="E71" s="55">
-        <v>337910</v>
+        <v>712130</v>
       </c>
       <c r="F71" s="55">
-        <v>234</v>
+        <v>88</v>
       </c>
       <c r="G71" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H71" s="54">
-        <v>43924</v>
+        <v>43941</v>
       </c>
       <c r="I71" s="55" t="s">
         <v>13</v>
@@ -8491,7 +8533,7 @@
         <v>70</v>
       </c>
       <c r="C79" s="55" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D79" s="55" t="s">
         <v>426</v>
@@ -8500,7 +8542,7 @@
         <v>623110</v>
       </c>
       <c r="F79" s="55">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G79" s="55" t="s">
         <v>16</v>
@@ -8527,16 +8569,16 @@
         <v>70</v>
       </c>
       <c r="C80" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="D80" s="55" t="s">
         <v>428</v>
-      </c>
-      <c r="D80" s="55" t="s">
-        <v>429</v>
       </c>
       <c r="E80" s="55">
         <v>623110</v>
       </c>
       <c r="F80" s="55">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G80" s="55" t="s">
         <v>16</v>
@@ -8548,7 +8590,7 @@
         <v>13</v>
       </c>
       <c r="J80" s="53" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K80" s="57" t="str">
         <f t="shared" si="1"/>
@@ -8563,16 +8605,16 @@
         <v>70</v>
       </c>
       <c r="C81" s="55" t="s">
+        <v>430</v>
+      </c>
+      <c r="D81" s="55" t="s">
         <v>431</v>
-      </c>
-      <c r="D81" s="55" t="s">
-        <v>432</v>
       </c>
       <c r="E81" s="55">
         <v>623110</v>
       </c>
       <c r="F81" s="55">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G81" s="55" t="s">
         <v>16</v>
@@ -8584,7 +8626,7 @@
         <v>13</v>
       </c>
       <c r="J81" s="53" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K81" s="57" t="str">
         <f t="shared" si="1"/>
@@ -8599,16 +8641,16 @@
         <v>70</v>
       </c>
       <c r="C82" s="55" t="s">
+        <v>433</v>
+      </c>
+      <c r="D82" s="55" t="s">
         <v>434</v>
-      </c>
-      <c r="D82" s="55" t="s">
-        <v>435</v>
       </c>
       <c r="E82" s="55">
         <v>623110</v>
       </c>
       <c r="F82" s="55">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G82" s="55" t="s">
         <v>16</v>
@@ -8620,7 +8662,7 @@
         <v>13</v>
       </c>
       <c r="J82" s="53" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K82" s="57" t="str">
         <f t="shared" si="1"/>
@@ -8635,7 +8677,7 @@
         <v>70</v>
       </c>
       <c r="C83" s="55" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D83" s="55" t="s">
         <v>437</v>
@@ -8671,7 +8713,7 @@
         <v>70</v>
       </c>
       <c r="C84" s="55" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="D84" s="55" t="s">
         <v>439</v>
@@ -8680,7 +8722,7 @@
         <v>623110</v>
       </c>
       <c r="F84" s="55">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G84" s="55" t="s">
         <v>16</v>
@@ -8743,7 +8785,7 @@
         <v>70</v>
       </c>
       <c r="C86" s="55" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="D86" s="55" t="s">
         <v>443</v>
@@ -8752,7 +8794,7 @@
         <v>623110</v>
       </c>
       <c r="F86" s="55">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G86" s="55" t="s">
         <v>16</v>
@@ -8779,7 +8821,7 @@
         <v>70</v>
       </c>
       <c r="C87" s="55" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="D87" s="55" t="s">
         <v>445</v>
@@ -8788,7 +8830,7 @@
         <v>623110</v>
       </c>
       <c r="F87" s="55">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G87" s="55" t="s">
         <v>16</v>
@@ -8815,22 +8857,22 @@
         <v>70</v>
       </c>
       <c r="C88" s="55" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="D88" s="55" t="s">
         <v>447</v>
       </c>
       <c r="E88" s="55">
-        <v>623110</v>
+        <v>423110</v>
       </c>
       <c r="F88" s="55">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="G88" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H88" s="54">
-        <v>43910</v>
+        <v>43934</v>
       </c>
       <c r="I88" s="55" t="s">
         <v>13</v>
@@ -8851,22 +8893,22 @@
         <v>70</v>
       </c>
       <c r="C89" s="55" t="s">
-        <v>434</v>
+        <v>273</v>
       </c>
       <c r="D89" s="55" t="s">
         <v>449</v>
       </c>
       <c r="E89" s="55">
-        <v>423110</v>
+        <v>623110</v>
       </c>
       <c r="F89" s="55">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="G89" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H89" s="54">
-        <v>43934</v>
+        <v>43910</v>
       </c>
       <c r="I89" s="55" t="s">
         <v>13</v>
@@ -8920,25 +8962,25 @@
         <v>43923</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D91" s="55" t="s">
         <v>453</v>
       </c>
       <c r="E91" s="55">
-        <v>721110</v>
+        <v>333999</v>
       </c>
       <c r="F91" s="55">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="G91" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H91" s="54">
-        <v>43910</v>
+        <v>43926</v>
       </c>
       <c r="I91" s="55" t="s">
         <v>13</v>
@@ -8956,25 +8998,25 @@
         <v>43923</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>258</v>
+        <v>128</v>
       </c>
       <c r="D92" s="55" t="s">
         <v>455</v>
       </c>
       <c r="E92" s="55">
-        <v>333999</v>
+        <v>721110</v>
       </c>
       <c r="F92" s="55">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G92" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H92" s="54">
-        <v>43926</v>
+        <v>43906</v>
       </c>
       <c r="I92" s="55" t="s">
         <v>13</v>
@@ -8992,10 +9034,10 @@
         <v>43923</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C93" s="55" t="s">
-        <v>128</v>
+        <v>273</v>
       </c>
       <c r="D93" s="55" t="s">
         <v>457</v>
@@ -9004,13 +9046,13 @@
         <v>721110</v>
       </c>
       <c r="F93" s="55">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="G93" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H93" s="54">
-        <v>43906</v>
+        <v>43910</v>
       </c>
       <c r="I93" s="55" t="s">
         <v>13</v>
@@ -9244,31 +9286,31 @@
         <v>43922</v>
       </c>
       <c r="B100" s="55" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="C100" s="55" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="D100" s="55" t="s">
-        <v>201</v>
+        <v>469</v>
       </c>
       <c r="E100" s="55">
-        <v>21211</v>
+        <v>541611</v>
       </c>
       <c r="F100" s="55">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G100" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H100" s="54">
-        <v>43984</v>
+        <v>43920</v>
       </c>
       <c r="I100" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J100" s="53" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K100" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9280,22 +9322,22 @@
         <v>43922</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C101" s="55" t="s">
-        <v>470</v>
+        <v>227</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>471</v>
+        <v>201</v>
       </c>
       <c r="E101" s="55">
         <v>21211</v>
       </c>
       <c r="F101" s="55">
-        <v>254</v>
+        <v>42</v>
       </c>
       <c r="G101" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H101" s="54">
         <v>43984</v>
@@ -9304,7 +9346,7 @@
         <v>13</v>
       </c>
       <c r="J101" s="53" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K101" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9316,19 +9358,19 @@
         <v>43922</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C102" s="55" t="s">
+        <v>472</v>
+      </c>
+      <c r="D102" s="55" t="s">
         <v>473</v>
       </c>
-      <c r="D102" s="55" t="s">
-        <v>474</v>
-      </c>
       <c r="E102" s="55">
-        <v>423520</v>
+        <v>21211</v>
       </c>
       <c r="F102" s="55">
-        <v>11</v>
+        <v>254</v>
       </c>
       <c r="G102" s="55" t="s">
         <v>11</v>
@@ -9340,7 +9382,7 @@
         <v>13</v>
       </c>
       <c r="J102" s="53" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K102" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9352,25 +9394,25 @@
         <v>43922</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C103" s="55" t="s">
-        <v>128</v>
+        <v>475</v>
       </c>
       <c r="D103" s="55" t="s">
         <v>476</v>
       </c>
       <c r="E103" s="55">
-        <v>541611</v>
+        <v>423520</v>
       </c>
       <c r="F103" s="55">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G103" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H103" s="54">
-        <v>43920</v>
+        <v>43984</v>
       </c>
       <c r="I103" s="55" t="s">
         <v>13</v>
@@ -14230,5 +14272,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27CEE514-E64C-4682-872F-66DA0246325F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB16EBAB-32CA-49E2-B7DE-DC6630660739}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73327EF8-0D9B-466A-87CF-0774DC3244F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1494741B-7B32-4357-B394-844278515F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="1520" windowWidth="19110" windowHeight="8970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="7" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="674">
   <si>
     <t>Date Received</t>
   </si>
@@ -1809,6 +1809,12 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000001oY17/5h0K2TokLeEb9PXrbvX4oWNviT4MCksNDEalEHDjlHE</t>
+  </si>
+  <si>
+    <t>OIA Global</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y0000055mBF/9imruPEg2sPxUkT2Lp99bCR71NbuzJsj2.328NtCRm8</t>
   </si>
   <si>
     <t>Charter Communications</t>
@@ -2672,7 +2678,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
@@ -2725,7 +2731,7 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
-        <v>45266</v>
+        <v>45273</v>
       </c>
       <c r="B2" s="55" t="s">
         <v>29</v>
@@ -2737,19 +2743,19 @@
         <v>587</v>
       </c>
       <c r="E2" s="55">
-        <v>561422</v>
+        <v>423840</v>
       </c>
       <c r="F2" s="55">
-        <v>227</v>
+        <v>89</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H2" s="54">
-        <v>45296</v>
+        <v>45303</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J2" s="53" t="s">
         <v>588</v>
@@ -2761,67 +2767,67 @@
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
-        <v>45261</v>
+        <v>45266</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C3" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" s="55" t="s">
         <v>589</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="E3" s="55">
+        <v>561422</v>
+      </c>
+      <c r="F3" s="55">
+        <v>227</v>
+      </c>
+      <c r="G3" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="54">
+        <v>45296</v>
+      </c>
+      <c r="I3" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="53" t="s">
         <v>590</v>
       </c>
-      <c r="E3" s="55">
-        <v>424420</v>
-      </c>
-      <c r="F3" s="55">
-        <v>3</v>
-      </c>
-      <c r="G3" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="54">
-        <v>45318</v>
-      </c>
-      <c r="I3" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="53" t="s">
-        <v>591</v>
-      </c>
       <c r="K3" s="57" t="str">
-        <f t="shared" ref="K3:K44" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <f t="shared" ref="K3:K45" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
         <v>WARN</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54">
-        <v>45222</v>
+        <v>45261</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>342</v>
+        <v>591</v>
       </c>
       <c r="D4" s="55" t="s">
         <v>592</v>
       </c>
       <c r="E4" s="55">
-        <v>488510</v>
+        <v>424420</v>
       </c>
       <c r="F4" s="55">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H4" s="54">
-        <v>45222</v>
+        <v>45318</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J4" s="53" t="s">
         <v>593</v>
@@ -2833,34 +2839,34 @@
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54">
-        <v>45191</v>
+        <v>45222</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C5" s="55" t="s">
+        <v>342</v>
+      </c>
+      <c r="D5" s="55" t="s">
         <v>594</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="E5" s="55">
+        <v>488510</v>
+      </c>
+      <c r="F5" s="55">
+        <v>135</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="54">
+        <v>45222</v>
+      </c>
+      <c r="I5" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="53" t="s">
         <v>595</v>
-      </c>
-      <c r="E5" s="55">
-        <v>445110</v>
-      </c>
-      <c r="F5" s="55">
-        <v>15</v>
-      </c>
-      <c r="G5" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="54">
-        <v>45196</v>
-      </c>
-      <c r="I5" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="53" t="s">
-        <v>596</v>
       </c>
       <c r="K5" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2869,28 +2875,28 @@
     </row>
     <row r="6" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54">
-        <v>45167</v>
+        <v>45191</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>333</v>
+        <v>596</v>
       </c>
       <c r="D6" s="55" t="s">
         <v>597</v>
       </c>
       <c r="E6" s="55">
-        <v>5221</v>
+        <v>445110</v>
       </c>
       <c r="F6" s="55">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G6" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H6" s="54">
-        <v>45260</v>
+        <v>45196</v>
       </c>
       <c r="I6" s="55" t="s">
         <v>13</v>
@@ -2905,31 +2911,31 @@
     </row>
     <row r="7" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54">
-        <v>45159</v>
+        <v>45167</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>15</v>
+        <v>332</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="D7" s="55" t="s">
         <v>599</v>
       </c>
       <c r="E7" s="55">
-        <v>326291</v>
+        <v>5221</v>
       </c>
       <c r="F7" s="55">
-        <v>221</v>
+        <v>17</v>
       </c>
       <c r="G7" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H7" s="54">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="I7" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J7" s="53" t="s">
         <v>600</v>
@@ -2941,31 +2947,31 @@
     </row>
     <row r="8" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="54">
-        <v>45139</v>
+        <v>45159</v>
       </c>
       <c r="B8" s="55" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>509</v>
+        <v>270</v>
       </c>
       <c r="D8" s="55" t="s">
         <v>601</v>
       </c>
       <c r="E8" s="55">
-        <v>624120</v>
+        <v>326291</v>
       </c>
       <c r="F8" s="55">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="G8" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="54">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="I8" s="55" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J8" s="53" t="s">
         <v>602</v>
@@ -2977,31 +2983,31 @@
     </row>
     <row r="9" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="54">
-        <v>45137</v>
+        <v>45139</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>226</v>
+        <v>509</v>
       </c>
       <c r="D9" s="55" t="s">
         <v>603</v>
       </c>
       <c r="E9" s="55">
-        <v>484110</v>
-      </c>
-      <c r="F9" s="55" t="s">
-        <v>10</v>
+        <v>624120</v>
+      </c>
+      <c r="F9" s="55">
+        <v>284</v>
       </c>
       <c r="G9" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="54">
-        <v>45137</v>
+        <v>45199</v>
       </c>
       <c r="I9" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J9" s="53" t="s">
         <v>604</v>
@@ -3016,13 +3022,13 @@
         <v>45137</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E10" s="55">
         <v>484110</v>
@@ -3040,7 +3046,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K10" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3052,13 +3058,13 @@
         <v>45137</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E11" s="55">
         <v>484110</v>
@@ -3076,7 +3082,7 @@
         <v>13</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K11" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3085,34 +3091,34 @@
     </row>
     <row r="12" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="54">
-        <v>45127</v>
+        <v>45137</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>517</v>
+        <v>605</v>
       </c>
       <c r="E12" s="55">
-        <v>336390</v>
-      </c>
-      <c r="F12" s="55">
-        <v>135</v>
+        <v>484110</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>10</v>
       </c>
       <c r="G12" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="54">
-        <v>45290</v>
+        <v>45137</v>
       </c>
       <c r="I12" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K12" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3124,25 +3130,25 @@
         <v>45127</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>608</v>
+        <v>517</v>
       </c>
       <c r="E13" s="55">
-        <v>2121</v>
+        <v>336390</v>
       </c>
       <c r="F13" s="55">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="G13" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H13" s="54">
-        <v>45179</v>
+        <v>45290</v>
       </c>
       <c r="I13" s="55" t="s">
         <v>13</v>
@@ -3172,7 +3178,7 @@
         <v>2121</v>
       </c>
       <c r="F14" s="55">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G14" s="55" t="s">
         <v>16</v>
@@ -3208,7 +3214,7 @@
         <v>2121</v>
       </c>
       <c r="F15" s="55">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G15" s="55" t="s">
         <v>16</v>
@@ -3244,13 +3250,13 @@
         <v>2121</v>
       </c>
       <c r="F16" s="55">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G16" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H16" s="54">
-        <v>45132</v>
+        <v>45179</v>
       </c>
       <c r="I16" s="55" t="s">
         <v>13</v>
@@ -3280,13 +3286,13 @@
         <v>2121</v>
       </c>
       <c r="F17" s="55">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G17" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H17" s="54">
-        <v>45179</v>
+        <v>45132</v>
       </c>
       <c r="I17" s="55" t="s">
         <v>13</v>
@@ -3316,7 +3322,7 @@
         <v>2121</v>
       </c>
       <c r="F18" s="55">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G18" s="55" t="s">
         <v>16</v>
@@ -3352,13 +3358,13 @@
         <v>2121</v>
       </c>
       <c r="F19" s="55">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="G19" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H19" s="54">
-        <v>45132</v>
+        <v>45179</v>
       </c>
       <c r="I19" s="55" t="s">
         <v>13</v>
@@ -3388,13 +3394,13 @@
         <v>2121</v>
       </c>
       <c r="F20" s="55">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G20" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="54">
-        <v>45179</v>
+        <v>45132</v>
       </c>
       <c r="I20" s="55" t="s">
         <v>13</v>
@@ -3409,31 +3415,31 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="54">
-        <v>45117</v>
+        <v>45127</v>
       </c>
       <c r="B21" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D21" s="55" t="s">
         <v>624</v>
       </c>
       <c r="E21" s="55">
-        <v>561440</v>
+        <v>2121</v>
       </c>
       <c r="F21" s="55">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G21" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H21" s="54">
-        <v>45175</v>
+        <v>45179</v>
       </c>
       <c r="I21" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J21" s="53" t="s">
         <v>625</v>
@@ -3445,28 +3451,28 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="54">
-        <v>45110</v>
+        <v>45117</v>
       </c>
       <c r="B22" s="55" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D22" s="55" t="s">
         <v>626</v>
       </c>
       <c r="E22" s="55">
-        <v>323111</v>
+        <v>561440</v>
       </c>
       <c r="F22" s="55">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="G22" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H22" s="54">
-        <v>45291</v>
+        <v>45175</v>
       </c>
       <c r="I22" s="55" t="s">
         <v>10</v>
@@ -3481,31 +3487,31 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="54">
-        <v>45097</v>
+        <v>45110</v>
       </c>
       <c r="B23" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>482</v>
+        <v>231</v>
       </c>
       <c r="D23" s="55" t="s">
         <v>628</v>
       </c>
       <c r="E23" s="55">
-        <v>324199</v>
+        <v>323111</v>
       </c>
       <c r="F23" s="55">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="G23" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H23" s="54">
-        <v>45163</v>
+        <v>45291</v>
       </c>
       <c r="I23" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J23" s="53" t="s">
         <v>629</v>
@@ -3517,31 +3523,31 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="54">
-        <v>45090</v>
+        <v>45097</v>
       </c>
       <c r="B24" s="55" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>227</v>
+        <v>482</v>
       </c>
       <c r="D24" s="55" t="s">
         <v>630</v>
       </c>
       <c r="E24" s="55">
-        <v>336390</v>
+        <v>324199</v>
       </c>
       <c r="F24" s="55">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="G24" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H24" s="54">
-        <v>45153</v>
+        <v>45163</v>
       </c>
       <c r="I24" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J24" s="53" t="s">
         <v>631</v>
@@ -3553,31 +3559,31 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="54">
-        <v>45083</v>
+        <v>45090</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="D25" s="55" t="s">
         <v>632</v>
       </c>
       <c r="E25" s="55">
-        <v>2121</v>
+        <v>336390</v>
       </c>
       <c r="F25" s="55">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="G25" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H25" s="54">
-        <v>45094</v>
+        <v>45153</v>
       </c>
       <c r="I25" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J25" s="53" t="s">
         <v>633</v>
@@ -3589,28 +3595,28 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="54">
-        <v>45079</v>
+        <v>45083</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="D26" s="55" t="s">
         <v>634</v>
       </c>
       <c r="E26" s="55">
-        <v>541219</v>
+        <v>2121</v>
       </c>
       <c r="F26" s="55">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="G26" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H26" s="54">
-        <v>45138</v>
+        <v>45094</v>
       </c>
       <c r="I26" s="55" t="s">
         <v>13</v>
@@ -3625,22 +3631,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="54">
-        <v>45078</v>
+        <v>45079</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D27" s="55" t="s">
         <v>636</v>
       </c>
       <c r="E27" s="55">
-        <v>621910</v>
+        <v>541219</v>
       </c>
       <c r="F27" s="55">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="G27" s="55" t="s">
         <v>16</v>
@@ -3664,10 +3670,10 @@
         <v>45078</v>
       </c>
       <c r="B28" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D28" s="55" t="s">
         <v>638</v>
@@ -3676,7 +3682,7 @@
         <v>621910</v>
       </c>
       <c r="F28" s="55">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="G28" s="55" t="s">
         <v>16</v>
@@ -3697,34 +3703,34 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="54">
-        <v>45076</v>
+        <v>45078</v>
       </c>
       <c r="B29" s="55" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C29" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="D29" s="55" t="s">
         <v>640</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="E29" s="55">
+        <v>621910</v>
+      </c>
+      <c r="F29" s="55">
+        <v>72</v>
+      </c>
+      <c r="G29" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="54">
+        <v>45138</v>
+      </c>
+      <c r="I29" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="53" t="s">
         <v>641</v>
-      </c>
-      <c r="E29" s="55">
-        <v>334514</v>
-      </c>
-      <c r="F29" s="55">
-        <v>235</v>
-      </c>
-      <c r="G29" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="54">
-        <v>45199</v>
-      </c>
-      <c r="I29" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J29" s="53" t="s">
-        <v>642</v>
       </c>
       <c r="K29" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3733,34 +3739,34 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="54">
-        <v>45062</v>
+        <v>45076</v>
       </c>
       <c r="B30" s="55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>251</v>
+        <v>642</v>
       </c>
       <c r="D30" s="55" t="s">
-        <v>558</v>
+        <v>643</v>
       </c>
       <c r="E30" s="55">
-        <v>722310</v>
+        <v>334514</v>
       </c>
       <c r="F30" s="55">
-        <v>59</v>
+        <v>235</v>
       </c>
       <c r="G30" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H30" s="54">
-        <v>45138</v>
+        <v>45199</v>
       </c>
       <c r="I30" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J30" s="53" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K30" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3769,28 +3775,28 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="54">
-        <v>45051</v>
+        <v>45062</v>
       </c>
       <c r="B31" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C31" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D31" s="55" t="s">
-        <v>644</v>
+        <v>558</v>
       </c>
       <c r="E31" s="55">
-        <v>624120</v>
+        <v>722310</v>
       </c>
       <c r="F31" s="55">
-        <v>450</v>
+        <v>59</v>
       </c>
       <c r="G31" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H31" s="54">
-        <v>45052</v>
+        <v>45138</v>
       </c>
       <c r="I31" s="55" t="s">
         <v>13</v>
@@ -3805,34 +3811,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="54">
-        <v>45044</v>
+        <v>45051</v>
       </c>
       <c r="B32" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>342</v>
+        <v>226</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>592</v>
+        <v>646</v>
       </c>
       <c r="E32" s="55">
-        <v>488510</v>
+        <v>624120</v>
       </c>
       <c r="F32" s="55">
-        <v>74</v>
+        <v>450</v>
       </c>
       <c r="G32" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H32" s="54">
-        <v>45113</v>
+        <v>45052</v>
       </c>
       <c r="I32" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J32" s="53" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K32" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3841,34 +3847,34 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="54">
-        <v>45042</v>
+        <v>45044</v>
       </c>
       <c r="B33" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>647</v>
+        <v>342</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>648</v>
+        <v>594</v>
       </c>
       <c r="E33" s="55">
-        <v>541614</v>
+        <v>488510</v>
       </c>
       <c r="F33" s="55">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G33" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="54">
-        <v>45138</v>
+        <v>45113</v>
       </c>
       <c r="I33" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J33" s="53" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="K33" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3880,28 +3886,28 @@
         <v>45042</v>
       </c>
       <c r="B34" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>342</v>
+        <v>649</v>
       </c>
       <c r="D34" s="55" t="s">
         <v>650</v>
       </c>
       <c r="E34" s="55">
-        <v>541714</v>
+        <v>541614</v>
       </c>
       <c r="F34" s="55">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G34" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H34" s="54">
-        <v>45044</v>
+        <v>45138</v>
       </c>
       <c r="I34" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J34" s="53" t="s">
         <v>651</v>
@@ -3913,31 +3919,31 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="54">
-        <v>45026</v>
+        <v>45042</v>
       </c>
       <c r="B35" s="55" t="s">
         <v>108</v>
       </c>
       <c r="C35" s="55" t="s">
-        <v>238</v>
+        <v>342</v>
       </c>
       <c r="D35" s="55" t="s">
         <v>652</v>
       </c>
       <c r="E35" s="55">
-        <v>33392</v>
+        <v>541714</v>
       </c>
       <c r="F35" s="55">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G35" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H35" s="54">
-        <v>45086</v>
+        <v>45044</v>
       </c>
       <c r="I35" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J35" s="53" t="s">
         <v>653</v>
@@ -3949,28 +3955,28 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="54">
-        <v>45019</v>
+        <v>45026</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="D36" s="55" t="s">
         <v>654</v>
       </c>
       <c r="E36" s="55">
-        <v>541614</v>
+        <v>33392</v>
       </c>
       <c r="F36" s="55">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="G36" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H36" s="54">
-        <v>45083</v>
+        <v>45086</v>
       </c>
       <c r="I36" s="55" t="s">
         <v>13</v>
@@ -3985,31 +3991,31 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="54">
-        <v>45006</v>
+        <v>45019</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>128</v>
+        <v>274</v>
       </c>
       <c r="D37" s="55" t="s">
         <v>656</v>
       </c>
       <c r="E37" s="55">
-        <v>323111</v>
+        <v>541614</v>
       </c>
       <c r="F37" s="55">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="G37" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H37" s="54">
-        <v>45066</v>
+        <v>45083</v>
       </c>
       <c r="I37" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J37" s="53" t="s">
         <v>657</v>
@@ -4021,28 +4027,28 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="54">
-        <v>44984</v>
+        <v>45006</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>239</v>
+        <v>128</v>
       </c>
       <c r="D38" s="55" t="s">
         <v>658</v>
       </c>
       <c r="E38" s="55">
-        <v>322130</v>
+        <v>323111</v>
       </c>
       <c r="F38" s="55">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="G38" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H38" s="54">
-        <v>45033</v>
+        <v>45066</v>
       </c>
       <c r="I38" s="55" t="s">
         <v>10</v>
@@ -4057,28 +4063,28 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="54">
-        <v>44956</v>
+        <v>44984</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C39" s="55" t="s">
-        <v>512</v>
+        <v>239</v>
       </c>
       <c r="D39" s="55" t="s">
         <v>660</v>
       </c>
       <c r="E39" s="55">
-        <v>332999</v>
+        <v>322130</v>
       </c>
       <c r="F39" s="55">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G39" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H39" s="54">
-        <v>44949</v>
+        <v>45033</v>
       </c>
       <c r="I39" s="55" t="s">
         <v>10</v>
@@ -4093,31 +4099,31 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="54">
-        <v>44950</v>
+        <v>44956</v>
       </c>
       <c r="B40" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>238</v>
+        <v>512</v>
       </c>
       <c r="D40" s="55" t="s">
         <v>662</v>
       </c>
       <c r="E40" s="55">
-        <v>493110</v>
+        <v>332999</v>
       </c>
       <c r="F40" s="55">
-        <v>236</v>
+        <v>90</v>
       </c>
       <c r="G40" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H40" s="54">
-        <v>45107</v>
+        <v>44949</v>
       </c>
       <c r="I40" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J40" s="53" t="s">
         <v>663</v>
@@ -4129,28 +4135,28 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="54">
-        <v>44945</v>
+        <v>44950</v>
       </c>
       <c r="B41" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D41" s="55" t="s">
         <v>664</v>
       </c>
       <c r="E41" s="55">
-        <v>336323</v>
+        <v>493110</v>
       </c>
       <c r="F41" s="55">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="G41" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H41" s="54">
-        <v>45017</v>
+        <v>45107</v>
       </c>
       <c r="I41" s="55" t="s">
         <v>13</v>
@@ -4165,31 +4171,31 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="54">
-        <v>44943</v>
+        <v>44945</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="D42" s="55" t="s">
         <v>666</v>
       </c>
       <c r="E42" s="55">
-        <v>488210</v>
+        <v>336323</v>
       </c>
       <c r="F42" s="55">
-        <v>93</v>
+        <v>212</v>
       </c>
       <c r="G42" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H42" s="54">
-        <v>45016</v>
+        <v>45017</v>
       </c>
       <c r="I42" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J42" s="53" t="s">
         <v>667</v>
@@ -4201,31 +4207,31 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="54">
-        <v>44937</v>
+        <v>44943</v>
       </c>
       <c r="B43" s="55" t="s">
         <v>108</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>128</v>
+        <v>259</v>
       </c>
       <c r="D43" s="55" t="s">
         <v>668</v>
       </c>
       <c r="E43" s="55">
-        <v>321199</v>
+        <v>488210</v>
       </c>
       <c r="F43" s="55">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="G43" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="54">
-        <v>44990</v>
+        <v>45016</v>
       </c>
       <c r="I43" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J43" s="53" t="s">
         <v>669</v>
@@ -4240,33 +4246,69 @@
         <v>44937</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>332</v>
+        <v>108</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>333</v>
+        <v>128</v>
       </c>
       <c r="D44" s="55" t="s">
         <v>670</v>
       </c>
       <c r="E44" s="55">
-        <v>485320</v>
+        <v>321199</v>
       </c>
       <c r="F44" s="55">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="G44" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H44" s="54">
-        <v>44977</v>
+        <v>44990</v>
       </c>
       <c r="I44" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J44" s="53" t="s">
         <v>671</v>
       </c>
       <c r="K44" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A45" s="54">
+        <v>44937</v>
+      </c>
+      <c r="B45" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="C45" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="D45" s="55" t="s">
+        <v>672</v>
+      </c>
+      <c r="E45" s="55">
+        <v>485320</v>
+      </c>
+      <c r="F45" s="55">
+        <v>90</v>
+      </c>
+      <c r="G45" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="54">
+        <v>44977</v>
+      </c>
+      <c r="I45" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="J45" s="53" t="s">
+        <v>673</v>
+      </c>
+      <c r="K45" s="57" t="str">
         <f t="shared" si="0"/>
         <v>WARN</v>
       </c>
@@ -14272,5 +14314,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB16EBAB-32CA-49E2-B7DE-DC6630660739}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47624555-4F2C-41C2-8CC5-0BDFF12AFE6C}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,27 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1494741B-7B32-4357-B394-844278515F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12BCDBE2-D66F-4534-8337-024AC56F0318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="1520" windowWidth="19110" windowHeight="8970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2023" sheetId="7" r:id="rId1"/>
-    <sheet name="2022" sheetId="6" r:id="rId2"/>
-    <sheet name="2021" sheetId="5" r:id="rId3"/>
-    <sheet name="2020" sheetId="4" r:id="rId4"/>
-    <sheet name="2019" sheetId="3" r:id="rId5"/>
-    <sheet name="2018" sheetId="1" r:id="rId6"/>
-    <sheet name="2017" sheetId="2" r:id="rId7"/>
+    <sheet name="2024" sheetId="8" r:id="rId1"/>
+    <sheet name="2023" sheetId="7" r:id="rId2"/>
+    <sheet name="2022" sheetId="6" r:id="rId3"/>
+    <sheet name="2021" sheetId="5" r:id="rId4"/>
+    <sheet name="2020" sheetId="4" r:id="rId5"/>
+    <sheet name="2019" sheetId="3" r:id="rId6"/>
+    <sheet name="2018" sheetId="1" r:id="rId7"/>
+    <sheet name="2017" sheetId="2" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2017'!$A$1:$K$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2018'!$A$1:$K$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'2019'!$A$1:$K$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'2020'!$A$1:$J$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2021'!$A$1:$J$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2022'!$A$1:$J$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'2023'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2017'!$A$1:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2018'!$A$1:$K$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2019'!$A$1:$K$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'2020'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'2021'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2022'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2023'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'2024'!$A$1:$J$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="687">
   <si>
     <t>Date Received</t>
   </si>
@@ -938,12 +940,12 @@
     <t>P.F. CHANG'S CHINA BISTRO, INC.</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DnAi/PsQ06rfrLt2A8hC1UKmSPXyLtRhTdP2bt3fWa.P3Mao</t>
+  </si>
+  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001Dn9p/B92tz6zaPaYm5.lAsW0F6GS2hq_bm.DPaGZFyNbmJNI</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DnAi/PsQ06rfrLt2A8hC1UKmSPXyLtRhTdP2bt3fWa.P3Mao</t>
-  </si>
-  <si>
     <t>Galt House Hotel &amp; Suites</t>
   </si>
   <si>
@@ -968,18 +970,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000nXqL/60wOB.ZYyAFW_S_R8hleRIp7jxvj5pSKHPafgMy.D34</t>
   </si>
   <si>
+    <t>Vino Volo</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n3UK/pGrkwz.TW4TwVggStmZ08DA7.gkV29a2hXqMxuex7_w</t>
+  </si>
+  <si>
     <t>WestRock Comany</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n28b/Jn1rUm_cAXF2P3ZrPaqixkhcq2ejA4cVozic81IBDBc</t>
   </si>
   <si>
-    <t>Vino Volo</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n3UK/pGrkwz.TW4TwVggStmZ08DA7.gkV29a2hXqMxuex7_w</t>
-  </si>
-  <si>
     <t>Republic Airline Inc.</t>
   </si>
   <si>
@@ -1004,24 +1006,24 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjW4/G_5.Fi2tenUK8iONlECvyrpM3qeWoSn_lcSPHmqPLhs</t>
   </si>
   <si>
+    <t>Rhino Group LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHT/LD5kPxqA490uoPjJTUYgS_DByLIc4TIotUjmADqJaU0</t>
+  </si>
+  <si>
+    <t>CAM  Mining LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHd/LirRegwEOo6tABsdbsKLD3wZvWNuvAk8O7lo662CRW4</t>
+  </si>
+  <si>
     <t>Rhino Energy LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHO/J4gmK3FhqJupdRaSOCMq.CU3rKIt8M2k3PeCmNPgsTk</t>
   </si>
   <si>
-    <t>Rhino Group LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHT/LD5kPxqA490uoPjJTUYgS_DByLIc4TIotUjmADqJaU0</t>
-  </si>
-  <si>
-    <t>CAM  Mining LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHd/LirRegwEOo6tABsdbsKLD3wZvWNuvAk8O7lo662CRW4</t>
-  </si>
-  <si>
     <t>Kenco Logistic Services, LLC</t>
   </si>
   <si>
@@ -1085,18 +1087,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000m0hj/ncG1LQqkdvtnvX2of3ZE2UcNY2sAzm5C4kUOomgoTLg</t>
   </si>
   <si>
+    <t>RYDER TRUCK-Burlington KY</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lzgt/.fnaoiWvrbSTrYPyqxB2Zx0lRhBdDvaC7xBQN7Eds7w</t>
+  </si>
+  <si>
     <t>Jacobsen|Daniel’s Enterprise Inc.-SDF</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lzgA/7J0V94vN.WBDIApE.ddY6W3JupaPtqsO0Sm4yOKqVIs</t>
   </si>
   <si>
-    <t>RYDER TRUCK-Burlington KY</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lzgt/.fnaoiWvrbSTrYPyqxB2Zx0lRhBdDvaC7xBQN7Eds7w</t>
-  </si>
-  <si>
     <t>Jacobsen|Daniels Enterprise d.b.a Fly Away Valet - CVG</t>
   </si>
   <si>
@@ -1178,24 +1180,24 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lHSh/K0STGdn5RioZCNnefjssHgRYhvyegfO5stZN_W4HKGc</t>
   </si>
   <si>
+    <t>Copart</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFvN/E_nV4ZiPQXnnjdzptfU3GYUGocuIOqaU.Y9H1GQf.O0</t>
+  </si>
+  <si>
+    <t>Hendrickson</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFy7/Yv5x__FLS4A2m1cTlMmbBkJ72jQVKesqE4aS843KqbM</t>
+  </si>
+  <si>
     <t>Bloomin' Brands Inc.</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFnJ/4P1OqyziA7PB0Bwl_6nFu_TYtWbVZmItGG0ajc_A4io</t>
   </si>
   <si>
-    <t>Copart</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFvN/E_nV4ZiPQXnnjdzptfU3GYUGocuIOqaU.Y9H1GQf.O0</t>
-  </si>
-  <si>
-    <t>Hendrickson</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFy7/Yv5x__FLS4A2m1cTlMmbBkJ72jQVKesqE4aS843KqbM</t>
-  </si>
-  <si>
     <t>Domtar Paper Company LLC</t>
   </si>
   <si>
@@ -1229,39 +1231,39 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFAl/oO700mhoM_QHeowhHaKcjxvMIWN0lrbxd1SLp.he9w8</t>
   </si>
   <si>
-    <t>BOGE Rubber &amp; Plastics USA LLC</t>
+    <t>Boge Rubber &amp; Plastics USA LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owme/I70OYWW_BMsm.L1gecTbBndG80GLYaujN7Bys19qF0E</t>
   </si>
   <si>
+    <t>AVIS BUDGET CAR RENTAL LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlM/.Zk80i_XFS7aZoaHWgUxXaHRiKaZbtC_7AhdxqU6wug</t>
+  </si>
+  <si>
+    <t>AVIS BUDGET CAR RENTAL LLC-Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlW/CYo8uyV1lqLUe_XJLwXgKKbMGcUSOnm2YuFWlCcEjao</t>
+  </si>
+  <si>
     <t>Clark Material Handling Co.</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlC/hEdK2CiuQJ0bVuYeIRqwIFPEy53bOvrnmZtKCFG3OTk</t>
   </si>
   <si>
-    <t>AVIS BUDGET CAR RENTAL LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlM/.Zk80i_XFS7aZoaHWgUxXaHRiKaZbtC_7AhdxqU6wug</t>
-  </si>
-  <si>
-    <t>AVIS BUDGET CAR RENTAL LLC-Louisville</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlW/CYo8uyV1lqLUe_XJLwXgKKbMGcUSOnm2YuFWlCcEjao</t>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owfY/PmJV_yGxFZQyYhZo1Z3JUNNKeymCbhxmj4tTRLPEQdQ</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe6/AOd4ALEemb0aAShUt5dhhnJlPDFohiL8zcc9JttELyY</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe1/_JzvIyNP00OZFCdiwLq50NqX4Pv5uhASRmnOON4x7JM</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owfY/PmJV_yGxFZQyYhZo1Z3JUNNKeymCbhxmj4tTRLPEQdQ</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe6/AOd4ALEemb0aAShUt5dhhnJlPDFohiL8zcc9JttELyY</t>
-  </si>
-  <si>
     <t>GUESS Distribution Center</t>
   </si>
   <si>
@@ -1409,24 +1411,24 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVY/2COXMu6Bd1MCYgNNs.Sc62L0asFJOG..KVsIGQuqD5g</t>
   </si>
   <si>
+    <t>SCHULTE COMPANIES</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVT/U2oN7sbm_kSzNb7xiYNnrUVaoC_094PGtzzEyvZMQHo</t>
+  </si>
+  <si>
+    <t>IHG Army Hotels &amp; Holiday Inn Express</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
+  </si>
+  <si>
     <t>Huhtamaki, Inc.</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUa/gQ7KCmO7r.5JxftEeBG61Dp0YG0btnF0QmbfOv3Jqwg</t>
   </si>
   <si>
-    <t>SCHULTE COMPANIES</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVT/U2oN7sbm_kSzNb7xiYNnrUVaoC_094PGtzzEyvZMQHo</t>
-  </si>
-  <si>
-    <t>IHG Army Hotels &amp; Holiday Inn Express</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUQ/kIkf6vaRVWxJL33J4laXNMoRoo4Ps.CEaVYB4.M3PIU</t>
   </si>
   <si>
@@ -1457,33 +1459,33 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUB/Q4XhuwPlCqUiegEdy255dEODFtbl._noeWqruyQLy9c</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVE/C0OZ4Bz9aNkrc9YrcMiSzi1G1WqI2.arpnDnUUJqUr8</t>
+  </si>
+  <si>
+    <t>Muhlenberg</t>
+  </si>
+  <si>
+    <t>THE MUHLENBERG COUNTY COAL COMPANY</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVJ/Dg9.VOc4xZE0CzOT2WBULH9AF2F_W3myXxa4ijm196A</t>
+  </si>
+  <si>
+    <t>Bourbon</t>
+  </si>
+  <si>
+    <t>Murray Euipment &amp; Machine</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVO/fRo8DiZxbz2baMUvWanGYLiXkNdGw2BDb3YAGYVqjWI</t>
+  </si>
+  <si>
     <t>ALJSCO</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUL/QiUorU3I0MCyonZFb9WQqn78BNq1UIJjwP_tw34J1Sw</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVE/C0OZ4Bz9aNkrc9YrcMiSzi1G1WqI2.arpnDnUUJqUr8</t>
-  </si>
-  <si>
-    <t>Muhlenberg</t>
-  </si>
-  <si>
-    <t>THE MUHLENBERG COUNTY COAL COMPANY</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVJ/Dg9.VOc4xZE0CzOT2WBULH9AF2F_W3myXxa4ijm196A</t>
-  </si>
-  <si>
-    <t>Bourbon</t>
-  </si>
-  <si>
-    <t>Murray Euipment &amp; Machine</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVO/fRo8DiZxbz2baMUvWanGYLiXkNdGw2BDb3YAGYVqjWI</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owPN/jDHwTapPX.yBsZhb3qC7qy.geYOtPuuz3LjGauQ08h8</t>
   </si>
   <si>
@@ -1562,7 +1564,7 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000cRpa/FhXx5qmiMk8LEffcKqwhZD.RPrbCYHQRmDk1TwaTpE0</t>
   </si>
   <si>
-    <t>Our Lady of Bellefonte Hospital, L.L.C.</t>
+    <t>Our Lady of Bellefonte Hospital, LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000cRls/iReAoQajVybKDYSG3.slx51EZwROrWfJQq8Lxz49EB4</t>
@@ -2070,6 +2072,45 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y0000044AjY/AIrRiUx57cQN91Gt3GEskluAye9VTB5lmjzmRGMobI4</t>
+  </si>
+  <si>
+    <t>TF-Metal USA, LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005BdYf/aLuKB36i_ErCGp3pPAbg4Vo9Dr9tWbBR3IM8LaQg3aY</t>
+  </si>
+  <si>
+    <t>GDI Integrated Facility Services</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005Aabo/V_hfVFWEIfnIQH57FqfbR9BdouHsTK6yDVavS3W.yC4</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005Aaxr/KwrVbJWv9bt4iW0MMP6gybrw6S28RfEL_VJ2mbxlYXI</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005Aajf/_s09zrUsBYJdgPCh.PqdjhGXOuSG1CnCX_R06f6cUpw</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005AaYZ/nOhlGCeHWJakUVLtYFLpq2QXY.WDel0jlYO6gs7mer8</t>
+  </si>
+  <si>
+    <t>Electro Cycle, Inc.</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005B9V5/dXaH3O3I1HdhrcpkJ74_d.Rpp1eJVkMhtnhTSMRZteE</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005B3Sg/lFNQFnskUI.qZ2tJB_IQZVUfqW_wm8i740w1gzmZ_aA</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005B6JD/vfcC_JC53AH8idj8myVgt_oKXDPT_HvdtMKwXKEzXpY</t>
+  </si>
+  <si>
+    <t>Radial Fulfillment Center</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y0000059JY9/.N6HoGkECR.LWLyKrovcNZspopu8ARwkYUFsIi3u3Aw</t>
   </si>
 </sst>
 </file>
@@ -2678,6 +2719,428 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="34.26953125" style="24" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" style="24" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="24" customWidth="1"/>
+    <col min="7" max="8" width="12.81640625" style="24" customWidth="1"/>
+    <col min="9" max="9" width="7.54296875" style="24" customWidth="1"/>
+    <col min="10" max="10" width="137.81640625" style="24" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" style="24" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="26" x14ac:dyDescent="0.35">
+      <c r="A1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="54">
+        <v>45302</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>674</v>
+      </c>
+      <c r="E2" s="55">
+        <v>336110</v>
+      </c>
+      <c r="F2" s="55">
+        <v>49</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="54">
+        <v>45365</v>
+      </c>
+      <c r="I2" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="53" t="s">
+        <v>675</v>
+      </c>
+      <c r="K2" s="57" t="str">
+        <f>IF(ISBLANK(J2),"",HYPERLINK(J2,"WARN"))</f>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="54">
+        <v>45299</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>676</v>
+      </c>
+      <c r="E3" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F3" s="55">
+        <v>26</v>
+      </c>
+      <c r="G3" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="54">
+        <v>45299</v>
+      </c>
+      <c r="I3" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="53" t="s">
+        <v>677</v>
+      </c>
+      <c r="K3" s="57" t="str">
+        <f t="shared" ref="K3:K11" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="54">
+        <v>45299</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>676</v>
+      </c>
+      <c r="E4" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F4" s="55">
+        <v>39</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="54">
+        <v>45299</v>
+      </c>
+      <c r="I4" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="53" t="s">
+        <v>678</v>
+      </c>
+      <c r="K4" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="54">
+        <v>45299</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>676</v>
+      </c>
+      <c r="E5" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F5" s="55">
+        <v>40</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="54">
+        <v>45299</v>
+      </c>
+      <c r="I5" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="53" t="s">
+        <v>679</v>
+      </c>
+      <c r="K5" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="54">
+        <v>45299</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>676</v>
+      </c>
+      <c r="E6" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F6" s="55">
+        <v>67</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="54">
+        <v>45299</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="53" t="s">
+        <v>680</v>
+      </c>
+      <c r="K6" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="54">
+        <v>45295</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>681</v>
+      </c>
+      <c r="E7" s="55">
+        <v>331400</v>
+      </c>
+      <c r="F7" s="55">
+        <v>57</v>
+      </c>
+      <c r="G7" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="54">
+        <v>45295</v>
+      </c>
+      <c r="I7" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="54">
+        <v>45295</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>676</v>
+      </c>
+      <c r="E8" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F8" s="55">
+        <v>48</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="54">
+        <v>45356</v>
+      </c>
+      <c r="I8" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="53" t="s">
+        <v>682</v>
+      </c>
+      <c r="K8" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="54">
+        <v>45295</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>676</v>
+      </c>
+      <c r="E9" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F9" s="55">
+        <v>40</v>
+      </c>
+      <c r="G9" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="54">
+        <v>45356</v>
+      </c>
+      <c r="I9" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="53" t="s">
+        <v>683</v>
+      </c>
+      <c r="K9" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="54">
+        <v>45295</v>
+      </c>
+      <c r="B10" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>676</v>
+      </c>
+      <c r="E10" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F10" s="55">
+        <v>40</v>
+      </c>
+      <c r="G10" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="54">
+        <v>45356</v>
+      </c>
+      <c r="I10" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="53" t="s">
+        <v>684</v>
+      </c>
+      <c r="K10" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="54">
+        <v>45293</v>
+      </c>
+      <c r="B11" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>685</v>
+      </c>
+      <c r="E11" s="55">
+        <v>541714</v>
+      </c>
+      <c r="F11" s="55">
+        <v>136</v>
+      </c>
+      <c r="G11" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="54">
+        <v>45351</v>
+      </c>
+      <c r="I11" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="53" t="s">
+        <v>686</v>
+      </c>
+      <c r="K11" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="70" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -4319,8 +4782,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4921,8 +5384,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5739,8 +6202,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6160,10 +6623,10 @@
         <v>44092</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D12" s="55" t="s">
         <v>295</v>
@@ -6196,10 +6659,10 @@
         <v>44092</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D13" s="55" t="s">
         <v>295</v>
@@ -6376,25 +6839,25 @@
         <v>44050</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D18" s="55" t="s">
         <v>306</v>
       </c>
       <c r="E18" s="55">
-        <v>3221</v>
+        <v>72251</v>
       </c>
       <c r="F18" s="55">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G18" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H18" s="54">
-        <v>44104</v>
+        <v>43926</v>
       </c>
       <c r="I18" s="55" t="s">
         <v>13</v>
@@ -6412,25 +6875,25 @@
         <v>44050</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D19" s="55" t="s">
         <v>308</v>
       </c>
       <c r="E19" s="55">
-        <v>72251</v>
+        <v>3221</v>
       </c>
       <c r="F19" s="55">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G19" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H19" s="54">
-        <v>43926</v>
+        <v>44104</v>
       </c>
       <c r="I19" s="55" t="s">
         <v>13</v>
@@ -6604,16 +7067,16 @@
         <v>213113</v>
       </c>
       <c r="F24" s="55">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G24" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="54">
-        <v>44094</v>
+        <v>44098</v>
       </c>
       <c r="I24" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J24" s="53" t="s">
         <v>319</v>
@@ -6628,10 +7091,10 @@
         <v>44035</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D25" s="55" t="s">
         <v>320</v>
@@ -6640,13 +7103,13 @@
         <v>213113</v>
       </c>
       <c r="F25" s="55">
-        <v>5</v>
+        <v>194</v>
       </c>
       <c r="G25" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H25" s="54">
-        <v>44098</v>
+        <v>44094</v>
       </c>
       <c r="I25" s="55" t="s">
         <v>13</v>
@@ -6664,10 +7127,10 @@
         <v>44035</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="D26" s="55" t="s">
         <v>322</v>
@@ -6676,7 +7139,7 @@
         <v>213113</v>
       </c>
       <c r="F26" s="55">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="G26" s="55" t="s">
         <v>11</v>
@@ -6685,7 +7148,7 @@
         <v>44094</v>
       </c>
       <c r="I26" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J26" s="53" t="s">
         <v>323</v>
@@ -7024,25 +7487,25 @@
         <v>43997</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>342</v>
+        <v>225</v>
       </c>
       <c r="D36" s="55" t="s">
         <v>345</v>
       </c>
       <c r="E36" s="55">
-        <v>488190</v>
+        <v>493110</v>
       </c>
       <c r="F36" s="55">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="G36" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H36" s="54">
-        <v>43994</v>
+        <v>44055</v>
       </c>
       <c r="I36" s="55" t="s">
         <v>13</v>
@@ -7060,25 +7523,25 @@
         <v>43997</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>225</v>
+        <v>342</v>
       </c>
       <c r="D37" s="55" t="s">
         <v>347</v>
       </c>
       <c r="E37" s="55">
-        <v>493110</v>
+        <v>488190</v>
       </c>
       <c r="F37" s="55">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="G37" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H37" s="54">
-        <v>44055</v>
+        <v>43994</v>
       </c>
       <c r="I37" s="55" t="s">
         <v>13</v>
@@ -7600,25 +8063,25 @@
         <v>43948</v>
       </c>
       <c r="B52" s="55" t="s">
-        <v>332</v>
+        <v>40</v>
       </c>
       <c r="C52" s="55" t="s">
-        <v>333</v>
+        <v>226</v>
       </c>
       <c r="D52" s="55" t="s">
         <v>376</v>
       </c>
       <c r="E52" s="55">
-        <v>722511</v>
+        <v>423110</v>
       </c>
       <c r="F52" s="55">
-        <v>1134</v>
+        <v>50</v>
       </c>
       <c r="G52" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H52" s="54">
-        <v>43905</v>
+        <v>43948</v>
       </c>
       <c r="I52" s="55" t="s">
         <v>13</v>
@@ -7636,22 +8099,22 @@
         <v>43948</v>
       </c>
       <c r="B53" s="55" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C53" s="55" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D53" s="55" t="s">
         <v>378</v>
       </c>
       <c r="E53" s="55">
-        <v>423110</v>
+        <v>336390</v>
       </c>
       <c r="F53" s="55">
-        <v>50</v>
+        <v>179</v>
       </c>
       <c r="G53" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H53" s="54">
         <v>43948</v>
@@ -7672,25 +8135,25 @@
         <v>43948</v>
       </c>
       <c r="B54" s="55" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="C54" s="55" t="s">
-        <v>236</v>
+        <v>333</v>
       </c>
       <c r="D54" s="55" t="s">
         <v>380</v>
       </c>
       <c r="E54" s="55">
-        <v>336390</v>
+        <v>722511</v>
       </c>
       <c r="F54" s="55">
-        <v>179</v>
+        <v>1134</v>
       </c>
       <c r="G54" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H54" s="54">
-        <v>43948</v>
+        <v>43905</v>
       </c>
       <c r="I54" s="55" t="s">
         <v>13</v>
@@ -7960,25 +8423,25 @@
         <v>43938</v>
       </c>
       <c r="B62" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C62" s="55" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D62" s="55" t="s">
         <v>395</v>
       </c>
       <c r="E62" s="55">
-        <v>33392</v>
+        <v>532111</v>
       </c>
       <c r="F62" s="55">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G62" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H62" s="54">
-        <v>43936</v>
+        <v>43903</v>
       </c>
       <c r="I62" s="55" t="s">
         <v>13</v>
@@ -7996,10 +8459,10 @@
         <v>43938</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C63" s="55" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="D63" s="55" t="s">
         <v>397</v>
@@ -8008,7 +8471,7 @@
         <v>532111</v>
       </c>
       <c r="F63" s="55">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G63" s="55" t="s">
         <v>16</v>
@@ -8032,25 +8495,25 @@
         <v>43938</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C64" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D64" s="55" t="s">
         <v>399</v>
       </c>
       <c r="E64" s="55">
-        <v>532111</v>
+        <v>33392</v>
       </c>
       <c r="F64" s="55">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H64" s="54">
-        <v>43903</v>
+        <v>43936</v>
       </c>
       <c r="I64" s="55" t="s">
         <v>13</v>
@@ -8068,19 +8531,19 @@
         <v>43936</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C65" s="55" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>349</v>
+        <v>133</v>
       </c>
       <c r="E65" s="55">
-        <v>488190</v>
+        <v>337215</v>
       </c>
       <c r="F65" s="55">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="G65" s="55" t="s">
         <v>16</v>
@@ -8107,16 +8570,16 @@
         <v>40</v>
       </c>
       <c r="C66" s="55" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D66" s="55" t="s">
         <v>133</v>
       </c>
       <c r="E66" s="55">
-        <v>337215</v>
+        <v>33791</v>
       </c>
       <c r="F66" s="55">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="G66" s="55" t="s">
         <v>16</v>
@@ -8140,19 +8603,19 @@
         <v>43936</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>133</v>
+        <v>349</v>
       </c>
       <c r="E67" s="55">
-        <v>33791</v>
+        <v>488190</v>
       </c>
       <c r="F67" s="55">
-        <v>271</v>
+        <v>17</v>
       </c>
       <c r="G67" s="55" t="s">
         <v>16</v>
@@ -9004,25 +9467,25 @@
         <v>43923</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>258</v>
+        <v>128</v>
       </c>
       <c r="D91" s="55" t="s">
         <v>453</v>
       </c>
       <c r="E91" s="55">
-        <v>333999</v>
+        <v>721110</v>
       </c>
       <c r="F91" s="55">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G91" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H91" s="54">
-        <v>43926</v>
+        <v>43906</v>
       </c>
       <c r="I91" s="55" t="s">
         <v>13</v>
@@ -9040,10 +9503,10 @@
         <v>43923</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>128</v>
+        <v>273</v>
       </c>
       <c r="D92" s="55" t="s">
         <v>455</v>
@@ -9052,13 +9515,13 @@
         <v>721110</v>
       </c>
       <c r="F92" s="55">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="G92" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H92" s="54">
-        <v>43906</v>
+        <v>43910</v>
       </c>
       <c r="I92" s="55" t="s">
         <v>13</v>
@@ -9076,25 +9539,25 @@
         <v>43923</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="C93" s="55" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D93" s="55" t="s">
         <v>457</v>
       </c>
       <c r="E93" s="55">
-        <v>721110</v>
+        <v>333999</v>
       </c>
       <c r="F93" s="55">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="G93" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H93" s="54">
-        <v>43910</v>
+        <v>43926</v>
       </c>
       <c r="I93" s="55" t="s">
         <v>13</v>
@@ -9328,31 +9791,31 @@
         <v>43922</v>
       </c>
       <c r="B100" s="55" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C100" s="55" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="D100" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="E100" s="55">
+        <v>21211</v>
+      </c>
+      <c r="F100" s="55">
+        <v>42</v>
+      </c>
+      <c r="G100" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="54">
+        <v>43984</v>
+      </c>
+      <c r="I100" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="53" t="s">
         <v>469</v>
-      </c>
-      <c r="E100" s="55">
-        <v>541611</v>
-      </c>
-      <c r="F100" s="55">
-        <v>4</v>
-      </c>
-      <c r="G100" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H100" s="54">
-        <v>43920</v>
-      </c>
-      <c r="I100" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J100" s="53" t="s">
-        <v>470</v>
       </c>
       <c r="K100" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9364,22 +9827,22 @@
         <v>43922</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C101" s="55" t="s">
-        <v>227</v>
+        <v>470</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>201</v>
+        <v>471</v>
       </c>
       <c r="E101" s="55">
         <v>21211</v>
       </c>
       <c r="F101" s="55">
-        <v>42</v>
+        <v>254</v>
       </c>
       <c r="G101" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H101" s="54">
         <v>43984</v>
@@ -9388,7 +9851,7 @@
         <v>13</v>
       </c>
       <c r="J101" s="53" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K101" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9400,19 +9863,19 @@
         <v>43922</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C102" s="55" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D102" s="55" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E102" s="55">
-        <v>21211</v>
+        <v>423520</v>
       </c>
       <c r="F102" s="55">
-        <v>254</v>
+        <v>11</v>
       </c>
       <c r="G102" s="55" t="s">
         <v>11</v>
@@ -9424,7 +9887,7 @@
         <v>13</v>
       </c>
       <c r="J102" s="53" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K102" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9436,25 +9899,25 @@
         <v>43922</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C103" s="55" t="s">
-        <v>475</v>
+        <v>128</v>
       </c>
       <c r="D103" s="55" t="s">
         <v>476</v>
       </c>
       <c r="E103" s="55">
-        <v>423520</v>
+        <v>541611</v>
       </c>
       <c r="F103" s="55">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G103" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H103" s="54">
-        <v>43984</v>
+        <v>43920</v>
       </c>
       <c r="I103" s="55" t="s">
         <v>13</v>
@@ -10265,8 +10728,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11615,16 +12078,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K21" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-    <hyperlink ref="J15" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="K21" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="J15" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="62" orientation="landscape" r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -12995,8 +13458,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -14130,7 +14593,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K30" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:K30" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14145,12 +14608,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0C1C9366252B4C838708442C71C5AA" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="623745db76138c409ead4834ced54ea8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="62511544-38af-49c2-8996-37c0f6a636fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c1a1049adbb8cd97fc988c6af4986c32" ns2:_="">
     <xsd:import namespace="62511544-38af-49c2-8996-37c0f6a636fd"/>
@@ -14290,6 +14747,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
   <ds:schemaRefs>
@@ -14299,6 +14762,10 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F95DCE-7EDC-4B2F-BF77-FCA5513DAA7E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEB26DE-B3FC-45A8-BF93-B326AF5FAB7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -14311,8 +14778,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47624555-4F2C-41C2-8CC5-0BDFF12AFE6C}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12BCDBE2-D66F-4534-8337-024AC56F0318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE834477-D322-4F99-9EA1-578E4226F551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="693">
   <si>
     <t>Date Received</t>
   </si>
@@ -907,18 +907,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001Duxy/OQSRyQ_.aYQHhrFXq8Tdiv.MgS0Rz2oZW0hbEdodBXY</t>
   </si>
   <si>
+    <t>Meggitt Polymers and Composites - Erlanger</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DsDM/G0wP5hdwHVxpG7glqsx.P.Bu.ufe7zp6pACAhUX6gDA</t>
+  </si>
+  <si>
     <t>Omni Hotels &amp; Resorts</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DsAc/VBX3AB_6wodTw6SXAtFGoYfEaBMIRx8Y1R1QDhgqJho</t>
   </si>
   <si>
-    <t>Meggitt Polymers and Composites - Erlanger</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DsDM/G0wP5hdwHVxpG7glqsx.P.Bu.ufe7zp6pACAhUX6gDA</t>
-  </si>
-  <si>
     <t>ABM c/o The Hertz Corporation - CVG</t>
   </si>
   <si>
@@ -1006,24 +1006,24 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjW4/G_5.Fi2tenUK8iONlECvyrpM3qeWoSn_lcSPHmqPLhs</t>
   </si>
   <si>
+    <t>CAM  Mining LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHd/LirRegwEOo6tABsdbsKLD3wZvWNuvAk8O7lo662CRW4</t>
+  </si>
+  <si>
+    <t>Rhino Energy LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHO/J4gmK3FhqJupdRaSOCMq.CU3rKIt8M2k3PeCmNPgsTk</t>
+  </si>
+  <si>
     <t>Rhino Group LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHT/LD5kPxqA490uoPjJTUYgS_DByLIc4TIotUjmADqJaU0</t>
   </si>
   <si>
-    <t>CAM  Mining LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHd/LirRegwEOo6tABsdbsKLD3wZvWNuvAk8O7lo662CRW4</t>
-  </si>
-  <si>
-    <t>Rhino Energy LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHO/J4gmK3FhqJupdRaSOCMq.CU3rKIt8M2k3PeCmNPgsTk</t>
-  </si>
-  <si>
     <t>Kenco Logistic Services, LLC</t>
   </si>
   <si>
@@ -1087,18 +1087,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000m0hj/ncG1LQqkdvtnvX2of3ZE2UcNY2sAzm5C4kUOomgoTLg</t>
   </si>
   <si>
+    <t>Jacobsen|Daniel’s Enterprise Inc.-SDF</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lzgA/7J0V94vN.WBDIApE.ddY6W3JupaPtqsO0Sm4yOKqVIs</t>
+  </si>
+  <si>
     <t>RYDER TRUCK-Burlington KY</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lzgt/.fnaoiWvrbSTrYPyqxB2Zx0lRhBdDvaC7xBQN7Eds7w</t>
   </si>
   <si>
-    <t>Jacobsen|Daniel’s Enterprise Inc.-SDF</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lzgA/7J0V94vN.WBDIApE.ddY6W3JupaPtqsO0Sm4yOKqVIs</t>
-  </si>
-  <si>
     <t>Jacobsen|Daniels Enterprise d.b.a Fly Away Valet - CVG</t>
   </si>
   <si>
@@ -1129,18 +1129,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000leL1/SnG3sVRdWjFQMCr8LETwNOCbLpaaGRlfQEhLqrDI3L8</t>
   </si>
   <si>
+    <t>MSSC US, INC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000ltac/RzIOWPGwYHCFP6cxNIWDpNwrH4SL6H5XqNJy0KCDiO8</t>
+  </si>
+  <si>
     <t>21c Museum Hotel Lexington</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000leLV/SG3RH__XeMSmDA.BzF5J9gLLQ9R0VtgAocKowWhdEL4</t>
   </si>
   <si>
-    <t>MSSC US, INC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000ltac/RzIOWPGwYHCFP6cxNIWDpNwrH4SL6H5XqNJy0KCDiO8</t>
-  </si>
-  <si>
     <t>Enterprise Rent A Car - CVG</t>
   </si>
   <si>
@@ -1192,16 +1192,22 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFy7/Yv5x__FLS4A2m1cTlMmbBkJ72jQVKesqE4aS843KqbM</t>
   </si>
   <si>
+    <t>Domtar Paper Company LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lG1B/4Fd5SUVur4FncgJi63EeLKzz9wTruSFuhn9yeHQp8b0</t>
+  </si>
+  <si>
     <t>Bloomin' Brands Inc.</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFnJ/4P1OqyziA7PB0Bwl_6nFu_TYtWbVZmItGG0ajc_A4io</t>
   </si>
   <si>
-    <t>Domtar Paper Company LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lG1B/4Fd5SUVur4FncgJi63EeLKzz9wTruSFuhn9yeHQp8b0</t>
+    <t>Leggett &amp; Platt, Inc</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFhk/YXvfnj9glnybML0caPMSROnboavSXn.klKEWtkrTQy8</t>
   </si>
   <si>
     <t>EAN Holdings, LLC dba/Enterprise Rent-A-Car/Alamo/National</t>
@@ -1219,12 +1225,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFRh/UszfPVKKroq1QAKiNquy4pybhgj_l.wWTgrzPpPoae0</t>
   </si>
   <si>
-    <t>Leggett &amp; Platt, Inc</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFhk/YXvfnj9glnybML0caPMSROnboavSXn.klKEWtkrTQy8</t>
-  </si>
-  <si>
     <t>Visionworks, Inc.</t>
   </si>
   <si>
@@ -1237,6 +1237,12 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owme/I70OYWW_BMsm.L1gecTbBndG80GLYaujN7Bys19qF0E</t>
   </si>
   <si>
+    <t>Clark Material Handling Co.</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlC/hEdK2CiuQJ0bVuYeIRqwIFPEy53bOvrnmZtKCFG3OTk</t>
+  </si>
+  <si>
     <t>AVIS BUDGET CAR RENTAL LLC</t>
   </si>
   <si>
@@ -1249,12 +1255,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlW/CYo8uyV1lqLUe_XJLwXgKKbMGcUSOnm2YuFWlCcEjao</t>
   </si>
   <si>
-    <t>Clark Material Handling Co.</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlC/hEdK2CiuQJ0bVuYeIRqwIFPEy53bOvrnmZtKCFG3OTk</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owfY/PmJV_yGxFZQyYhZo1Z3JUNNKeymCbhxmj4tTRLPEQdQ</t>
   </si>
   <si>
@@ -1270,24 +1270,24 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owbq/UyrAEX7r.ENTpYJbgJLT8Cg7CPlnvxwl2yKnTp7J72s</t>
   </si>
   <si>
+    <t>Bedding Acquisition LLC-Hollander Sleep Products</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc0/YfonXN9YuzXLk_UAXU4_FKNeT7YOIM6p5kka_JgwN0Y</t>
+  </si>
+  <si>
+    <t>Newport Aquarium LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owce/l.sHHNbu0GPlyDLBohqkTc6rmr3iMKC.C7bGdM4pAc0</t>
+  </si>
+  <si>
     <t>Glidewell Laboratories-Crown World Dental Lab</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc5/NegKIAQd.3f3pmcw73INUcvkRVIbZTkujR6EIS0ot58</t>
   </si>
   <si>
-    <t>Bedding Acquisition LLC-Hollander Sleep Products</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc0/YfonXN9YuzXLk_UAXU4_FKNeT7YOIM6p5kka_JgwN0Y</t>
-  </si>
-  <si>
-    <t>Newport Aquarium LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owce/l.sHHNbu0GPlyDLBohqkTc6rmr3iMKC.C7bGdM4pAc0</t>
-  </si>
-  <si>
     <t>Vitro Automotive/Pittsburgh Glass Works</t>
   </si>
   <si>
@@ -1324,93 +1324,99 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owYS/48f5c5_B5wyiPJ9Uy_H1cNlwWBdNMLD_pYAS8WUMQM8</t>
   </si>
   <si>
+    <t>Breckinridge</t>
+  </si>
+  <si>
+    <t>Communicare Clinic LLC - Hardinsburg</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWR/145nfIPWN0_U_cemfoWJlEEcFSVIRIo8wdyDtysKwiE</t>
+  </si>
+  <si>
+    <t>Marion</t>
+  </si>
+  <si>
+    <t>Hendrickson Trailer Commercial Vehicle Systems</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX0/V6hwrqZ0Qlr_eFlMYEYrZXlE5AKDheKuIEjfBsUaPdQ</t>
+  </si>
+  <si>
     <t>HOOTERS of America LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVx/qvIScRk9GM5Elj.GBDk.q4vXbyNWeEoZlek.EdFKUGs</t>
   </si>
   <si>
+    <t>Communicare Services - Bardstown</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW7/vxvDkskTDW8u8rCe_lHYjJe3ywqVHolgywHu7LkriIg</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Communicare Services - Springfield</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWC/G1vvtarZYPJdOhvrIz1yR8EPnXsOq0_BH2dWoGiRDP4</t>
+  </si>
+  <si>
+    <t>Communicare Clinic - Lebanon</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWW/6KnRleJzURSaBY_6FARK03ypKCpBzXNzxwnFAWGUcwk</t>
+  </si>
+  <si>
+    <t>Communicare Services - Lebanon</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWg/9p9FS.JQp0PTPMhD3HxrAxxsoxTEr_upxaagBfFMogM</t>
+  </si>
+  <si>
+    <t>Communicare Clinic - Radcliff</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWl/rS8vJCQrLNj0CL7FyoK6cd2Ubo0vr1icry6WlMYbX7U</t>
+  </si>
+  <si>
+    <t>Communicare Services - Radcliff</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWq/Vfpl8UYl0gbX_iFIJoUfIBUwxuS8TiJTC_7F4sKJFYw</t>
+  </si>
+  <si>
+    <t>Communicare Services - Leitchfield</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX5/hqgTkrEKeD2diZgwtvYubxlNzxik77T983Z_rFk92oU</t>
+  </si>
+  <si>
+    <t>Communicare  Services - Brandenburg</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owXA/mAUPSS8QJjeTFI7E27u8VQgWHFFi6LRZfcfzfkHq1Jo</t>
+  </si>
+  <si>
     <t>Communicare Professional Counselling and Treatment Service</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW2/m6.18mqxu4V91wnL7oO6sVnlaLN8Ty2M97cFVaRMbUI</t>
   </si>
   <si>
-    <t>Communicare Services - Bardstown</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW7/vxvDkskTDW8u8rCe_lHYjJe3ywqVHolgywHu7LkriIg</t>
-  </si>
-  <si>
-    <t>Washington</t>
-  </si>
-  <si>
-    <t>Communicare Services - Springfield</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWC/G1vvtarZYPJdOhvrIz1yR8EPnXsOq0_BH2dWoGiRDP4</t>
-  </si>
-  <si>
-    <t>Breckinridge</t>
-  </si>
-  <si>
-    <t>Communicare Clinic LLC - Hardinsburg</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWR/145nfIPWN0_U_cemfoWJlEEcFSVIRIo8wdyDtysKwiE</t>
-  </si>
-  <si>
-    <t>Marion</t>
-  </si>
-  <si>
-    <t>Communicare Clinic - Lebanon</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWW/6KnRleJzURSaBY_6FARK03ypKCpBzXNzxwnFAWGUcwk</t>
-  </si>
-  <si>
-    <t>Communicare Services - Lebanon</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWg/9p9FS.JQp0PTPMhD3HxrAxxsoxTEr_upxaagBfFMogM</t>
-  </si>
-  <si>
-    <t>Communicare Clinic - Radcliff</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWl/rS8vJCQrLNj0CL7FyoK6cd2Ubo0vr1icry6WlMYbX7U</t>
-  </si>
-  <si>
-    <t>Communicare Services - Radcliff</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWq/Vfpl8UYl0gbX_iFIJoUfIBUwxuS8TiJTC_7F4sKJFYw</t>
-  </si>
-  <si>
-    <t>Communicare Services - Leitchfield</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX5/hqgTkrEKeD2diZgwtvYubxlNzxik77T983Z_rFk92oU</t>
-  </si>
-  <si>
-    <t>Hendrickson Trailer Commercial Vehicle Systems</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX0/V6hwrqZ0Qlr_eFlMYEYrZXlE5AKDheKuIEjfBsUaPdQ</t>
-  </si>
-  <si>
-    <t>Communicare  Services - Brandenburg</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owXA/mAUPSS8QJjeTFI7E27u8VQgWHFFi6LRZfcfzfkHq1Jo</t>
-  </si>
-  <si>
     <t>Jackson Warewashing Systems</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVY/2COXMu6Bd1MCYgNNs.Sc62L0asFJOG..KVsIGQuqD5g</t>
   </si>
   <si>
+    <t>Huhtamaki, Inc.</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUa/gQ7KCmO7r.5JxftEeBG61Dp0YG0btnF0QmbfOv3Jqwg</t>
+  </si>
+  <si>
     <t>SCHULTE COMPANIES</t>
   </si>
   <si>
@@ -1423,63 +1429,57 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
   </si>
   <si>
-    <t>Huhtamaki, Inc.</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUa/gQ7KCmO7r.5JxftEeBG61Dp0YG0btnF0QmbfOv3Jqwg</t>
+    <t>Embassy Suites Jefferson Co - Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owTw/ZCaGJxEMniVjvqFnhoI_lXZxfMOTDOnfnNr.YyZ_aFs</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVE/C0OZ4Bz9aNkrc9YrcMiSzi1G1WqI2.arpnDnUUJqUr8</t>
+  </si>
+  <si>
+    <t>Bourbon</t>
+  </si>
+  <si>
+    <t>Murray Euipment &amp; Machine</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVO/fRo8DiZxbz2baMUvWanGYLiXkNdGw2BDb3YAGYVqjWI</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUQ/kIkf6vaRVWxJL33J4laXNMoRoo4Ps.CEaVYB4.M3PIU</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUB/Q4XhuwPlCqUiegEdy255dEODFtbl._noeWqruyQLy9c</t>
+  </si>
+  <si>
     <t>Crowne Plaza Hotel</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owU1/cmWTeASpvF33aHX13OmKNTSglY1CKyn1mH.iVuE4fs0</t>
   </si>
   <si>
+    <t>Paper Source</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owQu/m2vDq7l1wLeK_e1Ptqh35ndxEEbdElyIHgPfZOFdJUc</t>
+  </si>
+  <si>
+    <t>Muhlenberg</t>
+  </si>
+  <si>
+    <t>THE MUHLENBERG COUNTY COAL COMPANY</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVJ/Dg9.VOc4xZE0CzOT2WBULH9AF2F_W3myXxa4ijm196A</t>
+  </si>
+  <si>
     <t>Cinemark Holdings,Inc.-Cinemark Movies 10</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owQQ/GkNpTgbS1O.ynAUO2lRhhohP0a9SFLAzTXhbo.1Jdyw</t>
   </si>
   <si>
-    <t>Paper Source</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owQu/m2vDq7l1wLeK_e1Ptqh35ndxEEbdElyIHgPfZOFdJUc</t>
-  </si>
-  <si>
-    <t>Embassy Suites Jefferson Co - Louisville</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owTw/ZCaGJxEMniVjvqFnhoI_lXZxfMOTDOnfnNr.YyZ_aFs</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUB/Q4XhuwPlCqUiegEdy255dEODFtbl._noeWqruyQLy9c</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVE/C0OZ4Bz9aNkrc9YrcMiSzi1G1WqI2.arpnDnUUJqUr8</t>
-  </si>
-  <si>
-    <t>Muhlenberg</t>
-  </si>
-  <si>
-    <t>THE MUHLENBERG COUNTY COAL COMPANY</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVJ/Dg9.VOc4xZE0CzOT2WBULH9AF2F_W3myXxa4ijm196A</t>
-  </si>
-  <si>
-    <t>Bourbon</t>
-  </si>
-  <si>
-    <t>Murray Euipment &amp; Machine</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVO/fRo8DiZxbz2baMUvWanGYLiXkNdGw2BDb3YAGYVqjWI</t>
-  </si>
-  <si>
     <t>ALJSCO</t>
   </si>
   <si>
@@ -2074,10 +2074,28 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y0000044AjY/AIrRiUx57cQN91Gt3GEskluAye9VTB5lmjzmRGMobI4</t>
   </si>
   <si>
+    <t>Computer World Services, Corp (CWS)</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005F6GT/hczKIaARsuYpaKQAaTi4A_zNL7wOLhWx22fDoMXEKEw</t>
+  </si>
+  <si>
+    <t>Michael's College of Hair Design</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005EQsW/eGH3r6BxDqVQz60yQGUlrUul3F5PboNsbzx0MnTe1QA</t>
+  </si>
+  <si>
     <t>TF-Metal USA, LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005BdYf/aLuKB36i_ErCGp3pPAbg4Vo9Dr9tWbBR3IM8LaQg3aY</t>
+  </si>
+  <si>
+    <t>Piston Automotive</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005CSYX/K9PIWizbR2Ht_iyPPvR1jK.WnO4XyjCarpYQsEynm4s</t>
   </si>
   <si>
     <t>GDI Integrated Facility Services</t>
@@ -2719,7 +2737,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
@@ -2772,31 +2790,31 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
-        <v>45302</v>
+        <v>45320</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D2" s="55" t="s">
         <v>674</v>
       </c>
       <c r="E2" s="55">
-        <v>336110</v>
+        <v>561611</v>
       </c>
       <c r="F2" s="55">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G2" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="54">
-        <v>45365</v>
+        <v>45380</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J2" s="53" t="s">
         <v>675</v>
@@ -2808,70 +2826,70 @@
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
-        <v>45299</v>
+        <v>45315</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="D3" s="55" t="s">
         <v>676</v>
       </c>
       <c r="E3" s="55">
-        <v>561720</v>
+        <v>611511</v>
       </c>
       <c r="F3" s="55">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G3" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H3" s="54">
-        <v>45299</v>
+        <v>45315</v>
       </c>
       <c r="I3" s="55" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J3" s="53" t="s">
         <v>677</v>
       </c>
       <c r="K3" s="57" t="str">
-        <f t="shared" ref="K3:K11" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <f t="shared" ref="K3:K14" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
         <v>WARN</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54">
-        <v>45299</v>
+        <v>45302</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="D4" s="55" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E4" s="55">
-        <v>561720</v>
+        <v>336110</v>
       </c>
       <c r="F4" s="55">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G4" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H4" s="54">
-        <v>45299</v>
+        <v>45365</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J4" s="53" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="K4" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2880,34 +2898,34 @@
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54">
-        <v>45299</v>
+        <v>45301</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="E5" s="55">
-        <v>561720</v>
+        <v>336350</v>
       </c>
       <c r="F5" s="55">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G5" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H5" s="54">
-        <v>45299</v>
+        <v>45401</v>
       </c>
       <c r="I5" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="53" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="K5" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2925,13 +2943,13 @@
         <v>238</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="E6" s="55">
         <v>561720</v>
       </c>
       <c r="F6" s="55">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G6" s="55" t="s">
         <v>16</v>
@@ -2943,7 +2961,7 @@
         <v>13</v>
       </c>
       <c r="J6" s="53" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="K6" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2952,34 +2970,34 @@
     </row>
     <row r="7" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E7" s="55">
-        <v>331400</v>
+        <v>561720</v>
       </c>
       <c r="F7" s="55">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G7" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H7" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="I7" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" s="53" t="s">
-        <v>10</v>
+        <v>684</v>
       </c>
       <c r="K7" s="57" t="str">
         <f t="shared" si="0"/>
@@ -2988,34 +3006,34 @@
     </row>
     <row r="8" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="E8" s="55">
         <v>561720</v>
       </c>
       <c r="F8" s="55">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G8" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="54">
-        <v>45356</v>
+        <v>45299</v>
       </c>
       <c r="I8" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="53" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="K8" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3024,34 +3042,34 @@
     </row>
     <row r="9" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="E9" s="55">
         <v>561720</v>
       </c>
       <c r="F9" s="55">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="G9" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="54">
-        <v>45356</v>
+        <v>45299</v>
       </c>
       <c r="I9" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="53" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="K9" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3063,31 +3081,31 @@
         <v>45295</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="E10" s="55">
-        <v>561720</v>
+        <v>331400</v>
       </c>
       <c r="F10" s="55">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G10" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H10" s="54">
-        <v>45356</v>
+        <v>45295</v>
       </c>
       <c r="I10" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>684</v>
+        <v>10</v>
       </c>
       <c r="K10" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3096,36 +3114,144 @@
     </row>
     <row r="11" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="54">
+        <v>45295</v>
+      </c>
+      <c r="B11" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="E11" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F11" s="55">
+        <v>48</v>
+      </c>
+      <c r="G11" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="54">
+        <v>45356</v>
+      </c>
+      <c r="I11" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="53" t="s">
+        <v>688</v>
+      </c>
+      <c r="K11" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="54">
+        <v>45295</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="E12" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F12" s="55">
+        <v>40</v>
+      </c>
+      <c r="G12" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="54">
+        <v>45356</v>
+      </c>
+      <c r="I12" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="53" t="s">
+        <v>689</v>
+      </c>
+      <c r="K12" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="54">
+        <v>45295</v>
+      </c>
+      <c r="B13" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="E13" s="55">
+        <v>561720</v>
+      </c>
+      <c r="F13" s="55">
+        <v>40</v>
+      </c>
+      <c r="G13" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="54">
+        <v>45356</v>
+      </c>
+      <c r="I13" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="53" t="s">
+        <v>690</v>
+      </c>
+      <c r="K13" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="54">
         <v>45293</v>
       </c>
-      <c r="B11" s="55" t="s">
+      <c r="B14" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C14" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="D11" s="55" t="s">
-        <v>685</v>
-      </c>
-      <c r="E11" s="55">
+      <c r="D14" s="55" t="s">
+        <v>691</v>
+      </c>
+      <c r="E14" s="55">
         <v>541714</v>
       </c>
-      <c r="F11" s="55">
+      <c r="F14" s="55">
         <v>136</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="G14" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="54">
+      <c r="H14" s="54">
         <v>45351</v>
       </c>
-      <c r="I11" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="53" t="s">
-        <v>686</v>
-      </c>
-      <c r="K11" s="57" t="str">
+      <c r="I14" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="53" t="s">
+        <v>692</v>
+      </c>
+      <c r="K14" s="57" t="str">
         <f t="shared" si="0"/>
         <v>WARN</v>
       </c>
@@ -6135,7 +6261,7 @@
         <v>258</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E21" s="55">
         <v>332613</v>
@@ -6443,25 +6569,25 @@
         <v>44097</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="D7" s="55" t="s">
         <v>285</v>
       </c>
       <c r="E7" s="55">
-        <v>721110</v>
+        <v>325211</v>
       </c>
       <c r="F7" s="55">
-        <v>294</v>
+        <v>164</v>
       </c>
       <c r="G7" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="54">
-        <v>43907</v>
+        <v>43973</v>
       </c>
       <c r="I7" s="55" t="s">
         <v>13</v>
@@ -6479,25 +6605,25 @@
         <v>44097</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="D8" s="55" t="s">
         <v>287</v>
       </c>
       <c r="E8" s="55">
-        <v>325211</v>
+        <v>721110</v>
       </c>
       <c r="F8" s="55">
-        <v>164</v>
+        <v>294</v>
       </c>
       <c r="G8" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="54">
-        <v>43973</v>
+        <v>43907</v>
       </c>
       <c r="I8" s="55" t="s">
         <v>13</v>
@@ -7055,10 +7181,10 @@
         <v>44035</v>
       </c>
       <c r="B24" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D24" s="55" t="s">
         <v>318</v>
@@ -7067,13 +7193,13 @@
         <v>213113</v>
       </c>
       <c r="F24" s="55">
-        <v>5</v>
+        <v>194</v>
       </c>
       <c r="G24" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H24" s="54">
-        <v>44098</v>
+        <v>44094</v>
       </c>
       <c r="I24" s="55" t="s">
         <v>13</v>
@@ -7091,10 +7217,10 @@
         <v>44035</v>
       </c>
       <c r="B25" s="55" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="D25" s="55" t="s">
         <v>320</v>
@@ -7103,7 +7229,7 @@
         <v>213113</v>
       </c>
       <c r="F25" s="55">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="G25" s="55" t="s">
         <v>11</v>
@@ -7112,7 +7238,7 @@
         <v>44094</v>
       </c>
       <c r="I25" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J25" s="53" t="s">
         <v>321</v>
@@ -7139,16 +7265,16 @@
         <v>213113</v>
       </c>
       <c r="F26" s="55">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G26" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H26" s="54">
-        <v>44094</v>
+        <v>44098</v>
       </c>
       <c r="I26" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J26" s="53" t="s">
         <v>323</v>
@@ -7487,25 +7613,25 @@
         <v>43997</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>225</v>
+        <v>342</v>
       </c>
       <c r="D36" s="55" t="s">
         <v>345</v>
       </c>
       <c r="E36" s="55">
-        <v>493110</v>
+        <v>488190</v>
       </c>
       <c r="F36" s="55">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="G36" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H36" s="54">
-        <v>44055</v>
+        <v>43994</v>
       </c>
       <c r="I36" s="55" t="s">
         <v>13</v>
@@ -7523,25 +7649,25 @@
         <v>43997</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>342</v>
+        <v>225</v>
       </c>
       <c r="D37" s="55" t="s">
         <v>347</v>
       </c>
       <c r="E37" s="55">
-        <v>488190</v>
+        <v>493110</v>
       </c>
       <c r="F37" s="55">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="G37" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H37" s="54">
-        <v>43994</v>
+        <v>44055</v>
       </c>
       <c r="I37" s="55" t="s">
         <v>13</v>
@@ -7739,28 +7865,28 @@
         <v>43973</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="D43" s="55" t="s">
         <v>359</v>
       </c>
       <c r="E43" s="55">
-        <v>721110</v>
+        <v>332613</v>
       </c>
       <c r="F43" s="55">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="G43" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H43" s="54">
-        <v>43979</v>
+        <v>44104</v>
       </c>
       <c r="I43" s="55" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J43" s="53" t="s">
         <v>360</v>
@@ -7775,28 +7901,28 @@
         <v>43973</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="D44" s="55" t="s">
         <v>361</v>
       </c>
       <c r="E44" s="55">
-        <v>332613</v>
+        <v>721110</v>
       </c>
       <c r="F44" s="55">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="G44" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H44" s="54">
-        <v>44104</v>
+        <v>43979</v>
       </c>
       <c r="I44" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J44" s="53" t="s">
         <v>362</v>
@@ -8135,25 +8261,25 @@
         <v>43948</v>
       </c>
       <c r="B54" s="55" t="s">
-        <v>332</v>
+        <v>47</v>
       </c>
       <c r="C54" s="55" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="D54" s="55" t="s">
         <v>380</v>
       </c>
       <c r="E54" s="55">
-        <v>722511</v>
+        <v>322121</v>
       </c>
       <c r="F54" s="55">
-        <v>1134</v>
+        <v>398</v>
       </c>
       <c r="G54" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H54" s="54">
-        <v>43905</v>
+        <v>43955</v>
       </c>
       <c r="I54" s="55" t="s">
         <v>13</v>
@@ -8171,25 +8297,25 @@
         <v>43948</v>
       </c>
       <c r="B55" s="55" t="s">
-        <v>47</v>
+        <v>332</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="D55" s="55" t="s">
         <v>382</v>
       </c>
       <c r="E55" s="55">
-        <v>322121</v>
+        <v>722511</v>
       </c>
       <c r="F55" s="55">
-        <v>398</v>
+        <v>1134</v>
       </c>
       <c r="G55" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H55" s="54">
-        <v>43955</v>
+        <v>43905</v>
       </c>
       <c r="I55" s="55" t="s">
         <v>13</v>
@@ -8207,25 +8333,25 @@
         <v>43945</v>
       </c>
       <c r="B56" s="55" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C56" s="55" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="D56" s="55" t="s">
         <v>384</v>
       </c>
       <c r="E56" s="55">
-        <v>532111</v>
+        <v>423210</v>
       </c>
       <c r="F56" s="55">
-        <v>102</v>
+        <v>210</v>
       </c>
       <c r="G56" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H56" s="54">
-        <v>43910</v>
+        <v>43935</v>
       </c>
       <c r="I56" s="55" t="s">
         <v>13</v>
@@ -8243,10 +8369,10 @@
         <v>43945</v>
       </c>
       <c r="B57" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D57" s="55" t="s">
         <v>386</v>
@@ -8255,7 +8381,7 @@
         <v>532111</v>
       </c>
       <c r="F57" s="55">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="G57" s="55" t="s">
         <v>16</v>
@@ -8285,25 +8411,25 @@
         <v>128</v>
       </c>
       <c r="D58" s="55" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E58" s="55">
         <v>532111</v>
       </c>
       <c r="F58" s="55">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="G58" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H58" s="54">
-        <v>43951</v>
+        <v>43910</v>
       </c>
       <c r="I58" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J58" s="53" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K58" s="57" t="str">
         <f t="shared" si="0"/>
@@ -8315,25 +8441,25 @@
         <v>43945</v>
       </c>
       <c r="B59" s="55" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>257</v>
+        <v>128</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E59" s="55">
-        <v>423210</v>
+        <v>532111</v>
       </c>
       <c r="F59" s="55">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="G59" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H59" s="54">
-        <v>43935</v>
+        <v>43951</v>
       </c>
       <c r="I59" s="55" t="s">
         <v>13</v>
@@ -8423,25 +8549,25 @@
         <v>43938</v>
       </c>
       <c r="B62" s="55" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C62" s="55" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D62" s="55" t="s">
         <v>395</v>
       </c>
       <c r="E62" s="55">
-        <v>532111</v>
+        <v>33392</v>
       </c>
       <c r="F62" s="55">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G62" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H62" s="54">
-        <v>43903</v>
+        <v>43936</v>
       </c>
       <c r="I62" s="55" t="s">
         <v>13</v>
@@ -8459,10 +8585,10 @@
         <v>43938</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C63" s="55" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="D63" s="55" t="s">
         <v>397</v>
@@ -8471,7 +8597,7 @@
         <v>532111</v>
       </c>
       <c r="F63" s="55">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G63" s="55" t="s">
         <v>16</v>
@@ -8495,25 +8621,25 @@
         <v>43938</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C64" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D64" s="55" t="s">
         <v>399</v>
       </c>
       <c r="E64" s="55">
-        <v>33392</v>
+        <v>532111</v>
       </c>
       <c r="F64" s="55">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G64" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H64" s="54">
-        <v>43936</v>
+        <v>43903</v>
       </c>
       <c r="I64" s="55" t="s">
         <v>13</v>
@@ -8684,19 +8810,19 @@
         <v>406</v>
       </c>
       <c r="E69" s="55">
-        <v>339116</v>
+        <v>337910</v>
       </c>
       <c r="F69" s="55">
-        <v>151</v>
+        <v>234</v>
       </c>
       <c r="G69" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H69" s="54">
-        <v>43917</v>
+        <v>43924</v>
       </c>
       <c r="I69" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J69" s="53" t="s">
         <v>407</v>
@@ -8711,25 +8837,25 @@
         <v>43935</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C70" s="55" t="s">
-        <v>128</v>
+        <v>267</v>
       </c>
       <c r="D70" s="55" t="s">
         <v>408</v>
       </c>
       <c r="E70" s="55">
-        <v>337910</v>
+        <v>712130</v>
       </c>
       <c r="F70" s="55">
-        <v>234</v>
+        <v>88</v>
       </c>
       <c r="G70" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H70" s="54">
-        <v>43924</v>
+        <v>43941</v>
       </c>
       <c r="I70" s="55" t="s">
         <v>13</v>
@@ -8747,28 +8873,28 @@
         <v>43935</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C71" s="55" t="s">
-        <v>267</v>
+        <v>128</v>
       </c>
       <c r="D71" s="55" t="s">
         <v>410</v>
       </c>
       <c r="E71" s="55">
-        <v>712130</v>
+        <v>339116</v>
       </c>
       <c r="F71" s="55">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="G71" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H71" s="54">
-        <v>43941</v>
+        <v>43917</v>
       </c>
       <c r="I71" s="55" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J71" s="53" t="s">
         <v>411</v>
@@ -8999,31 +9125,31 @@
         <v>43927</v>
       </c>
       <c r="B78" s="55" t="s">
-        <v>332</v>
+        <v>70</v>
       </c>
       <c r="C78" s="55" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
       <c r="D78" s="55" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E78" s="55">
-        <v>722511</v>
+        <v>623110</v>
       </c>
       <c r="F78" s="55">
-        <v>293</v>
+        <v>14</v>
       </c>
       <c r="G78" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H78" s="54">
-        <v>43906</v>
+        <v>43910</v>
       </c>
       <c r="I78" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J78" s="53" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K78" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9038,28 +9164,28 @@
         <v>70</v>
       </c>
       <c r="C79" s="55" t="s">
-        <v>273</v>
+        <v>427</v>
       </c>
       <c r="D79" s="55" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E79" s="55">
-        <v>623110</v>
+        <v>423110</v>
       </c>
       <c r="F79" s="55">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="G79" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H79" s="54">
-        <v>43910</v>
+        <v>43934</v>
       </c>
       <c r="I79" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J79" s="53" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K79" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9071,31 +9197,31 @@
         <v>43927</v>
       </c>
       <c r="B80" s="55" t="s">
-        <v>70</v>
+        <v>332</v>
       </c>
       <c r="C80" s="55" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="D80" s="55" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E80" s="55">
-        <v>623110</v>
+        <v>722511</v>
       </c>
       <c r="F80" s="55">
-        <v>27</v>
+        <v>293</v>
       </c>
       <c r="G80" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H80" s="54">
-        <v>43910</v>
+        <v>43906</v>
       </c>
       <c r="I80" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J80" s="53" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K80" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9110,16 +9236,16 @@
         <v>70</v>
       </c>
       <c r="C81" s="55" t="s">
-        <v>430</v>
+        <v>264</v>
       </c>
       <c r="D81" s="55" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E81" s="55">
         <v>623110</v>
       </c>
       <c r="F81" s="55">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G81" s="55" t="s">
         <v>16</v>
@@ -9131,7 +9257,7 @@
         <v>13</v>
       </c>
       <c r="J81" s="53" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K81" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9146,16 +9272,16 @@
         <v>70</v>
       </c>
       <c r="C82" s="55" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E82" s="55">
         <v>623110</v>
       </c>
       <c r="F82" s="55">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G82" s="55" t="s">
         <v>16</v>
@@ -9167,7 +9293,7 @@
         <v>13</v>
       </c>
       <c r="J82" s="53" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K82" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9182,7 +9308,7 @@
         <v>70</v>
       </c>
       <c r="C83" s="55" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="D83" s="55" t="s">
         <v>437</v>
@@ -9218,7 +9344,7 @@
         <v>70</v>
       </c>
       <c r="C84" s="55" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="D84" s="55" t="s">
         <v>439</v>
@@ -9362,22 +9488,22 @@
         <v>70</v>
       </c>
       <c r="C88" s="55" t="s">
-        <v>436</v>
+        <v>273</v>
       </c>
       <c r="D88" s="55" t="s">
         <v>447</v>
       </c>
       <c r="E88" s="55">
-        <v>423110</v>
+        <v>623110</v>
       </c>
       <c r="F88" s="55">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="G88" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H88" s="54">
-        <v>43934</v>
+        <v>43910</v>
       </c>
       <c r="I88" s="55" t="s">
         <v>13</v>
@@ -9407,7 +9533,7 @@
         <v>623110</v>
       </c>
       <c r="F89" s="55">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="G89" s="55" t="s">
         <v>16</v>
@@ -9467,25 +9593,25 @@
         <v>43923</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>128</v>
+        <v>258</v>
       </c>
       <c r="D91" s="55" t="s">
         <v>453</v>
       </c>
       <c r="E91" s="55">
-        <v>721110</v>
+        <v>333999</v>
       </c>
       <c r="F91" s="55">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G91" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H91" s="54">
-        <v>43906</v>
+        <v>43926</v>
       </c>
       <c r="I91" s="55" t="s">
         <v>13</v>
@@ -9503,10 +9629,10 @@
         <v>43923</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="D92" s="55" t="s">
         <v>455</v>
@@ -9515,13 +9641,13 @@
         <v>721110</v>
       </c>
       <c r="F92" s="55">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="G92" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H92" s="54">
-        <v>43910</v>
+        <v>43906</v>
       </c>
       <c r="I92" s="55" t="s">
         <v>13</v>
@@ -9539,25 +9665,25 @@
         <v>43923</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="C93" s="55" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="D93" s="55" t="s">
         <v>457</v>
       </c>
       <c r="E93" s="55">
-        <v>333999</v>
+        <v>721110</v>
       </c>
       <c r="F93" s="55">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="G93" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H93" s="54">
-        <v>43926</v>
+        <v>43910</v>
       </c>
       <c r="I93" s="55" t="s">
         <v>13</v>
@@ -9581,13 +9707,13 @@
         <v>128</v>
       </c>
       <c r="D94" s="55" t="s">
-        <v>298</v>
+        <v>459</v>
       </c>
       <c r="E94" s="55">
         <v>721110</v>
       </c>
       <c r="F94" s="55">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="G94" s="55" t="s">
         <v>16</v>
@@ -9599,7 +9725,7 @@
         <v>13</v>
       </c>
       <c r="J94" s="53" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K94" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9611,25 +9737,25 @@
         <v>43922</v>
       </c>
       <c r="B95" s="55" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C95" s="55" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="D95" s="55" t="s">
-        <v>460</v>
+        <v>201</v>
       </c>
       <c r="E95" s="55">
-        <v>721110</v>
+        <v>21211</v>
       </c>
       <c r="F95" s="55">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="G95" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H95" s="54">
-        <v>43920</v>
+        <v>43984</v>
       </c>
       <c r="I95" s="55" t="s">
         <v>13</v>
@@ -9647,31 +9773,31 @@
         <v>43922</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C96" s="55" t="s">
-        <v>254</v>
+        <v>462</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E96" s="55">
-        <v>512131</v>
+        <v>423520</v>
       </c>
       <c r="F96" s="55">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G96" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H96" s="54">
-        <v>43916</v>
+        <v>43984</v>
       </c>
       <c r="I96" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J96" s="53" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K96" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9689,19 +9815,19 @@
         <v>128</v>
       </c>
       <c r="D97" s="55" t="s">
-        <v>464</v>
+        <v>298</v>
       </c>
       <c r="E97" s="55">
-        <v>424110</v>
+        <v>721110</v>
       </c>
       <c r="F97" s="55">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G97" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H97" s="54">
-        <v>43919</v>
+        <v>43920</v>
       </c>
       <c r="I97" s="55" t="s">
         <v>13</v>
@@ -9725,13 +9851,13 @@
         <v>128</v>
       </c>
       <c r="D98" s="55" t="s">
-        <v>466</v>
+        <v>298</v>
       </c>
       <c r="E98" s="55">
         <v>721110</v>
       </c>
       <c r="F98" s="55">
-        <v>62</v>
+        <v>399</v>
       </c>
       <c r="G98" s="55" t="s">
         <v>16</v>
@@ -9743,7 +9869,7 @@
         <v>13</v>
       </c>
       <c r="J98" s="53" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K98" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9761,13 +9887,13 @@
         <v>128</v>
       </c>
       <c r="D99" s="55" t="s">
-        <v>298</v>
+        <v>467</v>
       </c>
       <c r="E99" s="55">
         <v>721110</v>
       </c>
       <c r="F99" s="55">
-        <v>399</v>
+        <v>150</v>
       </c>
       <c r="G99" s="55" t="s">
         <v>16</v>
@@ -9791,31 +9917,31 @@
         <v>43922</v>
       </c>
       <c r="B100" s="55" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="C100" s="55" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="D100" s="55" t="s">
-        <v>201</v>
+        <v>469</v>
       </c>
       <c r="E100" s="55">
-        <v>21211</v>
+        <v>424110</v>
       </c>
       <c r="F100" s="55">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G100" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H100" s="54">
-        <v>43984</v>
+        <v>43919</v>
       </c>
       <c r="I100" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J100" s="53" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K100" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9830,10 +9956,10 @@
         <v>38</v>
       </c>
       <c r="C101" s="55" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E101" s="55">
         <v>21211</v>
@@ -9851,7 +9977,7 @@
         <v>13</v>
       </c>
       <c r="J101" s="53" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K101" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9863,25 +9989,25 @@
         <v>43922</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C102" s="55" t="s">
-        <v>473</v>
+        <v>254</v>
       </c>
       <c r="D102" s="55" t="s">
         <v>474</v>
       </c>
       <c r="E102" s="55">
-        <v>423520</v>
+        <v>512131</v>
       </c>
       <c r="F102" s="55">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G102" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H102" s="54">
-        <v>43984</v>
+        <v>43916</v>
       </c>
       <c r="I102" s="55" t="s">
         <v>13</v>
@@ -14599,6 +14725,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -14607,7 +14739,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0C1C9366252B4C838708442C71C5AA" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="623745db76138c409ead4834ced54ea8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="62511544-38af-49c2-8996-37c0f6a636fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c1a1049adbb8cd97fc988c6af4986c32" ns2:_="">
     <xsd:import namespace="62511544-38af-49c2-8996-37c0f6a636fd"/>
@@ -14747,25 +14879,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F95DCE-7EDC-4B2F-BF77-FCA5513DAA7E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEB26DE-B3FC-45A8-BF93-B326AF5FAB7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -14778,4 +14892,16 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79D7268F-83EE-4BEC-9A9E-C30212D56F81}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE834477-D322-4F99-9EA1-578E4226F551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB5D5F2F-C43B-41B5-AEB5-0757C4F900D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1342,6 +1342,12 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX0/V6hwrqZ0Qlr_eFlMYEYrZXlE5AKDheKuIEjfBsUaPdQ</t>
   </si>
   <si>
+    <t>Communicare Clinic - Radcliff</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWl/rS8vJCQrLNj0CL7FyoK6cd2Ubo0vr1icry6WlMYbX7U</t>
+  </si>
+  <si>
     <t>HOOTERS of America LLC</t>
   </si>
   <si>
@@ -1375,12 +1381,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWg/9p9FS.JQp0PTPMhD3HxrAxxsoxTEr_upxaagBfFMogM</t>
   </si>
   <si>
-    <t>Communicare Clinic - Radcliff</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWl/rS8vJCQrLNj0CL7FyoK6cd2Ubo0vr1icry6WlMYbX7U</t>
-  </si>
-  <si>
     <t>Communicare Services - Radcliff</t>
   </si>
   <si>
@@ -1411,6 +1411,12 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVY/2COXMu6Bd1MCYgNNs.Sc62L0asFJOG..KVsIGQuqD5g</t>
   </si>
   <si>
+    <t>IHG Army Hotels &amp; Holiday Inn Express</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
+  </si>
+  <si>
     <t>Huhtamaki, Inc.</t>
   </si>
   <si>
@@ -1423,10 +1429,10 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVT/U2oN7sbm_kSzNb7xiYNnrUVaoC_094PGtzzEyvZMQHo</t>
   </si>
   <si>
-    <t>IHG Army Hotels &amp; Holiday Inn Express</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
+    <t>Crowne Plaza Hotel</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owU1/cmWTeASpvF33aHX13OmKNTSglY1CKyn1mH.iVuE4fs0</t>
   </si>
   <si>
     <t>Embassy Suites Jefferson Co - Louisville</t>
@@ -1451,12 +1457,6 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUB/Q4XhuwPlCqUiegEdy255dEODFtbl._noeWqruyQLy9c</t>
-  </si>
-  <si>
-    <t>Crowne Plaza Hotel</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owU1/cmWTeASpvF33aHX13OmKNTSglY1CKyn1mH.iVuE4fs0</t>
   </si>
   <si>
     <t>Paper Source</t>
@@ -2850,7 +2850,7 @@
         <v>45315</v>
       </c>
       <c r="I3" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J3" s="53" t="s">
         <v>677</v>
@@ -2886,7 +2886,7 @@
         <v>45365</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J4" s="53" t="s">
         <v>679</v>
@@ -9197,25 +9197,25 @@
         <v>43927</v>
       </c>
       <c r="B80" s="55" t="s">
-        <v>332</v>
+        <v>70</v>
       </c>
       <c r="C80" s="55" t="s">
-        <v>333</v>
+        <v>273</v>
       </c>
       <c r="D80" s="55" t="s">
         <v>430</v>
       </c>
       <c r="E80" s="55">
-        <v>722511</v>
+        <v>623110</v>
       </c>
       <c r="F80" s="55">
-        <v>293</v>
+        <v>17</v>
       </c>
       <c r="G80" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H80" s="54">
-        <v>43906</v>
+        <v>43910</v>
       </c>
       <c r="I80" s="55" t="s">
         <v>13</v>
@@ -9233,25 +9233,25 @@
         <v>43927</v>
       </c>
       <c r="B81" s="55" t="s">
-        <v>70</v>
+        <v>332</v>
       </c>
       <c r="C81" s="55" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="D81" s="55" t="s">
         <v>432</v>
       </c>
       <c r="E81" s="55">
-        <v>623110</v>
+        <v>722511</v>
       </c>
       <c r="F81" s="55">
-        <v>27</v>
+        <v>293</v>
       </c>
       <c r="G81" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H81" s="54">
-        <v>43910</v>
+        <v>43906</v>
       </c>
       <c r="I81" s="55" t="s">
         <v>13</v>
@@ -9272,16 +9272,16 @@
         <v>70</v>
       </c>
       <c r="C82" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="D82" s="55" t="s">
         <v>434</v>
-      </c>
-      <c r="D82" s="55" t="s">
-        <v>435</v>
       </c>
       <c r="E82" s="55">
         <v>623110</v>
       </c>
       <c r="F82" s="55">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G82" s="55" t="s">
         <v>16</v>
@@ -9293,7 +9293,7 @@
         <v>13</v>
       </c>
       <c r="J82" s="53" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K82" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9308,7 +9308,7 @@
         <v>70</v>
       </c>
       <c r="C83" s="55" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D83" s="55" t="s">
         <v>437</v>
@@ -9380,7 +9380,7 @@
         <v>70</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>273</v>
+        <v>427</v>
       </c>
       <c r="D85" s="55" t="s">
         <v>441</v>
@@ -9389,7 +9389,7 @@
         <v>623110</v>
       </c>
       <c r="F85" s="55">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G85" s="55" t="s">
         <v>16</v>
@@ -9593,25 +9593,25 @@
         <v>43923</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="D91" s="55" t="s">
         <v>453</v>
       </c>
       <c r="E91" s="55">
-        <v>333999</v>
+        <v>721110</v>
       </c>
       <c r="F91" s="55">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="G91" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H91" s="54">
-        <v>43926</v>
+        <v>43910</v>
       </c>
       <c r="I91" s="55" t="s">
         <v>13</v>
@@ -9629,25 +9629,25 @@
         <v>43923</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>128</v>
+        <v>258</v>
       </c>
       <c r="D92" s="55" t="s">
         <v>455</v>
       </c>
       <c r="E92" s="55">
-        <v>721110</v>
+        <v>333999</v>
       </c>
       <c r="F92" s="55">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G92" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H92" s="54">
-        <v>43906</v>
+        <v>43926</v>
       </c>
       <c r="I92" s="55" t="s">
         <v>13</v>
@@ -9665,10 +9665,10 @@
         <v>43923</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C93" s="55" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="D93" s="55" t="s">
         <v>457</v>
@@ -9677,13 +9677,13 @@
         <v>721110</v>
       </c>
       <c r="F93" s="55">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="G93" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H93" s="54">
-        <v>43910</v>
+        <v>43906</v>
       </c>
       <c r="I93" s="55" t="s">
         <v>13</v>
@@ -9713,7 +9713,7 @@
         <v>721110</v>
       </c>
       <c r="F94" s="55">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="G94" s="55" t="s">
         <v>16</v>
@@ -9737,31 +9737,31 @@
         <v>43922</v>
       </c>
       <c r="B95" s="55" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="C95" s="55" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="D95" s="55" t="s">
-        <v>201</v>
+        <v>461</v>
       </c>
       <c r="E95" s="55">
-        <v>21211</v>
+        <v>721110</v>
       </c>
       <c r="F95" s="55">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G95" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H95" s="54">
-        <v>43984</v>
+        <v>43920</v>
       </c>
       <c r="I95" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J95" s="53" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K95" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9773,22 +9773,22 @@
         <v>43922</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C96" s="55" t="s">
-        <v>462</v>
+        <v>227</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>463</v>
+        <v>201</v>
       </c>
       <c r="E96" s="55">
-        <v>423520</v>
+        <v>21211</v>
       </c>
       <c r="F96" s="55">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="G96" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H96" s="54">
         <v>43984</v>
@@ -9797,7 +9797,7 @@
         <v>13</v>
       </c>
       <c r="J96" s="53" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K96" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9809,31 +9809,31 @@
         <v>43922</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C97" s="55" t="s">
-        <v>128</v>
+        <v>464</v>
       </c>
       <c r="D97" s="55" t="s">
-        <v>298</v>
+        <v>465</v>
       </c>
       <c r="E97" s="55">
-        <v>721110</v>
+        <v>423520</v>
       </c>
       <c r="F97" s="55">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G97" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H97" s="54">
-        <v>43920</v>
+        <v>43984</v>
       </c>
       <c r="I97" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J97" s="53" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K97" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9857,7 +9857,7 @@
         <v>721110</v>
       </c>
       <c r="F98" s="55">
-        <v>399</v>
+        <v>2</v>
       </c>
       <c r="G98" s="55" t="s">
         <v>16</v>
@@ -9869,7 +9869,7 @@
         <v>13</v>
       </c>
       <c r="J98" s="53" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K98" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9887,13 +9887,13 @@
         <v>128</v>
       </c>
       <c r="D99" s="55" t="s">
-        <v>467</v>
+        <v>298</v>
       </c>
       <c r="E99" s="55">
         <v>721110</v>
       </c>
       <c r="F99" s="55">
-        <v>150</v>
+        <v>399</v>
       </c>
       <c r="G99" s="55" t="s">
         <v>16</v>
@@ -14725,21 +14725,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0C1C9366252B4C838708442C71C5AA" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="623745db76138c409ead4834ced54ea8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="62511544-38af-49c2-8996-37c0f6a636fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c1a1049adbb8cd97fc988c6af4986c32" ns2:_="">
     <xsd:import namespace="62511544-38af-49c2-8996-37c0f6a636fd"/>
@@ -14879,7 +14864,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C14CA432-9072-454B-AF4E-ADB605838576}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEB26DE-B3FC-45A8-BF93-B326AF5FAB7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -14894,14 +14898,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79D7268F-83EE-4BEC-9A9E-C30212D56F81}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB5D5F2F-C43B-41B5-AEB5-0757C4F900D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDF24993-6373-4854-833F-D2128C061150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="1830" windowWidth="15180" windowHeight="8970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="8" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="695">
   <si>
     <t>Date Received</t>
   </si>
@@ -907,18 +907,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001Duxy/OQSRyQ_.aYQHhrFXq8Tdiv.MgS0Rz2oZW0hbEdodBXY</t>
   </si>
   <si>
+    <t>Omni Hotels &amp; Resorts</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DsAc/VBX3AB_6wodTw6SXAtFGoYfEaBMIRx8Y1R1QDhgqJho</t>
+  </si>
+  <si>
     <t>Meggitt Polymers and Composites - Erlanger</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DsDM/G0wP5hdwHVxpG7glqsx.P.Bu.ufe7zp6pACAhUX6gDA</t>
   </si>
   <si>
-    <t>Omni Hotels &amp; Resorts</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DsAc/VBX3AB_6wodTw6SXAtFGoYfEaBMIRx8Y1R1QDhgqJho</t>
-  </si>
-  <si>
     <t>ABM c/o The Hertz Corporation - CVG</t>
   </si>
   <si>
@@ -940,12 +940,12 @@
     <t>P.F. CHANG'S CHINA BISTRO, INC.</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001Dn9p/B92tz6zaPaYm5.lAsW0F6GS2hq_bm.DPaGZFyNbmJNI</t>
+  </si>
+  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001DnAi/PsQ06rfrLt2A8hC1UKmSPXyLtRhTdP2bt3fWa.P3Mao</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000001Dn9p/B92tz6zaPaYm5.lAsW0F6GS2hq_bm.DPaGZFyNbmJNI</t>
-  </si>
-  <si>
     <t>Galt House Hotel &amp; Suites</t>
   </si>
   <si>
@@ -970,18 +970,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000nXqL/60wOB.ZYyAFW_S_R8hleRIp7jxvj5pSKHPafgMy.D34</t>
   </si>
   <si>
+    <t>WestRock Comany</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n28b/Jn1rUm_cAXF2P3ZrPaqixkhcq2ejA4cVozic81IBDBc</t>
+  </si>
+  <si>
     <t>Vino Volo</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n3UK/pGrkwz.TW4TwVggStmZ08DA7.gkV29a2hXqMxuex7_w</t>
   </si>
   <si>
-    <t>WestRock Comany</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000n28b/Jn1rUm_cAXF2P3ZrPaqixkhcq2ejA4cVozic81IBDBc</t>
-  </si>
-  <si>
     <t>Republic Airline Inc.</t>
   </si>
   <si>
@@ -1006,24 +1006,24 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjW4/G_5.Fi2tenUK8iONlECvyrpM3qeWoSn_lcSPHmqPLhs</t>
   </si>
   <si>
+    <t>Rhino Energy LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHO/J4gmK3FhqJupdRaSOCMq.CU3rKIt8M2k3PeCmNPgsTk</t>
+  </si>
+  <si>
+    <t>Rhino Group LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHT/LD5kPxqA490uoPjJTUYgS_DByLIc4TIotUjmADqJaU0</t>
+  </si>
+  <si>
     <t>CAM  Mining LLC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHd/LirRegwEOo6tABsdbsKLD3wZvWNuvAk8O7lo662CRW4</t>
   </si>
   <si>
-    <t>Rhino Energy LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHO/J4gmK3FhqJupdRaSOCMq.CU3rKIt8M2k3PeCmNPgsTk</t>
-  </si>
-  <si>
-    <t>Rhino Group LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000mjHT/LD5kPxqA490uoPjJTUYgS_DByLIc4TIotUjmADqJaU0</t>
-  </si>
-  <si>
     <t>Kenco Logistic Services, LLC</t>
   </si>
   <si>
@@ -1129,18 +1129,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000leL1/SnG3sVRdWjFQMCr8LETwNOCbLpaaGRlfQEhLqrDI3L8</t>
   </si>
   <si>
+    <t>21c Museum Hotel Lexington</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000leLV/SG3RH__XeMSmDA.BzF5J9gLLQ9R0VtgAocKowWhdEL4</t>
+  </si>
+  <si>
     <t>MSSC US, INC</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000ltac/RzIOWPGwYHCFP6cxNIWDpNwrH4SL6H5XqNJy0KCDiO8</t>
   </si>
   <si>
-    <t>21c Museum Hotel Lexington</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000leLV/SG3RH__XeMSmDA.BzF5J9gLLQ9R0VtgAocKowWhdEL4</t>
-  </si>
-  <si>
     <t>Enterprise Rent A Car - CVG</t>
   </si>
   <si>
@@ -1180,6 +1180,12 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lHSh/K0STGdn5RioZCNnefjssHgRYhvyegfO5stZN_W4HKGc</t>
   </si>
   <si>
+    <t>Bloomin' Brands Inc.</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFnJ/4P1OqyziA7PB0Bwl_6nFu_TYtWbVZmItGG0ajc_A4io</t>
+  </si>
+  <si>
     <t>Copart</t>
   </si>
   <si>
@@ -1198,10 +1204,19 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lG1B/4Fd5SUVur4FncgJi63EeLKzz9wTruSFuhn9yeHQp8b0</t>
   </si>
   <si>
-    <t>Bloomin' Brands Inc.</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFnJ/4P1OqyziA7PB0Bwl_6nFu_TYtWbVZmItGG0ajc_A4io</t>
+    <t>EAN Holdings, LLC dba/Enterprise Rent-A-Car/Alamo/National</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFDB/kRPBe.4UKGSTGSllBCkX9k7zMUm.j5e7.dzfx1Or6tU</t>
+  </si>
+  <si>
+    <t>Enterprise Rent-A-Car</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFQo/Dd0iim4d5jjd4TYBWh2lMYNeVGc37N7hRYP1WAOvxGA</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFRh/UszfPVKKroq1QAKiNquy4pybhgj_l.wWTgrzPpPoae0</t>
   </si>
   <si>
     <t>Leggett &amp; Platt, Inc</t>
@@ -1210,21 +1225,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFhk/YXvfnj9glnybML0caPMSROnboavSXn.klKEWtkrTQy8</t>
   </si>
   <si>
-    <t>EAN Holdings, LLC dba/Enterprise Rent-A-Car/Alamo/National</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFDB/kRPBe.4UKGSTGSllBCkX9k7zMUm.j5e7.dzfx1Or6tU</t>
-  </si>
-  <si>
-    <t>Enterprise Rent-A-Car</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFQo/Dd0iim4d5jjd4TYBWh2lMYNeVGc37N7hRYP1WAOvxGA</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000lFRh/UszfPVKKroq1QAKiNquy4pybhgj_l.wWTgrzPpPoae0</t>
-  </si>
-  <si>
     <t>Visionworks, Inc.</t>
   </si>
   <si>
@@ -1255,21 +1255,27 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owlW/CYo8uyV1lqLUe_XJLwXgKKbMGcUSOnm2YuFWlCcEjao</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe1/_JzvIyNP00OZFCdiwLq50NqX4Pv5uhASRmnOON4x7JM</t>
+  </si>
+  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owfY/PmJV_yGxFZQyYhZo1Z3JUNNKeymCbhxmj4tTRLPEQdQ</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe6/AOd4ALEemb0aAShUt5dhhnJlPDFohiL8zcc9JttELyY</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owe1/_JzvIyNP00OZFCdiwLq50NqX4Pv5uhASRmnOON4x7JM</t>
-  </si>
-  <si>
     <t>GUESS Distribution Center</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owbq/UyrAEX7r.ENTpYJbgJLT8Cg7CPlnvxwl2yKnTp7J72s</t>
   </si>
   <si>
+    <t>Glidewell Laboratories-Crown World Dental Lab</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc5/NegKIAQd.3f3pmcw73INUcvkRVIbZTkujR6EIS0ot58</t>
+  </si>
+  <si>
     <t>Bedding Acquisition LLC-Hollander Sleep Products</t>
   </si>
   <si>
@@ -1282,12 +1288,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owce/l.sHHNbu0GPlyDLBohqkTc6rmr3iMKC.C7bGdM4pAc0</t>
   </si>
   <si>
-    <t>Glidewell Laboratories-Crown World Dental Lab</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owc5/NegKIAQd.3f3pmcw73INUcvkRVIbZTkujR6EIS0ot58</t>
-  </si>
-  <si>
     <t>Vitro Automotive/Pittsburgh Glass Works</t>
   </si>
   <si>
@@ -1324,6 +1324,33 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owYS/48f5c5_B5wyiPJ9Uy_H1cNlwWBdNMLD_pYAS8WUMQM8</t>
   </si>
   <si>
+    <t>HOOTERS of America LLC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVx/qvIScRk9GM5Elj.GBDk.q4vXbyNWeEoZlek.EdFKUGs</t>
+  </si>
+  <si>
+    <t>Communicare Professional Counselling and Treatment Service</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW2/m6.18mqxu4V91wnL7oO6sVnlaLN8Ty2M97cFVaRMbUI</t>
+  </si>
+  <si>
+    <t>Communicare Services - Bardstown</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW7/vxvDkskTDW8u8rCe_lHYjJe3ywqVHolgywHu7LkriIg</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Communicare Services - Springfield</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWC/G1vvtarZYPJdOhvrIz1yR8EPnXsOq0_BH2dWoGiRDP4</t>
+  </si>
+  <si>
     <t>Breckinridge</t>
   </si>
   <si>
@@ -1336,97 +1363,73 @@
     <t>Marion</t>
   </si>
   <si>
+    <t>Communicare Clinic - Lebanon</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWW/6KnRleJzURSaBY_6FARK03ypKCpBzXNzxwnFAWGUcwk</t>
+  </si>
+  <si>
+    <t>Communicare Services - Lebanon</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWg/9p9FS.JQp0PTPMhD3HxrAxxsoxTEr_upxaagBfFMogM</t>
+  </si>
+  <si>
+    <t>Communicare Clinic - Radcliff</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWl/rS8vJCQrLNj0CL7FyoK6cd2Ubo0vr1icry6WlMYbX7U</t>
+  </si>
+  <si>
+    <t>Communicare Services - Radcliff</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWq/Vfpl8UYl0gbX_iFIJoUfIBUwxuS8TiJTC_7F4sKJFYw</t>
+  </si>
+  <si>
+    <t>Communicare Services - Leitchfield</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX5/hqgTkrEKeD2diZgwtvYubxlNzxik77T983Z_rFk92oU</t>
+  </si>
+  <si>
     <t>Hendrickson Trailer Commercial Vehicle Systems</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX0/V6hwrqZ0Qlr_eFlMYEYrZXlE5AKDheKuIEjfBsUaPdQ</t>
   </si>
   <si>
-    <t>Communicare Clinic - Radcliff</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWl/rS8vJCQrLNj0CL7FyoK6cd2Ubo0vr1icry6WlMYbX7U</t>
-  </si>
-  <si>
-    <t>HOOTERS of America LLC</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVx/qvIScRk9GM5Elj.GBDk.q4vXbyNWeEoZlek.EdFKUGs</t>
-  </si>
-  <si>
-    <t>Communicare Services - Bardstown</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW7/vxvDkskTDW8u8rCe_lHYjJe3ywqVHolgywHu7LkriIg</t>
-  </si>
-  <si>
-    <t>Washington</t>
-  </si>
-  <si>
-    <t>Communicare Services - Springfield</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWC/G1vvtarZYPJdOhvrIz1yR8EPnXsOq0_BH2dWoGiRDP4</t>
-  </si>
-  <si>
-    <t>Communicare Clinic - Lebanon</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWW/6KnRleJzURSaBY_6FARK03ypKCpBzXNzxwnFAWGUcwk</t>
-  </si>
-  <si>
-    <t>Communicare Services - Lebanon</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWg/9p9FS.JQp0PTPMhD3HxrAxxsoxTEr_upxaagBfFMogM</t>
-  </si>
-  <si>
-    <t>Communicare Services - Radcliff</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owWq/Vfpl8UYl0gbX_iFIJoUfIBUwxuS8TiJTC_7F4sKJFYw</t>
-  </si>
-  <si>
-    <t>Communicare Services - Leitchfield</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owX5/hqgTkrEKeD2diZgwtvYubxlNzxik77T983Z_rFk92oU</t>
-  </si>
-  <si>
     <t>Communicare  Services - Brandenburg</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owXA/mAUPSS8QJjeTFI7E27u8VQgWHFFi6LRZfcfzfkHq1Jo</t>
   </si>
   <si>
-    <t>Communicare Professional Counselling and Treatment Service</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owW2/m6.18mqxu4V91wnL7oO6sVnlaLN8Ty2M97cFVaRMbUI</t>
-  </si>
-  <si>
     <t>Jackson Warewashing Systems</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVY/2COXMu6Bd1MCYgNNs.Sc62L0asFJOG..KVsIGQuqD5g</t>
   </si>
   <si>
+    <t>Huhtamaki, Inc.</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUa/gQ7KCmO7r.5JxftEeBG61Dp0YG0btnF0QmbfOv3Jqwg</t>
+  </si>
+  <si>
+    <t>SCHULTE COMPANIES</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVT/U2oN7sbm_kSzNb7xiYNnrUVaoC_094PGtzzEyvZMQHo</t>
+  </si>
+  <si>
     <t>IHG Army Hotels &amp; Holiday Inn Express</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVi/IMPz0uy5.8DXS8aWGuSQX3cPDNWc6wEkkwZwPlw6wyc</t>
   </si>
   <si>
-    <t>Huhtamaki, Inc.</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUa/gQ7KCmO7r.5JxftEeBG61Dp0YG0btnF0QmbfOv3Jqwg</t>
-  </si>
-  <si>
-    <t>SCHULTE COMPANIES</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVT/U2oN7sbm_kSzNb7xiYNnrUVaoC_094PGtzzEyvZMQHo</t>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUQ/kIkf6vaRVWxJL33J4laXNMoRoo4Ps.CEaVYB4.M3PIU</t>
   </si>
   <si>
     <t>Crowne Plaza Hotel</t>
@@ -1435,15 +1438,45 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owU1/cmWTeASpvF33aHX13OmKNTSglY1CKyn1mH.iVuE4fs0</t>
   </si>
   <si>
+    <t>Cinemark Holdings,Inc.-Cinemark Movies 10</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owQQ/GkNpTgbS1O.ynAUO2lRhhohP0a9SFLAzTXhbo.1Jdyw</t>
+  </si>
+  <si>
+    <t>Paper Source</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owQu/m2vDq7l1wLeK_e1Ptqh35ndxEEbdElyIHgPfZOFdJUc</t>
+  </si>
+  <si>
     <t>Embassy Suites Jefferson Co - Louisville</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owTw/ZCaGJxEMniVjvqFnhoI_lXZxfMOTDOnfnNr.YyZ_aFs</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUB/Q4XhuwPlCqUiegEdy255dEODFtbl._noeWqruyQLy9c</t>
+  </si>
+  <si>
+    <t>ALJSCO</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUL/QiUorU3I0MCyonZFb9WQqn78BNq1UIJjwP_tw34J1Sw</t>
+  </si>
+  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVE/C0OZ4Bz9aNkrc9YrcMiSzi1G1WqI2.arpnDnUUJqUr8</t>
   </si>
   <si>
+    <t>Muhlenberg</t>
+  </si>
+  <si>
+    <t>THE MUHLENBERG COUNTY COAL COMPANY</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVJ/Dg9.VOc4xZE0CzOT2WBULH9AF2F_W3myXxa4ijm196A</t>
+  </si>
+  <si>
     <t>Bourbon</t>
   </si>
   <si>
@@ -1453,39 +1486,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVO/fRo8DiZxbz2baMUvWanGYLiXkNdGw2BDb3YAGYVqjWI</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUQ/kIkf6vaRVWxJL33J4laXNMoRoo4Ps.CEaVYB4.M3PIU</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUB/Q4XhuwPlCqUiegEdy255dEODFtbl._noeWqruyQLy9c</t>
-  </si>
-  <si>
-    <t>Paper Source</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owQu/m2vDq7l1wLeK_e1Ptqh35ndxEEbdElyIHgPfZOFdJUc</t>
-  </si>
-  <si>
-    <t>Muhlenberg</t>
-  </si>
-  <si>
-    <t>THE MUHLENBERG COUNTY COAL COMPANY</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owVJ/Dg9.VOc4xZE0CzOT2WBULH9AF2F_W3myXxa4ijm196A</t>
-  </si>
-  <si>
-    <t>Cinemark Holdings,Inc.-Cinemark Movies 10</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owQQ/GkNpTgbS1O.ynAUO2lRhhohP0a9SFLAzTXhbo.1Jdyw</t>
-  </si>
-  <si>
-    <t>ALJSCO</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owUL/QiUorU3I0MCyonZFb9WQqn78BNq1UIJjwP_tw34J1Sw</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/t0000000owPN/jDHwTapPX.yBsZhb3qC7qy.geYOtPuuz3LjGauQ08h8</t>
   </si>
   <si>
@@ -2072,6 +2072,12 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y0000044AjY/AIrRiUx57cQN91Gt3GEskluAye9VTB5lmjzmRGMobI4</t>
+  </si>
+  <si>
+    <t>Wolverine Worldwide 502</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005Lkhh/16ZxfoY4UYNVp8NSCL2i.Im.Q7k0xxjpNn_725NxzFQ</t>
   </si>
   <si>
     <t>Computer World Services, Corp (CWS)</t>
@@ -2737,7 +2743,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
@@ -2790,31 +2796,31 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
-        <v>45320</v>
+        <v>45348</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="D2" s="55" t="s">
         <v>674</v>
       </c>
       <c r="E2" s="55">
-        <v>561611</v>
+        <v>316200</v>
       </c>
       <c r="F2" s="55">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="G2" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="54">
-        <v>45380</v>
+        <v>45415</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J2" s="53" t="s">
         <v>675</v>
@@ -2826,28 +2832,28 @@
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
-        <v>45315</v>
+        <v>45320</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D3" s="55" t="s">
         <v>676</v>
       </c>
       <c r="E3" s="55">
-        <v>611511</v>
+        <v>561611</v>
       </c>
       <c r="F3" s="55">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="G3" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="54">
-        <v>45315</v>
+        <v>45380</v>
       </c>
       <c r="I3" s="55" t="s">
         <v>13</v>
@@ -2856,13 +2862,13 @@
         <v>677</v>
       </c>
       <c r="K3" s="57" t="str">
-        <f t="shared" ref="K3:K14" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <f t="shared" ref="K3:K15" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
         <v>WARN</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54">
-        <v>45302</v>
+        <v>45315</v>
       </c>
       <c r="B4" s="55" t="s">
         <v>29</v>
@@ -2874,16 +2880,16 @@
         <v>678</v>
       </c>
       <c r="E4" s="55">
-        <v>336110</v>
+        <v>611511</v>
       </c>
       <c r="F4" s="55">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="G4" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="54">
-        <v>45365</v>
+        <v>45315</v>
       </c>
       <c r="I4" s="55" t="s">
         <v>13</v>
@@ -2898,28 +2904,28 @@
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54">
-        <v>45301</v>
+        <v>45302</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D5" s="55" t="s">
         <v>680</v>
       </c>
       <c r="E5" s="55">
-        <v>336350</v>
+        <v>336110</v>
       </c>
       <c r="F5" s="55">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H5" s="54">
-        <v>45401</v>
+        <v>45365</v>
       </c>
       <c r="I5" s="55" t="s">
         <v>13</v>
@@ -2934,28 +2940,28 @@
     </row>
     <row r="6" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54">
-        <v>45299</v>
+        <v>45301</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D6" s="55" t="s">
         <v>682</v>
       </c>
       <c r="E6" s="55">
-        <v>561720</v>
+        <v>336350</v>
       </c>
       <c r="F6" s="55">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G6" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="54">
-        <v>45299</v>
+        <v>45401</v>
       </c>
       <c r="I6" s="55" t="s">
         <v>13</v>
@@ -2979,13 +2985,13 @@
         <v>238</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E7" s="55">
         <v>561720</v>
       </c>
       <c r="F7" s="55">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G7" s="55" t="s">
         <v>16</v>
@@ -2997,7 +3003,7 @@
         <v>13</v>
       </c>
       <c r="J7" s="53" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="K7" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3015,13 +3021,13 @@
         <v>238</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E8" s="55">
         <v>561720</v>
       </c>
       <c r="F8" s="55">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="55" t="s">
         <v>16</v>
@@ -3033,7 +3039,7 @@
         <v>13</v>
       </c>
       <c r="J8" s="53" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K8" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3051,13 +3057,13 @@
         <v>238</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E9" s="55">
         <v>561720</v>
       </c>
       <c r="F9" s="55">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="G9" s="55" t="s">
         <v>16</v>
@@ -3069,7 +3075,7 @@
         <v>13</v>
       </c>
       <c r="J9" s="53" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K9" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3078,34 +3084,34 @@
     </row>
     <row r="10" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E10" s="55">
-        <v>331400</v>
+        <v>561720</v>
       </c>
       <c r="F10" s="55">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G10" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H10" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="I10" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>10</v>
+        <v>688</v>
       </c>
       <c r="K10" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3117,31 +3123,31 @@
         <v>45295</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="E11" s="55">
-        <v>561720</v>
+        <v>331400</v>
       </c>
       <c r="F11" s="55">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G11" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H11" s="54">
-        <v>45356</v>
+        <v>45295</v>
       </c>
       <c r="I11" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>688</v>
+        <v>10</v>
       </c>
       <c r="K11" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3153,19 +3159,19 @@
         <v>45295</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E12" s="55">
         <v>561720</v>
       </c>
       <c r="F12" s="55">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G12" s="55" t="s">
         <v>16</v>
@@ -3177,7 +3183,7 @@
         <v>13</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K12" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3189,13 +3195,13 @@
         <v>45295</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E13" s="55">
         <v>561720</v>
@@ -3213,7 +3219,7 @@
         <v>13</v>
       </c>
       <c r="J13" s="53" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K13" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3222,28 +3228,28 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="54">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="E14" s="55">
-        <v>541714</v>
+        <v>561720</v>
       </c>
       <c r="F14" s="55">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G14" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H14" s="54">
-        <v>45351</v>
+        <v>45356</v>
       </c>
       <c r="I14" s="55" t="s">
         <v>13</v>
@@ -3252,6 +3258,42 @@
         <v>692</v>
       </c>
       <c r="K14" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="54">
+        <v>45293</v>
+      </c>
+      <c r="B15" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>693</v>
+      </c>
+      <c r="E15" s="55">
+        <v>541714</v>
+      </c>
+      <c r="F15" s="55">
+        <v>136</v>
+      </c>
+      <c r="G15" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="54">
+        <v>45351</v>
+      </c>
+      <c r="I15" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="53" t="s">
+        <v>694</v>
+      </c>
+      <c r="K15" s="57" t="str">
         <f t="shared" si="0"/>
         <v>WARN</v>
       </c>
@@ -6261,7 +6303,7 @@
         <v>258</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E21" s="55">
         <v>332613</v>
@@ -6569,25 +6611,25 @@
         <v>44097</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="D7" s="55" t="s">
         <v>285</v>
       </c>
       <c r="E7" s="55">
-        <v>325211</v>
+        <v>721110</v>
       </c>
       <c r="F7" s="55">
-        <v>164</v>
+        <v>294</v>
       </c>
       <c r="G7" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="54">
-        <v>43973</v>
+        <v>43907</v>
       </c>
       <c r="I7" s="55" t="s">
         <v>13</v>
@@ -6605,25 +6647,25 @@
         <v>44097</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="D8" s="55" t="s">
         <v>287</v>
       </c>
       <c r="E8" s="55">
-        <v>721110</v>
+        <v>325211</v>
       </c>
       <c r="F8" s="55">
-        <v>294</v>
+        <v>164</v>
       </c>
       <c r="G8" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="54">
-        <v>43907</v>
+        <v>43973</v>
       </c>
       <c r="I8" s="55" t="s">
         <v>13</v>
@@ -6749,10 +6791,10 @@
         <v>44092</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D12" s="55" t="s">
         <v>295</v>
@@ -6785,10 +6827,10 @@
         <v>44092</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D13" s="55" t="s">
         <v>295</v>
@@ -6965,25 +7007,25 @@
         <v>44050</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D18" s="55" t="s">
         <v>306</v>
       </c>
       <c r="E18" s="55">
-        <v>72251</v>
+        <v>3221</v>
       </c>
       <c r="F18" s="55">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G18" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H18" s="54">
-        <v>43926</v>
+        <v>44104</v>
       </c>
       <c r="I18" s="55" t="s">
         <v>13</v>
@@ -7001,25 +7043,25 @@
         <v>44050</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D19" s="55" t="s">
         <v>308</v>
       </c>
       <c r="E19" s="55">
-        <v>3221</v>
+        <v>72251</v>
       </c>
       <c r="F19" s="55">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G19" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H19" s="54">
-        <v>44104</v>
+        <v>43926</v>
       </c>
       <c r="I19" s="55" t="s">
         <v>13</v>
@@ -7181,10 +7223,10 @@
         <v>44035</v>
       </c>
       <c r="B24" s="55" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="D24" s="55" t="s">
         <v>318</v>
@@ -7193,7 +7235,7 @@
         <v>213113</v>
       </c>
       <c r="F24" s="55">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="G24" s="55" t="s">
         <v>11</v>
@@ -7202,7 +7244,7 @@
         <v>44094</v>
       </c>
       <c r="I24" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J24" s="53" t="s">
         <v>319</v>
@@ -7229,16 +7271,16 @@
         <v>213113</v>
       </c>
       <c r="F25" s="55">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G25" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H25" s="54">
-        <v>44094</v>
+        <v>44098</v>
       </c>
       <c r="I25" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="53" t="s">
         <v>321</v>
@@ -7253,10 +7295,10 @@
         <v>44035</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D26" s="55" t="s">
         <v>322</v>
@@ -7265,13 +7307,13 @@
         <v>213113</v>
       </c>
       <c r="F26" s="55">
-        <v>5</v>
+        <v>194</v>
       </c>
       <c r="G26" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H26" s="54">
-        <v>44098</v>
+        <v>44094</v>
       </c>
       <c r="I26" s="55" t="s">
         <v>13</v>
@@ -7865,28 +7907,28 @@
         <v>43973</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="D43" s="55" t="s">
         <v>359</v>
       </c>
       <c r="E43" s="55">
-        <v>332613</v>
+        <v>721110</v>
       </c>
       <c r="F43" s="55">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="G43" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H43" s="54">
-        <v>44104</v>
+        <v>43979</v>
       </c>
       <c r="I43" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J43" s="53" t="s">
         <v>360</v>
@@ -7901,28 +7943,28 @@
         <v>43973</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="D44" s="55" t="s">
         <v>361</v>
       </c>
       <c r="E44" s="55">
-        <v>721110</v>
+        <v>332613</v>
       </c>
       <c r="F44" s="55">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="G44" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H44" s="54">
-        <v>43979</v>
+        <v>44104</v>
       </c>
       <c r="I44" s="55" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J44" s="53" t="s">
         <v>362</v>
@@ -8189,25 +8231,25 @@
         <v>43948</v>
       </c>
       <c r="B52" s="55" t="s">
-        <v>40</v>
+        <v>332</v>
       </c>
       <c r="C52" s="55" t="s">
-        <v>226</v>
+        <v>333</v>
       </c>
       <c r="D52" s="55" t="s">
         <v>376</v>
       </c>
       <c r="E52" s="55">
-        <v>423110</v>
+        <v>722511</v>
       </c>
       <c r="F52" s="55">
-        <v>50</v>
+        <v>1134</v>
       </c>
       <c r="G52" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H52" s="54">
-        <v>43948</v>
+        <v>43905</v>
       </c>
       <c r="I52" s="55" t="s">
         <v>13</v>
@@ -8225,22 +8267,22 @@
         <v>43948</v>
       </c>
       <c r="B53" s="55" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C53" s="55" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D53" s="55" t="s">
         <v>378</v>
       </c>
       <c r="E53" s="55">
-        <v>336390</v>
+        <v>423110</v>
       </c>
       <c r="F53" s="55">
-        <v>179</v>
+        <v>50</v>
       </c>
       <c r="G53" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H53" s="54">
         <v>43948</v>
@@ -8261,25 +8303,25 @@
         <v>43948</v>
       </c>
       <c r="B54" s="55" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C54" s="55" t="s">
-        <v>367</v>
+        <v>236</v>
       </c>
       <c r="D54" s="55" t="s">
         <v>380</v>
       </c>
       <c r="E54" s="55">
-        <v>322121</v>
+        <v>336390</v>
       </c>
       <c r="F54" s="55">
-        <v>398</v>
+        <v>179</v>
       </c>
       <c r="G54" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H54" s="54">
-        <v>43955</v>
+        <v>43948</v>
       </c>
       <c r="I54" s="55" t="s">
         <v>13</v>
@@ -8297,25 +8339,25 @@
         <v>43948</v>
       </c>
       <c r="B55" s="55" t="s">
-        <v>332</v>
+        <v>47</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>333</v>
+        <v>367</v>
       </c>
       <c r="D55" s="55" t="s">
         <v>382</v>
       </c>
       <c r="E55" s="55">
-        <v>722511</v>
+        <v>322121</v>
       </c>
       <c r="F55" s="55">
-        <v>1134</v>
+        <v>398</v>
       </c>
       <c r="G55" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H55" s="54">
-        <v>43905</v>
+        <v>43955</v>
       </c>
       <c r="I55" s="55" t="s">
         <v>13</v>
@@ -8333,25 +8375,25 @@
         <v>43945</v>
       </c>
       <c r="B56" s="55" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C56" s="55" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="D56" s="55" t="s">
         <v>384</v>
       </c>
       <c r="E56" s="55">
-        <v>423210</v>
+        <v>532111</v>
       </c>
       <c r="F56" s="55">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="G56" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H56" s="54">
-        <v>43935</v>
+        <v>43910</v>
       </c>
       <c r="I56" s="55" t="s">
         <v>13</v>
@@ -8369,10 +8411,10 @@
         <v>43945</v>
       </c>
       <c r="B57" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>226</v>
+        <v>128</v>
       </c>
       <c r="D57" s="55" t="s">
         <v>386</v>
@@ -8381,7 +8423,7 @@
         <v>532111</v>
       </c>
       <c r="F57" s="55">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G57" s="55" t="s">
         <v>16</v>
@@ -8411,25 +8453,25 @@
         <v>128</v>
       </c>
       <c r="D58" s="55" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E58" s="55">
         <v>532111</v>
       </c>
       <c r="F58" s="55">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="G58" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H58" s="54">
-        <v>43910</v>
+        <v>43951</v>
       </c>
       <c r="I58" s="55" t="s">
         <v>13</v>
       </c>
       <c r="J58" s="53" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K58" s="57" t="str">
         <f t="shared" si="0"/>
@@ -8441,25 +8483,25 @@
         <v>43945</v>
       </c>
       <c r="B59" s="55" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>128</v>
+        <v>257</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E59" s="55">
-        <v>532111</v>
+        <v>423210</v>
       </c>
       <c r="F59" s="55">
-        <v>104</v>
+        <v>210</v>
       </c>
       <c r="G59" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H59" s="54">
-        <v>43951</v>
+        <v>43935</v>
       </c>
       <c r="I59" s="55" t="s">
         <v>13</v>
@@ -8657,19 +8699,19 @@
         <v>43936</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C65" s="55" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D65" s="55" t="s">
-        <v>133</v>
+        <v>349</v>
       </c>
       <c r="E65" s="55">
-        <v>337215</v>
+        <v>488190</v>
       </c>
       <c r="F65" s="55">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="G65" s="55" t="s">
         <v>16</v>
@@ -8696,16 +8738,16 @@
         <v>40</v>
       </c>
       <c r="C66" s="55" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D66" s="55" t="s">
         <v>133</v>
       </c>
       <c r="E66" s="55">
-        <v>33791</v>
+        <v>337215</v>
       </c>
       <c r="F66" s="55">
-        <v>271</v>
+        <v>151</v>
       </c>
       <c r="G66" s="55" t="s">
         <v>16</v>
@@ -8729,19 +8771,19 @@
         <v>43936</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D67" s="55" t="s">
-        <v>349</v>
+        <v>133</v>
       </c>
       <c r="E67" s="55">
-        <v>488190</v>
+        <v>33791</v>
       </c>
       <c r="F67" s="55">
-        <v>17</v>
+        <v>271</v>
       </c>
       <c r="G67" s="55" t="s">
         <v>16</v>
@@ -8810,19 +8852,19 @@
         <v>406</v>
       </c>
       <c r="E69" s="55">
-        <v>337910</v>
+        <v>339116</v>
       </c>
       <c r="F69" s="55">
-        <v>234</v>
+        <v>151</v>
       </c>
       <c r="G69" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H69" s="54">
-        <v>43924</v>
+        <v>43917</v>
       </c>
       <c r="I69" s="55" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J69" s="53" t="s">
         <v>407</v>
@@ -8837,25 +8879,25 @@
         <v>43935</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C70" s="55" t="s">
-        <v>267</v>
+        <v>128</v>
       </c>
       <c r="D70" s="55" t="s">
         <v>408</v>
       </c>
       <c r="E70" s="55">
-        <v>712130</v>
+        <v>337910</v>
       </c>
       <c r="F70" s="55">
-        <v>88</v>
+        <v>234</v>
       </c>
       <c r="G70" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H70" s="54">
-        <v>43941</v>
+        <v>43924</v>
       </c>
       <c r="I70" s="55" t="s">
         <v>13</v>
@@ -8873,28 +8915,28 @@
         <v>43935</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C71" s="55" t="s">
-        <v>128</v>
+        <v>267</v>
       </c>
       <c r="D71" s="55" t="s">
         <v>410</v>
       </c>
       <c r="E71" s="55">
-        <v>339116</v>
+        <v>712130</v>
       </c>
       <c r="F71" s="55">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="G71" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H71" s="54">
-        <v>43917</v>
+        <v>43941</v>
       </c>
       <c r="I71" s="55" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J71" s="53" t="s">
         <v>411</v>
@@ -9125,31 +9167,31 @@
         <v>43927</v>
       </c>
       <c r="B78" s="55" t="s">
-        <v>70</v>
+        <v>332</v>
       </c>
       <c r="C78" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="D78" s="55" t="s">
         <v>424</v>
       </c>
-      <c r="D78" s="55" t="s">
+      <c r="E78" s="55">
+        <v>722511</v>
+      </c>
+      <c r="F78" s="55">
+        <v>293</v>
+      </c>
+      <c r="G78" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="54">
+        <v>43906</v>
+      </c>
+      <c r="I78" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="53" t="s">
         <v>425</v>
-      </c>
-      <c r="E78" s="55">
-        <v>623110</v>
-      </c>
-      <c r="F78" s="55">
-        <v>14</v>
-      </c>
-      <c r="G78" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H78" s="54">
-        <v>43910</v>
-      </c>
-      <c r="I78" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="53" t="s">
-        <v>426</v>
       </c>
       <c r="K78" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9164,28 +9206,28 @@
         <v>70</v>
       </c>
       <c r="C79" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D79" s="55" t="s">
+        <v>426</v>
+      </c>
+      <c r="E79" s="55">
+        <v>623110</v>
+      </c>
+      <c r="F79" s="55">
+        <v>63</v>
+      </c>
+      <c r="G79" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" s="54">
+        <v>43910</v>
+      </c>
+      <c r="I79" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="53" t="s">
         <v>427</v>
-      </c>
-      <c r="D79" s="55" t="s">
-        <v>428</v>
-      </c>
-      <c r="E79" s="55">
-        <v>423110</v>
-      </c>
-      <c r="F79" s="55">
-        <v>117</v>
-      </c>
-      <c r="G79" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H79" s="54">
-        <v>43934</v>
-      </c>
-      <c r="I79" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="53" t="s">
-        <v>429</v>
       </c>
       <c r="K79" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9200,16 +9242,16 @@
         <v>70</v>
       </c>
       <c r="C80" s="55" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D80" s="55" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E80" s="55">
         <v>623110</v>
       </c>
       <c r="F80" s="55">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G80" s="55" t="s">
         <v>16</v>
@@ -9221,7 +9263,7 @@
         <v>13</v>
       </c>
       <c r="J80" s="53" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K80" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9233,31 +9275,31 @@
         <v>43927</v>
       </c>
       <c r="B81" s="55" t="s">
-        <v>332</v>
+        <v>70</v>
       </c>
       <c r="C81" s="55" t="s">
-        <v>333</v>
+        <v>430</v>
       </c>
       <c r="D81" s="55" t="s">
+        <v>431</v>
+      </c>
+      <c r="E81" s="55">
+        <v>623110</v>
+      </c>
+      <c r="F81" s="55">
+        <v>16</v>
+      </c>
+      <c r="G81" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="54">
+        <v>43910</v>
+      </c>
+      <c r="I81" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="53" t="s">
         <v>432</v>
-      </c>
-      <c r="E81" s="55">
-        <v>722511</v>
-      </c>
-      <c r="F81" s="55">
-        <v>293</v>
-      </c>
-      <c r="G81" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H81" s="54">
-        <v>43906</v>
-      </c>
-      <c r="I81" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="53" t="s">
-        <v>433</v>
       </c>
       <c r="K81" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9272,7 +9314,7 @@
         <v>70</v>
       </c>
       <c r="C82" s="55" t="s">
-        <v>264</v>
+        <v>433</v>
       </c>
       <c r="D82" s="55" t="s">
         <v>434</v>
@@ -9281,7 +9323,7 @@
         <v>623110</v>
       </c>
       <c r="F82" s="55">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G82" s="55" t="s">
         <v>16</v>
@@ -9344,7 +9386,7 @@
         <v>70</v>
       </c>
       <c r="C84" s="55" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D84" s="55" t="s">
         <v>439</v>
@@ -9380,7 +9422,7 @@
         <v>70</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>427</v>
+        <v>273</v>
       </c>
       <c r="D85" s="55" t="s">
         <v>441</v>
@@ -9389,7 +9431,7 @@
         <v>623110</v>
       </c>
       <c r="F85" s="55">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G85" s="55" t="s">
         <v>16</v>
@@ -9488,22 +9530,22 @@
         <v>70</v>
       </c>
       <c r="C88" s="55" t="s">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="D88" s="55" t="s">
         <v>447</v>
       </c>
       <c r="E88" s="55">
-        <v>623110</v>
+        <v>423110</v>
       </c>
       <c r="F88" s="55">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="G88" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H88" s="54">
-        <v>43910</v>
+        <v>43934</v>
       </c>
       <c r="I88" s="55" t="s">
         <v>13</v>
@@ -9533,7 +9575,7 @@
         <v>623110</v>
       </c>
       <c r="F89" s="55">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="G89" s="55" t="s">
         <v>16</v>
@@ -9593,25 +9635,25 @@
         <v>43923</v>
       </c>
       <c r="B91" s="55" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D91" s="55" t="s">
         <v>453</v>
       </c>
       <c r="E91" s="55">
-        <v>721110</v>
+        <v>333999</v>
       </c>
       <c r="F91" s="55">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="G91" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H91" s="54">
-        <v>43910</v>
+        <v>43926</v>
       </c>
       <c r="I91" s="55" t="s">
         <v>13</v>
@@ -9629,25 +9671,25 @@
         <v>43923</v>
       </c>
       <c r="B92" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>258</v>
+        <v>128</v>
       </c>
       <c r="D92" s="55" t="s">
         <v>455</v>
       </c>
       <c r="E92" s="55">
-        <v>333999</v>
+        <v>721110</v>
       </c>
       <c r="F92" s="55">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G92" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H92" s="54">
-        <v>43926</v>
+        <v>43906</v>
       </c>
       <c r="I92" s="55" t="s">
         <v>13</v>
@@ -9665,10 +9707,10 @@
         <v>43923</v>
       </c>
       <c r="B93" s="55" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C93" s="55" t="s">
-        <v>128</v>
+        <v>273</v>
       </c>
       <c r="D93" s="55" t="s">
         <v>457</v>
@@ -9677,13 +9719,13 @@
         <v>721110</v>
       </c>
       <c r="F93" s="55">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="G93" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H93" s="54">
-        <v>43906</v>
+        <v>43910</v>
       </c>
       <c r="I93" s="55" t="s">
         <v>13</v>
@@ -9707,13 +9749,13 @@
         <v>128</v>
       </c>
       <c r="D94" s="55" t="s">
-        <v>459</v>
+        <v>298</v>
       </c>
       <c r="E94" s="55">
         <v>721110</v>
       </c>
       <c r="F94" s="55">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="G94" s="55" t="s">
         <v>16</v>
@@ -9725,7 +9767,7 @@
         <v>13</v>
       </c>
       <c r="J94" s="53" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K94" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9743,13 +9785,13 @@
         <v>128</v>
       </c>
       <c r="D95" s="55" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E95" s="55">
         <v>721110</v>
       </c>
       <c r="F95" s="55">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="G95" s="55" t="s">
         <v>16</v>
@@ -9761,7 +9803,7 @@
         <v>13</v>
       </c>
       <c r="J95" s="53" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K95" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9773,25 +9815,25 @@
         <v>43922</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C96" s="55" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>201</v>
+        <v>462</v>
       </c>
       <c r="E96" s="55">
-        <v>21211</v>
+        <v>512131</v>
       </c>
       <c r="F96" s="55">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G96" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H96" s="54">
-        <v>43984</v>
+        <v>43916</v>
       </c>
       <c r="I96" s="55" t="s">
         <v>13</v>
@@ -9809,31 +9851,31 @@
         <v>43922</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="C97" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D97" s="55" t="s">
         <v>464</v>
       </c>
-      <c r="D97" s="55" t="s">
+      <c r="E97" s="55">
+        <v>424110</v>
+      </c>
+      <c r="F97" s="55">
+        <v>10</v>
+      </c>
+      <c r="G97" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="H97" s="54">
+        <v>43919</v>
+      </c>
+      <c r="I97" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J97" s="53" t="s">
         <v>465</v>
-      </c>
-      <c r="E97" s="55">
-        <v>423520</v>
-      </c>
-      <c r="F97" s="55">
-        <v>11</v>
-      </c>
-      <c r="G97" s="55" t="s">
-        <v>11</v>
-      </c>
-      <c r="H97" s="54">
-        <v>43984</v>
-      </c>
-      <c r="I97" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J97" s="53" t="s">
-        <v>466</v>
       </c>
       <c r="K97" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9851,13 +9893,13 @@
         <v>128</v>
       </c>
       <c r="D98" s="55" t="s">
-        <v>298</v>
+        <v>466</v>
       </c>
       <c r="E98" s="55">
         <v>721110</v>
       </c>
       <c r="F98" s="55">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="G98" s="55" t="s">
         <v>16</v>
@@ -9926,16 +9968,16 @@
         <v>469</v>
       </c>
       <c r="E100" s="55">
-        <v>424110</v>
+        <v>541611</v>
       </c>
       <c r="F100" s="55">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G100" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H100" s="54">
-        <v>43919</v>
+        <v>43920</v>
       </c>
       <c r="I100" s="55" t="s">
         <v>13</v>
@@ -9953,22 +9995,22 @@
         <v>43922</v>
       </c>
       <c r="B101" s="55" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C101" s="55" t="s">
-        <v>471</v>
+        <v>227</v>
       </c>
       <c r="D101" s="55" t="s">
-        <v>472</v>
+        <v>201</v>
       </c>
       <c r="E101" s="55">
         <v>21211</v>
       </c>
       <c r="F101" s="55">
-        <v>254</v>
+        <v>42</v>
       </c>
       <c r="G101" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H101" s="54">
         <v>43984</v>
@@ -9977,7 +10019,7 @@
         <v>13</v>
       </c>
       <c r="J101" s="53" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K101" s="57" t="str">
         <f t="shared" si="1"/>
@@ -9989,31 +10031,31 @@
         <v>43922</v>
       </c>
       <c r="B102" s="55" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C102" s="55" t="s">
+        <v>472</v>
+      </c>
+      <c r="D102" s="55" t="s">
+        <v>473</v>
+      </c>
+      <c r="E102" s="55">
+        <v>21211</v>
+      </c>
+      <c r="F102" s="55">
         <v>254</v>
       </c>
-      <c r="D102" s="55" t="s">
+      <c r="G102" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" s="54">
+        <v>43984</v>
+      </c>
+      <c r="I102" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="53" t="s">
         <v>474</v>
-      </c>
-      <c r="E102" s="55">
-        <v>512131</v>
-      </c>
-      <c r="F102" s="55">
-        <v>28</v>
-      </c>
-      <c r="G102" s="55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H102" s="54">
-        <v>43916</v>
-      </c>
-      <c r="I102" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="53" t="s">
-        <v>475</v>
       </c>
       <c r="K102" s="57" t="str">
         <f t="shared" si="1"/>
@@ -10025,25 +10067,25 @@
         <v>43922</v>
       </c>
       <c r="B103" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C103" s="55" t="s">
-        <v>128</v>
+        <v>475</v>
       </c>
       <c r="D103" s="55" t="s">
         <v>476</v>
       </c>
       <c r="E103" s="55">
-        <v>541611</v>
+        <v>423520</v>
       </c>
       <c r="F103" s="55">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G103" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H103" s="54">
-        <v>43920</v>
+        <v>43984</v>
       </c>
       <c r="I103" s="55" t="s">
         <v>13</v>
@@ -14725,6 +14767,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0C1C9366252B4C838708442C71C5AA" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="623745db76138c409ead4834ced54ea8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="62511544-38af-49c2-8996-37c0f6a636fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c1a1049adbb8cd97fc988c6af4986c32" ns2:_="">
     <xsd:import namespace="62511544-38af-49c2-8996-37c0f6a636fd"/>
@@ -14864,26 +14915,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C14CA432-9072-454B-AF4E-ADB605838576}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4F545EA-D03E-4930-8341-636201EC819E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEB26DE-B3FC-45A8-BF93-B326AF5FAB7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -14896,12 +14946,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDF24993-6373-4854-833F-D2128C061150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3103A16C-16CE-4B25-AC65-A1F08B1BF9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="1830" windowWidth="15180" windowHeight="8970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2024" sheetId="8" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="697">
   <si>
     <t>Date Received</t>
   </si>
@@ -2072,6 +2072,12 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y0000044AjY/AIrRiUx57cQN91Gt3GEskluAye9VTB5lmjzmRGMobI4</t>
+  </si>
+  <si>
+    <t>Guess? Inc</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005NnQa/qEmJQv7aNct3EcgWUyr2QdpPW4csItqqtY1R7UFUEoM</t>
   </si>
   <si>
     <t>Wolverine Worldwide 502</t>
@@ -2743,7 +2749,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
@@ -2796,7 +2802,7 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
-        <v>45348</v>
+        <v>45357</v>
       </c>
       <c r="B2" s="55" t="s">
         <v>108</v>
@@ -2808,19 +2814,19 @@
         <v>674</v>
       </c>
       <c r="E2" s="55">
-        <v>316200</v>
+        <v>493110</v>
       </c>
       <c r="F2" s="55">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G2" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="54">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J2" s="53" t="s">
         <v>675</v>
@@ -2832,64 +2838,64 @@
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
-        <v>45320</v>
+        <v>45348</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="D3" s="55" t="s">
         <v>676</v>
       </c>
       <c r="E3" s="55">
-        <v>561611</v>
+        <v>316200</v>
       </c>
       <c r="F3" s="55">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="G3" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="54">
-        <v>45380</v>
+        <v>45415</v>
       </c>
       <c r="I3" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J3" s="53" t="s">
         <v>677</v>
       </c>
       <c r="K3" s="57" t="str">
-        <f t="shared" ref="K3:K15" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <f t="shared" ref="K3:K16" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
         <v>WARN</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54">
-        <v>45315</v>
+        <v>45320</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D4" s="55" t="s">
         <v>678</v>
       </c>
       <c r="E4" s="55">
-        <v>611511</v>
+        <v>561611</v>
       </c>
       <c r="F4" s="55">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="G4" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="54">
-        <v>45315</v>
+        <v>45380</v>
       </c>
       <c r="I4" s="55" t="s">
         <v>13</v>
@@ -2904,7 +2910,7 @@
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54">
-        <v>45302</v>
+        <v>45315</v>
       </c>
       <c r="B5" s="55" t="s">
         <v>29</v>
@@ -2916,16 +2922,16 @@
         <v>680</v>
       </c>
       <c r="E5" s="55">
-        <v>336110</v>
+        <v>611511</v>
       </c>
       <c r="F5" s="55">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="G5" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="54">
-        <v>45365</v>
+        <v>45315</v>
       </c>
       <c r="I5" s="55" t="s">
         <v>13</v>
@@ -2940,28 +2946,28 @@
     </row>
     <row r="6" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54">
-        <v>45301</v>
+        <v>45302</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D6" s="55" t="s">
         <v>682</v>
       </c>
       <c r="E6" s="55">
-        <v>336350</v>
+        <v>336110</v>
       </c>
       <c r="F6" s="55">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G6" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H6" s="54">
-        <v>45401</v>
+        <v>45365</v>
       </c>
       <c r="I6" s="55" t="s">
         <v>13</v>
@@ -2976,28 +2982,28 @@
     </row>
     <row r="7" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54">
-        <v>45299</v>
+        <v>45301</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D7" s="55" t="s">
         <v>684</v>
       </c>
       <c r="E7" s="55">
-        <v>561720</v>
+        <v>336350</v>
       </c>
       <c r="F7" s="55">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G7" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H7" s="54">
-        <v>45299</v>
+        <v>45401</v>
       </c>
       <c r="I7" s="55" t="s">
         <v>13</v>
@@ -3021,13 +3027,13 @@
         <v>238</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E8" s="55">
         <v>561720</v>
       </c>
       <c r="F8" s="55">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G8" s="55" t="s">
         <v>16</v>
@@ -3039,7 +3045,7 @@
         <v>13</v>
       </c>
       <c r="J8" s="53" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K8" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3057,13 +3063,13 @@
         <v>238</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E9" s="55">
         <v>561720</v>
       </c>
       <c r="F9" s="55">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G9" s="55" t="s">
         <v>16</v>
@@ -3075,7 +3081,7 @@
         <v>13</v>
       </c>
       <c r="J9" s="53" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K9" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3093,13 +3099,13 @@
         <v>238</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E10" s="55">
         <v>561720</v>
       </c>
       <c r="F10" s="55">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="G10" s="55" t="s">
         <v>16</v>
@@ -3111,7 +3117,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K10" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3120,34 +3126,34 @@
     </row>
     <row r="11" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E11" s="55">
-        <v>331400</v>
+        <v>561720</v>
       </c>
       <c r="F11" s="55">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G11" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H11" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="I11" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>10</v>
+        <v>690</v>
       </c>
       <c r="K11" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3159,31 +3165,31 @@
         <v>45295</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="E12" s="55">
-        <v>561720</v>
+        <v>331400</v>
       </c>
       <c r="F12" s="55">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H12" s="54">
-        <v>45356</v>
+        <v>45295</v>
       </c>
       <c r="I12" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>690</v>
+        <v>10</v>
       </c>
       <c r="K12" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3195,19 +3201,19 @@
         <v>45295</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E13" s="55">
         <v>561720</v>
       </c>
       <c r="F13" s="55">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G13" s="55" t="s">
         <v>16</v>
@@ -3219,7 +3225,7 @@
         <v>13</v>
       </c>
       <c r="J13" s="53" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="K13" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3231,13 +3237,13 @@
         <v>45295</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E14" s="55">
         <v>561720</v>
@@ -3255,7 +3261,7 @@
         <v>13</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="K14" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3264,28 +3270,28 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="54">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="B15" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C15" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="E15" s="55">
-        <v>541714</v>
+        <v>561720</v>
       </c>
       <c r="F15" s="55">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G15" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H15" s="54">
-        <v>45351</v>
+        <v>45356</v>
       </c>
       <c r="I15" s="55" t="s">
         <v>13</v>
@@ -3294,6 +3300,42 @@
         <v>694</v>
       </c>
       <c r="K15" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="54">
+        <v>45293</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>695</v>
+      </c>
+      <c r="E16" s="55">
+        <v>541714</v>
+      </c>
+      <c r="F16" s="55">
+        <v>136</v>
+      </c>
+      <c r="G16" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="54">
+        <v>45351</v>
+      </c>
+      <c r="I16" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="53" t="s">
+        <v>696</v>
+      </c>
+      <c r="K16" s="57" t="str">
         <f t="shared" si="0"/>
         <v>WARN</v>
       </c>
@@ -14767,6 +14809,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -14775,7 +14823,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0C1C9366252B4C838708442C71C5AA" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="623745db76138c409ead4834ced54ea8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="62511544-38af-49c2-8996-37c0f6a636fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c1a1049adbb8cd97fc988c6af4986c32" ns2:_="">
     <xsd:import namespace="62511544-38af-49c2-8996-37c0f6a636fd"/>
@@ -14915,25 +14963,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4F545EA-D03E-4930-8341-636201EC819E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEB26DE-B3FC-45A8-BF93-B326AF5FAB7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -14946,4 +14976,16 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FAC6FF2-C1C2-40D0-BA3F-2749509B71AB}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3103A16C-16CE-4B25-AC65-A1F08B1BF9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7BC9C57-C31B-4914-9705-173C651B42C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="699">
   <si>
     <t>Date Received</t>
   </si>
@@ -2078,6 +2078,12 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005NnQa/qEmJQv7aNct3EcgWUyr2QdpPW4csItqqtY1R7UFUEoM</t>
+  </si>
+  <si>
+    <t>Pride Mine (formerly Survant Mine)</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005OvwZ/oe_tpVgNasO2oF.llfG2Os.flGmYVw_rnc8TodEPc0k</t>
   </si>
   <si>
     <t>Wolverine Worldwide 502</t>
@@ -2749,7 +2755,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
@@ -2838,67 +2844,67 @@
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
-        <v>45348</v>
+        <v>45352</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>128</v>
+        <v>472</v>
       </c>
       <c r="D3" s="55" t="s">
         <v>676</v>
       </c>
       <c r="E3" s="55">
-        <v>316200</v>
+        <v>21211</v>
       </c>
       <c r="F3" s="55">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="G3" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="54">
-        <v>45415</v>
+        <v>45411</v>
       </c>
       <c r="I3" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J3" s="53" t="s">
         <v>677</v>
       </c>
       <c r="K3" s="57" t="str">
-        <f t="shared" ref="K3:K16" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <f t="shared" ref="K3:K17" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
         <v>WARN</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54">
-        <v>45320</v>
+        <v>45348</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="D4" s="55" t="s">
         <v>678</v>
       </c>
       <c r="E4" s="55">
-        <v>561611</v>
+        <v>316200</v>
       </c>
       <c r="F4" s="55">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="G4" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="54">
-        <v>45380</v>
+        <v>45415</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J4" s="53" t="s">
         <v>679</v>
@@ -2910,28 +2916,28 @@
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54">
-        <v>45315</v>
+        <v>45320</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D5" s="55" t="s">
         <v>680</v>
       </c>
       <c r="E5" s="55">
-        <v>611511</v>
+        <v>561611</v>
       </c>
       <c r="F5" s="55">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="G5" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="54">
-        <v>45315</v>
+        <v>45380</v>
       </c>
       <c r="I5" s="55" t="s">
         <v>13</v>
@@ -2946,7 +2952,7 @@
     </row>
     <row r="6" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54">
-        <v>45302</v>
+        <v>45315</v>
       </c>
       <c r="B6" s="55" t="s">
         <v>29</v>
@@ -2958,16 +2964,16 @@
         <v>682</v>
       </c>
       <c r="E6" s="55">
-        <v>336110</v>
+        <v>611511</v>
       </c>
       <c r="F6" s="55">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="G6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="54">
-        <v>45365</v>
+        <v>45315</v>
       </c>
       <c r="I6" s="55" t="s">
         <v>13</v>
@@ -2982,28 +2988,28 @@
     </row>
     <row r="7" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54">
-        <v>45301</v>
+        <v>45302</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D7" s="55" t="s">
         <v>684</v>
       </c>
       <c r="E7" s="55">
-        <v>336350</v>
+        <v>336110</v>
       </c>
       <c r="F7" s="55">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G7" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H7" s="54">
-        <v>45401</v>
+        <v>45365</v>
       </c>
       <c r="I7" s="55" t="s">
         <v>13</v>
@@ -3018,28 +3024,28 @@
     </row>
     <row r="8" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="54">
-        <v>45299</v>
+        <v>45301</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D8" s="55" t="s">
         <v>686</v>
       </c>
       <c r="E8" s="55">
-        <v>561720</v>
+        <v>336350</v>
       </c>
       <c r="F8" s="55">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G8" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H8" s="54">
-        <v>45299</v>
+        <v>45401</v>
       </c>
       <c r="I8" s="55" t="s">
         <v>13</v>
@@ -3063,13 +3069,13 @@
         <v>238</v>
       </c>
       <c r="D9" s="55" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E9" s="55">
         <v>561720</v>
       </c>
       <c r="F9" s="55">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G9" s="55" t="s">
         <v>16</v>
@@ -3081,7 +3087,7 @@
         <v>13</v>
       </c>
       <c r="J9" s="53" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K9" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3099,13 +3105,13 @@
         <v>238</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E10" s="55">
         <v>561720</v>
       </c>
       <c r="F10" s="55">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" s="55" t="s">
         <v>16</v>
@@ -3117,7 +3123,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="K10" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3135,13 +3141,13 @@
         <v>238</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E11" s="55">
         <v>561720</v>
       </c>
       <c r="F11" s="55">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="G11" s="55" t="s">
         <v>16</v>
@@ -3153,7 +3159,7 @@
         <v>13</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K11" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3162,34 +3168,34 @@
     </row>
     <row r="12" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E12" s="55">
-        <v>331400</v>
+        <v>561720</v>
       </c>
       <c r="F12" s="55">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G12" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H12" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="I12" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>10</v>
+        <v>692</v>
       </c>
       <c r="K12" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3201,31 +3207,31 @@
         <v>45295</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="E13" s="55">
-        <v>561720</v>
+        <v>331400</v>
       </c>
       <c r="F13" s="55">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G13" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H13" s="54">
-        <v>45356</v>
+        <v>45295</v>
       </c>
       <c r="I13" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J13" s="53" t="s">
-        <v>692</v>
+        <v>10</v>
       </c>
       <c r="K13" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3237,19 +3243,19 @@
         <v>45295</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E14" s="55">
         <v>561720</v>
       </c>
       <c r="F14" s="55">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G14" s="55" t="s">
         <v>16</v>
@@ -3261,7 +3267,7 @@
         <v>13</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="K14" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3273,13 +3279,13 @@
         <v>45295</v>
       </c>
       <c r="B15" s="55" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C15" s="55" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E15" s="55">
         <v>561720</v>
@@ -3297,7 +3303,7 @@
         <v>13</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="K15" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3306,28 +3312,28 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="54">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="B16" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C16" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="E16" s="55">
-        <v>541714</v>
+        <v>561720</v>
       </c>
       <c r="F16" s="55">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G16" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H16" s="54">
-        <v>45351</v>
+        <v>45356</v>
       </c>
       <c r="I16" s="55" t="s">
         <v>13</v>
@@ -3336,6 +3342,42 @@
         <v>696</v>
       </c>
       <c r="K16" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="54">
+        <v>45293</v>
+      </c>
+      <c r="B17" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="55" t="s">
+        <v>697</v>
+      </c>
+      <c r="E17" s="55">
+        <v>541714</v>
+      </c>
+      <c r="F17" s="55">
+        <v>136</v>
+      </c>
+      <c r="G17" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="54">
+        <v>45351</v>
+      </c>
+      <c r="I17" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="53" t="s">
+        <v>698</v>
+      </c>
+      <c r="K17" s="57" t="str">
         <f t="shared" si="0"/>
         <v>WARN</v>
       </c>
@@ -14987,5 +15029,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FAC6FF2-C1C2-40D0-BA3F-2749509B71AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F46E2BC0-FC85-4269-B09E-194144E16A60}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\Rapid Response\WARN Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7BC9C57-C31B-4914-9705-173C651B42C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC42C61D-2FA6-4B8D-8FBA-471CF1158108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="701">
   <si>
     <t>Date Received</t>
   </si>
@@ -2072,6 +2072,12 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y0000044AjY/AIrRiUx57cQN91Gt3GEskluAye9VTB5lmjzmRGMobI4</t>
+  </si>
+  <si>
+    <t>PACKERS SANITATION SERVICES, INC</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/8y000005PTbi/liVJ16Dm05sakIEorMDLFyevLhq429zeBvi9u4yzLL4</t>
   </si>
   <si>
     <t>Guess? Inc</t>
@@ -2755,7 +2761,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" style="24" customWidth="1"/>
@@ -2808,31 +2814,31 @@
     </row>
     <row r="2" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
-        <v>45357</v>
+        <v>45363</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>128</v>
+        <v>584</v>
       </c>
       <c r="D2" s="55" t="s">
         <v>674</v>
       </c>
-      <c r="E2" s="55">
-        <v>493110</v>
+      <c r="E2" s="55" t="s">
+        <v>10</v>
       </c>
       <c r="F2" s="55">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="G2" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H2" s="54">
-        <v>45418</v>
+        <v>45366</v>
       </c>
       <c r="I2" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" s="53" t="s">
         <v>675</v>
@@ -2844,28 +2850,28 @@
     </row>
     <row r="3" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
-        <v>45352</v>
+        <v>45357</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>472</v>
+        <v>128</v>
       </c>
       <c r="D3" s="55" t="s">
         <v>676</v>
       </c>
       <c r="E3" s="55">
-        <v>21211</v>
+        <v>493110</v>
       </c>
       <c r="F3" s="55">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="G3" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H3" s="54">
-        <v>45411</v>
+        <v>45418</v>
       </c>
       <c r="I3" s="55" t="s">
         <v>13</v>
@@ -2874,37 +2880,37 @@
         <v>677</v>
       </c>
       <c r="K3" s="57" t="str">
-        <f t="shared" ref="K3:K17" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
+        <f t="shared" ref="K3:K18" si="0">IF(ISBLANK(J3),"",HYPERLINK(J3,"WARN"))</f>
         <v>WARN</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54">
-        <v>45348</v>
+        <v>45352</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>128</v>
+        <v>472</v>
       </c>
       <c r="D4" s="55" t="s">
         <v>678</v>
       </c>
       <c r="E4" s="55">
-        <v>316200</v>
+        <v>21211</v>
       </c>
       <c r="F4" s="55">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="G4" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="54">
-        <v>45415</v>
+        <v>45411</v>
       </c>
       <c r="I4" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J4" s="53" t="s">
         <v>679</v>
@@ -2916,31 +2922,31 @@
     </row>
     <row r="5" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54">
-        <v>45320</v>
+        <v>45348</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="D5" s="55" t="s">
         <v>680</v>
       </c>
       <c r="E5" s="55">
-        <v>561611</v>
+        <v>316200</v>
       </c>
       <c r="F5" s="55">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="G5" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="54">
-        <v>45380</v>
+        <v>45415</v>
       </c>
       <c r="I5" s="55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J5" s="53" t="s">
         <v>681</v>
@@ -2952,28 +2958,28 @@
     </row>
     <row r="6" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="54">
-        <v>45315</v>
+        <v>45320</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D6" s="55" t="s">
         <v>682</v>
       </c>
       <c r="E6" s="55">
-        <v>611511</v>
+        <v>561611</v>
       </c>
       <c r="F6" s="55">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="G6" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="54">
-        <v>45315</v>
+        <v>45380</v>
       </c>
       <c r="I6" s="55" t="s">
         <v>13</v>
@@ -2988,7 +2994,7 @@
     </row>
     <row r="7" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54">
-        <v>45302</v>
+        <v>45315</v>
       </c>
       <c r="B7" s="55" t="s">
         <v>29</v>
@@ -3000,16 +3006,16 @@
         <v>684</v>
       </c>
       <c r="E7" s="55">
-        <v>336110</v>
+        <v>611511</v>
       </c>
       <c r="F7" s="55">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="G7" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="54">
-        <v>45365</v>
+        <v>45315</v>
       </c>
       <c r="I7" s="55" t="s">
         <v>13</v>
@@ -3024,28 +3030,28 @@
     </row>
     <row r="8" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="54">
-        <v>45301</v>
+        <v>45302</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D8" s="55" t="s">
         <v>686</v>
       </c>
       <c r="E8" s="55">
-        <v>336350</v>
+        <v>336110</v>
       </c>
       <c r="F8" s="55">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G8" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H8" s="54">
-        <v>45401</v>
+        <v>45365</v>
       </c>
       <c r="I8" s="55" t="s">
         <v>13</v>
@@ -3060,28 +3066,28 @@
     </row>
     <row r="9" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="54">
-        <v>45299</v>
+        <v>45301</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D9" s="55" t="s">
         <v>688</v>
       </c>
       <c r="E9" s="55">
-        <v>561720</v>
+        <v>336350</v>
       </c>
       <c r="F9" s="55">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G9" s="55" t="s">
         <v>16</v>
       </c>
       <c r="H9" s="54">
-        <v>45299</v>
+        <v>45401</v>
       </c>
       <c r="I9" s="55" t="s">
         <v>13</v>
@@ -3105,13 +3111,13 @@
         <v>238</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E10" s="55">
         <v>561720</v>
       </c>
       <c r="F10" s="55">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G10" s="55" t="s">
         <v>16</v>
@@ -3123,7 +3129,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="53" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="K10" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3141,13 +3147,13 @@
         <v>238</v>
       </c>
       <c r="D11" s="55" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E11" s="55">
         <v>561720</v>
       </c>
       <c r="F11" s="55">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" s="55" t="s">
         <v>16</v>
@@ -3159,7 +3165,7 @@
         <v>13</v>
       </c>
       <c r="J11" s="53" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="K11" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3177,13 +3183,13 @@
         <v>238</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E12" s="55">
         <v>561720</v>
       </c>
       <c r="F12" s="55">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="G12" s="55" t="s">
         <v>16</v>
@@ -3195,7 +3201,7 @@
         <v>13</v>
       </c>
       <c r="J12" s="53" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="K12" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3204,34 +3210,34 @@
     </row>
     <row r="13" spans="1:11" s="55" customFormat="1" ht="21.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E13" s="55">
-        <v>331400</v>
+        <v>561720</v>
       </c>
       <c r="F13" s="55">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G13" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H13" s="54">
-        <v>45295</v>
+        <v>45299</v>
       </c>
       <c r="I13" s="55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" s="53" t="s">
-        <v>10</v>
+        <v>694</v>
       </c>
       <c r="K13" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3243,31 +3249,31 @@
         <v>45295</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="E14" s="55">
-        <v>561720</v>
+        <v>331400</v>
       </c>
       <c r="F14" s="55">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G14" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H14" s="54">
-        <v>45356</v>
+        <v>45295</v>
       </c>
       <c r="I14" s="55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J14" s="53" t="s">
-        <v>694</v>
+        <v>10</v>
       </c>
       <c r="K14" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3279,19 +3285,19 @@
         <v>45295</v>
       </c>
       <c r="B15" s="55" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C15" s="55" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E15" s="55">
         <v>561720</v>
       </c>
       <c r="F15" s="55">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G15" s="55" t="s">
         <v>16</v>
@@ -3303,7 +3309,7 @@
         <v>13</v>
       </c>
       <c r="J15" s="53" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="K15" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3315,13 +3321,13 @@
         <v>45295</v>
       </c>
       <c r="B16" s="55" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C16" s="55" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E16" s="55">
         <v>561720</v>
@@ -3339,7 +3345,7 @@
         <v>13</v>
       </c>
       <c r="J16" s="53" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="K16" s="57" t="str">
         <f t="shared" si="0"/>
@@ -3348,28 +3354,28 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="54">
-        <v>45293</v>
+        <v>45295</v>
       </c>
       <c r="B17" s="55" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C17" s="55" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="E17" s="55">
-        <v>541714</v>
+        <v>561720</v>
       </c>
       <c r="F17" s="55">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="G17" s="55" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H17" s="54">
-        <v>45351</v>
+        <v>45356</v>
       </c>
       <c r="I17" s="55" t="s">
         <v>13</v>
@@ -3378,6 +3384,42 @@
         <v>698</v>
       </c>
       <c r="K17" s="57" t="str">
+        <f t="shared" si="0"/>
+        <v>WARN</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="54">
+        <v>45293</v>
+      </c>
+      <c r="B18" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>699</v>
+      </c>
+      <c r="E18" s="55">
+        <v>541714</v>
+      </c>
+      <c r="F18" s="55">
+        <v>136</v>
+      </c>
+      <c r="G18" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="54">
+        <v>45351</v>
+      </c>
+      <c r="I18" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="53" t="s">
+        <v>700</v>
+      </c>
+      <c r="K18" s="57" t="str">
         <f t="shared" si="0"/>
         <v>WARN</v>
       </c>
@@ -14851,12 +14893,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -14865,7 +14901,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FF0C1C9366252B4C838708442C71C5AA" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="623745db76138c409ead4834ced54ea8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="62511544-38af-49c2-8996-37c0f6a636fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c1a1049adbb8cd97fc988c6af4986c32" ns2:_="">
     <xsd:import namespace="62511544-38af-49c2-8996-37c0f6a636fd"/>
@@ -15005,7 +15041,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D2AC05C-2CE2-4F5A-9F34-0E3CB64A8C57}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEB26DE-B3FC-45A8-BF93-B326AF5FAB7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -15018,16 +15072,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715615AF-A72B-4F14-880D-3272574D4C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F46E2BC0-FC85-4269-B09E-194144E16A60}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE18AC8F-5C4F-4ED3-B95C-C5A9F334B67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{236FF5C7-C75F-4F53-B208-4DE1742FFBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4A4EC8AD-7A1A-47A7-8ECD-F35EED928E0E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A36ACEF2-C6CD-496C-A02F-821A2781E289}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN Report 2026-02-04" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN Report-2026-02-18-10-00-04" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -76,9 +76,6 @@
     <t>Franklin</t>
   </si>
   <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I</t>
-  </si>
-  <si>
     <t>Non-Union</t>
   </si>
   <si>
@@ -130,6 +127,12 @@
     <t>Notice 2741</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L0m5N/dzNGJ0evF7p0eqe3gkJ1A2xmpiaHfNjC0uxTXzAc0aA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I </t>
+  </si>
+  <si>
     <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E </t>
   </si>
   <si>
@@ -143,9 +146,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L0m5N/dzNGJ0evF7p0eqe3gkJ1A2xmpiaHfNjC0uxTXzAc0aA </t>
   </si>
 </sst>
 </file>
@@ -638,10 +638,20 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1017,7 +1027,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6319FC77-B81F-4C5E-BC18-D8758F5F1A50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E75B166-0929-4EBC-B31F-2C7B40E1C06B}">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1026,53 +1036,52 @@
     <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="106.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1092,52 +1101,52 @@
       <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="5">
         <v>46057</v>
       </c>
       <c r="G2">
         <v>541611</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="J2" s="1">
         <v>46112</v>
       </c>
       <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
         <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="F3" s="5">
         <v>46056</v>
       </c>
       <c r="G3">
         <v>541330</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3">
         <v>8</v>
@@ -1146,36 +1155,36 @@
         <v>46128</v>
       </c>
       <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" t="s">
         <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="1">
+        <v>26</v>
+      </c>
+      <c r="F4" s="5">
         <v>46053</v>
       </c>
       <c r="G4">
         <v>517</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4">
         <v>74</v>
@@ -1184,39 +1193,39 @@
         <v>46114</v>
       </c>
       <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" t="s">
         <v>28</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="F5" s="5">
         <v>46051</v>
       </c>
       <c r="G5">
         <v>541715</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I5">
         <v>30</v>
@@ -1225,36 +1234,36 @@
         <v>46114</v>
       </c>
       <c r="L5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
         <v>19</v>
-      </c>
-      <c r="M5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="F6" s="5">
         <v>46041</v>
       </c>
       <c r="G6">
         <v>541330</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I6">
         <v>33</v>
@@ -1263,36 +1272,36 @@
         <v>46101</v>
       </c>
       <c r="L6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" t="s">
         <v>19</v>
-      </c>
-      <c r="M6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="F7" s="5">
         <v>46034</v>
       </c>
       <c r="G7">
         <v>541330</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -1301,36 +1310,36 @@
         <v>46107</v>
       </c>
       <c r="L7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" t="s">
         <v>19</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="F8" s="5">
         <v>46027</v>
       </c>
       <c r="G8">
         <v>541715</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I8">
         <v>60</v>
@@ -1339,36 +1348,28 @@
         <v>46086</v>
       </c>
       <c r="L8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" t="s">
         <v>19</v>
-      </c>
-      <c r="M8" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{8E64181C-133E-43CB-ACD3-6FD8BF4FDA9A}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{8B412AB9-20D9-48C1-8F5F-EDE85BB41557}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{ECDBD50A-F4B6-4546-BF71-15BA3FAC5D84}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{03911DAB-54F9-4D92-934D-E46CE26B57AD}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{2A7A8BE8-7061-4A9E-B885-D3D43F9285CD}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{11E9C159-C005-4E69-AACD-23608427DF9B}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{D50B9D55-A41D-4B73-B33B-F813D1142A2E}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{3AAD6392-B2B2-42BB-AFC7-3E17F1D06EA9}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{44FE0B79-01D9-4791-97BC-8810AD79F904}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{651E7818-BA95-4518-B446-3F24B693A70E}"/>
+    <hyperlink ref="H5" r:id="rId4" xr:uid="{910AF886-00BD-49AA-B2A1-7C75F99FED0D}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{6591C15F-3D66-4729-915A-F15C3C9EACE1}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{EA727525-C46A-4441-B63C-ECD6B1203489}"/>
+    <hyperlink ref="H8" r:id="rId7" xr:uid="{5CF7BB1B-933A-43AA-B0DA-60412BA3D5C4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId8"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004C7EC705FC200A4790775D01706F91EB" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94b9a123c94490f7abe5591ccbd17c77">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="ac1070bf-3ce6-4b87-ab2d-f70092a0dc57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08997c8a8d0ea3014a243e24c4d1c3c3" ns1:_="" ns2:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1525,6 +1526,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1535,38 +1545,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{854AFD19-BF44-4EEC-AA5F-64D2D1799594}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD11622E-A6CF-47A0-8035-439728EA751B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74166A90-6A9E-4489-9BF7-E176048F815C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="ac1070bf-3ce6-4b87-ab2d-f70092a0dc57"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AEACC44-86DE-45B1-82C2-DEA328EFD4E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B749FE5C-2CA4-4367-83DB-506A1153FD88}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED3317E-2C05-4859-A31A-9CB4BF7BCD5C}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{236FF5C7-C75F-4F53-B208-4DE1742FFBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DF32546-9719-4F0A-946F-70EF73FF382D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A36ACEF2-C6CD-496C-A02F-821A2781E289}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{30981C2D-1BF6-4F2A-8104-9DCD6CD5A2B0}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN Report-2026-02-18-10-00-04" sheetId="1" r:id="rId1"/>
+    <sheet name="Website-WARN Notice Report 0225" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,12 +61,33 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>FRAM First Brands Group, LLC</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2763</t>
+  </si>
+  <si>
+    <t>Closure</t>
+  </si>
+  <si>
+    <t>Boone</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000N9QpF/4EEzN4tM6NejTIykMYCa83PGBw3SZK1mgoh_UyK2LBY</t>
+  </si>
+  <si>
+    <t>Non-Union</t>
+  </si>
+  <si>
+    <t>Northern Kentucky</t>
+  </si>
+  <si>
     <t>HGS CX TECHNOLOGIES INC.</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2752</t>
   </si>
   <si>
@@ -76,7 +97,7 @@
     <t>Franklin</t>
   </si>
   <si>
-    <t>Non-Union</t>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I</t>
   </si>
   <si>
     <t>Bluegrass</t>
@@ -88,12 +109,12 @@
     <t>Notice 2751</t>
   </si>
   <si>
-    <t>Closure</t>
-  </si>
-  <si>
     <t>Madison</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E</t>
+  </si>
+  <si>
     <t>T-Mobile USA, Inc.</t>
   </si>
   <si>
@@ -103,6 +124,9 @@
     <t>Jefferson County - Louisville</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
@@ -115,44 +139,77 @@
     <t>Notice 2749</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M4S4L/LQzXQpOvkAZMAIHIvymYA.svisC5GHMdGM_kT4c1.lE</t>
+  </si>
+  <si>
     <t>Bechtel Parsons Blue Grass</t>
   </si>
   <si>
     <t>Notice 2746</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000LOTKv/q2vS9oQb.f2kr9RxJzzteN8ihZx.77HgJflmO2hsKsE</t>
+  </si>
+  <si>
     <t>Notice 2743</t>
   </si>
   <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng</t>
+  </si>
+  <si>
     <t>Notice 2741</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L0m5N/dzNGJ0evF7p0eqe3gkJ1A2xmpiaHfNjC0uxTXzAc0aA</t>
   </si>
   <si>
-    <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M4S4L/LQzXQpOvkAZMAIHIvymYA.svisC5GHMdGM_kT4c1.lE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000LOTKv/q2vS9oQb.f2kr9RxJzzteN8ihZx.77HgJflmO2hsKsE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng </t>
+    <t>Notice 2735</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000K4yZx/hjNHC46tUotP6fQSFooblwIQMdy9n7n9jwycpYtoK2A</t>
+  </si>
+  <si>
+    <t>Blue Oval SK Group/Battery Plant</t>
+  </si>
+  <si>
+    <t>Notice 2737</t>
+  </si>
+  <si>
+    <t>Hardin</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Mgcyf/R0rOEwqaqbq2_BLO_3h_bVZSr5L.ydfELzP9lSJBHds</t>
+  </si>
+  <si>
+    <t>Lincoln Trail</t>
+  </si>
+  <si>
+    <t>Thyssenkrupp</t>
+  </si>
+  <si>
+    <t>Notice 2734</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Jzw2X/XaV0.3wPmFgN09imJ4PSCxAVb1lNP0z6Glx2vjhIsrA</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Notice 2733</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000JzlTh/JZSB0EQsN_7JjzgrGG5lPxUfnNVre1K_KN5cOIxZ1aQ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,14 +344,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -593,7 +642,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -636,24 +685,12 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -687,7 +724,6 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1027,61 +1063,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E75B166-0929-4EBC-B31F-2C7B40E1C06B}">
-  <dimension ref="A1:M8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24226757-1630-4F14-B206-4E6B5318F041}">
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="106.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1101,271 +1124,454 @@
       <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="5">
-        <v>46057</v>
+      <c r="F2" s="1">
+        <v>46077</v>
       </c>
       <c r="G2">
-        <v>541611</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>36</v>
+        <v>423120</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="J2" s="1">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="5">
-        <v>46056</v>
+        <v>24</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46057</v>
       </c>
       <c r="G3">
-        <v>541330</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>37</v>
+        <v>541611</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>46128</v>
+        <v>46112</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46056</v>
+      </c>
+      <c r="G4">
+        <v>541330</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4" s="1">
+        <v>46128</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="5">
-        <v>46053</v>
-      </c>
-      <c r="G4">
-        <v>517</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4">
-        <v>74</v>
-      </c>
-      <c r="J4" s="1">
-        <v>46114</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="5">
-        <v>46051</v>
+        <v>33</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46053</v>
       </c>
       <c r="G5">
-        <v>541715</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>517</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
       </c>
       <c r="I5">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="J5" s="1">
         <v>46114</v>
       </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
       <c r="L5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="5">
-        <v>46041</v>
+        <v>29</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46051</v>
       </c>
       <c r="G6">
-        <v>541330</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>40</v>
+        <v>541715</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
       </c>
       <c r="I6">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J6" s="1">
-        <v>46101</v>
+        <v>46114</v>
       </c>
       <c r="L6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="5">
-        <v>46034</v>
+        <v>29</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46041</v>
       </c>
       <c r="G7">
         <v>541330</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>41</v>
+      <c r="H7" t="s">
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J7" s="1">
-        <v>46107</v>
+        <v>46101</v>
       </c>
       <c r="L7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="5">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46034</v>
+      </c>
+      <c r="G8">
+        <v>541330</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8">
+        <v>42</v>
+      </c>
+      <c r="J8" s="1">
+        <v>46107</v>
+      </c>
+      <c r="L8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1">
         <v>46027</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>541715</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8">
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9">
         <v>60</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J9" s="1">
         <v>46086</v>
       </c>
-      <c r="L8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" t="s">
+      <c r="L9" t="s">
         <v>19</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46008</v>
+      </c>
+      <c r="G10">
+        <v>541715</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10">
+        <v>17</v>
+      </c>
+      <c r="J10" s="1">
+        <v>46071</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46007</v>
+      </c>
+      <c r="G11">
+        <v>335911</v>
+      </c>
+      <c r="H11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11">
+        <v>1514</v>
+      </c>
+      <c r="J11" s="1">
+        <v>46112</v>
+      </c>
+      <c r="L11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G12">
+        <v>332991</v>
+      </c>
+      <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12">
+        <v>77</v>
+      </c>
+      <c r="J12" s="1">
+        <v>46066</v>
+      </c>
+      <c r="K12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G13">
+        <v>541330</v>
+      </c>
+      <c r="H13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13">
+        <v>32</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46038</v>
+      </c>
+      <c r="L13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{3AAD6392-B2B2-42BB-AFC7-3E17F1D06EA9}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{44FE0B79-01D9-4791-97BC-8810AD79F904}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{651E7818-BA95-4518-B446-3F24B693A70E}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{910AF886-00BD-49AA-B2A1-7C75F99FED0D}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{6591C15F-3D66-4729-915A-F15C3C9EACE1}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{EA727525-C46A-4441-B63C-ECD6B1203489}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{5CF7BB1B-933A-43AA-B0DA-60412BA3D5C4}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -1545,13 +1751,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD11622E-A6CF-47A0-8035-439728EA751B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02070FA-56E9-46FA-A14D-5E3FD902C7CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AEACC44-86DE-45B1-82C2-DEA328EFD4E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52CC3E98-F9E7-4C5B-83DC-C7BDC829C05F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED3317E-2C05-4859-A31A-9CB4BF7BCD5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D88E6974-241A-44A6-83F2-B18C0AB938A6}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DF32546-9719-4F0A-946F-70EF73FF382D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54289106-1DC5-4777-97D6-2428085C925D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{30981C2D-1BF6-4F2A-8104-9DCD6CD5A2B0}"/>
+    <workbookView xWindow="5088" yWindow="3384" windowWidth="17280" windowHeight="9960" xr2:uid="{FD517E05-2490-445A-AFFC-27BAA02A84B8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Website-WARN Notice Report 0225" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN Report-2026-03-04-10-00-02" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -85,61 +85,82 @@
     <t>Northern Kentucky</t>
   </si>
   <si>
+    <t>PARSONS CORPORATION</t>
+  </si>
+  <si>
+    <t>Notice 2751</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E</t>
+  </si>
+  <si>
+    <t>Bluegrass</t>
+  </si>
+  <si>
+    <t>Battelle Memorial Institute E3</t>
+  </si>
+  <si>
+    <t>Notice 2749</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M4S4L/LQzXQpOvkAZMAIHIvymYA.svisC5GHMdGM_kT4c1.lE</t>
+  </si>
+  <si>
+    <t>T-Mobile USA, Inc.</t>
+  </si>
+  <si>
+    <t>Notice 2750</t>
+  </si>
+  <si>
+    <t>Layoff</t>
+  </si>
+  <si>
+    <t>Jefferson County - Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Kentuckiana Works</t>
+  </si>
+  <si>
+    <t>Blue Oval SK Group/Battery Plant</t>
+  </si>
+  <si>
+    <t>Notice 2737</t>
+  </si>
+  <si>
+    <t>Hardin</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Mgcyf/R0rOEwqaqbq2_BLO_3h_bVZSr5L.ydfELzP9lSJBHds</t>
+  </si>
+  <si>
+    <t>Lincoln Trail</t>
+  </si>
+  <si>
     <t>HGS CX TECHNOLOGIES INC.</t>
   </si>
   <si>
     <t>Notice 2752</t>
   </si>
   <si>
-    <t>Layoff</t>
-  </si>
-  <si>
     <t>Franklin</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I</t>
   </si>
   <si>
-    <t>Bluegrass</t>
-  </si>
-  <si>
-    <t>PARSONS CORPORATION</t>
-  </si>
-  <si>
-    <t>Notice 2751</t>
-  </si>
-  <si>
-    <t>Madison</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E</t>
-  </si>
-  <si>
-    <t>T-Mobile USA, Inc.</t>
-  </si>
-  <si>
-    <t>Notice 2750</t>
-  </si>
-  <si>
-    <t>Jefferson County - Louisville</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Kentuckiana Works</t>
-  </si>
-  <si>
-    <t>Battelle Memorial Institute E3</t>
-  </si>
-  <si>
-    <t>Notice 2749</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M4S4L/LQzXQpOvkAZMAIHIvymYA.svisC5GHMdGM_kT4c1.lE</t>
+    <t>Notice 2743</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng</t>
   </si>
   <si>
     <t>Bechtel Parsons Blue Grass</t>
@@ -151,12 +172,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000LOTKv/q2vS9oQb.f2kr9RxJzzteN8ihZx.77HgJflmO2hsKsE</t>
   </si>
   <si>
-    <t>Notice 2743</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng</t>
-  </si>
-  <si>
     <t>Notice 2741</t>
   </si>
   <si>
@@ -167,21 +182,6 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000K4yZx/hjNHC46tUotP6fQSFooblwIQMdy9n7n9jwycpYtoK2A</t>
-  </si>
-  <si>
-    <t>Blue Oval SK Group/Battery Plant</t>
-  </si>
-  <si>
-    <t>Notice 2737</t>
-  </si>
-  <si>
-    <t>Hardin</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Mgcyf/R0rOEwqaqbq2_BLO_3h_bVZSr5L.ydfELzP9lSJBHds</t>
-  </si>
-  <si>
-    <t>Lincoln Trail</t>
   </si>
   <si>
     <t>Thyssenkrupp</t>
@@ -1063,7 +1063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24226757-1630-4F14-B206-4E6B5318F041}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79252FAC-4CB3-4A22-ACFC-C3ABCE91F602}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1157,86 +1157,86 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="1">
+        <v>46056</v>
+      </c>
+      <c r="G3">
+        <v>541330</v>
+      </c>
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G3">
-        <v>541611</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J3" s="1">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="L3" t="s">
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1">
-        <v>46056</v>
+        <v>46051</v>
       </c>
       <c r="G4">
-        <v>541330</v>
+        <v>541715</v>
       </c>
       <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4">
         <v>30</v>
       </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
       <c r="J4" s="1">
-        <v>46128</v>
+        <v>46114</v>
       </c>
       <c r="L4" t="s">
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
         <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
       </c>
       <c r="F5" s="1">
         <v>46053</v>
@@ -1245,7 +1245,7 @@
         <v>517</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I5">
         <v>74</v>
@@ -1254,106 +1254,106 @@
         <v>46114</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
         <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1">
-        <v>46051</v>
+        <v>46007</v>
       </c>
       <c r="G6">
-        <v>541715</v>
+        <v>335911</v>
       </c>
       <c r="H6" t="s">
         <v>39</v>
       </c>
       <c r="I6">
-        <v>30</v>
+        <v>1514</v>
       </c>
       <c r="J6" s="1">
-        <v>46114</v>
+        <v>46112</v>
       </c>
       <c r="L6" t="s">
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1">
-        <v>46041</v>
+        <v>46057</v>
       </c>
       <c r="G7">
-        <v>541330</v>
+        <v>541611</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="J7" s="1">
-        <v>46101</v>
+        <v>46112</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1">
         <v>46034</v>
@@ -1362,7 +1362,7 @@
         <v>541330</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -1374,121 +1374,121 @@
         <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1">
-        <v>46027</v>
+        <v>46041</v>
       </c>
       <c r="G9">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I9">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="J9" s="1">
-        <v>46086</v>
+        <v>46101</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1">
-        <v>46008</v>
+        <v>46027</v>
       </c>
       <c r="G10">
         <v>541715</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I10">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J10" s="1">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="L10" t="s">
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="G11">
-        <v>335911</v>
+        <v>541715</v>
       </c>
       <c r="H11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I11">
-        <v>1514</v>
+        <v>17</v>
       </c>
       <c r="J11" s="1">
-        <v>46112</v>
+        <v>46071</v>
       </c>
       <c r="L11" t="s">
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1546,7 +1546,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1">
         <v>46006</v>
@@ -1567,7 +1567,7 @@
         <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1751,13 +1751,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02070FA-56E9-46FA-A14D-5E3FD902C7CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F682C0E6-80C0-489F-BCFB-A97DB70CD43F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52CC3E98-F9E7-4C5B-83DC-C7BDC829C05F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA6495CA-3B95-4C1D-808A-078CDB4744DC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D88E6974-241A-44A6-83F2-B18C0AB938A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C911C79-E1FF-40B8-9CCC-A782114B0810}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54289106-1DC5-4777-97D6-2428085C925D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F8F16ED-1FD0-49B1-9808-1E47D122BF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5088" yWindow="3384" windowWidth="17280" windowHeight="9960" xr2:uid="{FD517E05-2490-445A-AFFC-27BAA02A84B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2D2669E7-8CD4-45C4-83DF-4051A8408014}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN Report-2026-03-04-10-00-02" sheetId="1" r:id="rId1"/>
+    <sheet name="Website-WARN Notice Report-0318" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,27 +61,45 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>Battelle Memorial Institute E3</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2777</t>
+  </si>
+  <si>
+    <t>Closure</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NkU99/oU8_gO4ZAXjo2Ew8cYx0YkQwqLrKuxfHbjNc4HWS0kg</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Non-Union</t>
+  </si>
+  <si>
+    <t>Bluegrass</t>
+  </si>
+  <si>
     <t>FRAM First Brands Group, LLC</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2763</t>
   </si>
   <si>
-    <t>Closure</t>
-  </si>
-  <si>
     <t>Boone</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000N9QpF/4EEzN4tM6NejTIykMYCa83PGBw3SZK1mgoh_UyK2LBY</t>
   </si>
   <si>
-    <t>Non-Union</t>
-  </si>
-  <si>
     <t>Northern Kentucky</t>
   </si>
   <si>
@@ -91,18 +109,9 @@
     <t>Notice 2751</t>
   </si>
   <si>
-    <t>Madison</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E</t>
   </si>
   <si>
-    <t>Bluegrass</t>
-  </si>
-  <si>
-    <t>Battelle Memorial Institute E3</t>
-  </si>
-  <si>
     <t>Notice 2749</t>
   </si>
   <si>
@@ -124,9 +133,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Kentuckiana Works</t>
   </si>
   <si>
@@ -163,6 +169,27 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng</t>
   </si>
   <si>
+    <t>CC Metals and Alloys</t>
+  </si>
+  <si>
+    <t>Notice 2781</t>
+  </si>
+  <si>
+    <t>Marshall</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000OLBic/__X6qXa.xkYBXDTiFJHDQ5BSQAz0cXx6rE7wdHGW04Y</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Western Kentucky</t>
+  </si>
+  <si>
     <t>Bechtel Parsons Blue Grass</t>
   </si>
   <si>
@@ -172,6 +199,21 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000LOTKv/q2vS9oQb.f2kr9RxJzzteN8ihZx.77HgJflmO2hsKsE</t>
   </si>
   <si>
+    <t>C2 Technologies</t>
+  </si>
+  <si>
+    <t>Notice 2778</t>
+  </si>
+  <si>
+    <t>Out of the State County</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NktkD/ZAn12UJAS6jJoJdozzCAp1D93Q3iZ0Q9vKA3kFS_R1s</t>
+  </si>
+  <si>
+    <t>Out of State</t>
+  </si>
+  <si>
     <t>Notice 2741</t>
   </si>
   <si>
@@ -191,12 +233,6 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Jzw2X/XaV0.3wPmFgN09imJ4PSCxAVb1lNP0z6Glx2vjhIsrA</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Both</t>
   </si>
   <si>
     <t>Notice 2733</t>
@@ -1063,8 +1099,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79252FAC-4CB3-4A22-ACFC-C3ABCE91F602}">
-  <dimension ref="A1:M13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDDF431-B95D-4968-8611-8019EFE62ED0}">
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1125,106 +1161,109 @@
         <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>46077</v>
+        <v>46086</v>
       </c>
       <c r="G2">
-        <v>423120</v>
+        <v>541715</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="J2" s="1">
-        <v>46142</v>
+        <v>46148</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1">
-        <v>46056</v>
+        <v>46077</v>
       </c>
       <c r="G3">
-        <v>541330</v>
+        <v>423120</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="J3" s="1">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G4">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I4">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J4" s="1">
-        <v>46114</v>
+        <v>46128</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -1233,191 +1272,191 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46051</v>
+      </c>
+      <c r="G5">
+        <v>541715</v>
+      </c>
+      <c r="H5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46053</v>
-      </c>
-      <c r="G5">
-        <v>517</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
       <c r="I5">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="J5" s="1">
         <v>46114</v>
       </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46053</v>
+      </c>
+      <c r="G6">
+        <v>517</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6">
+        <v>74</v>
+      </c>
+      <c r="J6" s="1">
+        <v>46114</v>
+      </c>
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46007</v>
-      </c>
-      <c r="G6">
-        <v>335911</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6">
-        <v>1514</v>
-      </c>
-      <c r="J6" s="1">
-        <v>46112</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1">
-        <v>46057</v>
+        <v>46007</v>
       </c>
       <c r="G7">
-        <v>541611</v>
+        <v>335911</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>1514</v>
       </c>
       <c r="J7" s="1">
         <v>46112</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
         <v>45</v>
       </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
       <c r="F8" s="1">
-        <v>46034</v>
+        <v>46057</v>
       </c>
       <c r="G8">
-        <v>541330</v>
+        <v>541611</v>
       </c>
       <c r="H8" t="s">
         <v>46</v>
       </c>
       <c r="I8">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="J8" s="1">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1">
-        <v>46041</v>
+        <v>46034</v>
       </c>
       <c r="G9">
         <v>541330</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I9">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J9" s="1">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -1426,148 +1465,265 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F10" s="1">
-        <v>46027</v>
+        <v>46098</v>
       </c>
       <c r="G10">
-        <v>541715</v>
+        <v>33331</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I10">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="J10" s="1">
-        <v>46086</v>
+        <v>46105</v>
+      </c>
+      <c r="K10" t="s">
+        <v>53</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1">
-        <v>46008</v>
+        <v>46041</v>
       </c>
       <c r="G11">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I11">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J11" s="1">
-        <v>46071</v>
+        <v>46101</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F12" s="1">
-        <v>46006</v>
+        <v>46087</v>
       </c>
       <c r="G12">
-        <v>332991</v>
+        <v>545410</v>
       </c>
       <c r="H12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I12">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="J12" s="1">
-        <v>46066</v>
-      </c>
-      <c r="K12" t="s">
-        <v>57</v>
+        <v>46087</v>
       </c>
       <c r="L12" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="M12" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1">
+        <v>46027</v>
+      </c>
+      <c r="G13">
+        <v>541715</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13">
+        <v>60</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46086</v>
+      </c>
+      <c r="L13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46008</v>
+      </c>
+      <c r="G14">
+        <v>541715</v>
+      </c>
+      <c r="H14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14">
+        <v>17</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46071</v>
+      </c>
+      <c r="L14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="1">
         <v>46006</v>
       </c>
-      <c r="G13">
+      <c r="G15">
+        <v>332991</v>
+      </c>
+      <c r="H15" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15">
+        <v>77</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46066</v>
+      </c>
+      <c r="K15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G16">
         <v>541330</v>
       </c>
-      <c r="H13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13">
+      <c r="H16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16">
         <v>32</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J16" s="1">
         <v>46038</v>
       </c>
-      <c r="L13" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" t="s">
-        <v>25</v>
+      <c r="L16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1751,13 +1907,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F682C0E6-80C0-489F-BCFB-A97DB70CD43F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE3DE10E-A623-4216-918E-1210C3974BF6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA6495CA-3B95-4C1D-808A-078CDB4744DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA17E30D-6CEC-4EB2-ACD0-240F261117B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C911C79-E1FF-40B8-9CCC-A782114B0810}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60FB87BF-87A4-4825-9FAD-1846C19BC84C}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F8F16ED-1FD0-49B1-9808-1E47D122BF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A717D32-B834-4AB0-9E77-23309098410B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2D2669E7-8CD4-45C4-83DF-4051A8408014}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{27965ED2-6AF1-4641-86DF-C77CA6F15057}"/>
   </bookViews>
   <sheets>
-    <sheet name="Website-WARN Notice Report-0318" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN Report-2026-04-08-10-00-10" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="79">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,18 +61,48 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>Legacy Supply Chain</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2785</t>
+  </si>
+  <si>
+    <t>Closure</t>
+  </si>
+  <si>
+    <t>Jefferson County - Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000PDRqP/Qx1TWK7zpU5r.9tnXH1SaSnmys5ktC.Y2JwvY0izamU</t>
+  </si>
+  <si>
+    <t>Non-Union</t>
+  </si>
+  <si>
+    <t>Kentuckiana Works</t>
+  </si>
+  <si>
+    <t>Bluegrass UPS Facility</t>
+  </si>
+  <si>
+    <t>Notice 2786</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000PDP8f/7oyf.yIT7bga4_8lwf6Gv0CBM6RWkfBtSueOExFzIEk</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
     <t>Battelle Memorial Institute E3</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2777</t>
   </si>
   <si>
-    <t>Closure</t>
-  </si>
-  <si>
     <t>Madison</t>
   </si>
   <si>
@@ -82,9 +112,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>Non-Union</t>
-  </si>
-  <si>
     <t>Bluegrass</t>
   </si>
   <si>
@@ -127,15 +154,9 @@
     <t>Layoff</t>
   </si>
   <si>
-    <t>Jefferson County - Louisville</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
   </si>
   <si>
-    <t>Kentuckiana Works</t>
-  </si>
-  <si>
     <t>Blue Oval SK Group/Battery Plant</t>
   </si>
   <si>
@@ -182,9 +203,6 @@
   </si>
   <si>
     <t>TBD</t>
-  </si>
-  <si>
-    <t>Both</t>
   </si>
   <si>
     <t>Western Kentucky</t>
@@ -722,9 +740,25 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1099,48 +1133,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDDF431-B95D-4968-8611-8019EFE62ED0}">
-  <dimension ref="A1:M16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE15098-1528-48EE-8EB8-87C7580995E3}">
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="106.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="6"/>
+    <col min="12" max="12" width="23" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.44140625" style="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1151,579 +1200,649 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>46086</v>
-      </c>
-      <c r="G2">
-        <v>541715</v>
+        <v>46113</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2" s="1">
-        <v>46148</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="I2" s="2">
+        <v>123</v>
+      </c>
+      <c r="J2" s="7">
+        <v>46179</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46113</v>
+      </c>
+      <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="I3" s="2">
+        <v>65</v>
+      </c>
+      <c r="J3" s="7">
+        <v>46175</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1">
-        <v>46077</v>
-      </c>
-      <c r="G3">
-        <v>423120</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3">
-        <v>76</v>
-      </c>
-      <c r="J3" s="1">
-        <v>46142</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G4">
+        <v>541715</v>
+      </c>
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1">
-        <v>46056</v>
-      </c>
-      <c r="G4">
-        <v>541330</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" s="2">
+        <v>5</v>
+      </c>
+      <c r="J4" s="7">
+        <v>46148</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4" s="1">
-        <v>46128</v>
-      </c>
-      <c r="L4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" t="s">
-        <v>21</v>
+      <c r="L4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
-        <v>17</v>
+      <c r="E5" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="F5" s="1">
-        <v>46051</v>
+        <v>46077</v>
       </c>
       <c r="G5">
-        <v>541715</v>
+        <v>423120</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5">
-        <v>30</v>
-      </c>
-      <c r="J5" s="1">
-        <v>46114</v>
-      </c>
-      <c r="L5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" t="s">
-        <v>21</v>
+        <v>34</v>
+      </c>
+      <c r="I5" s="2">
+        <v>76</v>
+      </c>
+      <c r="J5" s="7">
+        <v>46142</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
+      <c r="C6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="F6" s="1">
-        <v>46053</v>
+        <v>46056</v>
       </c>
       <c r="G6">
-        <v>517</v>
+        <v>541330</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6">
-        <v>74</v>
-      </c>
-      <c r="J6" s="1">
-        <v>46114</v>
-      </c>
-      <c r="K6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8</v>
+      </c>
+      <c r="J6" s="7">
+        <v>46128</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" t="s">
-        <v>37</v>
+      <c r="M6" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46051</v>
+      </c>
+      <c r="G7">
+        <v>541715</v>
+      </c>
+      <c r="H7" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="1">
-        <v>46007</v>
-      </c>
-      <c r="G7">
-        <v>335911</v>
-      </c>
-      <c r="H7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7">
-        <v>1514</v>
-      </c>
-      <c r="J7" s="1">
-        <v>46112</v>
-      </c>
-      <c r="L7" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
+      <c r="I7" s="2">
+        <v>30</v>
+      </c>
+      <c r="J7" s="7">
+        <v>46114</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46053</v>
+      </c>
+      <c r="G8">
+        <v>517</v>
+      </c>
+      <c r="H8" t="s">
         <v>44</v>
       </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G8">
-        <v>541611</v>
-      </c>
-      <c r="H8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>46112</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="I8" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" s="7">
+        <v>46114</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
       <c r="F9" s="1">
-        <v>46034</v>
+        <v>46007</v>
       </c>
       <c r="G9">
-        <v>541330</v>
+        <v>335911</v>
       </c>
       <c r="H9" t="s">
         <v>48</v>
       </c>
-      <c r="I9">
-        <v>42</v>
-      </c>
-      <c r="J9" s="1">
-        <v>46107</v>
-      </c>
-      <c r="L9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" t="s">
-        <v>21</v>
+      <c r="I9" s="2">
+        <v>1514</v>
+      </c>
+      <c r="J9" s="7">
+        <v>46112</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C10" s="6" t="s">
         <v>51</v>
       </c>
+      <c r="D10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="F10" s="1">
-        <v>46098</v>
+        <v>46057</v>
       </c>
       <c r="G10">
-        <v>33331</v>
+        <v>541611</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10">
-        <v>114</v>
-      </c>
-      <c r="J10" s="1">
-        <v>46105</v>
-      </c>
-      <c r="K10" t="s">
         <v>53</v>
       </c>
-      <c r="L10" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" t="s">
-        <v>55</v>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7">
+        <v>46112</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E11" t="s">
-        <v>17</v>
+      <c r="E11" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="F11" s="1">
-        <v>46041</v>
+        <v>46034</v>
       </c>
       <c r="G11">
         <v>541330</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11">
-        <v>33</v>
-      </c>
-      <c r="J11" s="1">
-        <v>46101</v>
-      </c>
-      <c r="L11" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" t="s">
-        <v>21</v>
+        <v>55</v>
+      </c>
+      <c r="I11" s="2">
+        <v>42</v>
+      </c>
+      <c r="J11" s="7">
+        <v>46107</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G12">
+        <v>33331</v>
+      </c>
+      <c r="H12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="2">
+        <v>114</v>
+      </c>
+      <c r="J12" s="7">
+        <v>46105</v>
+      </c>
+      <c r="K12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="L12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46087</v>
-      </c>
-      <c r="G12">
-        <v>545410</v>
-      </c>
-      <c r="H12" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12" s="1">
-        <v>46087</v>
-      </c>
-      <c r="L12" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46041</v>
+      </c>
+      <c r="G13">
+        <v>541330</v>
+      </c>
+      <c r="H13" t="s">
         <v>64</v>
       </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46027</v>
-      </c>
-      <c r="G13">
-        <v>541715</v>
-      </c>
-      <c r="H13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13">
-        <v>60</v>
-      </c>
-      <c r="J13" s="1">
-        <v>46086</v>
-      </c>
-      <c r="L13" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" t="s">
-        <v>21</v>
+      <c r="I13" s="2">
+        <v>33</v>
+      </c>
+      <c r="J13" s="7">
+        <v>46101</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>17</v>
+      <c r="D14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="F14" s="1">
-        <v>46008</v>
+        <v>46087</v>
       </c>
       <c r="G14">
-        <v>541715</v>
+        <v>545410</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14">
-        <v>17</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46071</v>
-      </c>
-      <c r="L14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" t="s">
-        <v>21</v>
+        <v>68</v>
+      </c>
+      <c r="I14" s="2">
+        <v>2</v>
+      </c>
+      <c r="J14" s="7">
+        <v>46087</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E15" t="s">
-        <v>24</v>
+      <c r="E15" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="F15" s="1">
-        <v>46006</v>
+        <v>46027</v>
       </c>
       <c r="G15">
-        <v>332991</v>
+        <v>541715</v>
       </c>
       <c r="H15" t="s">
-        <v>70</v>
-      </c>
-      <c r="I15">
-        <v>77</v>
-      </c>
-      <c r="J15" s="1">
-        <v>46066</v>
-      </c>
-      <c r="K15" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" t="s">
-        <v>26</v>
+        <v>71</v>
+      </c>
+      <c r="I15" s="2">
+        <v>60</v>
+      </c>
+      <c r="J15" s="7">
+        <v>46086</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46008</v>
+      </c>
+      <c r="G16">
+        <v>541715</v>
+      </c>
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="2">
         <v>17</v>
       </c>
-      <c r="F16" s="1">
+      <c r="J16" s="7">
+        <v>46071</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="1">
         <v>46006</v>
       </c>
-      <c r="G16">
+      <c r="G17">
+        <v>332991</v>
+      </c>
+      <c r="H17" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="2">
+        <v>77</v>
+      </c>
+      <c r="J17" s="7">
+        <v>46066</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G18">
         <v>541330</v>
       </c>
-      <c r="H16" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16">
+      <c r="H18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="2">
         <v>32</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J18" s="7">
         <v>46038</v>
       </c>
-      <c r="L16" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
+      <c r="L18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1907,13 +2026,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE3DE10E-A623-4216-918E-1210C3974BF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0199BA5E-3301-4CC3-8C01-F117130F7EA5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA17E30D-6CEC-4EB2-ACD0-240F261117B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{823CC96B-BEA2-4A0A-AEDA-87A21C6DBA2D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60FB87BF-87A4-4825-9FAD-1846C19BC84C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D65212B-5552-4D5C-988C-89154065649A}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A717D32-B834-4AB0-9E77-23309098410B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4602A6C5-AA85-4910-8D76-6A508D1B5219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{27965ED2-6AF1-4641-86DF-C77CA6F15057}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6997269C-7D9E-4644-9404-E1DA62029B18}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN Report-2026-04-08-10-00-10" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN Report-2026-04-22-10-00-03" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="81">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -97,6 +97,18 @@
     <t>Both</t>
   </si>
   <si>
+    <t>Marsden Services LLC</t>
+  </si>
+  <si>
+    <t>Notice 2795</t>
+  </si>
+  <si>
+    <t>Layoff</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Battelle Memorial Institute E3</t>
   </si>
   <si>
@@ -109,9 +121,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NkU99/oU8_gO4ZAXjo2Ew8cYx0YkQwqLrKuxfHbjNc4HWS0kg</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Bluegrass</t>
   </si>
   <si>
@@ -149,9 +158,6 @@
   </si>
   <si>
     <t>Notice 2750</t>
-  </si>
-  <si>
-    <t>Layoff</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
@@ -740,25 +746,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1133,63 +1123,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE15098-1528-48EE-8EB8-87C7580995E3}">
-  <dimension ref="A1:M18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF83CFB6-C288-4190-9741-6C46C949FB82}">
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="106.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" style="6"/>
-    <col min="12" max="12" width="23" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" style="6" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1200,13 +1175,13 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="1">
@@ -1215,16 +1190,16 @@
       <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2">
         <v>123</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="1">
         <v>46179</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1235,13 +1210,13 @@
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="1">
@@ -1250,16 +1225,16 @@
       <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
         <v>65</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="1">
         <v>46175</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1270,482 +1245,476 @@
       <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" t="s">
         <v>27</v>
       </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
       <c r="F4" s="1">
-        <v>46086</v>
-      </c>
-      <c r="G4">
-        <v>541715</v>
-      </c>
-      <c r="H4" t="s">
+        <v>46128</v>
+      </c>
+      <c r="I4">
+        <v>106</v>
+      </c>
+      <c r="J4" s="1">
+        <v>46152</v>
+      </c>
+      <c r="K4" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="2">
-        <v>5</v>
-      </c>
-      <c r="J4" s="7">
-        <v>46148</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>30</v>
+      <c r="M4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G5">
+        <v>541715</v>
+      </c>
+      <c r="H5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="1">
+        <v>46148</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
         <v>33</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46077</v>
-      </c>
-      <c r="G5">
-        <v>423120</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="2">
-        <v>76</v>
-      </c>
-      <c r="J5" s="7">
-        <v>46142</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46077</v>
+      </c>
+      <c r="G6">
+        <v>423120</v>
+      </c>
+      <c r="H6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46056</v>
-      </c>
-      <c r="G6">
-        <v>541330</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6">
+        <v>76</v>
+      </c>
+      <c r="J6" s="1">
+        <v>46142</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
         <v>38</v>
-      </c>
-      <c r="I6" s="2">
-        <v>8</v>
-      </c>
-      <c r="J6" s="7">
-        <v>46128</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>27</v>
+      <c r="E7" t="s">
+        <v>31</v>
       </c>
       <c r="F7" s="1">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G7">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="2">
-        <v>30</v>
-      </c>
-      <c r="J7" s="7">
-        <v>46114</v>
-      </c>
-      <c r="L7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="J7" s="1">
+        <v>46128</v>
+      </c>
+      <c r="L7" t="s">
         <v>19</v>
       </c>
-      <c r="M7" s="6" t="s">
-        <v>30</v>
+      <c r="M7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46051</v>
+      </c>
+      <c r="G8">
+        <v>541715</v>
+      </c>
+      <c r="H8" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46053</v>
-      </c>
-      <c r="G8">
-        <v>517</v>
-      </c>
-      <c r="H8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" s="7">
+      <c r="I8">
+        <v>30</v>
+      </c>
+      <c r="J8" s="1">
         <v>46114</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" t="s">
         <v>19</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>20</v>
+      <c r="M8" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46053</v>
+      </c>
+      <c r="G9">
+        <v>517</v>
+      </c>
+      <c r="H9" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46007</v>
-      </c>
-      <c r="G9">
-        <v>335911</v>
-      </c>
-      <c r="H9" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1514</v>
-      </c>
-      <c r="J9" s="7">
-        <v>46112</v>
-      </c>
-      <c r="L9" s="6" t="s">
+      <c r="I9">
+        <v>74</v>
+      </c>
+      <c r="J9" s="1">
+        <v>46114</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="6" t="s">
-        <v>49</v>
+      <c r="M9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46007</v>
+      </c>
+      <c r="G10">
+        <v>335911</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10">
+        <v>1514</v>
+      </c>
+      <c r="J10" s="1">
+        <v>46112</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G10">
-        <v>541611</v>
-      </c>
-      <c r="H10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="7">
-        <v>46112</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="F11" s="1">
-        <v>46034</v>
+        <v>46057</v>
       </c>
       <c r="G11">
-        <v>541330</v>
+        <v>541611</v>
       </c>
       <c r="H11" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="2">
-        <v>42</v>
-      </c>
-      <c r="J11" s="7">
-        <v>46107</v>
-      </c>
-      <c r="L11" s="6" t="s">
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>46112</v>
+      </c>
+      <c r="L11" t="s">
         <v>19</v>
       </c>
-      <c r="M11" s="6" t="s">
-        <v>30</v>
+      <c r="M11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46034</v>
+      </c>
+      <c r="G12">
+        <v>541330</v>
+      </c>
+      <c r="H12" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46098</v>
-      </c>
-      <c r="G12">
-        <v>33331</v>
-      </c>
-      <c r="H12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="2">
-        <v>114</v>
-      </c>
-      <c r="J12" s="7">
-        <v>46105</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>61</v>
+      <c r="I12">
+        <v>42</v>
+      </c>
+      <c r="J12" s="1">
+        <v>46107</v>
+      </c>
+      <c r="L12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G13">
+        <v>33331</v>
+      </c>
+      <c r="H13" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13">
+        <v>114</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46105</v>
+      </c>
+      <c r="K13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" t="s">
         <v>63</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46041</v>
-      </c>
-      <c r="G13">
-        <v>541330</v>
-      </c>
-      <c r="H13" t="s">
-        <v>64</v>
-      </c>
-      <c r="I13" s="2">
-        <v>33</v>
-      </c>
-      <c r="J13" s="7">
-        <v>46101</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46041</v>
+      </c>
+      <c r="G14">
+        <v>541330</v>
+      </c>
+      <c r="H14" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46087</v>
-      </c>
-      <c r="G14">
-        <v>545410</v>
-      </c>
-      <c r="H14" t="s">
-        <v>68</v>
-      </c>
-      <c r="I14" s="2">
-        <v>2</v>
-      </c>
-      <c r="J14" s="7">
-        <v>46087</v>
-      </c>
-      <c r="L14" s="6" t="s">
+      <c r="I14">
+        <v>33</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46101</v>
+      </c>
+      <c r="L14" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="6" t="s">
-        <v>69</v>
+      <c r="M14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G15">
+        <v>545410</v>
+      </c>
+      <c r="H15" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46027</v>
-      </c>
-      <c r="G15">
-        <v>541715</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46087</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" t="s">
         <v>71</v>
-      </c>
-      <c r="I15" s="2">
-        <v>60</v>
-      </c>
-      <c r="J15" s="7">
-        <v>46086</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>27</v>
+      <c r="E16" t="s">
+        <v>31</v>
       </c>
       <c r="F16" s="1">
-        <v>46008</v>
+        <v>46027</v>
       </c>
       <c r="G16">
         <v>541715</v>
@@ -1753,96 +1722,134 @@
       <c r="H16" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="2">
-        <v>17</v>
-      </c>
-      <c r="J16" s="7">
-        <v>46071</v>
-      </c>
-      <c r="L16" s="6" t="s">
+      <c r="I16">
+        <v>60</v>
+      </c>
+      <c r="J16" s="1">
+        <v>46086</v>
+      </c>
+      <c r="L16" t="s">
         <v>19</v>
       </c>
-      <c r="M16" s="6" t="s">
-        <v>30</v>
+      <c r="M16" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46008</v>
+      </c>
+      <c r="G17">
+        <v>541715</v>
+      </c>
+      <c r="H17" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="I17">
+        <v>17</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46071</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" t="s">
         <v>33</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46006</v>
-      </c>
-      <c r="G17">
-        <v>332991</v>
-      </c>
-      <c r="H17" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="2">
-        <v>77</v>
-      </c>
-      <c r="J17" s="7">
-        <v>46066</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>27</v>
+      <c r="E18" t="s">
+        <v>36</v>
       </c>
       <c r="F18" s="1">
         <v>46006</v>
       </c>
       <c r="G18">
-        <v>541330</v>
+        <v>332991</v>
       </c>
       <c r="H18" t="s">
         <v>78</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18">
+        <v>77</v>
+      </c>
+      <c r="J18" s="1">
+        <v>46066</v>
+      </c>
+      <c r="K18" t="s">
+        <v>62</v>
+      </c>
+      <c r="L18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G19">
+        <v>541330</v>
+      </c>
+      <c r="H19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19">
         <v>32</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J19" s="1">
         <v>46038</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L19" t="s">
         <v>19</v>
       </c>
-      <c r="M18" s="6" t="s">
-        <v>30</v>
+      <c r="M19" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2026,13 +2033,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0199BA5E-3301-4CC3-8C01-F117130F7EA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF704DD7-B39A-4F85-B4BD-8AA814F0E6F6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{823CC96B-BEA2-4A0A-AEDA-87A21C6DBA2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C605239C-E556-435D-AC62-0A34434C8E8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D65212B-5552-4D5C-988C-89154065649A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{316ECB00-586C-4873-B685-ED432D4EFD07}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931BCE55-491F-47B3-AA69-5DC73CBE11DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7ADBDA-8440-4555-85C3-8DD07836F363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A9C58431-D549-4E12-A792-C2AD218BB1A9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CB55AF16-CE95-4EC2-9FEA-84FC7C74AC18}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN Report-2026-05-06-10-00-01" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN Report-2026-05-13-10-00-03" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="98">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,27 +61,42 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>Battelle Memorial Institute E3</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2804</t>
+  </si>
+  <si>
+    <t>Closure</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000R7S85/ChUHYkuIxmZGber7XiEFcOqgFvRKvnc5c98o33VA13M</t>
+  </si>
+  <si>
+    <t>Non-Union</t>
+  </si>
+  <si>
+    <t>Bluegrass</t>
+  </si>
+  <si>
     <t>Stella-Jones Corporation</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2798</t>
   </si>
   <si>
-    <t>Closure</t>
-  </si>
-  <si>
     <t>Fulton</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QbOyr/8QOonL2ZzmNjafz_Iy2AlWTpg0fhL6GmSd9ElrJhDe4</t>
   </si>
   <si>
-    <t>Non-Union</t>
-  </si>
-  <si>
     <t>Western Kentucky</t>
   </si>
   <si>
@@ -103,9 +118,6 @@
     <t>Both</t>
   </si>
   <si>
-    <t>Bluegrass</t>
-  </si>
-  <si>
     <t>University of Kentucky College of Medicine, Department of Behavioral Science</t>
   </si>
   <si>
@@ -160,13 +172,7 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QBhib/Axgartu79FnT.1puuR2ziNCjL_vVob8mjuIb4H_1rgY</t>
   </si>
   <si>
-    <t>Battelle Memorial Institute E3</t>
-  </si>
-  <si>
     <t>Notice 2777</t>
-  </si>
-  <si>
-    <t>Madison</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NkU99/oU8_gO4ZAXjo2Ew8cYx0YkQwqLrKuxfHbjNc4HWS0kg</t>
@@ -314,7 +320,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -449,14 +455,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -755,7 +753,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -798,15 +796,21 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -840,7 +844,6 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1180,62 +1183,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C67578-004A-4C95-B905-8C52D3D74F44}">
-  <dimension ref="A1:M23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9037945C-C169-44AF-82BC-0519E8437017}">
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="106.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1246,34 +1250,34 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1">
-        <v>46142</v>
+      <c r="F2" s="2">
+        <v>46149</v>
       </c>
       <c r="G2">
-        <v>321114</v>
-      </c>
-      <c r="H2" s="3" t="s">
+        <v>541715</v>
+      </c>
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2">
-        <v>67</v>
-      </c>
-      <c r="J2" s="1">
-        <v>46204</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="I2" s="1">
+        <v>3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>46209</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1284,225 +1288,225 @@
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="1">
-        <v>46141</v>
+      <c r="F3" s="2">
+        <v>46142</v>
       </c>
       <c r="G3">
-        <v>722310</v>
-      </c>
-      <c r="H3" s="3" t="s">
+        <v>321114</v>
+      </c>
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="I3">
-        <v>923</v>
-      </c>
-      <c r="J3" s="1">
-        <v>46203</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="I3" s="1">
+        <v>67</v>
+      </c>
+      <c r="J3" s="2">
+        <v>46204</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46141</v>
+      </c>
+      <c r="G4">
+        <v>722310</v>
+      </c>
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1">
-        <v>46147</v>
-      </c>
-      <c r="G4">
-        <v>611310</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="1">
+        <v>923</v>
+      </c>
+      <c r="J4" s="2">
+        <v>46203</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I4">
-        <v>36</v>
-      </c>
-      <c r="J4" s="1">
-        <v>46203</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>27</v>
+      <c r="L4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="C5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2">
         <v>46147</v>
       </c>
       <c r="G5">
         <v>611310</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5">
-        <v>61</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="1">
+        <v>36</v>
+      </c>
+      <c r="J5" s="2">
         <v>46203</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M5" t="s">
-        <v>27</v>
+      <c r="M5" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46113</v>
+      <c r="E6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46147</v>
       </c>
       <c r="G6">
-        <v>488510</v>
-      </c>
-      <c r="H6" s="3" t="s">
+        <v>611310</v>
+      </c>
+      <c r="H6" t="s">
         <v>37</v>
       </c>
-      <c r="I6">
-        <v>123</v>
-      </c>
-      <c r="J6" s="1">
-        <v>46179</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="I6" s="1">
+        <v>61</v>
+      </c>
+      <c r="J6" s="2">
+        <v>46203</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M6" t="s">
-        <v>38</v>
+      <c r="M6" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <v>46113</v>
       </c>
       <c r="G7">
-        <v>492110</v>
-      </c>
-      <c r="H7" s="3" t="s">
+        <v>488510</v>
+      </c>
+      <c r="H7" t="s">
         <v>41</v>
       </c>
-      <c r="I7">
-        <v>65</v>
-      </c>
-      <c r="J7" s="1">
-        <v>46175</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>38</v>
+      <c r="I7" s="1">
+        <v>123</v>
+      </c>
+      <c r="J7" s="2">
+        <v>46179</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46128</v>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46113</v>
       </c>
       <c r="G8">
-        <v>56172</v>
-      </c>
-      <c r="H8" s="3" t="s">
+        <v>492110</v>
+      </c>
+      <c r="H8" t="s">
         <v>45</v>
       </c>
-      <c r="I8">
-        <v>106</v>
-      </c>
-      <c r="J8" s="1">
-        <v>46152</v>
-      </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" t="s">
-        <v>38</v>
+      <c r="I8" s="1">
+        <v>65</v>
+      </c>
+      <c r="J8" s="2">
+        <v>46175</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1512,605 +1516,620 @@
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="1">
-        <v>46086</v>
+      <c r="E9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46128</v>
       </c>
       <c r="G9">
-        <v>541715</v>
-      </c>
-      <c r="H9" s="3" t="s">
+        <v>56172</v>
+      </c>
+      <c r="H9" t="s">
         <v>49</v>
       </c>
-      <c r="I9">
-        <v>5</v>
-      </c>
-      <c r="J9" s="1">
-        <v>46148</v>
-      </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" t="s">
-        <v>27</v>
+      <c r="I9" s="1">
+        <v>106</v>
+      </c>
+      <c r="J9" s="2">
+        <v>46152</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46086</v>
+      </c>
+      <c r="G10">
+        <v>541715</v>
+      </c>
+      <c r="H10" t="s">
         <v>51</v>
       </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46077</v>
-      </c>
-      <c r="G10">
-        <v>423120</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10">
-        <v>76</v>
-      </c>
-      <c r="J10" s="1">
-        <v>46142</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="2">
+        <v>46148</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M10" t="s">
-        <v>54</v>
+      <c r="M10" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46077</v>
+      </c>
+      <c r="G11">
+        <v>423120</v>
+      </c>
+      <c r="H11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="1">
+        <v>76</v>
+      </c>
+      <c r="J11" s="2">
+        <v>46142</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46056</v>
-      </c>
-      <c r="G11">
-        <v>541330</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11" s="1">
-        <v>46128</v>
-      </c>
-      <c r="L11" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46051</v>
+      <c r="E12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46056</v>
       </c>
       <c r="G12">
-        <v>541715</v>
-      </c>
-      <c r="H12" s="3" t="s">
+        <v>541330</v>
+      </c>
+      <c r="H12" t="s">
         <v>59</v>
       </c>
-      <c r="I12">
-        <v>30</v>
-      </c>
-      <c r="J12" s="1">
-        <v>46114</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="I12" s="1">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2">
+        <v>46128</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M12" t="s">
-        <v>27</v>
+      <c r="M12" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G13">
+        <v>541715</v>
+      </c>
+      <c r="H13" t="s">
         <v>61</v>
       </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46053</v>
-      </c>
-      <c r="G13">
-        <v>517</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13">
-        <v>74</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="I13" s="1">
+        <v>30</v>
+      </c>
+      <c r="J13" s="2">
         <v>46114</v>
       </c>
-      <c r="K13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="L13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M13" t="s">
-        <v>38</v>
+      <c r="M13" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="2">
+        <v>46053</v>
+      </c>
+      <c r="G14">
+        <v>517</v>
+      </c>
+      <c r="H14" t="s">
         <v>64</v>
       </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46007</v>
-      </c>
-      <c r="G14">
-        <v>335911</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14">
-        <v>1514</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46112</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="I14" s="1">
+        <v>74</v>
+      </c>
+      <c r="J14" s="2">
+        <v>46114</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M14" t="s">
-        <v>67</v>
+      <c r="M14" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="2">
+        <v>46007</v>
+      </c>
+      <c r="G15">
+        <v>335911</v>
+      </c>
+      <c r="H15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1514</v>
+      </c>
+      <c r="J15" s="2">
+        <v>46112</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G15">
-        <v>541611</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15" s="1">
-        <v>46112</v>
-      </c>
-      <c r="L15" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46034</v>
+      <c r="F16" s="2">
+        <v>46057</v>
       </c>
       <c r="G16">
-        <v>541330</v>
+        <v>541611</v>
       </c>
       <c r="H16" t="s">
         <v>73</v>
       </c>
-      <c r="I16">
-        <v>42</v>
-      </c>
-      <c r="J16" s="1">
-        <v>46107</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>46112</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M16" t="s">
-        <v>27</v>
+      <c r="M16" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="2">
+        <v>46034</v>
+      </c>
+      <c r="G17">
+        <v>541330</v>
+      </c>
+      <c r="H17" t="s">
         <v>75</v>
       </c>
-      <c r="D17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46098</v>
-      </c>
-      <c r="G17">
-        <v>33331</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I17">
-        <v>114</v>
-      </c>
-      <c r="J17" s="1">
-        <v>46105</v>
-      </c>
-      <c r="K17" t="s">
-        <v>78</v>
-      </c>
-      <c r="L17" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" t="s">
+      <c r="I17" s="1">
+        <v>42</v>
+      </c>
+      <c r="J17" s="2">
+        <v>46107</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="2">
+        <v>46098</v>
+      </c>
+      <c r="G18">
+        <v>33331</v>
+      </c>
+      <c r="H18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="1">
+        <v>114</v>
+      </c>
+      <c r="J18" s="2">
+        <v>46105</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="1">
-        <v>46041</v>
-      </c>
-      <c r="G18">
-        <v>541330</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I18">
-        <v>33</v>
-      </c>
-      <c r="J18" s="1">
-        <v>46101</v>
-      </c>
-      <c r="L18" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" t="s">
-        <v>27</v>
+      <c r="L18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="2">
+        <v>46041</v>
+      </c>
+      <c r="G19">
+        <v>541330</v>
+      </c>
+      <c r="H19" t="s">
         <v>83</v>
       </c>
-      <c r="D19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46087</v>
-      </c>
-      <c r="G19">
-        <v>545410</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I19">
-        <v>2</v>
-      </c>
-      <c r="J19" s="1">
-        <v>46087</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="I19" s="1">
+        <v>33</v>
+      </c>
+      <c r="J19" s="2">
+        <v>46101</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M19" t="s">
-        <v>86</v>
+      <c r="M19" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="2">
+        <v>46087</v>
+      </c>
+      <c r="G20">
+        <v>545410</v>
+      </c>
+      <c r="H20" t="s">
         <v>87</v>
       </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="1">
-        <v>46027</v>
-      </c>
-      <c r="G20">
-        <v>541715</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="1">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>46087</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="I20">
-        <v>60</v>
-      </c>
-      <c r="J20" s="1">
-        <v>46086</v>
-      </c>
-      <c r="L20" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E21" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46008</v>
+      <c r="E21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="2">
+        <v>46027</v>
       </c>
       <c r="G21">
         <v>541715</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" t="s">
         <v>90</v>
       </c>
-      <c r="I21">
-        <v>17</v>
-      </c>
-      <c r="J21" s="1">
-        <v>46071</v>
-      </c>
-      <c r="L21" t="s">
+      <c r="I21" s="1">
+        <v>60</v>
+      </c>
+      <c r="J21" s="2">
+        <v>46086</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M21" t="s">
-        <v>27</v>
+      <c r="M21" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="2">
+        <v>46008</v>
+      </c>
+      <c r="G22">
+        <v>541715</v>
+      </c>
+      <c r="H22" t="s">
         <v>92</v>
       </c>
-      <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" s="1">
-        <v>46006</v>
-      </c>
-      <c r="G22">
-        <v>332991</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I22">
-        <v>77</v>
-      </c>
-      <c r="J22" s="1">
-        <v>46066</v>
-      </c>
-      <c r="K22" t="s">
-        <v>78</v>
-      </c>
-      <c r="L22" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" t="s">
-        <v>54</v>
+      <c r="I22" s="1">
+        <v>17</v>
+      </c>
+      <c r="J22" s="2">
+        <v>46071</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E23" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="E23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="2">
         <v>46006</v>
       </c>
       <c r="G23">
+        <v>332991</v>
+      </c>
+      <c r="H23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" s="1">
+        <v>77</v>
+      </c>
+      <c r="J23" s="2">
+        <v>46066</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="2">
+        <v>46006</v>
+      </c>
+      <c r="G24">
         <v>541330</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23">
+      <c r="H24" t="s">
+        <v>97</v>
+      </c>
+      <c r="I24" s="1">
         <v>32</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J24" s="2">
         <v>46038</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M23" t="s">
-        <v>27</v>
+      <c r="M24" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{0EE5414C-8034-4369-924A-8EBAD68129E8}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{A6281208-20FF-4EB3-B95F-6B77CE741544}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{3D669171-A278-46EC-922A-3C7CC173D866}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{E1AA4C17-301A-421C-BAE5-8A9620CEE360}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{E32F0A14-201B-4BB5-B772-967D2AC69501}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{B0A9FA57-99B6-4E33-B785-F545BDC311CE}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{5EBC4F0E-5475-4DF1-AE10-91F95B0FCCCA}"/>
-    <hyperlink ref="H9" r:id="rId8" xr:uid="{DF7B844A-8B72-493D-8B1B-EC32B3C8D92B}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{4A28A3FD-2778-4E8C-A84A-A88B1273381F}"/>
-    <hyperlink ref="H11" r:id="rId10" xr:uid="{E7714766-F379-49B5-8DD5-5A9BD29A95B8}"/>
-    <hyperlink ref="H12" r:id="rId11" xr:uid="{C175F022-A638-448A-A586-406D8D8C915C}"/>
-    <hyperlink ref="H13" r:id="rId12" xr:uid="{65D87244-2094-4448-8867-C7CB3F16FCEA}"/>
-    <hyperlink ref="H14" r:id="rId13" xr:uid="{63110504-F03B-4C5E-9379-E4255A8BBAEE}"/>
-    <hyperlink ref="H15" r:id="rId14" xr:uid="{06691651-DA14-4FBB-B1F6-6CF715688183}"/>
-    <hyperlink ref="H17" r:id="rId15" xr:uid="{A2634185-A33F-4722-B0B8-C95F3FFC3F63}"/>
-    <hyperlink ref="H18" r:id="rId16" xr:uid="{92A1E284-AE12-4726-BFF5-B02B7C68E046}"/>
-    <hyperlink ref="H19" r:id="rId17" xr:uid="{BBD2AE37-0CB0-494B-9D79-E07F20D877DC}"/>
-    <hyperlink ref="H20" r:id="rId18" xr:uid="{81922489-8B2C-41A8-9CB5-B1C238C77C7F}"/>
-    <hyperlink ref="H21" r:id="rId19" xr:uid="{BC7FBDE8-15C6-4D74-A0B1-D5171A96D045}"/>
-    <hyperlink ref="H22" r:id="rId20" xr:uid="{448A459D-940C-4F78-B2AA-329C48710FF7}"/>
-    <hyperlink ref="H23" r:id="rId21" xr:uid="{1F585A00-3944-4F63-8FAA-1B0B589BA319}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2291,13 +2310,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6B592CE-320B-4077-A92A-AFCC574C8A4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDC73380-9F2A-4DEC-97E8-4C9161777AE9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F94ACDE8-45E7-442A-8094-EC5DEAE81C12}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F787BA-CF3C-4EB6-85C5-299C042CB260}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DB839D9-6A4A-4C34-950B-C73D5D3F7AE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80425D59-1B66-4BEB-B700-EE857EB34EBB}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7ADBDA-8440-4555-85C3-8DD07836F363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDE21B2E-EBA7-4701-B7D1-8EEDA7F657F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CB55AF16-CE95-4EC2-9FEA-84FC7C74AC18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DA529436-E93B-4F9C-A12E-E48CCB2EDC8E}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN Report-2026-05-13-10-00-03" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN Report-2026-07-01-10-00-01" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="119">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,30 +61,117 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>Carrier Corporation (Franklin Operation)</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2808</t>
+  </si>
+  <si>
+    <t>Closure</t>
+  </si>
+  <si>
+    <t>Simpson</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SaT9p/KKnZ71hXi0EL978hIuC.v3Bd1U65RB8O0A2hOPjfuTw</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Non-Union</t>
+  </si>
+  <si>
+    <t>South Central</t>
+  </si>
+  <si>
+    <t>Levi Strauss &amp; Co</t>
+  </si>
+  <si>
+    <t>Notice 2817</t>
+  </si>
+  <si>
+    <t>Boone</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TM9VN/lwgxGibuF2npQU7o2QpLEJU5UWHFF10IbsYKzWUrR7Q</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Northern Kentucky</t>
+  </si>
+  <si>
+    <t>Conduent (Corporate)</t>
+  </si>
+  <si>
+    <t>Notice 2815</t>
+  </si>
+  <si>
+    <t>Layoff</t>
+  </si>
+  <si>
+    <t>Jefferson County - Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TFVZ7/Z75_yQpDBRaY9kpSdMax3j_6lKPopGX68JLiqAIsIuo</t>
+  </si>
+  <si>
+    <t>Kentuckiana Works</t>
+  </si>
+  <si>
+    <t>Congo Brands (Alani, Prime, 3D Energy)</t>
+  </si>
+  <si>
+    <t>Notice 2814</t>
+  </si>
+  <si>
+    <t>Jefferson</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TEkTh/ibPumihpj4EjnXfxGEvZueBWuVei8CvUvM1T1u5fOGA</t>
+  </si>
+  <si>
+    <t>RNDC of Kentucky, LLC</t>
+  </si>
+  <si>
+    <t>Notice 2812</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000StexZ/xFnTv1YungNS7J7_kvieFmn654APdTR96QljGfhiY4I</t>
+  </si>
+  <si>
+    <t>Vestis</t>
+  </si>
+  <si>
+    <t>Notice 2809</t>
+  </si>
+  <si>
+    <t>Fayette</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SeoCU/dznB7.9oNP3vwVa5FKsBBRVo1lYORfgFck9ve6izIGc</t>
+  </si>
+  <si>
+    <t>Bluegrass</t>
+  </si>
+  <si>
     <t>Battelle Memorial Institute E3</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2804</t>
   </si>
   <si>
-    <t>Closure</t>
-  </si>
-  <si>
     <t>Madison</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000R7S85/ChUHYkuIxmZGber7XiEFcOqgFvRKvnc5c98o33VA13M</t>
   </si>
   <si>
-    <t>Non-Union</t>
-  </si>
-  <si>
-    <t>Bluegrass</t>
-  </si>
-  <si>
     <t>Stella-Jones Corporation</t>
   </si>
   <si>
@@ -100,24 +187,15 @@
     <t>Western Kentucky</t>
   </si>
   <si>
-    <t>Aramark Campus, LLC</t>
+    <t>Aramark Campus, LLC (University of Kentucky)</t>
   </si>
   <si>
     <t>Notice 2799</t>
   </si>
   <si>
-    <t>Fayette</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QbQKk/97HSOQBTsXu3P4fz4CdBvLx2l.wNmuRx4f4ngCfIIGc</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Both</t>
-  </si>
-  <si>
     <t>University of Kentucky College of Medicine, Department of Behavioral Science</t>
   </si>
   <si>
@@ -142,15 +220,9 @@
     <t>Notice 2785</t>
   </si>
   <si>
-    <t>Jefferson County - Louisville</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000PDRqP/Qx1TWK7zpU5r.9tnXH1SaSnmys5ktC.Y2JwvY0izamU</t>
   </si>
   <si>
-    <t>Kentuckiana Works</t>
-  </si>
-  <si>
     <t>Bluegrass UPS Facility</t>
   </si>
   <si>
@@ -166,9 +238,6 @@
     <t>Notice 2795</t>
   </si>
   <si>
-    <t>Layoff</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QBhib/Axgartu79FnT.1puuR2ziNCjL_vVob8mjuIb4H_1rgY</t>
   </si>
   <si>
@@ -184,13 +253,7 @@
     <t>Notice 2763</t>
   </si>
   <si>
-    <t>Boone</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000N9QpF/4EEzN4tM6NejTIykMYCa83PGBw3SZK1mgoh_UyK2LBY</t>
-  </si>
-  <si>
-    <t>Northern Kentucky</t>
   </si>
   <si>
     <t>PARSONS CORPORATION</t>
@@ -797,18 +860,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1183,63 +1237,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9037945C-C169-44AF-82BC-0519E8437017}">
-  <dimension ref="A1:M24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D38A8E8-6DE1-4187-86ED-1E269BEB91A6}">
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="106.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1250,883 +1299,1117 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2">
-        <v>46149</v>
+      <c r="F2" s="1">
+        <v>46185</v>
       </c>
       <c r="G2">
-        <v>541715</v>
+        <v>333415</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>46209</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="I2">
+        <v>70</v>
+      </c>
+      <c r="J2" s="1">
+        <v>46264</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="L2" t="s">
         <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46142</v>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46203</v>
       </c>
       <c r="G3">
-        <v>321114</v>
+        <v>315250</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1">
-        <v>67</v>
-      </c>
-      <c r="J3" s="2">
-        <v>46204</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="I3">
+        <v>303</v>
+      </c>
+      <c r="J3" s="1">
+        <v>46264</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46141</v>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46202</v>
       </c>
       <c r="G4">
-        <v>722310</v>
+        <v>561110</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="1">
-        <v>923</v>
-      </c>
-      <c r="J4" s="2">
-        <v>46203</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4">
+        <v>24</v>
+      </c>
+      <c r="J4" s="1">
+        <v>46262</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
         <v>20</v>
+      </c>
+      <c r="M4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46199</v>
+      </c>
+      <c r="G5">
+        <v>312111</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1">
+        <v>46260</v>
+      </c>
+      <c r="K5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" t="s">
         <v>33</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2">
-        <v>46147</v>
-      </c>
-      <c r="G5">
-        <v>611310</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="1">
-        <v>36</v>
-      </c>
-      <c r="J5" s="2">
-        <v>46203</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="2">
-        <v>46147</v>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46191</v>
       </c>
       <c r="G6">
-        <v>611310</v>
+        <v>424820</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="1">
-        <v>61</v>
-      </c>
-      <c r="J6" s="2">
-        <v>46203</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>20</v>
+        <v>40</v>
+      </c>
+      <c r="I6">
+        <v>174</v>
+      </c>
+      <c r="J6" s="1">
+        <v>46251</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="2">
-        <v>46113</v>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46189</v>
       </c>
       <c r="G7">
-        <v>488510</v>
+        <v>812332</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="1">
-        <v>123</v>
-      </c>
-      <c r="J7" s="2">
-        <v>46179</v>
-      </c>
-      <c r="L7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7">
+        <v>32</v>
+      </c>
+      <c r="J7" s="1">
+        <v>46249</v>
+      </c>
+      <c r="K7" t="s">
         <v>19</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>42</v>
+      <c r="L7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2">
-        <v>46113</v>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46149</v>
       </c>
       <c r="G8">
-        <v>492110</v>
+        <v>541715</v>
       </c>
       <c r="H8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1">
+        <v>46209</v>
+      </c>
+      <c r="L8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" t="s">
         <v>45</v>
-      </c>
-      <c r="I8" s="1">
-        <v>65</v>
-      </c>
-      <c r="J8" s="2">
-        <v>46175</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="2">
-        <v>46128</v>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46142</v>
       </c>
       <c r="G9">
-        <v>56172</v>
+        <v>321114</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="1">
-        <v>106</v>
-      </c>
-      <c r="J9" s="2">
-        <v>46152</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="I9">
+        <v>67</v>
+      </c>
+      <c r="J9" s="1">
+        <v>46204</v>
+      </c>
+      <c r="L9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="2">
-        <v>46086</v>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46141</v>
       </c>
       <c r="G10">
-        <v>541715</v>
+        <v>722310</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="1">
-        <v>5</v>
-      </c>
-      <c r="J10" s="2">
-        <v>46148</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10">
+        <v>923</v>
+      </c>
+      <c r="J10" s="1">
+        <v>46203</v>
+      </c>
+      <c r="K10" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>20</v>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="2">
-        <v>46077</v>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46147</v>
       </c>
       <c r="G11">
-        <v>423120</v>
+        <v>611310</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="1">
-        <v>76</v>
-      </c>
-      <c r="J11" s="2">
-        <v>46142</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="I11">
+        <v>36</v>
+      </c>
+      <c r="J11" s="1">
+        <v>46203</v>
+      </c>
+      <c r="L11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="2">
-        <v>46056</v>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46147</v>
       </c>
       <c r="G12">
-        <v>541330</v>
+        <v>611310</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="1">
-        <v>8</v>
-      </c>
-      <c r="J12" s="2">
-        <v>46128</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12">
+        <v>61</v>
+      </c>
+      <c r="J12" s="1">
+        <v>46203</v>
+      </c>
+      <c r="L12" t="s">
         <v>20</v>
+      </c>
+      <c r="M12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="2">
-        <v>46051</v>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46113</v>
       </c>
       <c r="G13">
-        <v>541715</v>
+        <v>488510</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="1">
-        <v>30</v>
-      </c>
-      <c r="J13" s="2">
-        <v>46114</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13">
+        <v>123</v>
+      </c>
+      <c r="J13" s="1">
+        <v>46179</v>
+      </c>
+      <c r="L13" t="s">
         <v>20</v>
+      </c>
+      <c r="M13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="2">
-        <v>46053</v>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46113</v>
       </c>
       <c r="G14">
-        <v>517</v>
+        <v>492110</v>
       </c>
       <c r="H14" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="1">
-        <v>74</v>
-      </c>
-      <c r="J14" s="2">
-        <v>46114</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
+      </c>
+      <c r="I14">
+        <v>65</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46175</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="2">
-        <v>46007</v>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46128</v>
       </c>
       <c r="G15">
-        <v>335911</v>
+        <v>56172</v>
       </c>
       <c r="H15" t="s">
-        <v>68</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1514</v>
-      </c>
-      <c r="J15" s="2">
-        <v>46112</v>
-      </c>
-      <c r="L15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15">
+        <v>106</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46152</v>
+      </c>
+      <c r="K15" t="s">
         <v>19</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>69</v>
+      <c r="M15" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="2">
-        <v>46057</v>
+      <c r="F16" s="1">
+        <v>46086</v>
       </c>
       <c r="G16">
-        <v>541611</v>
+        <v>541715</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2">
-        <v>46112</v>
-      </c>
-      <c r="L16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16" s="1">
+        <v>46148</v>
+      </c>
+      <c r="K16" t="s">
         <v>19</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="L16" t="s">
         <v>20</v>
+      </c>
+      <c r="M16" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="2">
-        <v>46034</v>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46077</v>
       </c>
       <c r="G17">
-        <v>541330</v>
+        <v>423120</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" s="1">
-        <v>42</v>
-      </c>
-      <c r="J17" s="2">
-        <v>46107</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17">
+        <v>76</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46142</v>
+      </c>
+      <c r="L17" t="s">
         <v>20</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="2">
-        <v>46098</v>
+      <c r="F18" s="1">
+        <v>46056</v>
       </c>
       <c r="G18">
-        <v>33331</v>
+        <v>541330</v>
       </c>
       <c r="H18" t="s">
-        <v>79</v>
-      </c>
-      <c r="I18" s="1">
-        <v>114</v>
-      </c>
-      <c r="J18" s="2">
-        <v>46105</v>
-      </c>
-      <c r="K18" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>25</v>
+      <c r="I18">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1">
+        <v>46128</v>
+      </c>
+      <c r="L18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
         <v>81</v>
       </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46051</v>
+      </c>
+      <c r="G19">
+        <v>541715</v>
+      </c>
+      <c r="H19" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="2">
-        <v>46041</v>
-      </c>
-      <c r="G19">
-        <v>541330</v>
-      </c>
-      <c r="H19" t="s">
-        <v>83</v>
-      </c>
-      <c r="I19" s="1">
-        <v>33</v>
-      </c>
-      <c r="J19" s="2">
-        <v>46101</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" s="1" t="s">
+      <c r="I19">
+        <v>30</v>
+      </c>
+      <c r="J19" s="1">
+        <v>46114</v>
+      </c>
+      <c r="L19" t="s">
         <v>20</v>
+      </c>
+      <c r="M19" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
         <v>84</v>
       </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="1">
+        <v>46053</v>
+      </c>
+      <c r="G20">
+        <v>517112</v>
+      </c>
+      <c r="H20" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F20" s="2">
-        <v>46087</v>
-      </c>
-      <c r="G20">
-        <v>545410</v>
-      </c>
-      <c r="H20" t="s">
-        <v>87</v>
-      </c>
-      <c r="I20" s="1">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2">
-        <v>46087</v>
-      </c>
-      <c r="L20" s="1" t="s">
+      <c r="I20">
+        <v>74</v>
+      </c>
+      <c r="J20" s="1">
+        <v>46114</v>
+      </c>
+      <c r="K20" t="s">
         <v>19</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>88</v>
+      <c r="L20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46007</v>
+      </c>
+      <c r="G21">
+        <v>335911</v>
+      </c>
+      <c r="H21" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="2">
-        <v>46027</v>
-      </c>
-      <c r="G21">
-        <v>541715</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="I21">
+        <v>1514</v>
+      </c>
+      <c r="J21" s="1">
+        <v>46112</v>
+      </c>
+      <c r="L21" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" t="s">
         <v>90</v>
-      </c>
-      <c r="I21" s="1">
-        <v>60</v>
-      </c>
-      <c r="J21" s="2">
-        <v>46086</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="2">
-        <v>46008</v>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="1">
+        <v>46057</v>
       </c>
       <c r="G22">
-        <v>541715</v>
+        <v>541611</v>
       </c>
       <c r="H22" t="s">
-        <v>92</v>
-      </c>
-      <c r="I22" s="1">
-        <v>17</v>
-      </c>
-      <c r="J22" s="2">
-        <v>46071</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>46112</v>
+      </c>
+      <c r="L22" t="s">
         <v>20</v>
+      </c>
+      <c r="M22" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="2">
-        <v>46006</v>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46034</v>
       </c>
       <c r="G23">
-        <v>332991</v>
+        <v>541330</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" s="1">
-        <v>77</v>
-      </c>
-      <c r="J23" s="2">
-        <v>46066</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>56</v>
+        <v>96</v>
+      </c>
+      <c r="I23">
+        <v>42</v>
+      </c>
+      <c r="J23" s="1">
+        <v>46107</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="1">
+        <v>46098</v>
+      </c>
+      <c r="G24">
+        <v>33331</v>
+      </c>
+      <c r="H24" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>114</v>
+      </c>
+      <c r="J24" s="1">
+        <v>46105</v>
+      </c>
+      <c r="K24" t="s">
+        <v>101</v>
+      </c>
+      <c r="L24" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
         <v>16</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="1">
+        <v>46041</v>
+      </c>
+      <c r="G25">
+        <v>541330</v>
+      </c>
+      <c r="H25" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25">
+        <v>33</v>
+      </c>
+      <c r="J25" s="1">
+        <v>46101</v>
+      </c>
+      <c r="L25" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46087</v>
+      </c>
+      <c r="G26">
+        <v>545410</v>
+      </c>
+      <c r="H26" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26" s="1">
+        <v>46087</v>
+      </c>
+      <c r="L26" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46027</v>
+      </c>
+      <c r="G27">
+        <v>541715</v>
+      </c>
+      <c r="H27" t="s">
+        <v>111</v>
+      </c>
+      <c r="I27">
+        <v>60</v>
+      </c>
+      <c r="J27" s="1">
+        <v>46086</v>
+      </c>
+      <c r="L27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46008</v>
+      </c>
+      <c r="G28">
+        <v>541715</v>
+      </c>
+      <c r="H28" t="s">
+        <v>113</v>
+      </c>
+      <c r="I28">
         <v>17</v>
       </c>
-      <c r="F24" s="2">
+      <c r="J28" s="1">
+        <v>46071</v>
+      </c>
+      <c r="L28" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1">
         <v>46006</v>
       </c>
-      <c r="G24">
+      <c r="G29">
+        <v>332991</v>
+      </c>
+      <c r="H29" t="s">
+        <v>116</v>
+      </c>
+      <c r="I29">
+        <v>77</v>
+      </c>
+      <c r="J29" s="1">
+        <v>46066</v>
+      </c>
+      <c r="K29" t="s">
+        <v>101</v>
+      </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G30">
         <v>541330</v>
       </c>
-      <c r="H24" t="s">
-        <v>97</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="H30" t="s">
+        <v>118</v>
+      </c>
+      <c r="I30">
         <v>32</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J30" s="1">
         <v>46038</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M24" s="1" t="s">
+      <c r="L30" t="s">
         <v>20</v>
+      </c>
+      <c r="M30" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2310,13 +2593,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDC73380-9F2A-4DEC-97E8-4C9161777AE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{851C0AD5-BA3F-4A00-9185-B7774E96179B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F787BA-CF3C-4EB6-85C5-299C042CB260}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67BE8CB2-DF45-4880-B87C-95F3E971B583}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80425D59-1B66-4BEB-B700-EE857EB34EBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91D683C8-6211-448E-A4D8-3B6351CE4D84}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDE21B2E-EBA7-4701-B7D1-8EEDA7F657F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D953905B-3ADC-465F-8865-624A3A61E61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DA529436-E93B-4F9C-A12E-E48CCB2EDC8E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6414ACC-BC32-49BD-9AFE-9BCDF960C6C9}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN Report-2026-07-01-10-00-01" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN Report 08052026" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="127">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,117 +61,162 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>80 Acres Farm</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2831</t>
+  </si>
+  <si>
+    <t>Closure</t>
+  </si>
+  <si>
+    <t>Boone</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000UxY4Q/GF0gz3XikIqoUSgtEsWvpqt7e_5PwKLvyRqhww3LW.c</t>
+  </si>
+  <si>
+    <t>Non-Union</t>
+  </si>
+  <si>
+    <t>Northern Kentucky</t>
+  </si>
+  <si>
+    <t>Battelle Memorial Institute E3</t>
+  </si>
+  <si>
+    <t>Notice 2820</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000CLJC1/DbyYp68sVwKoN.GQkRf5EyzUntPUC3BOkVG9L_FcJUc</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Bluegrass</t>
+  </si>
+  <si>
+    <t>Geodis</t>
+  </si>
+  <si>
+    <t>Notice 2818</t>
+  </si>
+  <si>
+    <t>Layoff</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TnvHN/MsOC3lIkOTZLTZOZQRMslPIsqoxbV_q80J1A.Yw1omU</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Levi Strauss &amp; Co</t>
+  </si>
+  <si>
+    <t>Notice 2817</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TM9VN/lwgxGibuF2npQU7o2QpLEJU5UWHFF10IbsYKzWUrR7Q</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Conduent (Corporate)</t>
+  </si>
+  <si>
+    <t>Notice 2815</t>
+  </si>
+  <si>
+    <t>Jefferson County - Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TFVZ7/Z75_yQpDBRaY9kpSdMax3j_6lKPopGX68JLiqAIsIuo</t>
+  </si>
+  <si>
+    <t>Kentuckiana Works</t>
+  </si>
+  <si>
+    <t>Congo Brands (Alani, Prime, 3D Energy)</t>
+  </si>
+  <si>
+    <t>Notice 2814</t>
+  </si>
+  <si>
+    <t>Jefferson</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TEkTh/ibPumihpj4EjnXfxGEvZueBWuVei8CvUvM1T1u5fOGA</t>
+  </si>
+  <si>
+    <t>RNDC of Kentucky, LLC</t>
+  </si>
+  <si>
+    <t>Notice 2812</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000StexZ/xFnTv1YungNS7J7_kvieFmn654APdTR96QljGfhiY4I</t>
+  </si>
+  <si>
+    <t>Vestis</t>
+  </si>
+  <si>
+    <t>Notice 2809</t>
+  </si>
+  <si>
+    <t>Fayette</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SeoCU/dznB7.9oNP3vwVa5FKsBBRVo1lYORfgFck9ve6izIGc</t>
+  </si>
+  <si>
     <t>Carrier Corporation (Franklin Operation)</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2808</t>
   </si>
   <si>
-    <t>Closure</t>
-  </si>
-  <si>
     <t>Simpson</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SaT9p/KKnZ71hXi0EL978hIuC.v3Bd1U65RB8O0A2hOPjfuTw</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Non-Union</t>
-  </si>
-  <si>
     <t>South Central</t>
   </si>
   <si>
-    <t>Levi Strauss &amp; Co</t>
-  </si>
-  <si>
-    <t>Notice 2817</t>
-  </si>
-  <si>
-    <t>Boone</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TM9VN/lwgxGibuF2npQU7o2QpLEJU5UWHFF10IbsYKzWUrR7Q</t>
-  </si>
-  <si>
-    <t>Both</t>
-  </si>
-  <si>
-    <t>Northern Kentucky</t>
-  </si>
-  <si>
-    <t>Conduent (Corporate)</t>
-  </si>
-  <si>
-    <t>Notice 2815</t>
-  </si>
-  <si>
-    <t>Layoff</t>
-  </si>
-  <si>
-    <t>Jefferson County - Louisville</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TFVZ7/Z75_yQpDBRaY9kpSdMax3j_6lKPopGX68JLiqAIsIuo</t>
-  </si>
-  <si>
-    <t>Kentuckiana Works</t>
-  </si>
-  <si>
-    <t>Congo Brands (Alani, Prime, 3D Energy)</t>
-  </si>
-  <si>
-    <t>Notice 2814</t>
-  </si>
-  <si>
-    <t>Jefferson</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TEkTh/ibPumihpj4EjnXfxGEvZueBWuVei8CvUvM1T1u5fOGA</t>
-  </si>
-  <si>
-    <t>RNDC of Kentucky, LLC</t>
-  </si>
-  <si>
-    <t>Notice 2812</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000StexZ/xFnTv1YungNS7J7_kvieFmn654APdTR96QljGfhiY4I</t>
-  </si>
-  <si>
-    <t>Vestis</t>
-  </si>
-  <si>
-    <t>Notice 2809</t>
-  </si>
-  <si>
-    <t>Fayette</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SeoCU/dznB7.9oNP3vwVa5FKsBBRVo1lYORfgFck9ve6izIGc</t>
-  </si>
-  <si>
-    <t>Bluegrass</t>
-  </si>
-  <si>
-    <t>Battelle Memorial Institute E3</t>
-  </si>
-  <si>
     <t>Notice 2804</t>
   </si>
   <si>
-    <t>Madison</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000R7S85/ChUHYkuIxmZGber7XiEFcOqgFvRKvnc5c98o33VA13M</t>
   </si>
   <si>
+    <t>University of Kentucky College of Medicine, Department of Behavioral Science</t>
+  </si>
+  <si>
+    <t>Notice 2801</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QijIb/GEjtAjS7YOxjX3f2jFXLvD9xWYiGkSG8L2omIcWr.kc</t>
+  </si>
+  <si>
+    <t>UK HealthCare-HIV Program Operations (KIRP)</t>
+  </si>
+  <si>
+    <t>Notice 2802</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QiwhG/SbJ3ukBMv1baTmB89A4sXIh4i4KSDZr2HIX7P0PTOLo</t>
+  </si>
+  <si>
     <t>Stella-Jones Corporation</t>
   </si>
   <si>
@@ -196,22 +241,13 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QbQKk/97HSOQBTsXu3P4fz4CdBvLx2l.wNmuRx4f4ngCfIIGc</t>
   </si>
   <si>
-    <t>University of Kentucky College of Medicine, Department of Behavioral Science</t>
-  </si>
-  <si>
-    <t>Notice 2801</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QijIb/GEjtAjS7YOxjX3f2jFXLvD9xWYiGkSG8L2omIcWr.kc</t>
-  </si>
-  <si>
-    <t>UK HealthCare-HIV Program Operations (KIRP)</t>
-  </si>
-  <si>
-    <t>Notice 2802</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QiwhG/SbJ3ukBMv1baTmB89A4sXIh4i4KSDZr2HIX7P0PTOLo</t>
+    <t>Marsden Services LLC</t>
+  </si>
+  <si>
+    <t>Notice 2795</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QBhib/Axgartu79FnT.1puuR2ziNCjL_vVob8mjuIb4H_1rgY</t>
   </si>
   <si>
     <t>Legacy Supply Chain</t>
@@ -232,13 +268,31 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000PDP8f/7oyf.yIT7bga4_8lwf6Gv0CBM6RWkfBtSueOExFzIEk</t>
   </si>
   <si>
-    <t>Marsden Services LLC</t>
-  </si>
-  <si>
-    <t>Notice 2795</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QBhib/Axgartu79FnT.1puuR2ziNCjL_vVob8mjuIb4H_1rgY</t>
+    <t>CC Metals and Alloys</t>
+  </si>
+  <si>
+    <t>Notice 2781</t>
+  </si>
+  <si>
+    <t>Marshall</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000OLBic/__X6qXa.xkYBXDTiFJHDQ5BSQAz0cXx6rE7wdHGW04Y</t>
+  </si>
+  <si>
+    <t>C2 Technologies</t>
+  </si>
+  <si>
+    <t>Notice 2778</t>
+  </si>
+  <si>
+    <t>Out of the State County</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NktkD/ZAn12UJAS6jJoJdozzCAp1D93Q3iZ0Q9vKA3kFS_R1s</t>
+  </si>
+  <si>
+    <t>Out of State</t>
   </si>
   <si>
     <t>Notice 2777</t>
@@ -256,6 +310,18 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000N9QpF/4EEzN4tM6NejTIykMYCa83PGBw3SZK1mgoh_UyK2LBY</t>
   </si>
   <si>
+    <t>HGS CX TECHNOLOGIES INC.</t>
+  </si>
+  <si>
+    <t>Notice 2752</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I</t>
+  </si>
+  <si>
     <t>PARSONS CORPORATION</t>
   </si>
   <si>
@@ -265,19 +331,46 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E</t>
   </si>
   <si>
+    <t>T-Mobile USA, Inc.</t>
+  </si>
+  <si>
+    <t>Notice 2750</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
+  </si>
+  <si>
     <t>Notice 2749</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M4S4L/LQzXQpOvkAZMAIHIvymYA.svisC5GHMdGM_kT4c1.lE</t>
   </si>
   <si>
-    <t>T-Mobile USA, Inc.</t>
-  </si>
-  <si>
-    <t>Notice 2750</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
+    <t>Bechtel Parsons Blue Grass</t>
+  </si>
+  <si>
+    <t>Notice 2746</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000LOTKv/q2vS9oQb.f2kr9RxJzzteN8ihZx.77HgJflmO2hsKsE</t>
+  </si>
+  <si>
+    <t>Notice 2743</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng</t>
+  </si>
+  <si>
+    <t>Notice 2741</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L0m5N/dzNGJ0evF7p0eqe3gkJ1A2xmpiaHfNjC0uxTXzAc0aA</t>
+  </si>
+  <si>
+    <t>Notice 2735</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000K4yZx/hjNHC46tUotP6fQSFooblwIQMdy9n7n9jwycpYtoK2A</t>
   </si>
   <si>
     <t>Blue Oval SK Group/Battery Plant</t>
@@ -295,73 +388,10 @@
     <t>Lincoln Trail</t>
   </si>
   <si>
-    <t>HGS CX TECHNOLOGIES INC.</t>
-  </si>
-  <si>
-    <t>Notice 2752</t>
-  </si>
-  <si>
-    <t>Franklin</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I</t>
-  </si>
-  <si>
-    <t>Notice 2743</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng</t>
-  </si>
-  <si>
-    <t>CC Metals and Alloys</t>
-  </si>
-  <si>
-    <t>Notice 2781</t>
-  </si>
-  <si>
-    <t>Marshall</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000OLBic/__X6qXa.xkYBXDTiFJHDQ5BSQAz0cXx6rE7wdHGW04Y</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Bechtel Parsons Blue Grass</t>
-  </si>
-  <si>
-    <t>Notice 2746</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000LOTKv/q2vS9oQb.f2kr9RxJzzteN8ihZx.77HgJflmO2hsKsE</t>
-  </si>
-  <si>
-    <t>C2 Technologies</t>
-  </si>
-  <si>
-    <t>Notice 2778</t>
-  </si>
-  <si>
-    <t>Out of the State County</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NktkD/ZAn12UJAS6jJoJdozzCAp1D93Q3iZ0Q9vKA3kFS_R1s</t>
-  </si>
-  <si>
-    <t>Out of State</t>
-  </si>
-  <si>
-    <t>Notice 2741</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L0m5N/dzNGJ0evF7p0eqe3gkJ1A2xmpiaHfNjC0uxTXzAc0aA</t>
-  </si>
-  <si>
-    <t>Notice 2735</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000K4yZx/hjNHC46tUotP6fQSFooblwIQMdy9n7n9jwycpYtoK2A</t>
+    <t>Notice 2733</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000JzlTh/JZSB0EQsN_7JjzgrGG5lPxUfnNVre1K_KN5cOIxZ1aQ</t>
   </si>
   <si>
     <t>Thyssenkrupp</t>
@@ -371,12 +401,6 @@
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Jzw2X/XaV0.3wPmFgN09imJ4PSCxAVb1lNP0z6Glx2vjhIsrA</t>
-  </si>
-  <si>
-    <t>Notice 2733</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000JzlTh/JZSB0EQsN_7JjzgrGG5lPxUfnNVre1K_KN5cOIxZ1aQ</t>
   </si>
 </sst>
 </file>
@@ -1237,19 +1261,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D38A8E8-6DE1-4187-86ED-1E269BEB91A6}">
-  <dimension ref="A1:M30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C981694F-F4EB-4915-9BE9-7CBF662BEBC9}">
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="63.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1309,180 +1323,186 @@
         <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>46185</v>
+        <v>46237</v>
       </c>
       <c r="G2">
-        <v>333415</v>
+        <v>11141</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="J2" s="1">
-        <v>46264</v>
-      </c>
-      <c r="K2" t="s">
+        <v>46237</v>
+      </c>
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>20</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G3">
+        <v>541715</v>
+      </c>
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1">
-        <v>46203</v>
-      </c>
-      <c r="G3">
-        <v>315250</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1">
+        <v>46289</v>
+      </c>
+      <c r="K3" t="s">
         <v>25</v>
       </c>
-      <c r="I3">
-        <v>303</v>
-      </c>
-      <c r="J3" s="1">
-        <v>46264</v>
-      </c>
       <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
         <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46213</v>
+      </c>
+      <c r="G4">
+        <v>493110</v>
+      </c>
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4">
+        <v>73</v>
+      </c>
+      <c r="J4" s="1">
+        <v>46273</v>
+      </c>
+      <c r="K4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1">
-        <v>46202</v>
-      </c>
-      <c r="G4">
-        <v>561110</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4">
-        <v>24</v>
-      </c>
-      <c r="J4" s="1">
-        <v>46262</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>19</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>20</v>
-      </c>
-      <c r="M4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46203</v>
+      </c>
+      <c r="G5">
+        <v>315250</v>
+      </c>
+      <c r="H5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="I5">
+        <v>303</v>
+      </c>
+      <c r="J5" s="1">
+        <v>46264</v>
+      </c>
+      <c r="L5" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46199</v>
-      </c>
-      <c r="G5">
-        <v>312111</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5">
-        <v>28</v>
-      </c>
-      <c r="J5" s="1">
-        <v>46260</v>
-      </c>
-      <c r="K5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>20</v>
-      </c>
-      <c r="M5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F6" s="1">
+        <v>46202</v>
+      </c>
+      <c r="G6">
+        <v>561110</v>
+      </c>
+      <c r="H6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46191</v>
-      </c>
-      <c r="G6">
-        <v>424820</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6">
+        <v>24</v>
+      </c>
+      <c r="J6" s="1">
+        <v>46262</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
         <v>40</v>
-      </c>
-      <c r="I6">
-        <v>174</v>
-      </c>
-      <c r="J6" s="1">
-        <v>46251</v>
-      </c>
-      <c r="M6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -1496,203 +1516,203 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
         <v>43</v>
       </c>
       <c r="F7" s="1">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="G7">
-        <v>812332</v>
+        <v>312111</v>
       </c>
       <c r="H7" t="s">
         <v>44</v>
       </c>
       <c r="I7">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J7" s="1">
-        <v>46249</v>
+        <v>46260</v>
       </c>
       <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
         <v>19</v>
       </c>
-      <c r="L7" t="s">
-        <v>20</v>
-      </c>
       <c r="M7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
         <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1">
-        <v>46149</v>
+        <v>46191</v>
       </c>
       <c r="G8">
-        <v>541715</v>
+        <v>424820</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>174</v>
       </c>
       <c r="J8" s="1">
-        <v>46209</v>
-      </c>
-      <c r="L8" t="s">
-        <v>20</v>
+        <v>46251</v>
       </c>
       <c r="M8" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F9" s="1">
-        <v>46142</v>
+        <v>46189</v>
       </c>
       <c r="G9">
-        <v>321114</v>
+        <v>812332</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I9">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="J9" s="1">
-        <v>46204</v>
+        <v>46249</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F10" s="1">
-        <v>46141</v>
+        <v>46185</v>
       </c>
       <c r="G10">
-        <v>722310</v>
+        <v>333415</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I10">
-        <v>923</v>
+        <v>70</v>
       </c>
       <c r="J10" s="1">
-        <v>46203</v>
+        <v>46264</v>
       </c>
       <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
         <v>19</v>
       </c>
-      <c r="L10" t="s">
-        <v>26</v>
-      </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G11">
+        <v>541715</v>
+      </c>
+      <c r="H11" t="s">
         <v>58</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46147</v>
-      </c>
-      <c r="G11">
-        <v>611310</v>
-      </c>
-      <c r="H11" t="s">
-        <v>60</v>
-      </c>
       <c r="I11">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="J11" s="1">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1">
         <v>46147</v>
@@ -1701,95 +1721,95 @@
         <v>611310</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I12">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J12" s="1">
         <v>46203</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F13" s="1">
-        <v>46113</v>
+        <v>46147</v>
       </c>
       <c r="G13">
-        <v>488510</v>
+        <v>611310</v>
       </c>
       <c r="H13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I13">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="J13" s="1">
-        <v>46179</v>
+        <v>46203</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="F14" s="1">
-        <v>46113</v>
+        <v>46142</v>
       </c>
       <c r="G14">
-        <v>492110</v>
+        <v>321114</v>
       </c>
       <c r="H14" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14">
+        <v>67</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46204</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" t="s">
         <v>69</v>
-      </c>
-      <c r="I14">
-        <v>65</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46175</v>
-      </c>
-      <c r="L14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1803,425 +1823,428 @@
         <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F15" s="1">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="G15">
-        <v>56172</v>
+        <v>722310</v>
       </c>
       <c r="H15" t="s">
         <v>72</v>
       </c>
       <c r="I15">
-        <v>106</v>
+        <v>923</v>
       </c>
       <c r="J15" s="1">
-        <v>46152</v>
+        <v>46203</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>35</v>
       </c>
       <c r="M15" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F16" s="1">
-        <v>46086</v>
+        <v>46128</v>
       </c>
       <c r="G16">
-        <v>541715</v>
+        <v>56172</v>
       </c>
       <c r="H16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="J16" s="1">
-        <v>46148</v>
+        <v>46152</v>
       </c>
       <c r="K16" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F17" s="1">
-        <v>46077</v>
+        <v>46113</v>
       </c>
       <c r="G17">
-        <v>423120</v>
+        <v>488510</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I17">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="J17" s="1">
-        <v>46142</v>
+        <v>46179</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M17" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F18" s="1">
-        <v>46056</v>
+        <v>46113</v>
       </c>
       <c r="G18">
-        <v>541330</v>
+        <v>492110</v>
       </c>
       <c r="H18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="J18" s="1">
-        <v>46128</v>
+        <v>46175</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M18" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F19" s="1">
-        <v>46051</v>
+        <v>46098</v>
       </c>
       <c r="G19">
-        <v>541715</v>
+        <v>33331</v>
       </c>
       <c r="H19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I19">
-        <v>30</v>
+        <v>114</v>
       </c>
       <c r="J19" s="1">
-        <v>46114</v>
+        <v>46105</v>
+      </c>
+      <c r="K19" t="s">
+        <v>31</v>
       </c>
       <c r="L19" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M19" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="F20" s="1">
-        <v>46053</v>
+        <v>46087</v>
       </c>
       <c r="G20">
-        <v>517112</v>
+        <v>545410</v>
       </c>
       <c r="H20" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I20">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="J20" s="1">
-        <v>46114</v>
-      </c>
-      <c r="K20" t="s">
+        <v>46087</v>
+      </c>
+      <c r="L20" t="s">
         <v>19</v>
       </c>
-      <c r="L20" t="s">
-        <v>20</v>
-      </c>
       <c r="M20" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="F21" s="1">
-        <v>46007</v>
+        <v>46086</v>
       </c>
       <c r="G21">
-        <v>335911</v>
+        <v>541715</v>
       </c>
       <c r="H21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I21">
-        <v>1514</v>
+        <v>5</v>
       </c>
       <c r="J21" s="1">
-        <v>46112</v>
+        <v>46148</v>
+      </c>
+      <c r="K21" t="s">
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="F22" s="1">
-        <v>46057</v>
+        <v>46077</v>
       </c>
       <c r="G22">
-        <v>541611</v>
+        <v>423120</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="J22" s="1">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="L22" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" t="s">
         <v>20</v>
-      </c>
-      <c r="M22" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F23" s="1">
-        <v>46034</v>
+        <v>46057</v>
       </c>
       <c r="G23">
-        <v>541330</v>
+        <v>541611</v>
       </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I23">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="J23" s="1">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M23" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="F24" s="1">
-        <v>46098</v>
+        <v>46056</v>
       </c>
       <c r="G24">
-        <v>33331</v>
+        <v>541330</v>
       </c>
       <c r="H24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I24">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="J24" s="1">
-        <v>46105</v>
-      </c>
-      <c r="K24" t="s">
-        <v>101</v>
+        <v>46128</v>
       </c>
       <c r="L24" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" t="s">
         <v>26</v>
-      </c>
-      <c r="M24" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F25" s="1">
-        <v>46041</v>
+        <v>46053</v>
       </c>
       <c r="G25">
-        <v>541330</v>
+        <v>517112</v>
       </c>
       <c r="H25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I25">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="J25" s="1">
-        <v>46101</v>
+        <v>46114</v>
+      </c>
+      <c r="K25" t="s">
+        <v>25</v>
       </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M25" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -2230,186 +2253,300 @@
         <v>106</v>
       </c>
       <c r="D26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46051</v>
+      </c>
+      <c r="G26">
+        <v>541715</v>
+      </c>
+      <c r="H26" t="s">
+        <v>107</v>
+      </c>
+      <c r="I26">
         <v>30</v>
       </c>
-      <c r="E26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46087</v>
-      </c>
-      <c r="G26">
-        <v>545410</v>
-      </c>
-      <c r="H26" t="s">
-        <v>108</v>
-      </c>
-      <c r="I26">
-        <v>2</v>
-      </c>
       <c r="J26" s="1">
-        <v>46087</v>
+        <v>46114</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M26" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F27" s="1">
-        <v>46027</v>
+        <v>46041</v>
       </c>
       <c r="G27">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I27">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="J27" s="1">
-        <v>46086</v>
+        <v>46101</v>
       </c>
       <c r="L27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M27" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>16</v>
       </c>
       <c r="E28" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F28" s="1">
-        <v>46008</v>
+        <v>46034</v>
       </c>
       <c r="G28">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I28">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="J28" s="1">
-        <v>46071</v>
+        <v>46107</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M28" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1">
-        <v>46006</v>
+        <v>46027</v>
       </c>
       <c r="G29">
-        <v>332991</v>
+        <v>541715</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I29">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="J29" s="1">
-        <v>46066</v>
-      </c>
-      <c r="K29" t="s">
-        <v>101</v>
+        <v>46086</v>
       </c>
       <c r="L29" t="s">
+        <v>19</v>
+      </c>
+      <c r="M29" t="s">
         <v>26</v>
-      </c>
-      <c r="M29" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
         <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1">
+        <v>46008</v>
+      </c>
+      <c r="G30">
+        <v>541715</v>
+      </c>
+      <c r="H30" t="s">
+        <v>116</v>
+      </c>
+      <c r="I30">
+        <v>17</v>
+      </c>
+      <c r="J30" s="1">
+        <v>46071</v>
+      </c>
+      <c r="L30" t="s">
+        <v>19</v>
+      </c>
+      <c r="M30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46007</v>
+      </c>
+      <c r="G31">
+        <v>335911</v>
+      </c>
+      <c r="H31" t="s">
+        <v>120</v>
+      </c>
+      <c r="I31">
+        <v>1514</v>
+      </c>
+      <c r="J31" s="1">
+        <v>46112</v>
+      </c>
+      <c r="L31" t="s">
+        <v>19</v>
+      </c>
+      <c r="M31" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="1">
         <v>46006</v>
       </c>
-      <c r="G30">
+      <c r="G32">
         <v>541330</v>
       </c>
-      <c r="H30" t="s">
-        <v>118</v>
-      </c>
-      <c r="I30">
+      <c r="H32" t="s">
+        <v>123</v>
+      </c>
+      <c r="I32">
         <v>32</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J32" s="1">
         <v>46038</v>
       </c>
-      <c r="L30" t="s">
+      <c r="L32" t="s">
+        <v>19</v>
+      </c>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G33">
+        <v>332991</v>
+      </c>
+      <c r="H33" t="s">
+        <v>126</v>
+      </c>
+      <c r="I33">
+        <v>77</v>
+      </c>
+      <c r="J33" s="1">
+        <v>46066</v>
+      </c>
+      <c r="K33" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" t="s">
         <v>20</v>
-      </c>
-      <c r="M30" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2418,8 +2555,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004C7EC705FC200A4790775D01706F91EB" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94b9a123c94490f7abe5591ccbd17c77">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="ac1070bf-3ce6-4b87-ab2d-f70092a0dc57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="08997c8a8d0ea3014a243e24c4d1c3c3" ns1:_="" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004C7EC705FC200A4790775D01706F91EB" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f7e2e47970e9e2329bc055aadd950cc0">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="ac1070bf-3ce6-4b87-ab2d-f70092a0dc57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3c3e2c4b5f2a88263a472d43dc6e806e" ns1:_="" ns2:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="ac1070bf-3ce6-4b87-ab2d-f70092a0dc57"/>
     <xsd:element name="properties">
@@ -2593,13 +2730,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{851C0AD5-BA3F-4A00-9185-B7774E96179B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2592280F-20D6-4DF3-B6D5-EA1E5B10E984}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67BE8CB2-DF45-4880-B87C-95F3E971B583}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5574EC29-CA24-477F-A168-38132AC75967}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91D683C8-6211-448E-A4D8-3B6351CE4D84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2600891-548E-4B9B-84C5-5A2673519CE1}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D953905B-3ADC-465F-8865-624A3A61E61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{10C10295-5BE9-4027-9176-EECA048656CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F6414ACC-BC32-49BD-9AFE-9BCDF960C6C9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6E0BF9D4-2591-4720-A4E7-9CC731411A1D}"/>
   </bookViews>
   <sheets>
-    <sheet name="WARN Report 08052026" sheetId="1" r:id="rId1"/>
+    <sheet name="Website-WARN Notice Report 0812" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="130">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,144 +61,183 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>SMBC Manubank</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2833</t>
+  </si>
+  <si>
+    <t>Closure</t>
+  </si>
+  <si>
+    <t>Out of the State County</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000VL2BR/5d9tGyNLzSi3WbE5tOFi3W5X_QW76ajmCZoBGb8Hgfo</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Out of State</t>
+  </si>
+  <si>
+    <t>Battelle Memorial Institute E3</t>
+  </si>
+  <si>
+    <t>Notice 2820</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000CLJC1/DbyYp68sVwKoN.GQkRf5EyzUntPUC3BOkVG9L_FcJUc</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Non-Union</t>
+  </si>
+  <si>
+    <t>Bluegrass</t>
+  </si>
+  <si>
+    <t>Geodis</t>
+  </si>
+  <si>
+    <t>Notice 2818</t>
+  </si>
+  <si>
+    <t>Layoff</t>
+  </si>
+  <si>
+    <t>Boone</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TnvHN/MsOC3lIkOTZLTZOZQRMslPIsqoxbV_q80J1A.Yw1omU</t>
+  </si>
+  <si>
+    <t>Northern Kentucky</t>
+  </si>
+  <si>
+    <t>Carrier Corporation (Franklin Operation)</t>
+  </si>
+  <si>
+    <t>Notice 2808</t>
+  </si>
+  <si>
+    <t>Simpson</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SaT9p/KKnZ71hXi0EL978hIuC.v3Bd1U65RB8O0A2hOPjfuTw</t>
+  </si>
+  <si>
+    <t>South Central</t>
+  </si>
+  <si>
+    <t>Levi Strauss &amp; Co</t>
+  </si>
+  <si>
+    <t>Notice 2817</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TM9VN/lwgxGibuF2npQU7o2QpLEJU5UWHFF10IbsYKzWUrR7Q</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Conduent (Corporate)</t>
+  </si>
+  <si>
+    <t>Notice 2815</t>
+  </si>
+  <si>
+    <t>Jefferson County - Louisville</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TFVZ7/Z75_yQpDBRaY9kpSdMax3j_6lKPopGX68JLiqAIsIuo</t>
+  </si>
+  <si>
+    <t>Kentuckiana Works</t>
+  </si>
+  <si>
+    <t>Congo Brands (Alani, Prime, 3D Energy)</t>
+  </si>
+  <si>
+    <t>Notice 2814</t>
+  </si>
+  <si>
+    <t>Jefferson</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TEkTh/ibPumihpj4EjnXfxGEvZueBWuVei8CvUvM1T1u5fOGA</t>
+  </si>
+  <si>
+    <t>RNDC of Kentucky, LLC</t>
+  </si>
+  <si>
+    <t>Notice 2812</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000StexZ/xFnTv1YungNS7J7_kvieFmn654APdTR96QljGfhiY4I</t>
+  </si>
+  <si>
+    <t>Vestis</t>
+  </si>
+  <si>
+    <t>Notice 2809</t>
+  </si>
+  <si>
+    <t>Fayette</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SeoCU/dznB7.9oNP3vwVa5FKsBBRVo1lYORfgFck9ve6izIGc</t>
+  </si>
+  <si>
     <t>80 Acres Farm</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2831</t>
   </si>
   <si>
-    <t>Closure</t>
-  </si>
-  <si>
-    <t>Boone</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000UxY4Q/GF0gz3XikIqoUSgtEsWvpqt7e_5PwKLvyRqhww3LW.c</t>
   </si>
   <si>
-    <t>Non-Union</t>
-  </si>
-  <si>
-    <t>Northern Kentucky</t>
-  </si>
-  <si>
-    <t>Battelle Memorial Institute E3</t>
-  </si>
-  <si>
-    <t>Notice 2820</t>
-  </si>
-  <si>
-    <t>Madison</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000CLJC1/DbyYp68sVwKoN.GQkRf5EyzUntPUC3BOkVG9L_FcJUc</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Bluegrass</t>
-  </si>
-  <si>
-    <t>Geodis</t>
-  </si>
-  <si>
-    <t>Notice 2818</t>
-  </si>
-  <si>
-    <t>Layoff</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TnvHN/MsOC3lIkOTZLTZOZQRMslPIsqoxbV_q80J1A.Yw1omU</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Levi Strauss &amp; Co</t>
-  </si>
-  <si>
-    <t>Notice 2817</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TM9VN/lwgxGibuF2npQU7o2QpLEJU5UWHFF10IbsYKzWUrR7Q</t>
-  </si>
-  <si>
-    <t>Both</t>
-  </si>
-  <si>
-    <t>Conduent (Corporate)</t>
-  </si>
-  <si>
-    <t>Notice 2815</t>
-  </si>
-  <si>
-    <t>Jefferson County - Louisville</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TFVZ7/Z75_yQpDBRaY9kpSdMax3j_6lKPopGX68JLiqAIsIuo</t>
-  </si>
-  <si>
-    <t>Kentuckiana Works</t>
-  </si>
-  <si>
-    <t>Congo Brands (Alani, Prime, 3D Energy)</t>
-  </si>
-  <si>
-    <t>Notice 2814</t>
-  </si>
-  <si>
-    <t>Jefferson</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TEkTh/ibPumihpj4EjnXfxGEvZueBWuVei8CvUvM1T1u5fOGA</t>
-  </si>
-  <si>
-    <t>RNDC of Kentucky, LLC</t>
-  </si>
-  <si>
-    <t>Notice 2812</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000StexZ/xFnTv1YungNS7J7_kvieFmn654APdTR96QljGfhiY4I</t>
-  </si>
-  <si>
-    <t>Vestis</t>
-  </si>
-  <si>
-    <t>Notice 2809</t>
-  </si>
-  <si>
-    <t>Fayette</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SeoCU/dznB7.9oNP3vwVa5FKsBBRVo1lYORfgFck9ve6izIGc</t>
-  </si>
-  <si>
-    <t>Carrier Corporation (Franklin Operation)</t>
-  </si>
-  <si>
-    <t>Notice 2808</t>
-  </si>
-  <si>
-    <t>Simpson</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000SaT9p/KKnZ71hXi0EL978hIuC.v3Bd1U65RB8O0A2hOPjfuTw</t>
-  </si>
-  <si>
-    <t>South Central</t>
-  </si>
-  <si>
     <t>Notice 2804</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000R7S85/ChUHYkuIxmZGber7XiEFcOqgFvRKvnc5c98o33VA13M</t>
   </si>
   <si>
+    <t>Stella-Jones Corporation</t>
+  </si>
+  <si>
+    <t>Notice 2798</t>
+  </si>
+  <si>
+    <t>Fulton</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QbOyr/8QOonL2ZzmNjafz_Iy2AlWTpg0fhL6GmSd9ElrJhDe4</t>
+  </si>
+  <si>
+    <t>Western Kentucky</t>
+  </si>
+  <si>
+    <t>Aramark Campus, LLC (University of Kentucky)</t>
+  </si>
+  <si>
+    <t>Notice 2799</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QbQKk/97HSOQBTsXu3P4fz4CdBvLx2l.wNmuRx4f4ngCfIIGc</t>
+  </si>
+  <si>
     <t>University of Kentucky College of Medicine, Department of Behavioral Science</t>
   </si>
   <si>
@@ -217,28 +256,22 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QiwhG/SbJ3ukBMv1baTmB89A4sXIh4i4KSDZr2HIX7P0PTOLo</t>
   </si>
   <si>
-    <t>Stella-Jones Corporation</t>
-  </si>
-  <si>
-    <t>Notice 2798</t>
-  </si>
-  <si>
-    <t>Fulton</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QbOyr/8QOonL2ZzmNjafz_Iy2AlWTpg0fhL6GmSd9ElrJhDe4</t>
-  </si>
-  <si>
-    <t>Western Kentucky</t>
-  </si>
-  <si>
-    <t>Aramark Campus, LLC (University of Kentucky)</t>
-  </si>
-  <si>
-    <t>Notice 2799</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QbQKk/97HSOQBTsXu3P4fz4CdBvLx2l.wNmuRx4f4ngCfIIGc</t>
+    <t>Legacy Supply Chain</t>
+  </si>
+  <si>
+    <t>Notice 2785</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000PDRqP/Qx1TWK7zpU5r.9tnXH1SaSnmys5ktC.Y2JwvY0izamU</t>
+  </si>
+  <si>
+    <t>Bluegrass UPS Facility</t>
+  </si>
+  <si>
+    <t>Notice 2786</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000PDP8f/7oyf.yIT7bga4_8lwf6Gv0CBM6RWkfBtSueOExFzIEk</t>
   </si>
   <si>
     <t>Marsden Services LLC</t>
@@ -250,22 +283,76 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000QBhib/Axgartu79FnT.1puuR2ziNCjL_vVob8mjuIb4H_1rgY</t>
   </si>
   <si>
-    <t>Legacy Supply Chain</t>
-  </si>
-  <si>
-    <t>Notice 2785</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000PDRqP/Qx1TWK7zpU5r.9tnXH1SaSnmys5ktC.Y2JwvY0izamU</t>
-  </si>
-  <si>
-    <t>Bluegrass UPS Facility</t>
-  </si>
-  <si>
-    <t>Notice 2786</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000PDP8f/7oyf.yIT7bga4_8lwf6Gv0CBM6RWkfBtSueOExFzIEk</t>
+    <t>Notice 2777</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NkU99/oU8_gO4ZAXjo2Ew8cYx0YkQwqLrKuxfHbjNc4HWS0kg</t>
+  </si>
+  <si>
+    <t>FRAM First Brands Group, LLC</t>
+  </si>
+  <si>
+    <t>Notice 2763</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000N9QpF/4EEzN4tM6NejTIykMYCa83PGBw3SZK1mgoh_UyK2LBY</t>
+  </si>
+  <si>
+    <t>PARSONS CORPORATION</t>
+  </si>
+  <si>
+    <t>Notice 2751</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E</t>
+  </si>
+  <si>
+    <t>Notice 2749</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M4S4L/LQzXQpOvkAZMAIHIvymYA.svisC5GHMdGM_kT4c1.lE</t>
+  </si>
+  <si>
+    <t>T-Mobile USA, Inc.</t>
+  </si>
+  <si>
+    <t>Notice 2750</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
+  </si>
+  <si>
+    <t>Blue Oval SK Group/Battery Plant</t>
+  </si>
+  <si>
+    <t>Notice 2737</t>
+  </si>
+  <si>
+    <t>Hardin</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Mgcyf/R0rOEwqaqbq2_BLO_3h_bVZSr5L.ydfELzP9lSJBHds</t>
+  </si>
+  <si>
+    <t>Lincoln Trail</t>
+  </si>
+  <si>
+    <t>HGS CX TECHNOLOGIES INC.</t>
+  </si>
+  <si>
+    <t>Notice 2752</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I</t>
+  </si>
+  <si>
+    <t>Notice 2743</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng</t>
   </si>
   <si>
     <t>CC Metals and Alloys</t>
@@ -280,87 +367,24 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000OLBic/__X6qXa.xkYBXDTiFJHDQ5BSQAz0cXx6rE7wdHGW04Y</t>
   </si>
   <si>
+    <t>Bechtel Parsons Blue Grass</t>
+  </si>
+  <si>
+    <t>Notice 2746</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000LOTKv/q2vS9oQb.f2kr9RxJzzteN8ihZx.77HgJflmO2hsKsE</t>
+  </si>
+  <si>
     <t>C2 Technologies</t>
   </si>
   <si>
     <t>Notice 2778</t>
   </si>
   <si>
-    <t>Out of the State County</t>
-  </si>
-  <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NktkD/ZAn12UJAS6jJoJdozzCAp1D93Q3iZ0Q9vKA3kFS_R1s</t>
   </si>
   <si>
-    <t>Out of State</t>
-  </si>
-  <si>
-    <t>Notice 2777</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000NkU99/oU8_gO4ZAXjo2Ew8cYx0YkQwqLrKuxfHbjNc4HWS0kg</t>
-  </si>
-  <si>
-    <t>FRAM First Brands Group, LLC</t>
-  </si>
-  <si>
-    <t>Notice 2763</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000N9QpF/4EEzN4tM6NejTIykMYCa83PGBw3SZK1mgoh_UyK2LBY</t>
-  </si>
-  <si>
-    <t>HGS CX TECHNOLOGIES INC.</t>
-  </si>
-  <si>
-    <t>Notice 2752</t>
-  </si>
-  <si>
-    <t>Franklin</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000MDak9/hF60Ln_.PdltYj6RXdpLbWKlUqLLtCsZ9.t8h7FgM0I</t>
-  </si>
-  <si>
-    <t>PARSONS CORPORATION</t>
-  </si>
-  <si>
-    <t>Notice 2751</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M8YzA/1d6nmValVuIvCOH01FjBHwsqJgHVTnU5UWcYQv8a21E</t>
-  </si>
-  <si>
-    <t>T-Mobile USA, Inc.</t>
-  </si>
-  <si>
-    <t>Notice 2750</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M6GGj/Yf18rFfiq7i9NKtvhRtKlBMX7v2yXq7s8g_.HwdUHDs</t>
-  </si>
-  <si>
-    <t>Notice 2749</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000M4S4L/LQzXQpOvkAZMAIHIvymYA.svisC5GHMdGM_kT4c1.lE</t>
-  </si>
-  <si>
-    <t>Bechtel Parsons Blue Grass</t>
-  </si>
-  <si>
-    <t>Notice 2746</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000LOTKv/q2vS9oQb.f2kr9RxJzzteN8ihZx.77HgJflmO2hsKsE</t>
-  </si>
-  <si>
-    <t>Notice 2743</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000L4jAX/ZQFgTnTm2P1TMZqWE4EBRk9m8L0F_Cvf9QY1j2M4Bng</t>
-  </si>
-  <si>
     <t>Notice 2741</t>
   </si>
   <si>
@@ -373,34 +397,19 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000K4yZx/hjNHC46tUotP6fQSFooblwIQMdy9n7n9jwycpYtoK2A</t>
   </si>
   <si>
-    <t>Blue Oval SK Group/Battery Plant</t>
-  </si>
-  <si>
-    <t>Notice 2737</t>
-  </si>
-  <si>
-    <t>Hardin</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Mgcyf/R0rOEwqaqbq2_BLO_3h_bVZSr5L.ydfELzP9lSJBHds</t>
-  </si>
-  <si>
-    <t>Lincoln Trail</t>
+    <t>Thyssenkrupp</t>
+  </si>
+  <si>
+    <t>Notice 2734</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Jzw2X/XaV0.3wPmFgN09imJ4PSCxAVb1lNP0z6Glx2vjhIsrA</t>
   </si>
   <si>
     <t>Notice 2733</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000JzlTh/JZSB0EQsN_7JjzgrGG5lPxUfnNVre1K_KN5cOIxZ1aQ</t>
-  </si>
-  <si>
-    <t>Thyssenkrupp</t>
-  </si>
-  <si>
-    <t>Notice 2734</t>
-  </si>
-  <si>
-    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Jzw2X/XaV0.3wPmFgN09imJ4PSCxAVb1lNP0z6Glx2vjhIsrA</t>
   </si>
 </sst>
 </file>
@@ -1261,8 +1270,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C981694F-F4EB-4915-9BE9-7CBF662BEBC9}">
-  <dimension ref="A1:M33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939CF104-FDE3-4B3C-8BF2-1A78776F5BD6}">
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1323,21 +1332,21 @@
         <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="G2">
-        <v>11141</v>
+        <v>522110</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="J2" s="1">
-        <v>46237</v>
-      </c>
-      <c r="L2" t="s">
+        <v>46304</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
       </c>
       <c r="M2" t="s">
@@ -1379,27 +1388,27 @@
         <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1">
         <v>46213</v>
@@ -1408,7 +1417,7 @@
         <v>493110</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4">
         <v>73</v>
@@ -1417,495 +1426,495 @@
         <v>46273</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F5" s="1">
-        <v>46203</v>
+        <v>46185</v>
       </c>
       <c r="G5">
-        <v>315250</v>
+        <v>333415</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>303</v>
+        <v>70</v>
       </c>
       <c r="J5" s="1">
         <v>46264</v>
       </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="G6">
-        <v>561110</v>
+        <v>315250</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I6">
-        <v>24</v>
+        <v>303</v>
       </c>
       <c r="J6" s="1">
-        <v>46262</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
+        <v>46264</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="M6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G7">
-        <v>312111</v>
+        <v>561110</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J7" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F8" s="1">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="G8">
-        <v>424820</v>
+        <v>312111</v>
       </c>
       <c r="H8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8">
+        <v>28</v>
+      </c>
+      <c r="J8" s="1">
+        <v>46260</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
         <v>47</v>
-      </c>
-      <c r="I8">
-        <v>174</v>
-      </c>
-      <c r="J8" s="1">
-        <v>46251</v>
-      </c>
-      <c r="M8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="G9">
-        <v>812332</v>
+        <v>424820</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I9">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="J9" s="1">
-        <v>46249</v>
-      </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>19</v>
+        <v>46251</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F10" s="1">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="G10">
-        <v>333415</v>
+        <v>812332</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I10">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="J10" s="1">
-        <v>46264</v>
+        <v>46249</v>
       </c>
       <c r="K10" t="s">
         <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
         <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1">
-        <v>46149</v>
+        <v>46237</v>
       </c>
       <c r="G11">
-        <v>541715</v>
+        <v>11141</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="J11" s="1">
-        <v>46209</v>
+        <v>46237</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="G12">
-        <v>611310</v>
+        <v>541715</v>
       </c>
       <c r="H12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I12">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="J12" s="1">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F13" s="1">
-        <v>46147</v>
+        <v>46142</v>
       </c>
       <c r="G13">
-        <v>611310</v>
+        <v>321114</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I13">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J13" s="1">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F14" s="1">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="G14">
-        <v>321114</v>
+        <v>722310</v>
       </c>
       <c r="H14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I14">
-        <v>67</v>
+        <v>923</v>
       </c>
       <c r="J14" s="1">
-        <v>46204</v>
+        <v>46203</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F15" s="1">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="G15">
-        <v>722310</v>
+        <v>611310</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I15">
-        <v>923</v>
+        <v>36</v>
       </c>
       <c r="J15" s="1">
         <v>46203</v>
       </c>
-      <c r="K15" t="s">
-        <v>25</v>
-      </c>
       <c r="L15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F16" s="1">
-        <v>46128</v>
+        <v>46147</v>
       </c>
       <c r="G16">
-        <v>56172</v>
+        <v>611310</v>
       </c>
       <c r="H16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I16">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="J16" s="1">
-        <v>46152</v>
-      </c>
-      <c r="K16" t="s">
-        <v>25</v>
+        <v>46203</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F17" s="1">
         <v>46113</v>
@@ -1914,7 +1923,7 @@
         <v>488510</v>
       </c>
       <c r="H17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I17">
         <v>123</v>
@@ -1923,27 +1932,27 @@
         <v>46179</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F18" s="1">
         <v>46113</v>
@@ -1952,7 +1961,7 @@
         <v>492110</v>
       </c>
       <c r="H18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I18">
         <v>65</v>
@@ -1961,56 +1970,53 @@
         <v>46175</v>
       </c>
       <c r="L18" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M18" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="F19" s="1">
-        <v>46098</v>
+        <v>46128</v>
       </c>
       <c r="G19">
-        <v>33331</v>
+        <v>56172</v>
       </c>
       <c r="H19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I19">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="J19" s="1">
-        <v>46105</v>
+        <v>46152</v>
       </c>
       <c r="K19" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -2019,232 +2025,232 @@
         <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G20">
+        <v>541715</v>
+      </c>
+      <c r="H20" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="1">
-        <v>46087</v>
-      </c>
-      <c r="G20">
-        <v>545410</v>
-      </c>
-      <c r="H20" t="s">
-        <v>89</v>
-      </c>
       <c r="I20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J20" s="1">
-        <v>46087</v>
+        <v>46148</v>
+      </c>
+      <c r="K20" t="s">
+        <v>25</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F21" s="1">
-        <v>46086</v>
+        <v>46077</v>
       </c>
       <c r="G21">
-        <v>541715</v>
+        <v>423120</v>
       </c>
       <c r="H21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="J21" s="1">
-        <v>46148</v>
-      </c>
-      <c r="K21" t="s">
-        <v>25</v>
+        <v>46142</v>
       </c>
       <c r="L21" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
         <v>93</v>
-      </c>
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
-        <v>94</v>
       </c>
       <c r="D22" t="s">
         <v>16</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F22" s="1">
-        <v>46077</v>
+        <v>46056</v>
       </c>
       <c r="G22">
-        <v>423120</v>
+        <v>541330</v>
       </c>
       <c r="H22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I22">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="J22" s="1">
-        <v>46142</v>
+        <v>46128</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46051</v>
+      </c>
+      <c r="G23">
+        <v>541715</v>
+      </c>
+      <c r="H23" t="s">
         <v>96</v>
       </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G23">
-        <v>541611</v>
-      </c>
-      <c r="H23" t="s">
-        <v>99</v>
-      </c>
       <c r="I23">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J23" s="1">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="L23" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F24" s="1">
-        <v>46056</v>
+        <v>46053</v>
       </c>
       <c r="G24">
-        <v>541330</v>
+        <v>517112</v>
       </c>
       <c r="H24" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="J24" s="1">
-        <v>46128</v>
+        <v>46114</v>
+      </c>
+      <c r="K24" t="s">
+        <v>25</v>
       </c>
       <c r="L24" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="1">
+        <v>46007</v>
+      </c>
+      <c r="G25">
+        <v>335911</v>
+      </c>
+      <c r="H25" t="s">
         <v>103</v>
       </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="I25">
+        <v>1514</v>
+      </c>
+      <c r="J25" s="1">
+        <v>46112</v>
+      </c>
+      <c r="L25" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="1">
-        <v>46053</v>
-      </c>
-      <c r="G25">
-        <v>517112</v>
-      </c>
-      <c r="H25" t="s">
-        <v>105</v>
-      </c>
-      <c r="I25">
-        <v>74</v>
-      </c>
-      <c r="J25" s="1">
-        <v>46114</v>
-      </c>
-      <c r="K25" t="s">
-        <v>25</v>
-      </c>
-      <c r="L25" t="s">
-        <v>19</v>
-      </c>
-      <c r="M25" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -2253,36 +2259,36 @@
         <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="F26" s="1">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="G26">
-        <v>541715</v>
+        <v>541611</v>
       </c>
       <c r="H26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I26">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J26" s="1">
-        <v>46114</v>
+        <v>46112</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -2297,7 +2303,7 @@
         <v>23</v>
       </c>
       <c r="F27" s="1">
-        <v>46041</v>
+        <v>46034</v>
       </c>
       <c r="G27">
         <v>541330</v>
@@ -2306,65 +2312,68 @@
         <v>110</v>
       </c>
       <c r="I27">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J27" s="1">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="L27" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="F28" s="1">
-        <v>46034</v>
+        <v>46098</v>
       </c>
       <c r="G28">
-        <v>541330</v>
+        <v>33331</v>
       </c>
       <c r="H28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I28">
+        <v>114</v>
+      </c>
+      <c r="J28" s="1">
+        <v>46105</v>
+      </c>
+      <c r="K28" t="s">
+        <v>19</v>
+      </c>
+      <c r="L28" t="s">
         <v>42</v>
       </c>
-      <c r="J28" s="1">
-        <v>46107</v>
-      </c>
-      <c r="L28" t="s">
-        <v>19</v>
-      </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
@@ -2373,112 +2382,112 @@
         <v>23</v>
       </c>
       <c r="F29" s="1">
-        <v>46027</v>
+        <v>46041</v>
       </c>
       <c r="G29">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H29" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I29">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="J29" s="1">
-        <v>46086</v>
+        <v>46101</v>
       </c>
       <c r="L29" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
         <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1">
-        <v>46008</v>
+        <v>46087</v>
       </c>
       <c r="G30">
-        <v>541715</v>
+        <v>545410</v>
       </c>
       <c r="H30" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I30">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J30" s="1">
-        <v>46071</v>
+        <v>46087</v>
       </c>
       <c r="L30" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
         <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="F31" s="1">
-        <v>46007</v>
+        <v>46027</v>
       </c>
       <c r="G31">
-        <v>335911</v>
+        <v>541715</v>
       </c>
       <c r="H31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I31">
-        <v>1514</v>
+        <v>60</v>
       </c>
       <c r="J31" s="1">
-        <v>46112</v>
+        <v>46086</v>
       </c>
       <c r="L31" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M31" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>16</v>
@@ -2487,42 +2496,42 @@
         <v>23</v>
       </c>
       <c r="F32" s="1">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="G32">
-        <v>541330</v>
+        <v>541715</v>
       </c>
       <c r="H32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I32">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J32" s="1">
-        <v>46038</v>
+        <v>46071</v>
       </c>
       <c r="L32" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F33" s="1">
         <v>46006</v>
@@ -2531,7 +2540,7 @@
         <v>332991</v>
       </c>
       <c r="H33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I33">
         <v>77</v>
@@ -2540,13 +2549,51 @@
         <v>46066</v>
       </c>
       <c r="K33" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L33" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M33" t="s">
-        <v>20</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G34">
+        <v>541330</v>
+      </c>
+      <c r="H34" t="s">
+        <v>129</v>
+      </c>
+      <c r="I34">
+        <v>32</v>
+      </c>
+      <c r="J34" s="1">
+        <v>46038</v>
+      </c>
+      <c r="L34" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2730,13 +2777,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2592280F-20D6-4DF3-B6D5-EA1E5B10E984}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32223532-BD7B-4599-A023-F14485C53794}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5574EC29-CA24-477F-A168-38132AC75967}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5EB10C8-7C72-4223-A44D-C831205159E5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2600891-548E-4B9B-84C5-5A2673519CE1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{967651C1-1E7C-4709-910B-F41D97790909}"/>
 </file>
--- a/data/warn-scraper/cache/ky/latest.xlsx
+++ b/data/warn-scraper/cache/ky/latest.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff.lee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10C10295-5BE9-4027-9176-EECA048656CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4864B7E3-A28F-409C-8F5A-BB93E67484A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6E0BF9D4-2591-4720-A4E7-9CC731411A1D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{EAB8D913-CB4E-4E9F-A882-46BBF92D3929}"/>
   </bookViews>
   <sheets>
-    <sheet name="Website-WARN Notice Report 0812" sheetId="1" r:id="rId1"/>
+    <sheet name="WARN-Notice Report 09092026" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="132">
   <si>
     <t>Company: Company Name</t>
   </si>
@@ -61,12 +61,36 @@
     <t>Workforce Board</t>
   </si>
   <si>
+    <t>Congo Brands (Alani, Prime, 3D Energy)</t>
+  </si>
+  <si>
+    <t>WARN Notice</t>
+  </si>
+  <si>
+    <t>Notice 2837</t>
+  </si>
+  <si>
+    <t>Layoff</t>
+  </si>
+  <si>
+    <t>Jefferson</t>
+  </si>
+  <si>
+    <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000Wfwlc/_D6YQqXQ0CMgesFKoD8pQ_7NHn59VpYrxtkZHJeYFnU</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Non-Union</t>
+  </si>
+  <si>
+    <t>Kentuckiana Works</t>
+  </si>
+  <si>
     <t>SMBC Manubank</t>
   </si>
   <si>
-    <t>WARN Notice</t>
-  </si>
-  <si>
     <t>Notice 2833</t>
   </si>
   <si>
@@ -79,9 +103,6 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000VL2BR/5d9tGyNLzSi3WbE5tOFi3W5X_QW76ajmCZoBGb8Hgfo</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>Out of State</t>
   </si>
   <si>
@@ -100,9 +121,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>Non-Union</t>
-  </si>
-  <si>
     <t>Bluegrass</t>
   </si>
   <si>
@@ -112,9 +130,6 @@
     <t>Notice 2818</t>
   </si>
   <si>
-    <t>Layoff</t>
-  </si>
-  <si>
     <t>Boone</t>
   </si>
   <si>
@@ -163,16 +178,7 @@
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TFVZ7/Z75_yQpDBRaY9kpSdMax3j_6lKPopGX68JLiqAIsIuo</t>
   </si>
   <si>
-    <t>Kentuckiana Works</t>
-  </si>
-  <si>
-    <t>Congo Brands (Alani, Prime, 3D Energy)</t>
-  </si>
-  <si>
     <t>Notice 2814</t>
-  </si>
-  <si>
-    <t>Jefferson</t>
   </si>
   <si>
     <t>https://kydev.my.salesforce.com/sfc/p/t00000004X3h/a/eq00000TEkTh/ibPumihpj4EjnXfxGEvZueBWuVei8CvUvM1T1u5fOGA</t>
@@ -1270,8 +1276,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939CF104-FDE3-4B3C-8BF2-1A78776F5BD6}">
-  <dimension ref="A1:M34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40372AC9-E032-45DE-9B69-B370B53C7216}">
+  <dimension ref="A1:M35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1332,63 +1338,63 @@
         <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>46244</v>
+        <v>46269</v>
       </c>
       <c r="G2">
-        <v>522110</v>
+        <v>312111</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J2" s="1">
-        <v>46304</v>
+        <v>46330</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
       </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1">
-        <v>46226</v>
+        <v>46244</v>
       </c>
       <c r="G3">
-        <v>541715</v>
+        <v>522110</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>46289</v>
+        <v>46304</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M3" t="s">
         <v>27</v>
@@ -1405,31 +1411,31 @@
         <v>29</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" s="1">
+        <v>46226</v>
+      </c>
+      <c r="G4">
+        <v>541715</v>
+      </c>
+      <c r="H4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1">
-        <v>46213</v>
-      </c>
-      <c r="G4">
-        <v>493110</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1">
+        <v>46289</v>
+      </c>
+      <c r="K4" t="s">
         <v>32</v>
       </c>
-      <c r="I4">
-        <v>73</v>
-      </c>
-      <c r="J4" s="1">
-        <v>46273</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M4" t="s">
         <v>33</v>
@@ -1452,25 +1458,25 @@
         <v>36</v>
       </c>
       <c r="F5" s="1">
-        <v>46185</v>
+        <v>46213</v>
       </c>
       <c r="G5">
-        <v>333415</v>
+        <v>493110</v>
       </c>
       <c r="H5" t="s">
         <v>37</v>
       </c>
       <c r="I5">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J5" s="1">
-        <v>46264</v>
+        <v>46273</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M5" t="s">
         <v>38</v>
@@ -1487,72 +1493,72 @@
         <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1">
-        <v>46203</v>
+        <v>46185</v>
       </c>
       <c r="G6">
-        <v>315250</v>
+        <v>333415</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6">
-        <v>303</v>
+        <v>70</v>
       </c>
       <c r="J6" s="1">
         <v>46264</v>
       </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="G7">
-        <v>561110</v>
+        <v>315250</v>
       </c>
       <c r="H7" t="s">
         <v>46</v>
       </c>
       <c r="I7">
-        <v>24</v>
+        <v>303</v>
       </c>
       <c r="J7" s="1">
-        <v>46262</v>
-      </c>
-      <c r="K7" t="s">
-        <v>25</v>
+        <v>46264</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="M7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1566,145 +1572,148 @@
         <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
         <v>50</v>
       </c>
       <c r="F8" s="1">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="G8">
-        <v>312111</v>
+        <v>561110</v>
       </c>
       <c r="H8" t="s">
         <v>51</v>
       </c>
       <c r="I8">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J8" s="1">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="K8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M8" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
         <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="G9">
-        <v>424820</v>
+        <v>312111</v>
       </c>
       <c r="H9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I9">
-        <v>174</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1">
-        <v>46251</v>
+        <v>46260</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>20</v>
       </c>
       <c r="M9" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46191</v>
+      </c>
+      <c r="G10">
+        <v>424820</v>
+      </c>
+      <c r="H10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46189</v>
-      </c>
-      <c r="G10">
-        <v>812332</v>
-      </c>
-      <c r="H10" t="s">
-        <v>58</v>
-      </c>
       <c r="I10">
-        <v>32</v>
+        <v>174</v>
       </c>
       <c r="J10" s="1">
-        <v>46249</v>
-      </c>
-      <c r="K10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" t="s">
-        <v>26</v>
+        <v>46251</v>
       </c>
       <c r="M10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
         <v>59</v>
       </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="F11" s="1">
+        <v>46189</v>
+      </c>
+      <c r="G11">
+        <v>812332</v>
+      </c>
+      <c r="H11" t="s">
         <v>60</v>
       </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46237</v>
-      </c>
-      <c r="G11">
-        <v>11141</v>
-      </c>
-      <c r="H11" t="s">
-        <v>61</v>
-      </c>
       <c r="I11">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="J11" s="1">
-        <v>46237</v>
+        <v>46249</v>
+      </c>
+      <c r="K11" t="s">
+        <v>32</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M11" t="s">
         <v>33</v>
@@ -1712,7 +1721,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1721,162 +1730,162 @@
         <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1">
-        <v>46149</v>
+        <v>46237</v>
       </c>
       <c r="G12">
-        <v>541715</v>
+        <v>11141</v>
       </c>
       <c r="H12" t="s">
         <v>63</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>127</v>
       </c>
       <c r="J12" s="1">
-        <v>46209</v>
+        <v>46237</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M12" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
         <v>64</v>
       </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46149</v>
+      </c>
+      <c r="G13">
+        <v>541715</v>
+      </c>
+      <c r="H13" t="s">
         <v>65</v>
       </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46142</v>
-      </c>
-      <c r="G13">
-        <v>321114</v>
-      </c>
-      <c r="H13" t="s">
-        <v>67</v>
-      </c>
       <c r="I13">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="J13" s="1">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M13" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46142</v>
+      </c>
+      <c r="G14">
+        <v>321114</v>
+      </c>
+      <c r="H14" t="s">
         <v>69</v>
       </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="I14">
+        <v>67</v>
+      </c>
+      <c r="J14" s="1">
+        <v>46204</v>
+      </c>
+      <c r="L14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" t="s">
         <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46141</v>
-      </c>
-      <c r="G14">
-        <v>722310</v>
-      </c>
-      <c r="H14" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14">
-        <v>923</v>
-      </c>
-      <c r="J14" s="1">
-        <v>46203</v>
-      </c>
-      <c r="K14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" t="s">
-        <v>42</v>
-      </c>
-      <c r="M14" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>72</v>
       </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46141</v>
+      </c>
+      <c r="G15">
+        <v>722310</v>
+      </c>
+      <c r="H15" t="s">
         <v>73</v>
       </c>
-      <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46147</v>
-      </c>
-      <c r="G15">
-        <v>611310</v>
-      </c>
-      <c r="H15" t="s">
-        <v>74</v>
-      </c>
       <c r="I15">
-        <v>36</v>
+        <v>923</v>
       </c>
       <c r="J15" s="1">
         <v>46203</v>
       </c>
+      <c r="K15" t="s">
+        <v>32</v>
+      </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="M15" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
         <v>75</v>
       </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F16" s="1">
         <v>46147</v>
@@ -1885,138 +1894,138 @@
         <v>611310</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I16">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J16" s="1">
         <v>46203</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
         <v>78</v>
       </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46147</v>
+      </c>
+      <c r="G17">
+        <v>611310</v>
+      </c>
+      <c r="H17" t="s">
         <v>79</v>
       </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46113</v>
-      </c>
-      <c r="G17">
-        <v>488510</v>
-      </c>
-      <c r="H17" t="s">
-        <v>80</v>
-      </c>
       <c r="I17">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="J17" s="1">
-        <v>46179</v>
+        <v>46203</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M17" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
         <v>81</v>
       </c>
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F18" s="1">
         <v>46113</v>
       </c>
       <c r="G18">
-        <v>492110</v>
+        <v>488510</v>
       </c>
       <c r="H18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I18">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="J18" s="1">
-        <v>46175</v>
+        <v>46179</v>
       </c>
       <c r="L18" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M18" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
         <v>84</v>
       </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46113</v>
+      </c>
+      <c r="G19">
+        <v>492110</v>
+      </c>
+      <c r="H19" t="s">
         <v>85</v>
       </c>
-      <c r="D19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="1">
-        <v>46128</v>
-      </c>
-      <c r="G19">
-        <v>56172</v>
-      </c>
-      <c r="H19" t="s">
-        <v>86</v>
-      </c>
       <c r="I19">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="J19" s="1">
-        <v>46152</v>
-      </c>
-      <c r="K19" t="s">
-        <v>25</v>
+        <v>46175</v>
+      </c>
+      <c r="L19" t="s">
+        <v>47</v>
       </c>
       <c r="M19" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -2028,66 +2037,66 @@
         <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F20" s="1">
-        <v>46086</v>
+        <v>46128</v>
       </c>
       <c r="G20">
-        <v>541715</v>
+        <v>56172</v>
       </c>
       <c r="H20" t="s">
         <v>88</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="J20" s="1">
-        <v>46148</v>
+        <v>46152</v>
       </c>
       <c r="K20" t="s">
-        <v>25</v>
-      </c>
-      <c r="L20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M20" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
         <v>89</v>
       </c>
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46086</v>
+      </c>
+      <c r="G21">
+        <v>541715</v>
+      </c>
+      <c r="H21" t="s">
         <v>90</v>
       </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="1">
-        <v>46077</v>
-      </c>
-      <c r="G21">
-        <v>423120</v>
-      </c>
-      <c r="H21" t="s">
-        <v>91</v>
-      </c>
       <c r="I21">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="J21" s="1">
-        <v>46142</v>
+        <v>46148</v>
+      </c>
+      <c r="K21" t="s">
+        <v>32</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M21" t="s">
         <v>33</v>
@@ -2095,45 +2104,45 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
         <v>92</v>
       </c>
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="1">
+        <v>46077</v>
+      </c>
+      <c r="G22">
+        <v>423120</v>
+      </c>
+      <c r="H22" t="s">
         <v>93</v>
       </c>
-      <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="1">
-        <v>46056</v>
-      </c>
-      <c r="G22">
-        <v>541330</v>
-      </c>
-      <c r="H22" t="s">
-        <v>94</v>
-      </c>
       <c r="I22">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="J22" s="1">
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -2142,308 +2151,308 @@
         <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F23" s="1">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G23">
-        <v>541715</v>
+        <v>541330</v>
       </c>
       <c r="H23" t="s">
         <v>96</v>
       </c>
       <c r="I23">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J23" s="1">
-        <v>46114</v>
+        <v>46128</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M23" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
         <v>97</v>
       </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="1">
+        <v>46051</v>
+      </c>
+      <c r="G24">
+        <v>541715</v>
+      </c>
+      <c r="H24" t="s">
         <v>98</v>
       </c>
-      <c r="D24" t="s">
+      <c r="I24">
         <v>30</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="1">
-        <v>46053</v>
-      </c>
-      <c r="G24">
-        <v>517112</v>
-      </c>
-      <c r="H24" t="s">
-        <v>99</v>
-      </c>
-      <c r="I24">
-        <v>74</v>
       </c>
       <c r="J24" s="1">
         <v>46114</v>
       </c>
-      <c r="K24" t="s">
-        <v>25</v>
-      </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M24" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
         <v>100</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
-        <v>101</v>
       </c>
       <c r="D25" t="s">
         <v>16</v>
       </c>
       <c r="E25" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="F25" s="1">
-        <v>46007</v>
+        <v>46053</v>
       </c>
       <c r="G25">
-        <v>335911</v>
+        <v>517112</v>
       </c>
       <c r="H25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I25">
-        <v>1514</v>
+        <v>74</v>
       </c>
       <c r="J25" s="1">
-        <v>46112</v>
+        <v>46114</v>
+      </c>
+      <c r="K25" t="s">
+        <v>32</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M25" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46007</v>
+      </c>
+      <c r="G26">
+        <v>335911</v>
+      </c>
+      <c r="H26" t="s">
         <v>105</v>
       </c>
-      <c r="B26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46057</v>
-      </c>
-      <c r="G26">
-        <v>541611</v>
-      </c>
-      <c r="H26" t="s">
-        <v>108</v>
-      </c>
       <c r="I26">
-        <v>1</v>
+        <v>1514</v>
       </c>
       <c r="J26" s="1">
         <v>46112</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M26" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
         <v>16</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="F27" s="1">
-        <v>46034</v>
+        <v>46057</v>
       </c>
       <c r="G27">
-        <v>541330</v>
+        <v>541611</v>
       </c>
       <c r="H27" t="s">
         <v>110</v>
       </c>
       <c r="I27">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="J27" s="1">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M27" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
         <v>111</v>
       </c>
-      <c r="B28" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46034</v>
+      </c>
+      <c r="G28">
+        <v>541330</v>
+      </c>
+      <c r="H28" t="s">
         <v>112</v>
       </c>
-      <c r="D28" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="1">
-        <v>46098</v>
-      </c>
-      <c r="G28">
-        <v>33331</v>
-      </c>
-      <c r="H28" t="s">
-        <v>114</v>
-      </c>
       <c r="I28">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="J28" s="1">
-        <v>46105</v>
-      </c>
-      <c r="K28" t="s">
-        <v>19</v>
+        <v>46107</v>
       </c>
       <c r="L28" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M28" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
         <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="F29" s="1">
-        <v>46041</v>
+        <v>46098</v>
       </c>
       <c r="G29">
-        <v>541330</v>
+        <v>33331</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I29">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="J29" s="1">
-        <v>46101</v>
+        <v>46105</v>
+      </c>
+      <c r="K29" t="s">
+        <v>19</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="M29" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
         <v>118</v>
       </c>
-      <c r="B30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46041</v>
+      </c>
+      <c r="G30">
+        <v>541330</v>
+      </c>
+      <c r="H30" t="s">
         <v>119</v>
       </c>
-      <c r="D30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="1">
-        <v>46087</v>
-      </c>
-      <c r="G30">
-        <v>545410</v>
-      </c>
-      <c r="H30" t="s">
-        <v>120</v>
-      </c>
       <c r="I30">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="J30" s="1">
-        <v>46087</v>
+        <v>46101</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M30" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="B31" t="s">
         <v>14</v>
@@ -2455,25 +2464,25 @@
         <v>16</v>
       </c>
       <c r="E31" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F31" s="1">
-        <v>46027</v>
+        <v>46087</v>
       </c>
       <c r="G31">
-        <v>541715</v>
+        <v>545410</v>
       </c>
       <c r="H31" t="s">
         <v>122</v>
       </c>
       <c r="I31">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="J31" s="1">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M31" t="s">
         <v>27</v>
@@ -2481,7 +2490,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -2490,13 +2499,13 @@
         <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F32" s="1">
-        <v>46008</v>
+        <v>46027</v>
       </c>
       <c r="G32">
         <v>541715</v>
@@ -2505,54 +2514,51 @@
         <v>124</v>
       </c>
       <c r="I32">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J32" s="1">
-        <v>46071</v>
+        <v>46086</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="M32" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
         <v>125</v>
       </c>
-      <c r="B33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46008</v>
+      </c>
+      <c r="G33">
+        <v>541715</v>
+      </c>
+      <c r="H33" t="s">
         <v>126</v>
       </c>
-      <c r="D33" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" t="s">
-        <v>31</v>
-      </c>
-      <c r="F33" s="1">
-        <v>46006</v>
-      </c>
-      <c r="G33">
-        <v>332991</v>
-      </c>
-      <c r="H33" t="s">
-        <v>127</v>
-      </c>
       <c r="I33">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="J33" s="1">
-        <v>46066</v>
-      </c>
-      <c r="K33" t="s">
-        <v>19</v>
+        <v>46071</v>
       </c>
       <c r="L33" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M33" t="s">
         <v>33</v>
@@ -2560,7 +2566,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="B34" t="s">
         <v>14</v>
@@ -2569,31 +2575,72 @@
         <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F34" s="1">
         <v>46006</v>
       </c>
       <c r="G34">
-        <v>541330</v>
+        <v>332991</v>
       </c>
       <c r="H34" t="s">
         <v>129</v>
       </c>
       <c r="I34">
+        <v>77</v>
+      </c>
+      <c r="J34" s="1">
+        <v>46066</v>
+      </c>
+      <c r="K34" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" t="s">
+        <v>47</v>
+      </c>
+      <c r="M34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="1">
+        <v>46006</v>
+      </c>
+      <c r="G35">
+        <v>541330</v>
+      </c>
+      <c r="H35" t="s">
+        <v>131</v>
+      </c>
+      <c r="I35">
         <v>32</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J35" s="1">
         <v>46038</v>
       </c>
-      <c r="L34" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" t="s">
-        <v>27</v>
+      <c r="L35" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2777,13 +2824,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32223532-BD7B-4599-A023-F14485C53794}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A5448D-99F8-4FA6-80D5-BF0375E6D9BF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5EB10C8-7C72-4223-A44D-C831205159E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00DB289B-4FC3-407A-A3BE-4467ECAEF91B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{967651C1-1E7C-4709-910B-F41D97790909}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A239435C-27B1-4E10-AB9A-3AFADEEB1F57}"/>
 </file>